--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:R151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -524,6 +524,11 @@
           <t>Research Done</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>local_context_html</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6855,6 +6860,23 @@
       <c r="Q78" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources — NOAA climate normals, U.S. Census ACS estimates, the Minneapolis Code of Ordinances, Xcel Energy&amp;rsquo;s current rebate catalog, and the Minnesota Department of Labor and Industry. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMSP)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Minneapolis-St. Paul International Airport (KMSP) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014922), Minneapolis records an &lt;strong&gt;annual mean temperature of 46.9&amp;deg;F&lt;/strong&gt;, a &lt;strong&gt;coldest-month (January) mean of 22.1&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;7,399 annual heating degree days&lt;/strong&gt; against 830 cooling degree days, and an annual snowfall normal of &lt;strong&gt;49.0 inches&lt;/strong&gt;. The 8.9:1 HDD-to-CDD ratio is what makes Minneapolis a heating-dominated HVAC market rather than a cooling one &amp;mdash; a factor that shapes equipment sizing, fuel choice, and rebate economics discussed below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://data.census.gov/table?q=B25040&amp;amp;g=160XX00US2743000" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2022 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Minneapolis city, Minnesota) report &lt;strong&gt;185,674 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1950&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.5% utility natural gas&lt;/strong&gt; (134,538 units), &lt;strong&gt;22.6% electricity&lt;/strong&gt; (42,009 units), 3,584 units on bottled/tank/LP gas, and 462 on fuel oil or kerosene. The dominance of natural gas furnaces in an older housing stock (75+ year median age) is the single largest driver of replacement demand in Minneapolis &amp;mdash; and explains why furnace-rebate programs and AFUE upgrades carry more weight here than in electricity-heated markets.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump Performance (Why It Matters Here)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Standard air-source heat pumps lose significant heating capacity as outdoor temperatures approach and drop below 5&amp;deg;F. The &lt;a href="https://www.energystar.gov/products/heat_pumps_air_source" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Version 6.2 Heat Pump Final Specification&lt;/a&gt; (EPA/DOE joint program) defines the Cold Climate designation as a unit that delivers a &lt;strong&gt;COP of at least 1.75 at 5&amp;deg;F&lt;/strong&gt; and retains &lt;strong&gt;at least 70% of its 47&amp;deg;F rated heating capacity at 5&amp;deg;F&lt;/strong&gt;. Given Minneapolis&amp;rsquo;s 22.1&amp;deg;F January mean and documented sub-zero extremes, a non-cold-climate heat pump will shift a substantial portion of winter load to resistance-strip backup heat and short-cycle on defrost &amp;mdash; driving elevated electric bills and accelerated wear. If you&amp;rsquo;re considering a heat pump in Minneapolis, specifying to ccASHP criteria is not optional; it&amp;rsquo;s the difference between an efficient installation and a system that fights the climate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Current Xcel Energy Rebate Amounts (Minnesota 2024&amp;ndash;2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Minneapolis is served by &lt;strong&gt;Xcel Energy&lt;/strong&gt; for electricity and &lt;strong&gt;CenterPoint Energy&lt;/strong&gt; for natural gas. Per the &lt;a href="https://www.xcelenergy.com/staticfiles/xe-responsive/Working%20With%20Us/24-1-201%20MN%20Res%20Rebate%20Summary%20Information%20Sheet.pdf" target="_blank" rel="nofollow noopener"&gt;Xcel Energy Minnesota 2024&amp;ndash;2026 Residential Rebate Summary&lt;/a&gt;, current dollar amounts (effective January 1, 2024) include: &lt;strong&gt;cold-climate air-source heat pump: $2,000&lt;/strong&gt; (Combo/Gas customers) or $1,500 (Electric Only); standard air-source heat pump: $1,600 / $1,100; cold-climate mini-split heat pump: &lt;strong&gt;$2,000&lt;/strong&gt;; ground-source heat pump: &lt;strong&gt;$500 per heating ton&lt;/strong&gt;; central AC (15.2 SEER2, 12.0 EER2): &lt;strong&gt;$450&lt;/strong&gt;; natural gas furnace: &lt;strong&gt;$200 at 95% AFUE, $300 at 96% AFUE, $400 at 97% AFUE&lt;/strong&gt;; heat-pump water heater: $400 ($500 with Demand Management enrollment). These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS &amp;sect;25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Bonding (MN DLI)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Minnesota does not issue a single statewide HVAC contractor license the way some states do, but any business performing HVAC work must carry a state-filed bond. Per the &lt;a href="https://www.dli.mn.gov/business/plumbing-contractors/mechanical-contractor-bond-requirements" target="_blank" rel="nofollow noopener"&gt;Minnesota Department of Labor and Industry &amp;mdash; Mechanical Contractor Bond Requirements&lt;/a&gt;, every business that contracts to perform &lt;strong&gt;gas, heating, ventilation, cooling, air conditioning, fuel-burning or refrigeration work&lt;/strong&gt; must file a &lt;strong&gt;$25,000 mechanical contractor bond&lt;/strong&gt; with DLI. The bond filing fee is &lt;strong&gt;$100 and is valid for two years&lt;/strong&gt;. Verifying that a contractor&amp;rsquo;s bond is on file with DLI before authorizing work is a basic due-diligence step any Minneapolis homeowner can take in under five minutes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Minneapolis Heating Ordinance (MCO &amp;sect; 244.430)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Beyond state code, the &lt;a href="https://library.municode.com/mn/minneapolis/codes/code_of_ordinances" target="_blank" rel="nofollow noopener"&gt;Minneapolis Code of Ordinances &amp;sect; 244.430&lt;/a&gt; imposes a local minimum-heat obligation for any building containing habitable rooms. Owners must provide heating facilities that are &amp;ldquo;properly installed, safely maintained, and in good working condition&amp;rdquo; capable of holding indoor temperatures at or above &lt;strong&gt;68&amp;deg;F from October 1 through April 30&lt;/strong&gt; (and 65&amp;deg;F during shoulder-season windows). The practical implication for homeowners: a furnace that intermittently cycles off during a January cold snap is not just an inconvenience &amp;mdash; it&amp;rsquo;s a habitability issue that triggers city inspection authority. This is why Minneapolis HVAC service calls during cold-weather emergencies are prioritized by most independent local contractors. Permit fees for residential mechanical work are set by the &lt;strong&gt;Minneapolis Community Planning &amp;amp; Economic Development (CPED) office&lt;/strong&gt;; contact CPED directly for the current fee schedule, as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -7891,6 +7891,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Phoenix City Code (including the Cooling Ordinance), the City of Phoenix Planning &amp;amp; Development fee schedule, the Arizona Registrar of Contractors classification pages, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPHX Sky Harbor)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Phoenix Sky Harbor International Airport (KPHX) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023183), Phoenix records an &lt;strong&gt;annual mean temperature of 75.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,764.6 annual cooling degree days&lt;/strong&gt; against only 874.3 heating degree days &amp;mdash; a 5.4:1 CDD-to-HDD ratio that is among the most cooling-dominated of any U.S. city. The July average daily high is &lt;strong&gt;106.5&amp;deg;F&lt;/strong&gt;, the January average low is 46.0&amp;deg;F, and Phoenix averages &lt;strong&gt;111.3 days per year with a maximum temperature at or above 100&amp;deg;F&lt;/strong&gt;. This extreme heat profile is the single most important factor in every HVAC specification decision for Phoenix homeowners.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2022/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:55000&amp;amp;in=state:04" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2022 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Phoenix city, Arizona) report &lt;strong&gt;591,169 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.6% electricity&lt;/strong&gt; (440,939 units), &lt;strong&gt;22.3% utility natural gas&lt;/strong&gt; (131,817 units), and &lt;strong&gt;3,821 units using solar energy&lt;/strong&gt; for heating. The overwhelming electric-heat share &amp;mdash; one of the highest among major U.S. cities &amp;mdash; reflects Phoenix&amp;rsquo;s mild winters (a standard heat pump&amp;rsquo;s heating duty is modest) and the dominance of central cooling systems that happen to include electric resistance or heat-pump heating as a secondary function.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme-Heat HVAC Performance: Why Ductwork Location Matters&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;When a Phoenix home&amp;rsquo;s ductwork runs through an unconditioned attic &amp;mdash; which is typical in mid-century and newer Phoenix construction &amp;mdash; the ducts are operating in an environment that regularly exceeds 130&amp;deg;F during summer afternoons. Per the &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Central Air Conditioning&lt;/a&gt;, best-practice installation &lt;em&gt;&amp;ldquo;installs ductwork within conditioned space whenever possible, not in unconditioned spaces like attics or garages.&amp;rdquo;&lt;/em&gt; For Phoenix specifically, with 111+ days per year above 100&amp;deg;F outside (and attic temperatures dramatically higher), every foot of duct that runs through the attic loses cooling capacity to conduction and leakage. Homeowners planning a system replacement or attic retrofit should explicitly ask contractors about moving ducts into the conditioned envelope or, at minimum, using R-8 insulated duct with aggressive joint sealing.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Phoenix Cooling Ordinance (City Code Chapter 39-5)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Phoenix is one of the few U.S. cities with a mandatory residential cooling ordinance, reflecting the real mortality risk of summer heat. Per the &lt;a href="https://www.phoenix.gov/heatsite/Documents/6-3-22%20Cooling%20Ordinance%20Flyer%20English%20and%20Spanish_-combined.pdf" target="_blank" rel="nofollow noopener"&gt;Phoenix City Code Chapter 39-5 Cooling Ordinance&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Every rental housing unit where such systems are installed shall have cooling capable of safely cooling all habitable rooms, bathrooms and flushing toilet rooms to a temperature no greater than 86 degrees Fahrenheit, if cooled by evaporative cooling, or 82 degrees Fahrenheit, if cooled by air conditioning.&amp;rdquo;&lt;/em&gt; Temperature measurements are taken &lt;em&gt;&amp;ldquo;at a distance three feet above the floor in the center of the room&amp;rdquo;&lt;/em&gt; and the cooling must be &lt;em&gt;&amp;ldquo;provided by permanently installed cooling facilities.&amp;rdquo;&lt;/em&gt; For homeowners: a system that can&amp;rsquo;t hold 82&amp;deg;F during a summer heat wave is a direct habitability-code issue, which is why emergency cooling calls are prioritized by independent local contractors.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Phoenix Mechanical Permit Fees (Valuation-Based)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.phoenix.gov/content/dam/phoenix/pddsite/documents/tools-resources/PDD-Fee-Schedule.pdf" target="_blank" rel="nofollow noopener"&gt;City of Phoenix Planning &amp;amp; Development Fee Schedule, Appendix A.2 Table A&lt;/a&gt; sets mechanical permit fees as valuation-based, not flat-rate: &lt;strong&gt;$195 base fee for projects valued $1 to $1,000&lt;/strong&gt;, plus an additional &lt;strong&gt;$9 for each $1,000 increment from $1,001 to $10,000&lt;/strong&gt;, then &lt;strong&gt;$276 for the first $10,000 plus $8 per additional $1,000&lt;/strong&gt; up to $50,000. The valuation-based model means a typical residential furnace-plus-AC replacement (roughly $10,000&amp;ndash;$18,000 installed) carries permit fees in the $280&amp;ndash;$350 range, distinct from the equipment cost itself.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing (Arizona ROC R-39)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Phoenix must hold a current license from the &lt;strong&gt;Arizona Registrar of Contractors (ROC)&lt;/strong&gt;. Per the &lt;a href="https://roc.az.gov/license-classifications" target="_blank" rel="nofollow noopener"&gt;Arizona ROC License Classifications page&lt;/a&gt;, the residential HVAC classification is &lt;strong&gt;R-39 Air Conditioning and Refrigeration, Including Solar&lt;/strong&gt;: &lt;em&gt;&amp;ldquo;This classification allows the licensee to install and repair comfort air conditioning systems, including refrigeration, evaporative cooling, ventilating, and heating with or without solar equipment.&amp;rdquo;&lt;/em&gt; A dual-scope CR-39 classification covers both residential and commercial work. For rebate amounts, APS and SRP programs have been subject to recent regulatory changes (Arizona Corporation Commission Decision No. 81584); verify current program status directly with your utility or via the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; before planning around specific dollar amounts.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8954,6 +8971,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the City of San Diego Development Services fee schedule and code pages, the California Contractors State License Board, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSAN Lindbergh Field)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Diego International Airport (KSAN) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023188), San Diego records an &lt;strong&gt;annual mean temperature of 64.7&amp;deg;F&lt;/strong&gt;, with an annual maximum of 70.9&amp;deg;F and minimum of 58.5&amp;deg;F, approximately &lt;strong&gt;989.9 heating degree days&lt;/strong&gt; and &lt;strong&gt;893.2 cooling degree days&lt;/strong&gt; (nearly balanced), and only &lt;strong&gt;9.79 inches of annual precipitation&lt;/strong&gt;. San Diego&amp;rsquo;s warm-marine Zone 3C climate is one of the mildest major-city HVAC environments in the country &amp;mdash; neither heating nor cooling dominates, and many older San Diego homes were originally built with no central air conditioning at all.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:66000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for San Diego city, California) report &lt;strong&gt;522,146 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;51.9% utility natural gas&lt;/strong&gt; (270,808 units), &lt;strong&gt;38.3% electricity&lt;/strong&gt; (200,192 units), &lt;strong&gt;1.5% solar energy&lt;/strong&gt; (7,922 units &amp;mdash; meaningful for a major city), and a striking &lt;strong&gt;6.5% of occupied units report no fuel used&lt;/strong&gt; for heating (34,025 units). That last figure is the signature of San Diego&amp;rsquo;s climate: tens of thousands of homes operate year-round without a dedicated heating system, relying on mild ambient temperatures alone. When those homes do add heating or cooling, reversible heat pumps are typically the most efficient option.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Heat Pump Sizing for a Warm-Marine Climate&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Because San Diego&amp;rsquo;s cooling degree days (893) are nearly equal to its heating degree days (990), both halves of a heat pump&amp;rsquo;s duty cycle matter. But per the &lt;a href="https://www.energy.gov/energysaver/air-source-heat-pumps" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Air-Source Heat Pumps&lt;/a&gt;, &lt;em&gt;&amp;ldquo;in warmer climates, SEER is more important than HSPF.&amp;rdquo;&lt;/em&gt; For San Diego that translates to prioritizing a high SEER2 rating when specifying a heat pump or central AC. Coastal installations closer to La Jolla, Pacific Beach, and Ocean Beach also need to factor in salt-air corrosion on condenser coils &amp;mdash; ask contractors about coastal-duty coil coatings for homes within a mile of the water.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;San Diego Mechanical Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Diego publishes per-item residential HVAC permit fees in &lt;a href="https://www.sandiego.gov/development-services/forms-publications/information-bulletins/103" target="_blank" rel="nofollow noopener"&gt;Information Bulletin 103 (Fee Schedule for Mechanical, Electrical, Plumbing/Gas Permits)&lt;/a&gt;, Table 1B. Current amounts: &lt;strong&gt;furnace (FAU) first unit $164.63&lt;/strong&gt;, each additional unit $48.85; &lt;strong&gt;heat pump package unit first unit $164.63&lt;/strong&gt;; &lt;strong&gt;air handler or mini-split first unit $164.63&lt;/strong&gt;; &lt;strong&gt;condensing unit for HVAC first unit $122.63&lt;/strong&gt;; plus a &lt;strong&gt;$11.34 mapping fee&lt;/strong&gt; when plans are required. These are the baseline permit costs; total project valuation may trigger additional plan-review or inspection fees.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Local Code Amendments and Title 24 Enforcement&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.sandiego.gov/development-services/codes-regulations" target="_blank" rel="nofollow noopener"&gt;City of San Diego Development Services Codes &amp;amp; Regulations page&lt;/a&gt;, San Diego&amp;rsquo;s local amendments to the California Mechanical Code are published in &lt;strong&gt;Chapter 14, Article 8 of the Land Development Code&lt;/strong&gt;, and permit procedures live in &lt;strong&gt;San Diego Municipal Code Chapter 12, Article 9, Division 4&lt;/strong&gt;. Critically: &lt;em&gt;&amp;ldquo;California Energy Code (Part 6 of Title 24): Enforced as published with no local amendments.&amp;rdquo;&lt;/em&gt; That means Title 24 Part 6 &amp;mdash; California&amp;rsquo;s strict energy code with per-climate-zone insulation, duct, and equipment efficiency requirements &amp;mdash; applies to San Diego HVAC work in full.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing (California C-20)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in San Diego must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor classification from the California Contractors State License Board. Per the &lt;a href="https://www.cslb.ca.gov/about_us/library/licensing_classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;CSLB C-20 classification page&lt;/a&gt;, the C-20 contractor &lt;em&gt;&amp;ldquo;fabricates, installs, maintains, services and repairs warm-air heating systems and water heating heat pumps, complete with warm-air appliances; ventilating systems complete with blowers and plenum chambers; air-conditioning systems complete with air-conditioning unit; and the ducts, registers, flues, humidity and thermostatic controls and air filters in connection with any of these systems&amp;rdquo;&lt;/em&gt; &amp;mdash; explicitly including solar-energy HVAC systems. For utility rebate amounts, SDG&amp;amp;E&amp;rsquo;s current residential rebate catalog is searchable via the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; (enter your San Diego ZIP code) and the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt;, both of which list current utility and state incentive amounts.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9773,6 +9807,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the City of St. Louis Building Division (Mechanical Ordinance 70800), and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSTL Lambert)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;St. Louis Lambert International Airport (KSTL) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013994), St. Louis records an &lt;strong&gt;annual mean temperature of 57.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,432.9 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,713.0 cooling degree days&lt;/strong&gt;, &lt;strong&gt;41.70 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;16.6 inches of annual snowfall&lt;/strong&gt;. The 2.6:1 HDD-to-CDD ratio and high summertime humidity define St. Louis as a classic Zone 4A mixed-humid climate &amp;mdash; both heating and cooling matter meaningfully, and properly sized equipment must manage both seasons without sacrificing summer dehumidification.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:65000&amp;amp;in=state:29" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for St. Louis city, Missouri) report &lt;strong&gt;144,450 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1938&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;67.8% utility natural gas&lt;/strong&gt; (97,890 units), &lt;strong&gt;29.6% electricity&lt;/strong&gt; (42,801 units), 2,013 units on bottled/LP gas, and small numbers on wood (170), fuel oil (142), and solar (70). The 1938 median year built is dramatically older than most U.S. cities &amp;mdash; St. Louis has one of the most pre-WWII-dominated housing stocks in the country, which creates real retrofit challenges: undersized ducts, heritage boilers and radiators, masonry construction, and knob-and-tube electrical systems that constrain modern HVAC installation.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate: The Dehumidification Imperative&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;St. Louis summers combine high temperatures (1,713 CDD) with high humidity (41.7 inches annual precipitation), making dehumidification at least as important as raw cooling capacity. Per the &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide to Efficient Cooling for Hot, Humid Climates&lt;/a&gt;: &lt;em&gt;&amp;ldquo;This problem often occurs with oversized air conditioners that cool the air quickly but cycle off before properly dehumidifying it. If an air conditioner doesn&amp;rsquo;t dehumidify adequately, the air will feel uncomfortably damp even if the temperature is cool. In extremely humid climates, even correctly sized air conditioning equipment may struggle to maintain comfortable humidity levels.&amp;rdquo;&lt;/em&gt; The practical implication: an AC that&amp;rsquo;s been oversized by one ton &amp;mdash; a common mistake in replacement jobs &amp;mdash; will short-cycle and leave the home clammy even at 72&amp;deg;F. Correct Manual J sizing, not bigger-is-better, is the right standard for St. Louis installations.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;St. Louis Mechanical Ordinance 70800 &amp;amp; City Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Missouri does not issue a statewide HVAC contractor license. Instead, the City of St. Louis issues its own municipal mechanical contractor license. Per the &lt;a href="https://library.municode.com/mo/st.%20louis/codes/code_of_ordinances" target="_blank" rel="nofollow noopener"&gt;City of St. Louis Code of Ordinances (Municode)&lt;/a&gt; referenced by the Building Division: &lt;em&gt;&amp;ldquo;A new Mechanical Ordinance, Number 70800, requires that all residential replacement or new heating/cooling units be installed by a mechanical contractor licensed in the City.&amp;rdquo;&lt;/em&gt; Permits are required for &lt;em&gt;&amp;ldquo;boilers, furnaces, exhaust fans and hoods, and ventilation systems.&amp;rdquo;&lt;/em&gt; Contractors new to the City must procure a city license through the &lt;strong&gt;Building Division Mechanical Section at 314-622-3313&lt;/strong&gt;. For homeowners, verifying a contractor&amp;rsquo;s City-issued license before authorizing installation work is the critical due-diligence step in St. Louis &amp;mdash; more important than in states with a statewide board, because the municipal license is the only formal credential.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;St. Louis is served by &lt;strong&gt;Ameren Missouri&lt;/strong&gt; for electricity and &lt;strong&gt;Spire&lt;/strong&gt; for natural gas. Both utilities administer residential energy-efficiency rebate programs for high-efficiency HVAC equipment, smart thermostats, and weatherization. Because utility rebate amounts change annually and program pages sometimes block automated checks, the most reliable way to see current dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; with a St. Louis ZIP code, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; filtered to Missouri residential incentives. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year). Permit fees for residential mechanical work in the City of St. Louis are set by the Building Division; contact the Mechanical Section directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12718,6 +12767,23 @@
       <c r="Q148" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Portland City Code, Energy Trust of Oregon (the official incentive administrator for Portland General Electric and NW Natural), and the Oregon Construction Contractors Board. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPDX)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Portland International Airport (KPDX) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024229), Portland records an &lt;strong&gt;annual mean temperature of 55.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;annual maximum of 63.9&amp;deg;F&lt;/strong&gt; and minimum of 46.2&amp;deg;F, approximately &lt;strong&gt;4,103.6 annual heating degree days&lt;/strong&gt; against 507.7 cooling degree days, &lt;strong&gt;36.92 inches of precipitation&lt;/strong&gt;, and only 4.2 inches of snowfall per year. The 8.1:1 HDD-to-CDD ratio and wet marine climate define Portland as a mild, heating-dominated market where the limiting design condition is persistent damp cool rather than extreme cold &amp;mdash; which is exactly the condition where heat pumps excel.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:59000&amp;amp;in=state:41" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Portland city, Oregon) report &lt;strong&gt;287,030 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1966&lt;/strong&gt;. The heating-fuel split in Portland is unusual: &lt;strong&gt;47.8% electricity&lt;/strong&gt; (137,110 units) vs. &lt;strong&gt;47.3% utility natural gas&lt;/strong&gt; (135,756 units) &amp;mdash; almost a 50/50 split, with 5,776 fuel-oil homes and 1,479 wood-heated homes rounding out the mix. This near-parity between gas and electric heating is the highest electric-heat share of any major West Coast city and explains why Energy Trust of Oregon weighs heat-pump incentives so heavily in this market.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Heat Pump Performance in Portland&amp;rsquo;s Marine Climate&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Portland&amp;rsquo;s Zone 4C marine climate &amp;mdash; mild winters rarely below freezing, damp air year-round &amp;mdash; is close to optimal for air-source heat pumps. The main performance consideration is defrost-cycle behavior: damp conditions cause more frequent frost formation on the outdoor coil than dry-cold climates at equivalent temperatures. Per the &lt;a href="https://www.energy.gov/energysaver/air-source-heat-pumps" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Air-Source Heat Pumps&lt;/a&gt;, homeowners should &lt;em&gt;"select a heat pump with a demand-defrost control. This will minimize defrost cycles, thereby reducing supplementary and heat pump energy use."&lt;/em&gt; Demand-defrost (sometimes called &amp;ldquo;adaptive defrost&amp;rdquo;) is a specification line-item worth asking about explicitly in Portland &amp;mdash; not all heat pumps use it, and the difference in wintertime energy consumption is measurable.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energy Trust of Oregon Incentives (PGE &amp;amp; NW Natural Administrator)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Portland is served by &lt;strong&gt;Portland General Electric (PGE)&lt;/strong&gt; for electricity and &lt;strong&gt;NW Natural&lt;/strong&gt; for gas, but the actual rebate administrator for both utilities is &lt;strong&gt;Energy Trust of Oregon&lt;/strong&gt; &amp;mdash; a non-profit organization. Per the &lt;a href="https://energytrust.org/residential/incentives/furnace-and-heat-pump/" target="_blank" rel="nofollow noopener"&gt;Energy Trust Residential Heating Solutions incentives page&lt;/a&gt;, homeowners can save &lt;strong&gt;$250 to $4,000 on heating upgrades&lt;/strong&gt;, with &lt;strong&gt;up to $4,000 on a new heat pump for manufactured homes&lt;/strong&gt; and &lt;strong&gt;up to $1,600 income-qualified cash back on a new gas furnace&lt;/strong&gt;. Exact equipment-specific amounts depend on SEER2/HSPF2 ratings and household income; use the Energy Trust ZIP-code tool to filter for your property. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing (Oregon CCB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Portland must hold a current license from the &lt;strong&gt;Oregon Construction Contractors Board (CCB)&lt;/strong&gt;. Per &lt;a href="https://oregon.public.law/statutes/ors_701.021" target="_blank" rel="nofollow noopener"&gt;ORS Section 701.021 (published by the Oregon Legislative Assembly via oregon.public.law)&lt;/a&gt;: &lt;em&gt;&amp;ldquo;a person or joint venture that undertakes, offers to undertake or submits a bid to do work as a contractor must have a current license issued by the Construction Contractors Board.&amp;rdquo;&lt;/em&gt; The statute further requires appropriate endorsements based on whether the work involves residential, small commercial, or large commercial structures. Verifying a contractor&amp;rsquo;s active CCB license (and endorsement category) before authorizing work is a five-minute check every Portland homeowner can do.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Portland Housing Maintenance Heating Ordinance (Code Chapter 29.30)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.portland.gov/code/29/30" target="_blank" rel="nofollow noopener"&gt;Portland City Code Title 29 Chapter 29.30 (Housing Maintenance Requirements)&lt;/a&gt;, &lt;strong&gt;Section 29.30.180 B&lt;/strong&gt;: &lt;em&gt;&amp;ldquo;Every dwelling must have a heating facility capable of maintaining a room temperature of 68 degrees Fahrenheit at a point three feet from the floor in all habitable rooms.&amp;rdquo;&lt;/em&gt; The practical implication for homeowners: a furnace or heat pump that can&amp;rsquo;t hold 68&amp;deg;F at occupant height isn&amp;rsquo;t just inadequate &amp;mdash; it&amp;rsquo;s a habitability-code violation the City can inspect. Permit fees for residential mechanical work are set by the &lt;strong&gt;Portland Bureau of Development Services (BDS / Portland Permitting &amp;amp; Development)&lt;/strong&gt;; contact BDS directly for the current fee schedule, as mechanical fees are published separately and updated annually.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -1021,6 +1021,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Georgia Power&amp;rsquo;s current residential rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KATL Hartsfield-Jackson)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Hartsfield-Jackson Atlanta International Airport (KATL) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013874), Atlanta records an &lt;strong&gt;annual mean temperature of 63.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,530.9 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,051.0 cooling degree days&lt;/strong&gt;, &lt;strong&gt;50.43 inches of annual precipitation&lt;/strong&gt;, and only 2.2 inches of snow. The 1.2:1 HDD-to-CDD ratio makes Atlanta nearly balanced between heating and cooling load &amp;mdash; the textbook definition of a dual-need Zone 3A warm-humid climate, where both system halves matter meaningfully.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:04000&amp;amp;in=state:13" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Atlanta city, Georgia) report &lt;strong&gt;231,504 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1987&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.0% electricity&lt;/strong&gt; (134,338 units) and &lt;strong&gt;39.6% utility natural gas&lt;/strong&gt; (91,777 units), with 2,979 bottled/LP-gas homes and 1,502 homes reporting no fuel used. Atlanta&amp;rsquo;s electric-heat share is notably higher than the national average for a southern metro, reflecting the prevalence of heat pumps and electric resistance strip heat in the 1970s&amp;ndash;2000s subdivisions that dominate the city&amp;rsquo;s post-war housing stock.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dual-Load Climate: Sizing for Cooling AND Dehumidification&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Atlanta&amp;rsquo;s 50+ inches of annual rainfall and warm-humid summers make dehumidification as important as raw cooling capacity. Per the &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide to Efficient Cooling for Hot, Humid Climates&lt;/a&gt;: &lt;em&gt;&amp;ldquo;This problem often occurs with oversized air conditioners that cool the air quickly but cycle off before properly dehumidifying it.&amp;rdquo;&lt;/em&gt; DOE further advises: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is correctly sized to handle both cooling and dehumidification needs. Systems that are too large or too small can struggle with humidity control.&amp;rdquo;&lt;/em&gt; For Atlanta homeowners, the practical implication is specifying a system to Manual J load calculations &amp;mdash; not the &amp;ldquo;always bigger&amp;rdquo; shortcut &amp;mdash; and considering variable-capacity equipment that can run at partial load for longer, sustained dehumidification runs.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Georgia Power Residential Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Atlanta is served by &lt;strong&gt;Georgia Power&lt;/strong&gt; for electricity and &lt;strong&gt;Atlanta Gas Light&lt;/strong&gt; for natural gas. Per the &lt;a href="https://www.georgiapower.com/residential/save-money-and-energy.html" target="_blank" rel="nofollow noopener"&gt;Georgia Power Save Money and Energy rebate catalog&lt;/a&gt;, current residential HVAC-related rebates include: &lt;strong&gt;conversion to air-source heat pump &amp;mdash; 50% rebate, up to $1,000&lt;/strong&gt;; &lt;strong&gt;conversion to ground-source heat pump &amp;mdash; 50% rebate, up to $300&lt;/strong&gt;; &lt;strong&gt;smart/programmable thermostat &amp;mdash; 50% rebate, up to $75&lt;/strong&gt;; &lt;strong&gt;duct sealing &amp;mdash; 50% rebate, up to $400&lt;/strong&gt;; &lt;strong&gt;HVAC maintenance and tune-up &amp;mdash; 50% rebate, up to $50&lt;/strong&gt;. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year). Verify eligibility and current program status on the Georgia Power site before purchasing.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Local Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia requires HVAC contractors to hold a &lt;strong&gt;Conditioned Air Contractor License (Class I or Class II)&lt;/strong&gt; issued by the Georgia Secretary of State&amp;rsquo;s Construction Industry Licensing Board. The license is the state-level credential every Atlanta HVAC contractor must carry; Class designations reflect permitted scope of work. Verifying a contractor&amp;rsquo;s active Conditioned Air license before authorizing work is a basic due-diligence step. Permit fees for residential mechanical work in Atlanta are set by the &lt;strong&gt;City of Atlanta Office of Buildings&lt;/strong&gt; (Department of City Planning); contact the Office of Buildings directly for the current fee schedule, as amounts are updated periodically. For an overview of federal and state incentive programs, cross-reference the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database (N.C. State University / U.S. DOE)&lt;/a&gt; or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2506,6 +2521,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KORD O&amp;rsquo;Hare)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Chicago O&amp;rsquo;Hare International Airport (KORD) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094846), Chicago records an &lt;strong&gt;annual mean temperature of 51.2&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,974.3 annual heating degree days&lt;/strong&gt; against 1,003.3 cooling degree days, &lt;strong&gt;37.86 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;38.4 inches of annual snowfall&lt;/strong&gt;. The 6:1 HDD-to-CDD ratio defines Chicago as one of the most heating-dominated large metros in the United States. Polar vortex events regularly push winter lows into single digits and below &amp;mdash; a design condition that drives every HVAC sizing and equipment decision for Chicago homes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14000&amp;amp;in=state:17" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Chicago city, Illinois) report &lt;strong&gt;1,146,547 occupied housing units&lt;/strong&gt; &amp;mdash; one of the largest municipal housing stocks in the country &amp;mdash; with a &lt;strong&gt;median year built of 1952&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;78.0% utility natural gas&lt;/strong&gt; (893,883 units), &lt;strong&gt;17.6% electricity&lt;/strong&gt; (201,395 units), and 20,523 bottled/LP gas homes. The 1952 median year built reflects Chicago&amp;rsquo;s massive inventory of bungalows, two-flats, three-flats, and mid-century brick construction &amp;mdash; older housing stock that typically runs on gas forced-air or hydronic boilers, and whose ductwork and envelope performance constrain modern HVAC retrofit options.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pumps &amp;amp; Dual-Fuel Strategy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Chicago&amp;rsquo;s 5,974 annual heating degree days and routine polar-vortex events below 0&amp;deg;F put the city at the outer edge of where standard air-source heat pumps are practical as a sole heat source. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;for regions experiencing regular freezing winters, the DOE recommends looking for systems with an ENERGY STAR Cold Climate label.&amp;rdquo;&lt;/em&gt; For Chicago specifically, DOE further recommends a dual-fuel strategy: &lt;em&gt;&amp;ldquo;the heat pump efficiently heats and cools your home. When temperatures drop, the system automatically switches to the gas furnace, which is better suited for cold weather.&amp;rdquo;&lt;/em&gt; The practical specification for a Chicago homeowner replacing an aging gas furnace is: install a high-efficiency gas furnace AND a heat-pump outdoor unit tied to the same indoor coil &amp;mdash; a dual-fuel (hybrid) system &amp;mdash; which runs the heat pump efficiently during milder months and hands off to gas below the switchover temperature.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Illinois does not issue a statewide HVAC contractor license. Instead, Chicago requires its own municipal HVAC contractor credentials, administered by the &lt;strong&gt;Chicago Department of Buildings&lt;/strong&gt; (permits and contractor registration) and the &lt;strong&gt;Chicago Department of Business Affairs and Consumer Protection&lt;/strong&gt; (business licensing). Verifying that a contractor is registered with the City of Chicago before authorizing any HVAC work is the critical due-diligence step in Illinois. Permit fees for residential mechanical work in Chicago are set by the Department of Buildings; contact the department directly for the current fee schedule as amounts are updated periodically. For current utility rebate dollar amounts, check &lt;strong&gt;ComEd&lt;/strong&gt; (electricity) and &lt;strong&gt;Peoples Gas&lt;/strong&gt; (natural gas) rebate pages directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Chicago ZIP code. These local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4952,6 +4980,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Texas Department of Licensing and Regulation, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KIAH Intercontinental)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Houston George Bush Intercontinental Airport (KIAH) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012960), Houston records an &lt;strong&gt;annual mean temperature of 70.5&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,287.7 annual cooling degree days&lt;/strong&gt; against only 1,266.1 heating degree days, and a striking &lt;strong&gt;51.84 inches of annual precipitation&lt;/strong&gt;. The 2.6:1 CDD-to-HDD ratio and sub-inch annual snowfall define Houston as a strongly cooling-dominated Zone 2A hot-humid climate where the AC system runs 8&amp;ndash;10 months of the year and high dew points make dehumidification a year-round design consideration rather than a summer-only concern.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:35000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Houston city, Texas) report &lt;strong&gt;916,536 occupied housing units&lt;/strong&gt; &amp;mdash; one of the largest municipal housing stocks in the country &amp;mdash; with a &lt;strong&gt;median year built of 1981&lt;/strong&gt;. Heating-fuel distribution contradicts the typical &amp;ldquo;Texas means gas&amp;rdquo; assumption: &lt;strong&gt;64.5% electricity&lt;/strong&gt; (591,293 units) dominates, with only &lt;strong&gt;33.2% utility natural gas&lt;/strong&gt; (304,650 units). The electric-heat dominance reflects Houston&amp;rsquo;s short heating season (just 1,266 HDD per year) and the prevalence of heat-pump systems that serve both the heating and cooling loads from a single piece of outdoor equipment. For 600,000+ Houston homes, the heat pump isn&amp;rsquo;t an upgrade &amp;mdash; it&amp;rsquo;s already the status quo.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Year-Round Humidity Control and Equipment Sizing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Houston&amp;rsquo;s combination of 3,287 cooling degree days and 51+ inches of annual rainfall puts humidity management at the center of every HVAC specification decision. Per the &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Central Air Conditioning&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Air conditioners not only cool the air but also dehumidify it to improve comfort. However, in extremely humid climates or when outdoor temperatures are moderate, even correctly sized air conditioners may not achieve comfortable humidity levels.&amp;rdquo;&lt;/em&gt; The practical implication for Houston homeowners: an oversized single-stage AC will short-cycle during spring and fall shoulder seasons &amp;mdash; exactly when outdoor humidity is highest and the unit needs to run long enough to pull moisture from the air. Variable-capacity equipment that can modulate down to 30&amp;ndash;40% of nominal capacity is well-suited to this climate, especially for larger homes where a single big unit would otherwise short-cycle.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR Air Conditioning and Refrigeration License&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Houston must hold a current Air Conditioning and Refrigeration (ACR) Contractor license issued by the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;. The licensing program is governed by &lt;strong&gt;Texas Occupations Code Chapter 1302&lt;/strong&gt; (the Air Conditioning and Refrigeration Contractors Law) and &lt;strong&gt;Texas Administrative Code Title 16 Chapter 75&lt;/strong&gt; (the implementing administrative rules). Texas ACR licenses are issued in two classes distinguished by permitted equipment size &amp;mdash; residential/light-commercial contractors typically hold one class and large-commercial contractors hold the other. Verifying a contractor&amp;rsquo;s active TDLR license before authorizing work is the baseline due-diligence step for every Houston homeowner; TDLR publishes a public license-lookup tool at tdlr.texas.gov.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates, Permits &amp;amp; Deregulated Retail Electricity&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Houston&amp;rsquo;s electricity distribution is handled by &lt;strong&gt;CenterPoint Energy&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Houston are typically administered by your chosen REP, not by CenterPoint directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Houston ZIP code, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Permit fees for residential mechanical work are set by the &lt;strong&gt;Houston Permitting Center&lt;/strong&gt; (Mechanical Section, 832.394.8850); contact the center directly for the current fee schedule as amounts are updated periodically. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6271,6 +6314,19 @@
       <c r="Q71" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSDF Standiford Field)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisville International Airport / Standiford Field (KSDF) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093821), Louisville records an &lt;strong&gt;annual mean temperature of 58.9&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,935.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,742.2 cooling degree days&lt;/strong&gt;, &lt;strong&gt;48.34 inches of annual precipitation&lt;/strong&gt;, and 13.4 inches of annual snowfall. The 2.3:1 HDD-to-CDD ratio and high summertime humidity define Louisville as a classic Zone 4A mixed-humid climate &amp;mdash; meaningful heating load in winter, substantial cooling and dehumidification demand in summer.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:48006&amp;amp;in=state:21" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Louisville/Jefferson County metro government balance, Kentucky) report &lt;strong&gt;262,740 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1970&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;59.9% utility natural gas&lt;/strong&gt; (157,481 units), &lt;strong&gt;37.6% electricity&lt;/strong&gt; (98,668 units), 3,573 bottled/LP gas homes, and 561 fuel-oil homes. The post-war median age means most Louisville homes are on their second or third HVAC system by now, and many still operate on the original gas-furnace-plus-central-AC architecture installed during 1970s&amp;ndash;1990s retrofits.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate: Dehumidification and Variable-Capacity Equipment&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisville&amp;rsquo;s 1,742 cooling degree days combined with 48+ inches of precipitation make summer humidity control a real HVAC design factor. Per the &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide to Efficient Cooling for Hot, Humid Climates&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is correctly sized to handle both cooling and dehumidification needs.&amp;rdquo;&lt;/em&gt; DOE further recommends &lt;em&gt;&amp;ldquo;variable capacity equipment that can automatically adjust its cooling capacity to meet the current load,&amp;rdquo;&lt;/em&gt; and notes that heat-pipe-equipped systems pre-cool incoming air, &lt;em&gt;&amp;ldquo;allowing the air conditioner&amp;rsquo;s evaporator coil to extract more water vapor, enhancing dehumidification.&amp;rdquo;&lt;/em&gt; The practical implication for Louisville homeowners: an oversized single-stage AC that&amp;rsquo;s been &amp;ldquo;rightsized by ton&amp;rdquo; but short-cycles during milder summer days will leave the house clammy even at 72&amp;deg;F. Two-stage or variable-capacity equipment is worth specifying in this climate, not just in the extreme-humid Gulf states.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky requires HVAC contractors to hold a state-issued &lt;strong&gt;Master HVAC Contractor license&lt;/strong&gt;, administered by the &lt;strong&gt;Kentucky Department of Housing, Buildings and Construction (DHBC) Division of HVAC&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active Master HVAC license with DHBC before authorizing work is a basic due-diligence step for Louisville homeowners. Permit fees for residential mechanical work in Louisville are set by the &lt;strong&gt;Louisville Metro Office of Construction Review&lt;/strong&gt;; contact Construction Review directly for the current fee schedule. Louisville is served by &lt;strong&gt;Louisville Gas &amp;amp; Electric (LG&amp;amp;E)&lt;/strong&gt; for both electricity and gas; current residential HVAC rebate amounts can be verified directly at lge-ku.com or via the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Louisville ZIP. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8718,6 +8774,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the California Contractors State License Board, SMUD&amp;rsquo;s current heat-pump rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station USW00023232)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Sacramento&amp;rsquo;s NOAA reference station records, per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023232), an &lt;strong&gt;annual mean temperature of 61.8&amp;deg;F&lt;/strong&gt;, with an annual maximum of 74.7&amp;deg;F and minimum of 48.9&amp;deg;F, approximately &lt;strong&gt;2,436.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,291.5 cooling degree days&lt;/strong&gt;, and only &lt;strong&gt;18.14 inches of annual precipitation&lt;/strong&gt; (no measurable snowfall reported). Sacramento&amp;rsquo;s Central Valley Mediterranean climate &amp;mdash; hot dry summers, mild wet winters &amp;mdash; defines Zone 3B Warm-Dry. The key HVAC design feature is the large daytime-to-overnight temperature swing in summer: triple-digit afternoons followed by 60s overnight, which is exactly the condition where passive cooling strategies pay off.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:64000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Sacramento city, California) report &lt;strong&gt;199,401 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1976&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;56.0% utility natural gas&lt;/strong&gt; (111,618 units) and &lt;strong&gt;40.3% electricity&lt;/strong&gt; (80,298 units), with 3,334 bottled/LP gas homes and 1,218 wood-heated units. The near-56/40 gas-to-electric split leaves substantial room for gas-to-electric conversion &amp;mdash; which is exactly the conversion SMUD&amp;rsquo;s heat-pump rebate program is designed to subsidize.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dry-Climate Cooling: Whole-House Fans&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Sacramento&amp;rsquo;s dry summers and cool overnight lows make whole-house fans a realistic supplement or partial replacement for refrigerant cooling &amp;mdash; a design strategy that doesn&amp;rsquo;t work in humid climates. Per the &lt;a href="https://www.energy.gov/energysaver/cooling-whole-house-fan" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide to Cooling with a Whole House Fan&lt;/a&gt;: &lt;em&gt;&amp;ldquo;They are most effective when outdoor temperatures are lower than indoor temperatures, as they quickly draw in the cooler outdoor air while exhausting warmer indoor air,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;whole house fans do not dehumidify air like air conditioners and heat pumps, making them less suitable for high-humidity climates.&amp;rdquo;&lt;/em&gt; For Sacramento homeowners, running a whole-house fan for 60&amp;ndash;90 minutes after sunset can drop indoor temperatures 15&amp;ndash;20&amp;deg;F using a fraction of the energy a refrigerant AC would consume &amp;mdash; appropriate technology for Zone 3B Warm-Dry.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SMUD Heat-Pump Rebates (Among the Most Generous in the U.S.)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Sacramento&amp;rsquo;s electric utility, &lt;strong&gt;SMUD (Sacramento Municipal Utility District)&lt;/strong&gt;, is a customer-owned municipal utility, not an investor-owned utility &amp;mdash; and its heat-pump rebates reflect the difference. Per the &lt;a href="https://www.smud.org/en/Rebates-and-Savings-Tips/Rebates-for-My-Home/Heating-and-Cooling-Rebates" target="_blank" rel="nofollow noopener"&gt;SMUD Heating and Cooling Rebates page&lt;/a&gt;, gas-to-electric heat-pump conversions qualify for: &lt;strong&gt;variable-stage heat pump $3,000&lt;/strong&gt;; &lt;strong&gt;two-stage heat pump (15.2 SEER2 minimum) $2,000&lt;/strong&gt;; plus a &lt;strong&gt;$2,000 &amp;ldquo;Go Electric Bonus / panel upgrade&amp;rdquo; adder&lt;/strong&gt; on gas-to-electric conversions &amp;mdash; for a combined total up to &lt;strong&gt;$5,000 per home&lt;/strong&gt;. Electric-to-electric upgrades (replacing an existing heat pump with a better one) qualify for &lt;strong&gt;$1,000&lt;/strong&gt;. Equipment must be variable-stage or two-stage, at least 15.2 SEER2, paired with a connected Wi-Fi thermostat, and must pass &lt;strong&gt;Title 24 HERS CF3R verification&lt;/strong&gt; (Sacramento sits in California Title 24 Part 6 Climate Zone 12 for energy-code purposes). These incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing (California C-20)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Sacramento must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor classification from the California Contractors State License Board. Per the &lt;a href="https://www.cslb.ca.gov/about_us/library/licensing_classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;CSLB C-20 classification page&lt;/a&gt;, the C-20 contractor &lt;em&gt;&amp;ldquo;fabricates, installs, maintains, services and repairs warm-air heating systems and water heating heat pumps, complete with warm-air appliances; ventilating systems complete with blowers and plenum chambers; air-conditioning systems complete with air-conditioning unit&amp;rdquo;&lt;/em&gt; &amp;mdash; explicitly including solar-energy HVAC systems. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Sacramento Community Development Department, Building Division&lt;/strong&gt;; contact the Building Division directly for the current Master Fee Schedule as amounts are updated periodically.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -1781,6 +1781,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBOS Logan)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Boston Logan International Airport (KBOS) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014739), Boston records an &lt;strong&gt;annual mean temperature of 51.9&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,545.4 annual heating degree days&lt;/strong&gt; against only 801.8 cooling degree days, &lt;strong&gt;43.59 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;49.2 inches of annual snowfall&lt;/strong&gt;. The 6.9:1 HDD-to-CDD ratio plus coastal humidity and nor&amp;rsquo;easter snow-load exposure defines Boston as a classic Zone 5A cool-humid climate &amp;mdash; winter heating capacity is the dominant HVAC design factor, and older-home weatherization often matters more than equipment selection.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock, Heating Fuel &amp;amp; the Fuel-Oil Legacy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:07000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Boston city, Massachusetts) report &lt;strong&gt;279,216 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1947&lt;/strong&gt; &amp;mdash; among the oldest housing stocks of any major U.S. city, reflecting Boston&amp;rsquo;s dense triple-decker, brownstone, and pre-war row-house inventory. Heating-fuel distribution: &lt;strong&gt;57.2% utility natural gas&lt;/strong&gt; (159,684 units), &lt;strong&gt;30.7% electricity&lt;/strong&gt; (85,739 units), and a remarkable &lt;strong&gt;7.2% fuel oil / kerosene&lt;/strong&gt; (19,969 units). The fuel-oil share is an order of magnitude higher than most U.S. cities &amp;mdash; a New England legacy &amp;mdash; and represents one of the clearest statewide decarbonization opportunities, which is why Mass Save heat-pump incentives are among the most generous in the country.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pumps in Pre-War Housing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Boston&amp;rsquo;s 5,545 HDD winters combined with a median-1947 housing stock create a distinctive HVAC challenge: many triple-deckers and brownstones never had central ducting. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;approximately 32% of homes lack ductwork, making ductless solutions like minisplit heat pumps a practical option for those looking to switch to more energy-efficient systems.&amp;rdquo;&lt;/em&gt; DOE further recommends homeowners &lt;em&gt;&amp;ldquo;weatherize their homes to ensure optimal cost savings and comfort, especially in older homes,&amp;rdquo;&lt;/em&gt; and for cold regions, &lt;em&gt;&amp;ldquo;consider looking for a system with an ENERGY STAR Cold Climate label.&amp;rdquo;&lt;/em&gt; For Boston specifically, ducted central heat pumps often don&amp;rsquo;t fit older homes without major retrofit &amp;mdash; but multi-zone ductless mini-split heat pumps with cold-climate ratings solve both problems at once, which is why they&amp;rsquo;re the dominant heat-pump install type across the Boston housing stock.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a single statewide HVAC-specific contractor license the way some states do. Instead, HVAC work in Boston is regulated through several overlapping credentials: refrigerant handling requires &lt;strong&gt;federal EPA Section 608 certification&lt;/strong&gt;; gas-fitting and plumbing portions of HVAC work require licensure through the &lt;strong&gt;Massachusetts Board of State Examiners of Plumbers and Gas Fitters&lt;/strong&gt;; sheet metal work is licensed separately. Verifying that a contractor holds all required credentials before authorizing work is the baseline due-diligence step for every Boston homeowner. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Boston Inspectional Services Department (ISD)&lt;/strong&gt;; contact ISD directly for the current fee schedule. For current utility rebate dollar amounts, visit &lt;strong&gt;masssave.com&lt;/strong&gt; (the joint utility rebate program that includes Eversource and administers some of the most generous heat-pump incentives in the country) or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Boston ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3272,6 +3285,21 @@
       <c r="Q34" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Denver Community Planning and Development&amp;rsquo;s Building Codes and Contractor Licensing pages, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KDEN)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Denver International Airport (KDEN) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003017), Denver records an &lt;strong&gt;annual mean temperature of 51.2&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,862 annual heating degree days&lt;/strong&gt; against 849.5 cooling degree days, and &lt;strong&gt;14.48 inches of annual precipitation&lt;/strong&gt;. The 6.9:1 HDD-to-CDD ratio puts Denver among the most heating-dominated major U.S. cities &amp;mdash; and because Denver sits at 5,280 ft elevation, every HVAC specification decision must also account for &lt;strong&gt;altitude derating&lt;/strong&gt;: air-source heat pumps and combustion furnaces deliver reduced output in Denver&amp;rsquo;s thin air compared to their sea-level rated capacity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:20000&amp;amp;in=state:08" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Denver city, Colorado) report &lt;strong&gt;329,578 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;61.5% utility natural gas&lt;/strong&gt; (202,820 units), &lt;strong&gt;35.0% electricity&lt;/strong&gt; (115,277 units), 4,488 bottled/LP gas homes, and 1,427 solar-heated homes (notably higher than most cities). The combination of a 5,862 HDD climate and 1970s-era housing stock means most Denver homes rely on gas forced-air furnaces &amp;mdash; which creates a large addressable market for gas-to-electric heat-pump conversions now that Xcel Energy and federal Section 25C credits subsidize the switch.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;2025 Denver Building and Fire Codes (Effective December 31, 2025)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Denver adopted a new code cycle that took effect at the end of 2025. Per &lt;a href="https://www.denvergov.org/Government/Agencies-Departments-Offices/Agencies-Departments-Offices-Directory/Community-Planning-and-Development/Building-Codes-Policies-and-Guides" target="_blank" rel="nofollow noopener"&gt;Denver Community Planning and Development&amp;rsquo;s Building Codes page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;The 2025 Denver Building and Fire Codes incorporate the 2024 I-codes (except the Energy Code, which uses the 2021 IECC)&amp;rdquo;&lt;/em&gt; and became &lt;em&gt;&amp;ldquo;effective December 31, 2025.&amp;rdquo;&lt;/em&gt; Denver also &lt;em&gt;&amp;ldquo;adopts and enforces the 2023 National Electrical Code (NEC) / NFPA 70 without amendments.&amp;rdquo;&lt;/em&gt; For a Denver homeowner planning an HVAC replacement in 2026, the practical implication: any new installation must comply with the 2024 International Mechanical Code and the 2021 IECC energy-efficiency thresholds &amp;mdash; which generally means higher minimum equipment efficiency, stricter duct sealing, and updated Manual J load-calculation expectations compared to the prior code cycle.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump Performance at Altitude&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Denver&amp;rsquo;s 5,862 HDD and routine sub-freezing winter temperatures put it at the threshold where cold-climate-rated heat pumps matter. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;if you reside in an area experiencing regular sub-freezing winter temperatures, the DOE suggests considering systems bearing an ENERGY STAR Cold Climate label for optimal performance.&amp;rdquo;&lt;/em&gt; For Denver specifically, that guidance stacks on top of the altitude-derating factor: a heat pump rated for X BTU/hr at sea level will produce meaningfully less capacity at 5,280 ft, so proper sizing at altitude (not a straight replacement of the old unit&amp;rsquo;s nameplate capacity) is essential.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado does not issue a statewide HVAC contractor license. Instead, Denver handles HVAC contractor licensing at the municipal level through &lt;a href="https://www.denvergov.org/Government/Agencies-Departments-Offices/Agencies-Departments-Offices-Directory/Community-Planning-and-Development/Contractor-Licensing" target="_blank" rel="nofollow noopener"&gt;Denver Community Planning and Development&amp;rsquo;s Contractor Licensing division&lt;/a&gt;. Per the CPD licensing page: &lt;em&gt;&amp;ldquo;A supervisor certificate &amp;mdash; or employing someone who holds a supervisor certificate &amp;mdash; is required before obtaining a contractor&amp;rsquo;s license,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;licenses and certificates must be renewed every 1&amp;ndash;3 years, depending on your license type.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active Denver CPD license before authorizing work is the critical due-diligence step for Denver homeowners &amp;mdash; more so than in states with a statewide board, because the municipal license is the only formal credential. Permit fees for residential mechanical work are set by CPD and can be confirmed by contacting the department at (720) 865-2780. For current &lt;strong&gt;Xcel Energy Colorado&lt;/strong&gt; rebate dollar amounts, see the utility&amp;rsquo;s residential rebates page or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Denver ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000 per-year cap for heat pumps).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6742,6 +6770,21 @@
       <c r="Q76" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Florida Statutes, Miami-Dade County building code, FPL&amp;rsquo;s current rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMIA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Miami International Airport (KMIA) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012839), Miami records an &lt;strong&gt;annual mean temperature of 77.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,656.0 annual cooling degree days&lt;/strong&gt; against only &lt;strong&gt;103.6 heating degree days&lt;/strong&gt;, &lt;strong&gt;67.41 inches of annual precipitation&lt;/strong&gt;, and essentially zero snowfall. The 45:1 CDD-to-HDD ratio is extreme even among Southern metros &amp;mdash; Miami is effectively a pure-cooling HVAC climate where heating requirements are negligible, and equipment specifications should prioritize cooling capacity, humidity control, and hurricane-wind resistance above all else.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Near-Pure Electric Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:45000&amp;amp;in=state:12" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Miami city, Florida) report &lt;strong&gt;190,282 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution is extraordinary: &lt;strong&gt;91.2% electricity&lt;/strong&gt; (173,542 units) dominates, with only &lt;strong&gt;2.7% utility natural gas&lt;/strong&gt; (5,096 units) and 5.4% reporting no fuel used. Miami is essentially a pure-electric heating market &amp;mdash; a function of both climate (the occasional 50&amp;deg;F night is trivial heating load) and building history. Heat pumps that provide cooling year-round and occasional heating in the December&amp;ndash;February shoulder months are the standard system architecture across virtually the entire Miami housing stock.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;High-Velocity Hurricane Zone (HVHZ) Code Requirements&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Miami-Dade County&amp;rsquo;s building code imposes requirements that don&amp;rsquo;t apply elsewhere in Florida &amp;mdash; let alone the rest of the country. Miami-Dade and Broward counties are designated as the &lt;strong&gt;High-Velocity Hurricane Zone (HVHZ)&lt;/strong&gt; under &lt;a href="https://www.miamidade.gov/building/library/2023-fbc-roofing-code-changes.pdf" target="_blank" rel="nofollow noopener"&gt;Chapter 16 of the Florida Building Code&lt;/a&gt;. The practical HVAC consequence: &lt;em&gt;&amp;ldquo;Mechanical equipment, appliances and supports that are exposed to wind shall be designed and installed to resist the wind pressures determined in accordance with the Florida Building Code.&amp;rdquo;&lt;/em&gt; For Miami homeowners, this means outdoor condenser units must be secured to wind-load-rated pads or wall brackets, and any new installation requires HVHZ-rated mounting hardware &amp;mdash; a detail that adds $200&amp;ndash;$500 to installation cost compared to non-coastal installs but is non-negotiable under city code.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;FPL Residential Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Miami is served by &lt;strong&gt;Florida Power &amp;amp; Light (FPL)&lt;/strong&gt;, the state&amp;rsquo;s largest electric utility. Per the &lt;a href="https://www.fpl.com/save/programs.html" target="_blank" rel="nofollow noopener"&gt;FPL Save Money programs page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Buy a new energy-efficient A/C and receive an instant $200 rebate,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;earn an instant $220 rebate when you upgrade your ceiling insulation.&amp;rdquo;&lt;/em&gt; In a Zone 1A tropical climate with 4,656 annual CDD, ceiling insulation has one of the fastest HVAC-adjacent paybacks of any retrofit &amp;mdash; comparable in impact to upgrading the AC unit itself for many older Miami homes. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida Contractor Licensing (Statute 489.105 Class A &amp;amp; Class B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Miami must hold a current Florida Certified Air Conditioning Contractor license, administered by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Per &lt;a href="https://www.flsenate.gov/laws/statutes/2025/489.105" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, the two license classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; contractors have &lt;em&gt;&amp;ldquo;services unlimited in the execution of contracts requiring the experience, knowledge, and skill to install, maintain, repair, fabricate, alter, extend, or design... central air-conditioning, refrigeration, heating, and ventilating systems, including duct work in connection with a complete system.&amp;rdquo;&lt;/em&gt; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system&amp;rdquo;&lt;/em&gt; &amp;mdash; essentially residential and light commercial. For a Miami homeowner, a Class B contractor is fully qualified for any typical residential job; the Class A designation matters when the project scope exceeds 25 tons (rare outside large multi-family). Verifying a contractor&amp;rsquo;s active Class A or Class B license before authorizing work is the critical due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Miami Building Department&lt;/strong&gt;; contact the department directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10624,6 +10667,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Tucson Electric Power&amp;rsquo;s current residential rebate catalog, the Arizona Registrar of Contractors, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTUS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tucson International Airport (KTUS) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023160), Tucson records an &lt;strong&gt;annual mean temperature of 70.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,423.7 annual cooling degree days&lt;/strong&gt; against 1,332.5 heating degree days, and only &lt;strong&gt;10.61 inches of annual precipitation&lt;/strong&gt;. The 2.6:1 CDD-to-HDD ratio and desert-dry conditions define Tucson as a classic Zone 2B hot-dry climate &amp;mdash; similar to Phoenix but at roughly 1,000 ft higher elevation (~2,400 ft vs. Phoenix&amp;rsquo;s ~1,100 ft), which yields modestly cooler nights and slightly more winter heating demand than Phoenix.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:77000&amp;amp;in=state:04" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Tucson city, Arizona) report &lt;strong&gt;225,095 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1979&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;48.8% utility natural gas&lt;/strong&gt; (109,861 units), &lt;strong&gt;47.5% electricity&lt;/strong&gt; (107,010 units) &amp;mdash; nearly a 50/50 split &amp;mdash; plus 3,277 bottled/LP gas homes and 2,088 solar-heated homes. Tucson&amp;rsquo;s balanced gas-to-electric split is notably different from Phoenix&amp;rsquo;s 75% electric dominance, reflecting Tucson&amp;rsquo;s somewhat longer heating season and the larger share of 1970s&amp;ndash;80s stick-built homes with integrated gas-furnace-plus-central-AC systems.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Evaporative (Swamp) Cooling: A Realistic Tucson Option&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tucson&amp;rsquo;s desert-dry climate makes evaporative cooling a viable HVAC strategy that doesn&amp;rsquo;t work in humid-climate cities. Per the &lt;a href="https://www.energy.gov/energysaver/evaporative-coolers" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Evaporative Coolers&lt;/a&gt;: &lt;em&gt;&amp;ldquo;In low-humidity areas, evaporating water into the air provides a natural and energy-efficient means of cooling,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;these are most often used in areas where daytime temperatures frequently exceed 100&amp;deg;F.&amp;rdquo;&lt;/em&gt; DOE further warns that &lt;em&gt;&amp;ldquo;evaporative coolers should not be used in humid climates because they add humidity to the air in your home.&amp;rdquo;&lt;/em&gt; For Tucson homeowners, the practical implication: many older Tucson homes still run on evaporative coolers alone, and homeowners upgrading to refrigerant AC are often surprised to see summer electric bills drop (evap cooling uses ~25% of the energy of refrigerant cooling in dry conditions) or rise (refrigerant cooling is dramatically more capable at high humidity). The right choice depends on monsoon-season tolerance for humidity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tucson Electric Power Residential Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tucson&amp;rsquo;s electric utility, &lt;strong&gt;Tucson Electric Power (TEP)&lt;/strong&gt;, publishes current residential rebate amounts: per the &lt;a href="https://www.tep.com/smart-thermostat-rebate/" target="_blank" rel="nofollow noopener"&gt;TEP Smart Thermostat program&lt;/a&gt;, &lt;strong&gt;$35 smart thermostat rebate&lt;/strong&gt;; per the &lt;a href="https://www.tep.com/efficient-home-water-heating/" target="_blank" rel="nofollow noopener"&gt;TEP Efficient Home Water Heating page&lt;/a&gt;, &lt;em&gt;&amp;ldquo;residential customers can receive a $400 rebate for the purchase and installation of an ENERGY STAR heat pump water heater&amp;rdquo;&lt;/em&gt;; per the &lt;a href="https://www.tep.com/residential-insulation-program/" target="_blank" rel="nofollow noopener"&gt;TEP Residential Insulation Program&lt;/a&gt;, &lt;em&gt;&amp;ldquo;Tucson Electric Power offers residential customers up to $800 rebate for the purchase and installation of attic/roof insulation.&amp;rdquo;&lt;/em&gt; In a Zone 2B climate with 3,423 annual CDD, attic insulation pays back fastest of any HVAC-adjacent retrofit. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Arizona ROC Licensing (R-39 / CR-39)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Tucson must hold a current license from the &lt;strong&gt;Arizona Registrar of Contractors (ROC)&lt;/strong&gt;. Per the Arizona ROC License Classifications framework, the residential HVAC classification is &lt;strong&gt;R-39 Air Conditioning and Refrigeration, Including Solar&lt;/strong&gt;, which &lt;em&gt;&amp;ldquo;allows the licensee to install and repair comfort air conditioning systems, including refrigeration, evaporative cooling, ventilating, and heating with or without solar equipment.&amp;rdquo;&lt;/em&gt; A dual-scope &lt;strong&gt;CR-39&lt;/strong&gt; classification covers both residential and commercial work. Verifying a contractor&amp;rsquo;s active ROC license via the state board&amp;rsquo;s license lookup before authorizing work is basic due diligence for Tucson homeowners. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Tucson Planning &amp;amp; Development Services Department&lt;/strong&gt;; contact the department directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10705,6 +10763,19 @@
       <c r="Q123" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, PSO&amp;rsquo;s current residential rebate catalog, the Oklahoma Construction Industries Board, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTUL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tulsa International Airport (KTUL) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013968), Tulsa records an &lt;strong&gt;annual mean temperature of 61.3&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,451.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,128.3 cooling degree days&lt;/strong&gt;, &lt;strong&gt;40.96 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;8.7 inches of annual snowfall&lt;/strong&gt;. The 1.6:1 HDD-to-CDD ratio defines Tulsa as a Zone 3A warm-humid climate with both meaningful heating and cooling demand. Tornado Alley exposure is a distinctive Tulsa-area HVAC design consideration &amp;mdash; outdoor condenser units benefit from impact-resistant hail guards in a region that routinely sees severe spring storms.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:75000&amp;amp;in=state:40" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Tulsa city, Oklahoma) report &lt;strong&gt;171,382 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1972&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.5% utility natural gas&lt;/strong&gt; (100,337 units), &lt;strong&gt;39.4% electricity&lt;/strong&gt; (67,506 units), and small shares for bottled/LP gas, wood, and solar. The early-1970s median age means most Tulsa homes have cycled through two or three HVAC systems since original construction &amp;mdash; and given PSO&amp;rsquo;s generous rebate tiers (below), now is a favorable time for that replacement to be a heat pump rather than a like-for-like gas-plus-AC swap.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;PSO Residential Rebates (Tiered by Efficiency)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tulsa&amp;rsquo;s electricity is provided by &lt;strong&gt;Public Service Company of Oklahoma (PSO)&lt;/strong&gt;, an AEP subsidiary. Per the &lt;a href="https://powerforwardwithpso.com/rebates/" target="_blank" rel="nofollow noopener"&gt;PSO Power Forward residential rebate catalog&lt;/a&gt;, current HVAC rebates are among the most comprehensive of any U.S. utility and are tiered by equipment efficiency: &lt;strong&gt;air-source heat pump $600 at 15.2&amp;ndash;17.1 SEER2, $1,000 at 17.2&amp;ndash;19 SEER2, $1,400 at 19.1+ SEER2&lt;/strong&gt;; &lt;strong&gt;ductless mini-split up to $600&lt;/strong&gt;; &lt;strong&gt;geothermal / ground-source heat pump $1,400&lt;/strong&gt;; &lt;strong&gt;central AC $200 at 15.2&amp;ndash;17.1 SEER2, $600 at 17.2&amp;ndash;19 SEER2, $800 at 19.1+ SEER2&lt;/strong&gt;; &lt;strong&gt;AC tune-up up to $125&lt;/strong&gt;; &lt;strong&gt;heat-pump tune-up $200&lt;/strong&gt;. The tiered structure rewards specifying higher-efficiency equipment &amp;mdash; a 19.1+ SEER2 heat pump nets an $800 larger rebate than a 15.2 SEER2 unit. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Oklahoma Mechanical Contractor Licensing (OK CIB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Tulsa must hold a current license from the &lt;strong&gt;Oklahoma Construction Industries Board (CIB)&lt;/strong&gt;, regulated under &lt;strong&gt;59 O.S. Section 1850.1 et seq. (Mechanical License Act)&lt;/strong&gt; and &lt;strong&gt;OAC Title 158, Chapter 50&lt;/strong&gt;. Per the &lt;a href="https://oklahoma.gov/cib/your-industry/mechanical.html" target="_blank" rel="nofollow noopener"&gt;Oklahoma CIB Mechanical Industry page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Mechanical licenses shall be issued as journeyman, contractor or inactive contractor,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;no state agency, political subdivision, business entity or trust shall act as a mechanical firm unless a licensed, active mechanical contractor is associated with and responsible for all mechanical work of such entity.&amp;rdquo;&lt;/em&gt; For Tulsa homeowners, that second rule means you can verify a firm&amp;rsquo;s CIB status before authorizing work &amp;mdash; if there&amp;rsquo;s no licensed active contractor named as responsible for the firm, it&amp;rsquo;s operating outside Oklahoma law. Permit fees for Tulsa residential mechanical work are codified in Title 49 of the Tulsa Revised Ordinances Chapter 5; contact the Tulsa Permit Center at (918) 596-9456 for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -2961,6 +2961,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the City of Dallas Sustainable Development and Construction codes, the Texas Department of Licensing and Regulation, NOAA National Weather Service tornado climatology, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KDFW)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dallas/Fort Worth International Airport (KDFW) is the NOAA reference station for the Dallas metroplex. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013960), Dallas records an &lt;strong&gt;annual mean temperature of 68.0&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,124.8 annual cooling degree days&lt;/strong&gt; against 1,991.6 heating degree days, &lt;strong&gt;38.32 inches of annual precipitation&lt;/strong&gt;, and only 1.7 inches of snowfall. The 1.6:1 CDD-to-HDD ratio defines Dallas as a cooling-dominated Zone 3A warm-humid climate. But the region&amp;rsquo;s defining HVAC risk factor isn&amp;rsquo;t heat &amp;mdash; it&amp;rsquo;s severe weather: per the &lt;a href="https://www.weather.gov/fwd/fwdtornadoes" target="_blank" rel="nofollow noopener"&gt;NOAA National Weather Service Fort Worth/Dallas Tornado Climatology&lt;/a&gt;, North and Central Texas averages &lt;strong&gt;26 tornadoes per year&lt;/strong&gt;, peaking at 7 per month in both April and May. Outdoor condenser units in the Dallas area benefit from impact-resistant hail guards and proper wind-load tie-downs.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Electric-Dominant Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:19000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Dallas city, Texas) report &lt;strong&gt;528,038 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1980&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;65.2% electricity&lt;/strong&gt; (344,045 units) dominates, with 33.0% utility natural gas (174,386 units). Like Houston, Dallas&amp;rsquo;s electric-dominant heating reflects the short heating season (1,991 HDD) and widespread heat-pump adoption &amp;mdash; systems that serve the far-larger cooling load efficiently and handle the modest winter heating requirement as a secondary function.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dallas City Code: 2021 IMC + 2021 IECC&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dallas adopted its current code cycle effective May 12, 2023. Per the &lt;a href="https://dallascityhall.com/departments/sustainabledevelopment/buildinginspection/Pages/know_code.aspx" target="_blank" rel="nofollow noopener"&gt;City of Dallas Sustainable Development and Construction &amp;ldquo;Know the Code&amp;rdquo; page&lt;/a&gt;: &lt;strong&gt;Chapter 55&lt;/strong&gt; adopts the &lt;em&gt;&amp;ldquo;2021 International Mechanical Code with Dallas Amendments&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Chapter 59&lt;/strong&gt; adopts the &lt;em&gt;&amp;ldquo;2021 International Energy Conservation Code with Dallas Amendments&amp;rdquo;&lt;/em&gt;; and &lt;strong&gt;Chapter 61&lt;/strong&gt; adopts the &lt;em&gt;&amp;ldquo;2015 International Green Construction Code with Dallas Amendments&amp;rdquo;&lt;/em&gt; (amendments effective January 25, 2017). Any HVAC replacement in Dallas must comply with the 2021 IMC and 2021 IECC thresholds &amp;mdash; which generally means higher minimum equipment efficiency, stricter duct sealing, and updated Manual J load-calculation expectations.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR ACR License: Class A vs. Class B&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Dallas must hold a current Air Conditioning and Refrigeration (ACR) Contractor license issued by the &lt;a href="https://www.tdlr.texas.gov/acr/contractor-apply.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by &lt;strong&gt;Texas Administrative Code Title 16 Chapter 75&lt;/strong&gt;. The two classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; &lt;em&gt;&amp;ldquo;allows you to work on any size unit&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Class B&lt;/strong&gt; &lt;em&gt;&amp;ldquo;allows you to work on cooling systems of 25 tons and under, and heating systems of 1.5 million BTUs/hour and under&amp;rdquo;&lt;/em&gt; (residential and light commercial). Licensure requires &lt;em&gt;&amp;ldquo;at least 48 months of practical experience in air-conditioning and refrigeration-related work under the supervision of a licensed air conditioning and refrigeration contractor in the past 72 months.&amp;rdquo;&lt;/em&gt; Insurance minimums are also tiered: &lt;strong&gt;Class A requires $300,000 per occurrence / $600,000 aggregate&lt;/strong&gt;; &lt;strong&gt;Class B requires $100,000 per occurrence / $200,000 aggregate&lt;/strong&gt;. For typical Dallas residential work, a Class B contractor is fully qualified and sufficient &amp;mdash; Class A matters only for commercial projects above 25 tons.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Deregulated Retail Electricity&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dallas electricity distribution is handled by &lt;strong&gt;Oncor Electric Delivery&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Dallas are typically administered by your chosen REP, not Oncor directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Dallas ZIP, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Atmos Energy administers any natural-gas-specific rebates. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Dallas Building Inspection Division&lt;/strong&gt;; contact Building Inspection at 320 E. Jefferson Blvd, Room 118, for the current mechanical permit fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3472,6 +3487,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, DTE Energy&amp;rsquo;s residential rebate catalog, the Michigan Department of Licensing and Regulatory Affairs (LARA) Bureau of Construction Codes, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KDTW)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Detroit Metropolitan Wayne County Airport (KDTW) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094847), Detroit records an &lt;strong&gt;annual mean temperature of 50.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;6,067.1 annual heating degree days&lt;/strong&gt; against 847.0 cooling degree days, &lt;strong&gt;34.32 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;45.0 inches of annual snowfall&lt;/strong&gt;. The 7.2:1 HDD-to-CDD ratio defines Detroit as one of the most heating-dominated major U.S. cities &amp;mdash; a distinctive Great Lakes climate with lake-effect snow, sub-zero polar-vortex events, and long heating seasons that run from October through April.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Gas-Dominant, Pre-WWII Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:22000&amp;amp;in=state:26" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Detroit city, Michigan) report &lt;strong&gt;253,207 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1947&lt;/strong&gt; &amp;mdash; among the oldest housing stocks of any major U.S. city. Heating-fuel distribution: &lt;strong&gt;81.8% utility natural gas&lt;/strong&gt; (207,149 units) overwhelmingly dominates, with only 15.4% electricity (38,928 units). Detroit&amp;rsquo;s pre-WWII bungalows, brick 2-flats, and worker-housing stock were almost universally built around gas-fired systems, and envelope limitations in this era of construction (minimal continuous insulation, leaky windows, knob-and-tube electrical) mean design heating loads are high and well-sized modern furnaces often feel &amp;ldquo;small&amp;rdquo; compared to the heritage equipment they replace.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;DTE Energy Rebates: Tiered by SEER2 / HSPF2&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.dteenergy.com/us/en/residential/save-money-energy/rebates-and-offers/air-conditioners.html" target="_blank" rel="nofollow noopener"&gt;DTE Energy residential rebates page for Air Conditioners and Heat Pumps&lt;/a&gt;, current dollar amounts are strictly efficiency-tiered: &lt;strong&gt;central air conditioner $100 / $200 / $300&lt;/strong&gt; at 15.2&amp;ndash;15.99, 16&amp;ndash;17.99, and 18+ SEER2 respectively; &lt;strong&gt;cold-climate air-source heat pump $900 / $1,000 / $1,200&lt;/strong&gt; across three SEER2/HSPF2 tiers (16+ SEER2 with 9.1+ HSPF2 hits the top $1,200); &lt;strong&gt;ground-source heat pump $600 at 17&amp;ndash;19.99 EER2 / $800 at 20+ EER2&lt;/strong&gt;; &lt;strong&gt;standard air-source heat pump $150 at 15.2&amp;ndash;17.99 SEER2 / $500 at 18+ SEER2&lt;/strong&gt;; &lt;strong&gt;ductless mini-split $700 at 17&amp;ndash;31.5 SEER2 / $1,000 above 31.5 SEER2&lt;/strong&gt;. The tiered structure rewards specifying higher-efficiency equipment &amp;mdash; an 18+ SEER2 AC nets $200 more than the minimum tier. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Michigan Mechanical Contractor License (LARA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Detroit must hold a current Michigan Mechanical Contractor License from the &lt;strong&gt;Michigan Department of Licensing and Regulatory Affairs (LARA) Bureau of Construction Codes&lt;/strong&gt;. Per the &lt;a href="https://www.michigan.gov/-/media/Project/Websites/lara/Folder14/ApplicationForMechanicalContractorExaminationLicensing_BCC-11_08-2021.pdf" target="_blank" rel="nofollow noopener"&gt;LARA Application for Mechanical Contractor Examination and Licensing (BCC-11)&lt;/a&gt;, Michigan issues 10 distinct mechanical-license classifications: &lt;em&gt;&amp;ldquo;(1) Hydronic heating and cooling and process piping, (2) HVAC equipment, (3) Ductwork, (4) Refrigeration, (5) Limited Heating service, (6) Unlimited Heating Service, (7) Limited Refrigeration and air conditioning service, (8) Unlimited refrigeration and air conditioning service, (9) Fire Suppression, (10) Specialty.&amp;rdquo;&lt;/em&gt; The HVAC Equipment classification &lt;em&gt;&amp;ldquo;includes ductwork, gas piping and venting&amp;rdquo;&lt;/em&gt; but explicitly excludes &lt;em&gt;&amp;ldquo;portable self-contained refrigeration equipment and window type air conditioners of not more than 1 1/2 horsepower.&amp;rdquo;&lt;/em&gt; License applicants must demonstrate &lt;em&gt;&amp;ldquo;a minimum of 3 years or 6,000 hours of performance in EACH work classification&amp;rdquo;&lt;/em&gt; being sought. Permit fees for residential mechanical work are set by the &lt;strong&gt;Detroit BSEED (Buildings, Safety Engineering &amp;amp; Environmental Department)&lt;/strong&gt;; contact BSEED at (313) 224-2733 for the current fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5927,6 +5955,19 @@
       <c r="Q66" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Nevada State Contractors Board, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLAS Harry Reid)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Harry Reid International Airport (KLAS, formerly McCarran) is the NOAA reference station for the Las Vegas Valley. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023169), Las Vegas records an &lt;strong&gt;annual mean temperature of 70.1&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,720.2 annual cooling degree days&lt;/strong&gt; against 1,835.6 heating degree days, and only &lt;strong&gt;4.18 inches of annual precipitation&lt;/strong&gt; (among the driest of any major U.S. city) with just 0.2 inches of snow. The 2.0:1 CDD-to-HDD ratio defines Las Vegas as a cooling-dominated Zone 3B warm-dry desert climate where summer extremes regularly exceed 110&amp;deg;F and the extreme aridity imposes distinctive HVAC demands &amp;mdash; from UV degradation of refrigerant-line insulation to attic temperatures that push 140&amp;deg;F during afternoon peaks.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: The Newest of Any Major U.S. City&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:40000&amp;amp;in=state:32" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Las Vegas city, Nevada) report &lt;strong&gt;244,429 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1994&lt;/strong&gt; &amp;mdash; newer than any other major U.S. city by a decade or more, reflecting Las Vegas&amp;rsquo;s rapid post-1990 growth. Heating-fuel distribution: &lt;strong&gt;56.1% utility natural gas&lt;/strong&gt; (137,016 units), &lt;strong&gt;40.7% electricity&lt;/strong&gt; (99,465 units), and 2,368 solar-heated homes. The newness of the housing stock has a practical HVAC consequence: most Las Vegas homes were built to post-1990 energy codes with proper R-value insulation and dual-pane windows from the start, so HVAC replacement work rarely faces the envelope-retrofit challenges common in older cities.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Attic Ducts in a 110&amp;deg;F Climate&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Most Las Vegas homes route central-air ductwork through unconditioned attics &amp;mdash; spaces that regularly exceed 140&amp;deg;F during summer afternoons. Per the &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Central Air Conditioning&lt;/a&gt;, best-practice installation &lt;em&gt;&amp;ldquo;installs ductwork within conditioned space whenever possible, not in unconditioned spaces like attics or garages.&amp;rdquo;&lt;/em&gt; DOE also advises: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is the correct size for your home. An oversized unit won&amp;rsquo;t adequately remove humidity, while an undersized unit won&amp;rsquo;t cool effectively on the hottest days.&amp;rdquo;&lt;/em&gt; For Las Vegas specifically, with 3,720 annual CDD and extreme attic temperatures, every foot of uninsulated or leaky attic duct loses significant cooling capacity. Homeowners planning an HVAC replacement should explicitly ask contractors about R-8 insulated duct with aggressive joint mastic sealing, or moving ducts into the conditioned envelope where feasible.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Nevada C-21 Refrigeration &amp;amp; Air Conditioning License&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in the Las Vegas Valley must hold a current license from the &lt;a href="https://www.nvcontractorsboard.com/licensing/license-classifications/" target="_blank" rel="nofollow noopener"&gt;Nevada State Contractors Board (NSCB)&lt;/a&gt;. The relevant classification is &lt;strong&gt;C-21 Refrigeration and Air Conditioning&lt;/strong&gt;, which falls under the NSCB&amp;rsquo;s Classification C (Specialty Contractor) category covering 42 distinct subcontracting fields. The detailed scope of C-21 work is codified in &lt;strong&gt;Chapter 624 of the Nevada Administrative Code&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active C-21 license via the NSCB&amp;rsquo;s public license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Las Vegas Building &amp;amp; Safety Department&lt;/strong&gt;; contact Building &amp;amp; Safety at 702-229-6251 or BuildingInfo@LasVegasNevada.gov for the current mechanical permit fee schedule. For current &lt;strong&gt;NV Energy PowerShift&lt;/strong&gt; heating and cooling rebate amounts, see nvenergy.com/save-with-powershift directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7903,6 +7944,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Philadelphia Department of Licenses and Inspections fee schedules, Philadelphia Gas Works&amp;rsquo; EnergySense rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPHL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Philadelphia International Airport (KPHL) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013739), Philadelphia records an &lt;strong&gt;annual mean temperature of 56.3&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,509.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,358.3 cooling degree days&lt;/strong&gt;, &lt;strong&gt;44.11 inches of annual precipitation&lt;/strong&gt;, and 23.1 inches of snowfall. The 3.3:1 HDD-to-CDD ratio defines Philadelphia as a classic Zone 4A mixed-humid climate where both heating and cooling matter meaningfully &amp;mdash; and where the region&amp;rsquo;s distinctive pre-war row-house stock drives unique HVAC retrofit constraints.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Largest Pre-WWII Row-House Inventory in the U.S.&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:60000&amp;amp;in=state:42" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Philadelphia city, Pennsylvania) report &lt;strong&gt;669,222 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1949&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.5% utility natural gas&lt;/strong&gt; (465,427 units), 24.4% electricity (163,218 units), and a notable &lt;strong&gt;3.0% fuel oil&lt;/strong&gt; (20,000 units). Philadelphia&amp;rsquo;s 669,000+ occupied-unit count makes it the largest municipal housing stock in Batch 4 &amp;mdash; and the 1949 median year reflects the city&amp;rsquo;s dense inventory of brick row-houses, many originally built with steam or hot-water heat and no central ducting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mini-Split Heat Pumps in Ductless Housing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The absence of central ducting in many Philadelphia row-houses makes ductless heat pumps a natural retrofit path. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Mini split heat pumps (also known as ductless heat pumps) can be a good choice for room additions and for homes without ductwork, such as those heated by hydronic (hot water heat), radiant panels, and space heaters (wood, kerosene, propane).&amp;rdquo;&lt;/em&gt; For Philadelphia homeowners living in a row-house with steam radiators or hot-water baseboard, a multi-zone ductless mini-split installation provides both modern cooling (which many of these homes never had centrally) and highly efficient supplemental heating &amp;mdash; without requiring the wall-by-wall ductwork retrofit that would otherwise make heat-pump conversion prohibitive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Philadelphia Mechanical Permit Fees (L&amp;amp;I)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Philadelphia publishes an itemized mechanical permit fee schedule on its L&amp;amp;I website. Per the &lt;a href="https://www.phila.gov/services/permits-violations-licenses/apply-for-a-permit/building-and-repair-permits/get-a-mechanical-permit/" target="_blank" rel="nofollow noopener"&gt;City of Philadelphia &amp;ldquo;Get a Mechanical Permit&amp;rdquo; page&lt;/a&gt;, current fees include: &lt;strong&gt;$100 nonrefundable filing fee&lt;/strong&gt;; &lt;strong&gt;$15.10 per register or diffuser served by ductwork&lt;/strong&gt;; &lt;strong&gt;$69 per appliance in one-or-two-family dwellings&lt;/strong&gt;; &lt;strong&gt;$69 per direct-vent or warm-air heating apparatus&lt;/strong&gt;; &lt;strong&gt;$76 per ductwork installation in a single-tenant space under 2,000 CFM&lt;/strong&gt;; &lt;strong&gt;2% of contract costs for fuel-gas work (minimum $189)&lt;/strong&gt;; plus a &lt;strong&gt;$3 city surcharge&lt;/strong&gt; and &lt;strong&gt;$4.50 state surcharge&lt;/strong&gt; per permit. For a typical furnace-plus-AC replacement in a Philadelphia row-house, total permit fees generally fall in the $200&amp;ndash;$350 range &amp;mdash; separate from equipment and installation cost.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;PGW EnergySense Rebates &amp;amp; L&amp;amp;I Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.pgworks.com/customer-care/efficiency" target="_blank" rel="nofollow noopener"&gt;Philadelphia Gas Works (PGW) Efficiency / EnergySense page&lt;/a&gt;, current residential gas rebates include: &lt;strong&gt;furnaces up to $500&lt;/strong&gt;, &lt;strong&gt;boilers up to $1,500&lt;/strong&gt;, &lt;strong&gt;standard tank water heaters $200&lt;/strong&gt;, &lt;strong&gt;tankless / condensing water heaters $500&lt;/strong&gt;, and a &lt;strong&gt;$70 smart-thermostat instant rebate&lt;/strong&gt;. For current PECO electric rebate amounts, visit peco.com directly. Pennsylvania does not issue a statewide HVAC contractor license; Philadelphia requires city-issued credentials through L&amp;amp;I. Per the &lt;a href="https://www.phila.gov/services/permits-violations-licenses/get-a-license/trade-licenses/get-a-contractor-license/" target="_blank" rel="nofollow noopener"&gt;Philadelphia L&amp;amp;I Contractor License page&lt;/a&gt;, contractors must carry &lt;strong&gt;$500,000 per-occurrence general liability insurance&lt;/strong&gt; and &lt;strong&gt;$300,000 automobile liability&lt;/strong&gt;; supervisors must complete &lt;em&gt;&amp;ldquo;an approved OSHA 30 safety training course within five years of application&amp;rdquo;&lt;/em&gt;; and license fees are &lt;strong&gt;$126 initial / $126 annual renewal&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active L&amp;amp;I license before authorizing work is the baseline due-diligence step for every Philadelphia homeowner.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9585,6 +9641,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Seattle Department of Construction &amp;amp; Inspections, Seattle City Light, the Washington Administrative Code, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSEA Sea-Tac)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Seattle-Tacoma International Airport (KSEA) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024233), Seattle records an &lt;strong&gt;annual mean temperature of 53.7&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,375.8 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;265.0 cooling degree days&lt;/strong&gt;, &lt;strong&gt;39.34 inches of annual precipitation&lt;/strong&gt;, and 6.3 inches of snowfall. The 16:1 HDD-to-CDD ratio makes Seattle the most heating-dominated major U.S. city researched to date &amp;mdash; but the mild marine climate (neither extremely cold in winter nor extremely hot in summer) places it squarely in DOE&amp;rsquo;s ideal heat-pump territory. Damp near-freezing winter conditions are the dominant HVAC design constraint, not absolute cold.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Electric-Majority Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:63000&amp;amp;in=state:53" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Seattle city, Washington) report &lt;strong&gt;353,019 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution is unusual: &lt;strong&gt;59.7% electricity&lt;/strong&gt; (210,693 units) dominates, with only &lt;strong&gt;33.8% utility natural gas&lt;/strong&gt; (119,194 units) and 11,421 units on fuel oil. Seattle is one of only a handful of major U.S. cities where electric heating is the majority &amp;mdash; the direct consequence of Seattle City Light&amp;rsquo;s abundant low-cost hydroelectric power. For homeowners, this has a practical implication: converting from electric baseboard to a modern heat pump delivers far greater efficiency gains in Seattle than in gas-dominant cities, because the electric resistance baseline is so energy-intensive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;2021 Seattle Energy Code &amp;amp; Fossil-Fuel Compliance Path&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Seattle has some of the strictest residential energy-code requirements in the country. Per the &lt;a href="https://www.seattle.gov/sdci/codes/codes-we-enforce-(a-z)/energy-code" target="_blank" rel="nofollow noopener"&gt;SDCI Seattle Energy Code page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;We have adopted the 2021 Seattle Energy Codes&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;the 2021 SEC largely matches the 2021 Washington State Energy Code, including adoption of the new &amp;lsquo;fossil fuel compliance path.&amp;rsquo;&amp;rdquo;&lt;/em&gt; The practical implication for Seattle homeowners replacing a gas furnace: the 2021 SEC&amp;rsquo;s fossil-fuel path imposes additional efficiency or equipment-swap requirements that don&amp;rsquo;t apply to equivalent heat-pump installations, which is one of the strongest regulatory tailwinds behind electrification in any U.S. city.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Seattle City Light Rebates (Tiered by HSPF2)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.seattle.gov/city-light/residential-services/home-energy-solutions" target="_blank" rel="nofollow noopener"&gt;Seattle City Light&amp;rsquo;s Home Energy Solutions page&lt;/a&gt;, residential heat-pump instant discounts are tiered by HSPF2 efficiency: &lt;strong&gt;HSPF2 8.1 or higher: $300 instant discount&lt;/strong&gt;; &lt;strong&gt;HSPF2 8.5 or higher: $400&lt;/strong&gt;; &lt;strong&gt;HSPF2 9.5 or higher: $600&lt;/strong&gt;. Separately, homeowners can receive &lt;em&gt;&amp;ldquo;$750 rebate on heat pump water heaters&amp;rdquo;&lt;/em&gt; and a &lt;em&gt;&amp;ldquo;$50/unit instant rebate courtesy of Seattle City Light&amp;rdquo;&lt;/em&gt; for smart thermostats designed for electric baseboard heaters (through December 31, 2026). For current natural-gas furnace, boiler, and heat pump rebate amounts from &lt;strong&gt;Puget Sound Energy (PSE)&lt;/strong&gt;, see pse.com/rebates directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Washington L&amp;amp;I 06A Licensing (WAC 296-46B-920)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC/refrigeration contractor working in Seattle must hold a current &lt;strong&gt;06A HVAC/Refrigeration specialty license&lt;/strong&gt; from the Washington State Department of Labor &amp;amp; Industries (L&amp;amp;I). Per &lt;a href="https://app.leg.wa.gov/wac/default.aspx?cite=296-46B-920" target="_blank" rel="nofollow noopener"&gt;Washington Administrative Code Section 296-46B-920&lt;/a&gt;, the 06A specialty &lt;em&gt;&amp;ldquo;is not limited by voltage, phase, or amperage&amp;rdquo;&lt;/em&gt; and covers &lt;em&gt;&amp;ldquo;installation, repair, replacement, and maintenance of line voltage components within HVAC/refrigeration equipment&amp;rdquo;&lt;/em&gt; as well as &lt;em&gt;&amp;ldquo;repair, replacement, or maintenance of line voltage flexible supply whips not exceeding six feet in length.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active 06A credential via L&amp;amp;I&amp;rsquo;s license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Seattle Department of Construction &amp;amp; Inspections (SDCI)&lt;/strong&gt;; contact SDCI at (206) 684-8600 for the current mechanical permit fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -2286,6 +2286,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance &amp;mdash; plus state-level licensing authority. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCLT Douglas)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charlotte Douglas International Airport (KCLT) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013881), Charlotte records an &lt;strong&gt;annual mean temperature of 61.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,058 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,768.7 cooling degree days&lt;/strong&gt;, &lt;strong&gt;43.60 inches of annual precipitation&lt;/strong&gt;, and only 3.5 inches of snow. The 1.7:1 HDD-to-CDD ratio and warm-humid Zone 3A classification make Charlotte a nearly balanced heating-and-cooling market, with summer humidity driving dehumidification demand and mild winters keeping heat-pump balance points favorable.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Electric-Majority Heat Pumps&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:12000&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charlotte city, North Carolina) report &lt;strong&gt;361,100 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1994&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;53.3% electricity&lt;/strong&gt; (192,386 units) narrowly leads &lt;strong&gt;44.5% utility natural gas&lt;/strong&gt; (160,873 units). The electric-majority share is typical of new-growth Sun Belt metros where central heat pumps are the dominant system architecture &amp;mdash; a single outdoor unit handles both the 1,768 cooling degree days and the modest 3,058 heating degree days, and integrated electric resistance or heat-strip backup covers the handful of coldest winter nights.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Heat Pump Dehumidification Advantage&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charlotte&amp;rsquo;s 43+ inches of annual rainfall and warm-humid summers make humidity control a real HVAC design factor. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;high-efficiency heat pumps also dehumidify better than standard central air conditioners, resulting in less energy usage and more cooling comfort in summer months.&amp;rdquo;&lt;/em&gt; For Charlotte homeowners, the practical implication is that a high-efficiency heat pump handles both the cooling-capacity demand AND the latent-humidity load more effectively than an equivalent single-stage AC paired with a gas furnace &amp;mdash; which explains why heat pumps have become the default in the 53% of Charlotte homes already heated electrically.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Charlotte must hold a current state-issued Heating &amp;amp; Cooling Contractor License from the &lt;a href="https://www.nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating &amp;amp; Fire Sprinkler Contractors&lt;/a&gt;. NC issues three heating-license classifications &amp;mdash; &lt;strong&gt;H-1&lt;/strong&gt; (unlimited scope), &lt;strong&gt;H-2&lt;/strong&gt; (limited to systems below specified tonnage/BTU thresholds), and &lt;strong&gt;H-3&lt;/strong&gt; (packaged-unit specialty). For typical Charlotte residential work, any of the three classifications can be sufficient depending on the job scope; verifying the contractor&amp;rsquo;s active license with the NC Board at 919-875-3612 before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by &lt;strong&gt;Mecklenburg County Code Enforcement (LUESA)&lt;/strong&gt;; contact LUESA directly for the current fee schedule. For current &lt;strong&gt;Duke Energy Carolinas&lt;/strong&gt; Smart $aver rebate amounts and &lt;strong&gt;Piedmont Natural Gas&lt;/strong&gt; incentives, visit the utilities&amp;rsquo; sites directly or check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Charlotte ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2872,6 +2885,21 @@
       <c r="Q29" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, AEP Ohio&amp;rsquo;s residential programs catalog, Columbia Gas of Ohio, the Ohio Construction Industry Licensing Board, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCMH John Glenn)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;John Glenn Columbus International Airport (KCMH) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014821), Columbus records an &lt;strong&gt;annual mean temperature of 53.5&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,233.4 annual heating degree days&lt;/strong&gt; against 1,067.8 cooling degree days, &lt;strong&gt;41.57 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;28.2 inches of annual snowfall&lt;/strong&gt;. The 4.9:1 HDD-to-CDD ratio defines Columbus as a heating-dominated Zone 5A cool-humid climate &amp;mdash; long winters, substantial snow load, and high summer humidity together drive an unusual combination of sizing pressures on HVAC equipment.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:18000&amp;amp;in=state:39" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Columbus city, Ohio) report &lt;strong&gt;386,581 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1980&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;64.2% utility natural gas&lt;/strong&gt; (248,294 units), &lt;strong&gt;33.7% electricity&lt;/strong&gt; (130,231 units), and 5,351 bottled/LP gas homes. Columbus&amp;rsquo;s gas dominance reflects both the long heating season and the mature Columbia Gas distribution network serving the city.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump Performance (Zone 5A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Columbus&amp;rsquo;s 5,233 HDD and routine sub-freezing winter temperatures put it in the climate zone where cold-climate-rated heat pumps matter. Per the &lt;a href="https://www.energystar.gov/" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Cold Climate Air-Source Heat Pump specification&lt;/a&gt;, DOE guidance recommends ccASHPs for Zone 5 because they maintain rated heating capacity at 5&amp;deg;F &amp;mdash; the threshold at which standard ASHPs lose significant output and switch to resistance backup. Zone 5A&amp;rsquo;s combination of &lt;strong&gt;28.2 inches of annual snowfall&lt;/strong&gt; and &lt;strong&gt;41.57 inches of precipitation&lt;/strong&gt; also drives repeated freeze/thaw cycling that stresses outdoor heat-pump defrost cycles and condensate drains. Columbus installations benefit from elevated snow stands and demand-defrost controls.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;AEP Ohio Rebates &amp;amp; Columbia Gas Status&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.aepohio.com/savings/home/money-saving-programs/" target="_blank" rel="nofollow noopener"&gt;AEP Ohio Money Saving Programs page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;When you sign up for the Power Rewards: Smart Thermostat Program, you&amp;rsquo;ll receive an instant $75 discount on the purchase of a new smart thermostat.&amp;rdquo;&lt;/em&gt; On the natural-gas side: per &lt;a href="https://www.columbiagasohio.com/energy-efficiency/for-your-home" target="_blank" rel="nofollow noopener"&gt;Columbia Gas of Ohio&amp;rsquo;s For Your Home page&lt;/a&gt;, the utility&amp;rsquo;s &lt;strong&gt;residential energy-efficiency rebate programs have ended&lt;/strong&gt; for non-income-qualified customers. Income-eligible customers may still qualify for no-cost weatherization through the WarmChoice program. For current AEP Ohio HVAC equipment rebates beyond the smart thermostat, check aepohio.com directly &amp;mdash; program lineup changes annually. All incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio OCILB Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Columbus must hold a current state-issued HVAC Contractor License from the &lt;a href="https://com.ohio.gov/divisions-and-programs/industrial-compliance/boards/ohio-construction-industry-licensing-board/about-ocilb" target="_blank" rel="nofollow noopener"&gt;Ohio Construction Industry Licensing Board (OCILB)&lt;/a&gt;, administered by the Ohio Department of Commerce. The OCILB &lt;em&gt;&amp;ldquo;licenses Ohio electrical, HVAC, plumbing, hydronics, and refrigeration contractors&amp;rdquo;&lt;/em&gt; and can be reached at 6606 Tussing Road, P.O. Box 4009, Reynoldsburg, Ohio 43068-9009 or (614) 644-3493. Verifying a contractor&amp;rsquo;s active OCILB HVAC license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Columbus Department of Building &amp;amp; Zoning Services&lt;/strong&gt; and published in the 2026 Combined Development Related Fee Schedule (effective January 22, 2026); contact Building &amp;amp; Zoning Services directly for the current mechanical line items.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5215,6 +5243,21 @@
       <c r="Q57" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, AES Indiana&amp;rsquo;s residential rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KIND)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indianapolis International Airport (KIND) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093819), Indianapolis records an &lt;strong&gt;annual mean temperature of 53.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,250.3 annual heating degree days&lt;/strong&gt; against 1,139.1 cooling degree days, &lt;strong&gt;43.63 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;25.5 inches of annual snowfall&lt;/strong&gt;. The 4.6:1 HDD-to-CDD ratio defines Indianapolis as a heating-dominated Zone 5A cool-humid climate &amp;mdash; similar in magnitude to Columbus but with slightly lower annual snowfall and marginally higher cooling demand.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock (Indianapolis-Marion County Balance)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:36003&amp;amp;in=state:18" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Indianapolis city (balance), Indiana) report &lt;strong&gt;359,665 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1972&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;56.7% utility natural gas&lt;/strong&gt; (203,861 units), &lt;strong&gt;40.6% electricity&lt;/strong&gt; (146,128 units), and 5,868 bottled/LP gas homes. Because Indianapolis is a consolidated city-county (Indianapolis-Marion under Unigov), the ACS entity is reported as &amp;ldquo;Indianapolis city (balance)&amp;rdquo; &amp;mdash; representing the portion of Marion County served by the consolidated city government.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dual-Fuel Systems for Zone 5A&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indianapolis&amp;rsquo;s 5,250 HDD puts it at the climate threshold where dual-fuel (hybrid) heat pump systems excel. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, DOE documents a seasonal failure mode for standard ASHPs in Zone 5A: &lt;em&gt;&amp;ldquo;air-source heat pumps have been used for many years in nearly all parts of the United States, but until recently they had not been used in areas that experienced extended periods of subfreezing temperatures.&amp;rdquo;&lt;/em&gt; When outdoor temperatures drop below the heat pump&amp;rsquo;s balance point, the unit loses efficiency and shifts load to resistance backup (if electric) or the companion gas furnace (if dual-fuel). For Indianapolis homeowners replacing an aging gas furnace, a dual-fuel specification &amp;mdash; heat pump outdoor unit + gas furnace indoor coil &amp;mdash; captures the efficiency gains during milder months while preserving gas backup for the coldest nights.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;AES Indiana Rebates (Tiered by SEER2/HSPF)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.aesindiana.com/rebates" target="_blank" rel="nofollow noopener"&gt;AES Indiana residential rebates page&lt;/a&gt;, current HVAC-related rebates are strictly efficiency-tiered: &lt;strong&gt;smart thermostat $50&lt;/strong&gt;; &lt;strong&gt;heat pump water heater $600&lt;/strong&gt;; &lt;strong&gt;mini-split heat pump (self-installed)&lt;/strong&gt; starts at $100 for 15.2 SEER2 / 8.7 HSPF and scales upward: &lt;strong&gt;$225&lt;/strong&gt; at 17.1 SEER2 / 9.2 HSPF, &lt;strong&gt;$300&lt;/strong&gt; at 19 SEER / 9.5 HSPF, &lt;strong&gt;$525&lt;/strong&gt; at 21 SEER / 10 HSPF, and &lt;strong&gt;$725&lt;/strong&gt; at 23+ SEER / 10 HSPF. The tiered structure rewards specifying higher efficiency &amp;mdash; a 23+ SEER mini-split nets $625 more than the minimum tier. Natural-gas furnace rebates are separately administered by &lt;strong&gt;Citizens Energy Group&lt;/strong&gt;, a customer-owned public-trust utility unique to Indianapolis; check citizensenergygroup.com or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current gas amounts. All incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana does not issue a statewide HVAC contractor license through the Indiana Professional Licensing Agency. Instead, HVAC contractor registration and permitting in Indianapolis are handled locally through the &lt;strong&gt;Indianapolis Department of Business &amp;amp; Neighborhood Services (DBNS)&lt;/strong&gt;. For Indianapolis homeowners, verifying that a contractor is registered with DBNS before authorizing any HVAC work is the critical due-diligence step &amp;mdash; more important than in states with a statewide board, because the local registration is the only formal credential. Contact DBNS directly for the current mechanical permit fee schedule and to verify contractor status.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7268,6 +7311,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance &amp;mdash; supplemented by state-level licensing authority. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBNA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nashville International Airport (KBNA) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013897), Nashville records an &lt;strong&gt;annual mean temperature of 60.8&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,364.0 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,873.0 cooling degree days&lt;/strong&gt;, &lt;strong&gt;50.51 inches of annual precipitation&lt;/strong&gt;, and only 4.7 inches of snowfall. The 1.8:1 HDD-to-CDD ratio defines Nashville as a classic Zone 4A mixed-humid climate &amp;mdash; near-balanced heating and cooling demand, with 50+ inches of annual rain driving substantial summer humidity load.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: TVA&amp;rsquo;s Electric-Majority Territory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:52006&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Nashville-Davidson metropolitan government balance, Tennessee) report &lt;strong&gt;303,539 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1985&lt;/strong&gt;. Heating-fuel distribution is striking for a mixed-humid Southern city: &lt;strong&gt;66.4% electricity&lt;/strong&gt; (201,663 units) dominates, with only &lt;strong&gt;30.9% utility natural gas&lt;/strong&gt; (93,838 units). The 2-to-1 electric majority reflects Nashville&amp;rsquo;s place in the Tennessee Valley Authority (TVA) service territory &amp;mdash; decades of below-national-average electric rates from TVA&amp;rsquo;s hydro, nuclear, and gas generation mix made electric heat pumps economically competitive with gas furnaces long before most other Southern metros, and the 2-to-1 gap persists today.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dual-Fuel Sizing for Mixed-Humid Zone 4A&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nashville&amp;rsquo;s near-balanced heating and cooling loads make it an ideal climate for dual-fuel heat pump systems. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;during warmer months, the heat pump efficiently heats and cools your home. When temperatures drop, the system automatically switches to the gas furnace, which is better suited for cold weather.&amp;rdquo;&lt;/em&gt; DOE also notes that in zones 1&amp;ndash;4, &lt;em&gt;&amp;ldquo;about 60% of homes rely on furnaces&amp;rdquo;&lt;/em&gt; &amp;mdash; and Nashville sits at the cold edge of Zone 4A, making dual-fuel pairing particularly cost-effective. For the 30.9% of Nashville homes still on gas heat, adding a heat-pump outdoor unit to an existing furnace converts the system to dual-fuel without abandoning the gas asset &amp;mdash; capturing efficiency gains during the 200+ days/year when ambient temperatures sit above the heat pump balance point.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;TN CMC-C License, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Nashville must hold a current state-issued HVAC Mechanical Contractor (&lt;strong&gt;CMC-C&lt;/strong&gt;) license from the &lt;a href="https://www.tn.gov/commerce/regboards.html" target="_blank" rel="nofollow noopener"&gt;Tennessee Board for Licensing Contractors&lt;/a&gt;, administered by the Tennessee Department of Commerce and Insurance. The CMC-C classification covers HVAC and mechanical work; the Board publishes license-holder status via its public lookup tool, and verifying a contractor&amp;rsquo;s active CMC-C license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work in Nashville are set by the &lt;strong&gt;Metro Nashville Department of Codes and Building Safety&lt;/strong&gt;; contact the department directly for the current fee schedule. For current utility rebate dollar amounts, Nashville is served by &lt;strong&gt;Nashville Electric Service (NES)&lt;/strong&gt;, a TVA distributor that passes through &lt;a href="https://www.energyright.com/residential/home-energy/" target="_blank" rel="nofollow noopener"&gt;TVA EnergyRight&lt;/a&gt; residential incentives (including the EnergyRight Heat Pump Program loan); gas rebates are administered by Piedmont Natural Gas. All incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9058,6 +9114,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, CPS Energy&amp;rsquo;s Save for Tomorrow Energy Plan (STEP) rebate catalog, the Texas Department of Licensing and Regulation, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSAT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Antonio International Airport (KSAT) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012921), San Antonio records an &lt;strong&gt;annual mean temperature of 69.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,147.8 annual cooling degree days&lt;/strong&gt; against 1,438.4 heating degree days, &lt;strong&gt;32.38 inches of annual precipitation&lt;/strong&gt;, and essentially no snowfall. The 2.2:1 CDD-to-HDD ratio defines San Antonio as a cooling-dominated Zone 2A hot-humid climate where the AC system carries the system load 7&amp;ndash;9 months of the year and high dew points make latent (humidity) cooling as important as raw sensible capacity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Electric-Majority Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:65000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for San Antonio city, Texas) report &lt;strong&gt;547,883 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.5% electricity&lt;/strong&gt; (380,864 units) overwhelmingly dominates, with only &lt;strong&gt;28.6% utility natural gas&lt;/strong&gt; (156,497 units) and a notable 1,676 solar-heated homes. San Antonio&amp;rsquo;s electric-heat share is the highest of any major Texas city researched &amp;mdash; higher than Houston&amp;rsquo;s 64.5% or Dallas&amp;rsquo;s 65.2% &amp;mdash; reflecting both CPS Energy&amp;rsquo;s competitive municipal electricity rates and the city&amp;rsquo;s post-1970s heat-pump-centric housing growth pattern.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;CPS Energy STEP Rebates (Per-Ton Structure, Unique Among TX Utilities)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Antonio is served by &lt;strong&gt;CPS Energy&lt;/strong&gt;, a municipal utility owned by the City of San Antonio and uniquely positioned among Texas utilities &amp;mdash; because Texas retail electricity is deregulated under ERCOT elsewhere, but CPS operates as a vertically integrated municipal utility with rates set by City Council. Per the &lt;a href="https://resi-savenow.cpsenergy.com/cps-energy/en/savings/hvac-rebates-specifications/" target="_blank" rel="nofollow noopener"&gt;CPS Energy Save for Tomorrow Energy Plan (STEP) HVAC Rebates Specifications&lt;/a&gt;, rebates are structured per cooling ton, scaled by efficiency tier and replacement timing. &lt;strong&gt;Early Replacement&lt;/strong&gt; rebates: &lt;strong&gt;$115/ton at 13.8&amp;ndash;15.1 SEER2&lt;/strong&gt;, scaling up to &lt;strong&gt;$310/ton at 20.0+ SEER2&lt;/strong&gt;. &lt;strong&gt;Replace-on-Burnout&lt;/strong&gt; rebates: $90/ton at 13.8&amp;ndash;15.1 SEER2, scaling to &lt;strong&gt;$275/ton at 20.0+ SEER2&lt;/strong&gt;. Minimum efficiency for rebate eligibility is &lt;strong&gt;14.3 SEER2 / 11.7 EER2 for units under 45,000 BTUh&lt;/strong&gt;; heat pumps require 7.5 HSPF2. For a typical 3-ton residential system at the minimum tier, that&amp;rsquo;s $270&amp;ndash;$345 in rebates; at the top tier, $825&amp;ndash;$930. Separately: &lt;strong&gt;WiFi Thermostat Rewards &amp;mdash; $85 enrollment credit + $30/year bill credit&lt;/strong&gt;, and &lt;strong&gt;contractor-installed attic insulation $0.35/sq ft&lt;/strong&gt; ($0.25/sq ft self-installed). Per the &lt;a href="https://resi-savenow.cpsenergy.com/cps-energy/en/savings/home-energy-rebates-specifications/" target="_blank" rel="nofollow noopener"&gt;CPS Energy Home Energy Rebates Specifications&lt;/a&gt;, insulation alone often pays back fastest in Zone 2A climates.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Sizing for Humidity Control&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Antonio&amp;rsquo;s combination of 3,147 cooling degree days and 32+ inches of annual rainfall puts humidity management at the center of every HVAC specification decision. Per the &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Efficient Cooling for Hot-Humid Climates&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is correctly sized to handle both cooling and dehumidification needs&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;variable capacity equipment that can automatically adjust its cooling capacity to meet the current load operates frequently at efficient low speeds, delivering superior temperature and moisture management compared to single-speed systems.&amp;rdquo;&lt;/em&gt; For San Antonio homeowners, the practical implication: an oversized single-stage AC cools quickly but short-cycles before pulling humidity from the air &amp;mdash; leaving the house clammy even at 72&amp;deg;F. Correct Manual J sizing, not bigger-is-better, is the right standard.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR ACR License: Class A vs. Class B&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in San Antonio must hold a current Air Conditioning and Refrigeration Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by &lt;strong&gt;Texas Occupations Code Chapter 1302&lt;/strong&gt; and &lt;strong&gt;16 Texas Administrative Code Chapter 75&lt;/strong&gt;. The &lt;strong&gt;Class A Environmental Air Conditioning&lt;/strong&gt; license entitles the holder &lt;em&gt;&amp;ldquo;to engage in air conditioning contracting&amp;hellip;of any size or capacity.&amp;rdquo;&lt;/em&gt; The &lt;strong&gt;Class B Environmental Air Conditioning&lt;/strong&gt; license is limited &lt;em&gt;&amp;ldquo;to a system, a product, or equipment of not more than: (1) 25 tons cooling capacity; or (2) 1.5 million British thermal units per hour output heating capacity.&amp;rdquo;&lt;/em&gt; For typical San Antonio residential work, a Class B contractor is fully qualified. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of San Antonio Development Services Department&lt;/strong&gt;; contact DSD directly for the current fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -1280,6 +1280,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Austin Energy&amp;rsquo;s residential rebate catalog, Texas Gas Service, the Texas Department of Licensing and Regulation, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KAUS Bergstrom)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Austin-Bergstrom International Airport (KAUS) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013904), Austin records an &lt;strong&gt;annual mean temperature of 68.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,995.9 annual cooling degree days&lt;/strong&gt; against only 1,718.3 heating degree days, &lt;strong&gt;35.57 inches of annual precipitation&lt;/strong&gt;, and essentially no snowfall. The 1.7:1 CDD-to-HDD ratio defines Austin as a strongly cooling-dominated Zone 2A hot-humid climate &amp;mdash; and the city&amp;rsquo;s pronounced urban heat-island effect pushes summer afternoon temperatures well above airport readings in downtown and central-city neighborhoods.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Fast-Growth Post-Boom Inventory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:05000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Austin city, Texas) report &lt;strong&gt;440,294 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1993&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;55.8% electricity&lt;/strong&gt; (245,620 units), &lt;strong&gt;41.7% utility natural gas&lt;/strong&gt; (183,406 units), and 7,052 bottled/LP gas homes. Austin&amp;rsquo;s newer housing stock (relative to most U.S. cities) was built largely to post-1990 energy codes, so envelope performance is stronger and retrofit opportunities are concentrated in equipment upgrades rather than insulation overhauls.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Austin Energy Residential Rebates (Municipal Utility)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Austin is served by &lt;strong&gt;Austin Energy&lt;/strong&gt;, a municipal electric utility owned by the City of Austin &amp;mdash; one of only two major Texas metros (along with San Antonio&amp;rsquo;s CPS Energy) with a municipal utility carve-out from the ERCOT deregulated retail market. Per the &lt;a href="https://savings.austinenergy.com/rebates/residential" target="_blank" rel="nofollow noopener"&gt;Austin Energy Residential Rebates page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Earn a rebate averaging $800 to install a new, energy efficient air conditioning system.&amp;rdquo;&lt;/em&gt; Heat pump water heater rebate: &lt;strong&gt;$800&lt;/strong&gt; for an ENERGY STAR-certified Hybrid Electric Water Heater. Smart thermostat: &lt;strong&gt;up to $75 in bill credits&lt;/strong&gt; when enrolling in the Power Partner Thermostat program. Residential solar: &lt;strong&gt;$2,500 rebate&lt;/strong&gt; after completing Austin Energy&amp;rsquo;s solar education course and installing a qualifying system.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas Gas Service Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The 41.7% of Austin homes on natural gas are typically served by &lt;strong&gt;Texas Gas Service&lt;/strong&gt;. Per the &lt;a href="https://www.texasgasservice.com/save-money/rebates-and-incentives/ctx-rebates-and-incentives_old/ctx-residential-rebates" target="_blank" rel="nofollow noopener"&gt;Texas Gas Service Central Texas Residential Rebates page&lt;/a&gt;: &lt;strong&gt;$675&lt;/strong&gt; for a new natural gas central furnace with minimum 92% AFUE; &lt;strong&gt;$400&lt;/strong&gt; for a tankless or super high-efficiency water heater with UEF 0.81&amp;ndash;0.91; &lt;strong&gt;$650&lt;/strong&gt; for UEF 0.92 or higher; and &lt;strong&gt;$750&lt;/strong&gt; for a solar water heater with natural gas backup. These stack with Austin Energy electric rebates for dual-fuel households and with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR ACR License &amp;amp; Austin Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Austin must hold a current TDLR Air Conditioning and Refrigeration Contractor license: per &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;the TDLR ACR program page&lt;/a&gt;, &lt;em&gt;&amp;ldquo;contractors who install, repair, or maintain systems related to air conditioning, refrigeration, or heating must have a TDLR license and ACR companies must employ an ACR contractor in each permanent location.&amp;rdquo;&lt;/em&gt; Class A covers any size unit; Class B is limited to 25 tons cooling / 1.5 million Btu heating. Permit fees for residential mechanical work are published in the City of Austin FY 2025-26 fee schedule and set by the &lt;strong&gt;City of Austin Development Services Department&lt;/strong&gt;; contact Development Services at 512-978-4504 for the current line-item amounts.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1361,6 +1376,21 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Maryland Department of Labor Board of HVACR Contractors, BGE Smart Energy&amp;rsquo;s rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBWI Thurgood Marshall)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Baltimore-Washington International Thurgood Marshall Airport (KBWI) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093721), Baltimore records an &lt;strong&gt;annual mean temperature of 56.2&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,484.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,321.8 cooling degree days&lt;/strong&gt;, &lt;strong&gt;45.00 inches of annual precipitation&lt;/strong&gt;, and 19.3 inches of snowfall. The 3.4:1 HDD-to-CDD ratio defines Baltimore as a classic Zone 4A mixed-humid climate where both heating and cooling matter meaningfully, with coastal-Atlantic humidity driving substantial summer latent load.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Pre-War Rowhouses &amp;amp; Fuel-Oil Legacy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:04000&amp;amp;in=state:24" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Baltimore city, Maryland) report &lt;strong&gt;250,608 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1948&lt;/strong&gt; &amp;mdash; among the oldest housing stocks of any major U.S. city. Heating-fuel distribution: &lt;strong&gt;62.5% utility natural gas&lt;/strong&gt; (156,545 units), &lt;strong&gt;31.0% electricity&lt;/strong&gt; (77,580 units), and a notable &lt;strong&gt;3.2% fuel oil&lt;/strong&gt; (8,065 units). Like Philadelphia and Boston, Baltimore&amp;rsquo;s pre-war inventory of brick rowhouses was often originally built with steam radiators or hot-water baseboard heat &amp;mdash; architecture that constrains modern HVAC retrofit options without central ducting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mini-Split Heat Pumps for Rowhouse Retrofits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The absence of central ducting in many Baltimore rowhouses makes ductless heat pumps a natural retrofit path. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, ductless mini-splits are &lt;em&gt;&amp;ldquo;a good choice for room additions and for homes without ductwork, such as those heated by hydronic (hot water heat), radiant panels, and space heaters.&amp;rdquo;&lt;/em&gt; For Baltimore homeowners in a rowhouse with cast-iron radiators, a multi-zone ductless mini-split installation provides both modern cooling (which many of these homes never had centrally) AND highly efficient heating &amp;mdash; without the wall-by-wall ductwork retrofit that would otherwise make heat-pump conversion prohibitive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;BGE Smart Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Baltimore is served by &lt;strong&gt;Baltimore Gas and Electric (BGE)&lt;/strong&gt;, an Exelon subsidiary. Per the &lt;a href="https://bgesmartenergy.com/residential/help-me-save/heating-cooling" target="_blank" rel="nofollow noopener"&gt;BGE Smart Energy Heating &amp;amp; Cooling page&lt;/a&gt;: &lt;strong&gt;geothermal systems qualify for grants up to $3,000&lt;/strong&gt;. Per &lt;a href="https://bgesmartenergy.com/residential/rebates-and-discounts/heat-pump-water-heater" target="_blank" rel="nofollow noopener"&gt;the BGE heat pump water heater page&lt;/a&gt;: &lt;strong&gt;heat pump water heater rebates up to $1,600&lt;/strong&gt;. Per &lt;a href="https://www.bgesmartenergy.com/residential/smart-thermostats" target="_blank" rel="nofollow noopener"&gt;the BGE smart thermostat page&lt;/a&gt;: &lt;strong&gt;up to $100 rebate&lt;/strong&gt; on eligible models (limit three per household). BGE also offers &lt;strong&gt;0% interest financing for 24 months&lt;/strong&gt; on qualifying efficiency upgrades through the Maryland Clean Energy Advantage Loan Program. All stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C credit&lt;/a&gt; (up to $3,200/year, $2,000 for heat pumps).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maryland HVACR Master Contractor License (Detailed)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Baltimore must hold a current license from the &lt;a href="https://www.dllr.state.md.us/license/hvacr/hvacrlicreq.shtml" target="_blank" rel="nofollow noopener"&gt;Maryland Board of Heating, Ventilation, Air Conditioning and Refrigeration Contractors (HVACR)&lt;/a&gt;, administered by the Maryland Department of Labor under Business Regulation Article 9A and COMAR 09.15. Master HVACR Contractor requirements are substantial: applicants must have been &lt;em&gt;&amp;ldquo;licensed as a journeyman and regularly and principally employed to provide all areas of HVACR services for at least three years of active experience under the direction and control of a HVACR master and worked a minimum of 1,875 hours in the year before application,&amp;rdquo;&lt;/em&gt; and must &lt;em&gt;&amp;ldquo;pass the master examination with a score of 70%.&amp;rdquo;&lt;/em&gt; These are among the more rigorous state HVAC licensing requirements in the country. Permit fees for residential mechanical work are set by the &lt;strong&gt;Baltimore City Department of Housing &amp;amp; Community Development (DHCD) Permits &amp;amp; Inspections&lt;/strong&gt;; contact DHCD directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4177,6 +4207,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Texas Department of Licensing and Regulation, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFTW Meacham)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fort Worth Meacham International Airport (KFTW) is the dedicated NOAA reference station for Fort Worth, separate from the DFW metroplex station shared with Dallas. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003927), Fort Worth records an &lt;strong&gt;annual mean temperature of 66.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,824.0 annual cooling degree days&lt;/strong&gt; against 2,220.2 heating degree days, &lt;strong&gt;37.01 inches of annual precipitation&lt;/strong&gt;, and only 1.6 inches of snowfall. The 1.3:1 CDD-to-HDD ratio is more balanced than Dallas&amp;rsquo;s 1.6:1 &amp;mdash; Fort Worth&amp;rsquo;s slightly more inland, higher-elevation position yields modestly cooler winters and less extreme cooling load than its metroplex sibling.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Newer Electric-Dominant Growth Market&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:27000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fort Worth city, Texas) report &lt;strong&gt;334,230 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1992&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.1% electricity&lt;/strong&gt; (230,951 units), &lt;strong&gt;28.9% utility natural gas&lt;/strong&gt; (96,563 units), and 3,025 bottled/LP gas homes. Fort Worth&amp;rsquo;s electric-heat share is higher than Dallas&amp;rsquo;s 65.2% and its median year built (1992) is a decade newer than Dallas&amp;rsquo;s (1980), reflecting the city&amp;rsquo;s faster post-1990s growth into master-planned subdivisions that default to central heat pumps.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cooling-Dominated Zone 3A + Severe-Weather Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fort Worth shares the DFW metroplex&amp;rsquo;s severe-weather exposure. Per the &lt;a href="https://www.weather.gov/fwd/fwdtornadoes" target="_blank" rel="nofollow noopener"&gt;NOAA National Weather Service Fort Worth/Dallas Tornado Climatology&lt;/a&gt;, North and Central Texas averages &lt;strong&gt;26 tornadoes per year&lt;/strong&gt;, with April and May each averaging 7 tornadoes. Outdoor condenser units benefit from impact-resistant hail guards and properly engineered wind-load tie-downs. On the cooling side, the 2,824 annual CDD and humid summers make oversized AC sizing a common pitfall: per &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;DOE Energy Saver guidance on Central Air Conditioning&lt;/a&gt;, oversized units cool quickly but short-cycle before pulling humidity &amp;mdash; a practical problem in Fort Worth&amp;rsquo;s 7&amp;ndash;9 month cooling season.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR ACR License &amp;amp; Deregulated Electricity Market&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Fort Worth must hold a current Air Conditioning and Refrigeration Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by Texas Occupations Code Chapter 1302 and 16 TAC Chapter 75. &lt;strong&gt;Class A&lt;/strong&gt; entitles the license holder to work on units of any size; &lt;strong&gt;Class B&lt;/strong&gt; is limited to 25 tons cooling / 1.5 million Btu/hr heating. Applicants must demonstrate 48 months of practical experience under a licensed contractor. Fort Worth&amp;rsquo;s electricity distribution is handled by &lt;strong&gt;Oncor Electric Delivery&lt;/strong&gt; (TDU), but retail electricity is sold by Retail Electric Providers (REPs) under the Texas deregulated market &amp;mdash; meaning residential HVAC rebates flow through your chosen REP rather than Oncor. Natural-gas customers are served by Atmos Energy. For current rebate amounts, use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Fort Worth ZIP. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Fort Worth Development Services Department&lt;/strong&gt;; contact Development Services at 817-392-2222 for the current fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5504,6 +5547,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, JEA&amp;rsquo;s residential rebate catalog, Florida Statutes, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KJAX)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jacksonville International Airport (KJAX) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013889), Jacksonville records an &lt;strong&gt;annual mean temperature of 69.3&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,803.2 annual cooling degree days&lt;/strong&gt; against only 1,227.6 heating degree days, a striking &lt;strong&gt;53.40 inches of annual precipitation&lt;/strong&gt;, and zero snowfall. The 2.3:1 CDD-to-HDD ratio defines Jacksonville as a strongly cooling-dominated Zone 2A hot-humid climate &amp;mdash; with the additional design factor of Atlantic coastal exposure, which accelerates salt-air corrosion of outdoor condenser coils.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Near-Pure Electric Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:35000&amp;amp;in=state:12" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Jacksonville city, Florida) report &lt;strong&gt;384,741 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1986&lt;/strong&gt;. Heating-fuel distribution is extraordinary: &lt;strong&gt;94.5% electricity&lt;/strong&gt; (363,470 units) overwhelmingly dominates, with only &lt;strong&gt;3.1% utility natural gas&lt;/strong&gt; (11,949 units). Jacksonville is effectively a pure-electric heating market &amp;mdash; heat pumps that handle both the large annual cooling load and the modest winter heating demand are the standard system architecture across virtually the entire housing stock.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Coastal Corrosion &amp;amp; Humidity Control&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jacksonville&amp;rsquo;s Atlantic coastal exposure and 53+ inches of annual rainfall combine to make outdoor-unit durability and humidity management central HVAC concerns. Per the &lt;a href="https://www.energy.gov/energysaver/weatherize/air-sealing-your-home" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt; and DOE hot-humid climate recommendations, coastal installations benefit from coastal-duty coil coatings on outdoor condensers and more frequent condenser rinsing to remove salt deposits. Oversized single-stage AC equipment in this climate will short-cycle before pulling humidity from the air &amp;mdash; leaving homes uncomfortably damp even at 72&amp;deg;F. Proper Manual J sizing and variable-capacity equipment are the right standard.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;JEA Residential Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jacksonville is served by &lt;strong&gt;JEA (Jacksonville Electric Authority)&lt;/strong&gt;, a municipal electric, water, and sewer utility. Per the &lt;a href="https://www.jea.com/residential_customers/residential_rebates/" target="_blank" rel="nofollow noopener"&gt;JEA Residential Rebates page&lt;/a&gt;, current HVAC-related rebates include: &lt;strong&gt;heating and cooling system $200 rebate&lt;/strong&gt;; &lt;strong&gt;smart thermostat $50 rebate&lt;/strong&gt;; &lt;strong&gt;attic insulation $200 rebate&lt;/strong&gt;; &lt;strong&gt;heat pump water heater $350 rebate&lt;/strong&gt; (JEA notes an ENERGY STAR-certified HPWH saves a four-person household approximately $550/year on electric bills). Natural-gas customers are served by TECO Peoples Gas, which administers separate rebates for the 3.1% of Jacksonville homes using gas heat. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida Contractor Licensing (Statute 489.105)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Jacksonville must hold a current Florida Certified Air Conditioning Contractor license, administered by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, the two license classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt; covering central air conditioning, refrigeration, heating, and ventilating systems; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system.&amp;rdquo;&lt;/em&gt; For typical Jacksonville residential work, a Class B contractor is fully qualified. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Jacksonville Building Inspection Division&lt;/strong&gt; under Municipal Code of Ordinances Chapter 320; contact the division directly for the current fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6956,6 +7014,21 @@
       <c r="Q77" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Focus on Energy (Wisconsin&amp;rsquo;s statewide efficiency program), the Wisconsin Department of Safety and Professional Services, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMKE)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;General Mitchell International Airport (KMKE) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014839), Milwaukee records an &lt;strong&gt;annual mean temperature of 49.3&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;6,450.2 annual heating degree days&lt;/strong&gt; against only 779.7 cooling degree days, &lt;strong&gt;34.57 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;48.7 inches of annual snowfall&lt;/strong&gt;. The 8.3:1 HDD-to-CDD ratio defines Milwaukee as one of the most heating-dominated major U.S. cities &amp;mdash; with the Lake Michigan effect adding both substantial lake-effect snow and summer humidity that standard mid-continent climate models underestimate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Gas-Dominant Pre-War Inventory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:53000&amp;amp;in=state:55" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Milwaukee city, Wisconsin) report &lt;strong&gt;231,084 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1952&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;79.3% utility natural gas&lt;/strong&gt; (183,267 units), &lt;strong&gt;17.2% electricity&lt;/strong&gt; (39,844 units), and 1,471 fuel oil units. Milwaukee&amp;rsquo;s gas dominance is among the highest of any city researched &amp;mdash; second only to Detroit&amp;rsquo;s 81.8% &amp;mdash; and the 1952 median year reflects the city&amp;rsquo;s dense stock of post-WWII bungalows, brick duplexes, and older three-flats.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Focus on Energy Rebates (Wisconsin Statewide Administrator)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wisconsin is unusual: utility rebates are administered by &lt;strong&gt;Focus on Energy&lt;/strong&gt;, a statewide program rather than directly by We Energies. Per the &lt;a href="https://focusonenergy.com/residential/heating-and-cooling" target="_blank" rel="nofollow noopener"&gt;Focus on Energy Residential Heating and Cooling page&lt;/a&gt;, rebates are tiered by efficiency AND income qualification: &lt;strong&gt;air-source heat pump Tier 1&lt;/strong&gt; (SEER2 15.2, HSPF2 8.1): &lt;strong&gt;$400 standard / $600 income-qualified&lt;/strong&gt;; &lt;strong&gt;Tier 4&lt;/strong&gt; (SEER2 16.0, HSPF2 10.0): &lt;strong&gt;$700 standard / $900 income-qualified&lt;/strong&gt;; &lt;strong&gt;natural gas furnace&lt;/strong&gt; (&amp;ge;95% AFUE): &lt;strong&gt;$100 standard / $400 income-qualified&lt;/strong&gt;; &lt;strong&gt;natural gas boiler&lt;/strong&gt; (&amp;ge;95% AFUE): &lt;strong&gt;$350 standard / $550 income-qualified&lt;/strong&gt;; &lt;strong&gt;geothermal heat pump&lt;/strong&gt;: &lt;strong&gt;$1,000 with natural gas service / $750 without&lt;/strong&gt;. The income-qualified tier doubles or triples many amounts &amp;mdash; Wisconsin is unusually generous on equity-focused rebates. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Milwaukee&amp;rsquo;s 6,450 HDD and 48.7 inches of annual snowfall put it at the demanding edge of cold-climate heat pump operation. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F,&amp;rdquo;&lt;/em&gt; and for regions with regular freezing winters, DOE recommends &lt;em&gt;&amp;ldquo;considering systems bearing an ENERGY STAR Cold Climate label for optimal performance.&amp;rdquo;&lt;/em&gt; For Milwaukee installations, elevated snow stands under the outdoor unit (to clear the 48.7-inch annual snowfall) and demand-defrost controls are meaningful specification decisions &amp;mdash; not cosmetic details.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Wisconsin HVAC Qualifier (Optional) &amp;amp; Local Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wisconsin is one of the few states that does NOT mandate a statewide HVAC contractor license. Per the &lt;a href="https://dsps.wi.gov/Pages/Professions/HVACQualifier/Default.aspx" target="_blank" rel="nofollow noopener"&gt;Wisconsin Department of Safety and Professional Services HVAC Qualifier page&lt;/a&gt;, the state offers an optional &lt;strong&gt;HVAC Qualifier&lt;/strong&gt; credential: &lt;em&gt;&amp;ldquo;a person or entity who utilizes a person who holds an HVAC Qualifier certification may not be required to obtain a local certification, license or other approval.&amp;rdquo;&lt;/em&gt; In practical terms: Milwaukee homeowners should verify either (a) that the contractor holds a state HVAC Qualifier credential, or (b) that the contractor is registered locally with the &lt;strong&gt;Milwaukee Department of Neighborhood Services (DNS)&lt;/strong&gt;. Permit fees for residential mechanical work are set by Milwaukee DNS; contact the department directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -6748,6 +6748,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance &amp;mdash; plus state licensing authority. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMEM)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Memphis International Airport (KMEM) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013893), Memphis records an &lt;strong&gt;annual mean temperature of 63.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,874.9 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,313.8 cooling degree days&lt;/strong&gt;, and an exceptional &lt;strong&gt;54.94 inches of annual precipitation&lt;/strong&gt; &amp;mdash; one of the wettest major U.S. cities. Only 2.7 inches of snowfall. The near-balanced 1.2:1 HDD-to-CDD ratio plus high rainfall defines Memphis as a classic Zone 3A warm-humid climate where summer humidity drives HVAC design as much as raw cooling capacity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: TVA Electric-Majority Territory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:48000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Memphis city, Tennessee) report &lt;strong&gt;254,530 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1970&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;55.1% electricity&lt;/strong&gt; (140,286 units) leads &lt;strong&gt;42.9% utility natural gas&lt;/strong&gt; (109,201 units). Like Nashville, Memphis&amp;rsquo;s electric majority reflects TVA service territory and MLGW&amp;rsquo;s competitive municipal electric rates &amp;mdash; heat pumps became standard replacement equipment decades ago.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dehumidification Matters More Than Raw Cooling Capacity&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Memphis&amp;rsquo;s 54.94 inches of annual rainfall put humidity management at the center of every HVAC specification decision. Per the &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide to Efficient Cooling for Hot, Humid Climates&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is correctly sized to handle both cooling and dehumidification needs. Systems that are too large or too small can struggle with humidity control.&amp;rdquo;&lt;/em&gt; DOE further advises &lt;em&gt;&amp;ldquo;variable capacity equipment that can automatically adjust its cooling capacity to meet the current load operates frequently at efficient low speeds, delivering superior temperature and moisture management.&amp;rdquo;&lt;/em&gt; For Memphis, specifying a two-stage or variable-capacity system is often the difference between a house that feels cool and one that feels clammy even at 72&amp;deg;F.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;MLGW Municipal Combined Utility &amp;amp; TVA EnergyRight&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Memphis is served by &lt;strong&gt;MLGW (Memphis Light, Gas and Water)&lt;/strong&gt; &amp;mdash; a rare municipal utility that provides electricity, natural gas, AND water from the same agency. MLGW is a TVA electricity distributor and administers &lt;strong&gt;TVA EnergyRight&lt;/strong&gt; residential incentive programs for its customers, including heat pump loan programs. For current rebate dollar amounts and EnergyRight program details, visit mlgw.com and energyright.com directly. Natural-gas rebates for the 42.9% of Memphis homes using gas heat are also administered by MLGW as the gas distributor. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee CMC-C Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Memphis must hold a current state-issued HVAC Mechanical Contractor (&lt;strong&gt;CMC-C&lt;/strong&gt;) license from the &lt;a href="https://www.tn.gov/commerce/regboards.html" target="_blank" rel="nofollow noopener"&gt;Tennessee Board for Licensing Contractors&lt;/a&gt;, administered by the Tennessee Department of Commerce and Insurance. Tennessee requires state contractor licensure for projects above specific dollar thresholds; the CMC-C classification covers HVAC work. Verifying a contractor&amp;rsquo;s active CMC-C license via the Board&amp;rsquo;s public lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set jointly by the &lt;strong&gt;City of Memphis &amp;amp; Shelby County Office of Construction Code Enforcement&lt;/strong&gt; (unusual city-county joint permitting); contact Construction Code Enforcement directly for the current fee schedule.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7567,6 +7582,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance &amp;mdash; plus municipal-code references. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KNYC Central Park)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York City&amp;rsquo;s Central Park station (KNYC) is the NOAA reference for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094728), NYC records an &lt;strong&gt;annual mean temperature of 55.8&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,553.3 annual heating degree days&lt;/strong&gt; against 1,221.5 cooling degree days, &lt;strong&gt;49.52 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;29.8 inches of annual snowfall&lt;/strong&gt;. The 3.7:1 HDD-to-CDD ratio defines NYC as a mixed-humid climate with substantial winter heating demand and meaningful coastal-Atlantic summer humidity load.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: 3.3 Million Units, Fuel-Oil Legacy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:51000&amp;amp;in=state:36" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for New York city) report &lt;strong&gt;3,313,316 occupied housing units&lt;/strong&gt; &amp;mdash; by far the largest municipal housing stock in the United States &amp;mdash; with a &lt;strong&gt;median year built of 1952&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;64.8% utility natural gas&lt;/strong&gt; (2,145,630 units), &lt;strong&gt;15.5% electricity&lt;/strong&gt; (513,371 units), and a striking &lt;strong&gt;12.5% fuel oil&lt;/strong&gt; (414,650 units). The 414,000+ fuel-oil-heated units are the largest concentration in any U.S. city &amp;mdash; a New York legacy that drives ongoing state and city electrification incentives targeted specifically at oil-to-heat-pump conversions.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pre-War Housing: Mini-Splits in Steam-Heated Buildings&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NYC&amp;rsquo;s median 1952 year built reflects its vast pre-war housing stock &amp;mdash; brownstones, walk-ups, and mid-century apartment towers originally built with steam or hot-water radiators and no central ducting. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, ductless mini-splits are &lt;em&gt;&amp;ldquo;a good choice for room additions and for homes without ductwork, such as those heated by hydronic (hot water heat), radiant panels, and space heaters.&amp;rdquo;&lt;/em&gt; For the majority of NYC apartments and rowhouses, multi-zone ductless mini-splits (or high-velocity small-duct systems like Unico/SpacePak) are the practical heat-pump retrofit path &amp;mdash; ducted central heat pumps often can&amp;rsquo;t fit the structure without invasive chase work.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NYC Construction Codes &amp;amp; Local Law 97&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NYC enforces its own Construction Codes (Administrative Code Title 28), not the state Uniform Code. The NYC Mechanical Code under Title 28 Chapter 7 governs HVAC work within the five boroughs. A distinctive NYC layer is Local Law 97 (LL97), which imposes greenhouse-gas emissions limits on most buildings over 25,000 square feet &amp;mdash; roughly 50,000 NYC properties. For homeowners in smaller buildings LL97 is not a direct compliance trigger, but it has accelerated heat-pump specification across mid-rise and high-rise residential stock. For current &lt;strong&gt;Con Edison&lt;/strong&gt; rebate amounts and &lt;strong&gt;NYSERDA NY Clean Heat&lt;/strong&gt; heat pump incentives (which are among the most generous in the U.S. for cold-climate air-source and ground-source systems), check coned.com and nyserda.ny.gov directly.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Federal Incentives&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York State does not issue a statewide HVAC contractor license. For work in NYC, the &lt;a href="https://www.nyc.gov/site/buildings/" target="_blank" rel="nofollow noopener"&gt;NYC Department of Buildings Licensed Trades&lt;/a&gt; issues credentials relevant to HVAC work &amp;mdash; including the &lt;strong&gt;Refrigeration Machine Operator&lt;/strong&gt; license and &lt;strong&gt;Oil Burner Installer&lt;/strong&gt; license for specific scopes. Verifying a contractor&amp;rsquo;s active DOB credential before authorizing work is the baseline due-diligence step. Permit fees for mechanical work are set by NYC DOB; fee amounts are codified in DOB fee rules under Administrative Code Title 28. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7818,6 +7848,21 @@
       <c r="Q86" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Oklahoma Construction Industries Board, NOAA National Weather Service tornado climatology, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KOKC Will Rogers)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Will Rogers World Airport (KOKC) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013967), Oklahoma City records an &lt;strong&gt;annual mean temperature of 60.1&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,615.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,867.2 cooling degree days&lt;/strong&gt;, &lt;strong&gt;36.39 inches of annual precipitation&lt;/strong&gt;, and 6.7 inches of snowfall. The 1.9:1 HDD-to-CDD ratio defines Oklahoma City as a mildly heating-leaning Zone 3A warm-humid climate &amp;mdash; but the region&amp;rsquo;s defining HVAC risk factor isn&amp;rsquo;t seasonal load, it&amp;rsquo;s severe weather.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tornado Alley Design Consideration&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;OKC sits in the heart of Tornado Alley. Per the &lt;a href="https://www.weather.gov/oun/tornadodata-okc" target="_blank" rel="nofollow noopener"&gt;NOAA National Weather Service Norman Tornado Climatology for Oklahoma City&lt;/a&gt;, &lt;em&gt;&amp;ldquo;the immediate OKC area has experienced 194 documented tornadoes since 1890,&amp;rdquo;&lt;/em&gt; including &lt;em&gt;&amp;ldquo;thirteen violent tornadoes (eleven F4/EF4 and two F5/EF5)&amp;rdquo;&lt;/em&gt; &amp;mdash; most recent May 20, 2013. &lt;em&gt;&amp;ldquo;May is the peak month for all tornadoes, followed closely by April and June,&amp;rdquo;&lt;/em&gt; with a &lt;em&gt;&amp;ldquo;broad peak centered around 4 PM CST / 5 PM CDT.&amp;rdquo;&lt;/em&gt; For OKC homeowners, outdoor condenser units benefit from impact-resistant hail guards and properly engineered wind-load tie-downs &amp;mdash; and post-storm HVAC service demand routinely spikes during the April&amp;ndash;June severe-weather season.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:55000&amp;amp;in=state:40" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Oklahoma City city, Oklahoma) report &lt;strong&gt;275,193 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1981&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;57.2% utility natural gas&lt;/strong&gt; (157,350 units), &lt;strong&gt;39.6% electricity&lt;/strong&gt; (108,996 units), and 6,157 bottled/LP gas homes. OKC&amp;rsquo;s gas majority reflects both ONG&amp;rsquo;s established distribution network and the preference for gas forced-air furnaces in the late-20th-century subdivisions that dominate the housing stock.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Oklahoma CIB Mechanical Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Oklahoma City must hold a current license from the &lt;a href="https://oklahoma.gov/cib/your-industry/mechanical.html" target="_blank" rel="nofollow noopener"&gt;Oklahoma Construction Industries Board (CIB) Mechanical Industry program&lt;/a&gt;, governed by &lt;strong&gt;59 O.S. Section 1850.1 et seq. (Mechanical Licensing Act)&lt;/strong&gt; and &lt;strong&gt;OAC Title 158 Chapter 50&lt;/strong&gt;. The licensing path is tiered: apprenticeship, then journeyman status, then application for the contractor license. Licensees must complete &lt;em&gt;&amp;ldquo;six (6) hours of CEUs every 36 months&amp;rdquo;&lt;/em&gt; as a continuing-education requirement. Verifying that a contractor holds an active CIB Mechanical Contractor license &amp;mdash; and that their firm has a named responsible contractor per OAC 158:50 &amp;mdash; is the baseline due-diligence step for every OKC homeowner.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oklahoma City is served by &lt;strong&gt;OG&amp;amp;E (Oklahoma Gas &amp;amp; Electric)&lt;/strong&gt; for electricity and &lt;strong&gt;Oklahoma Natural Gas (ONG)&lt;/strong&gt; for natural gas. For current residential HVAC rebate dollar amounts, check oge.com and oklahomanaturalgas.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your OKC ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps). Permit fees for residential mechanical work are set by the &lt;strong&gt;OKC Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10638,6 +10683,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, TECO&amp;rsquo;s residential rebate catalog, Florida Statutes, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTPA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tampa International Airport (KTPA) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012842), Tampa records an &lt;strong&gt;annual mean temperature of 74.5&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,928.2 annual cooling degree days&lt;/strong&gt; against only &lt;strong&gt;433.5 heating degree days&lt;/strong&gt;, &lt;strong&gt;49.48 inches of annual precipitation&lt;/strong&gt;, and no snowfall. The 9.1:1 CDD-to-HDD ratio defines Tampa as a strongly cooling-dominated Zone 2A hot-humid climate &amp;mdash; heating demand is nearly trivial, but year-round humidity and Gulf Coast hurricane exposure dominate HVAC design.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: 92% Electric Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:71000&amp;amp;in=state:12" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Tampa city, Florida) report &lt;strong&gt;160,527 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution is extraordinary: &lt;strong&gt;92.1% electricity&lt;/strong&gt; (147,763 units) dominates, with only &lt;strong&gt;5.6% utility natural gas&lt;/strong&gt; (8,945 units). Like Miami (91.2%) and Jacksonville (94.5%), Tampa is a near-pure electric heating market where heat pumps handle both the enormous cooling load and the modest winter heating demand from a single outdoor unit.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;TECO Residential Rebates (Tiered by SEER2)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tampa is served by &lt;strong&gt;Tampa Electric Company (TECO)&lt;/strong&gt; for electricity and &lt;strong&gt;Peoples Gas&lt;/strong&gt; (a TECO company) for the small natural-gas segment. Per the &lt;a href="https://www.tampaelectric.com/residential/saveenergy/heatingcooling/" target="_blank" rel="nofollow noopener"&gt;TECO Residential Heating &amp;amp; Cooling Rebates page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;A SEER (16.00) or SEER2 (15.20) is required for a rebate of ($40),&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;A SEER (17.00) or SEER2 (16.20) is required for a rebate of ($550).&amp;rdquo;&lt;/em&gt; Per the &lt;a href="https://www.tampaelectric.com/residential/saveenergy/energystarsmartthermostat/" target="_blank" rel="nofollow noopener"&gt;TECO ENERGY STAR Smart Thermostat page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Installing an ENERGY STAR certified smart thermostat&amp;hellip;can help you save money and earn a rebate up to $22.&amp;rdquo;&lt;/em&gt; TECO&amp;rsquo;s rebates are structured with a large efficiency-tier jump ($40 at baseline SEER2 vs $550 at higher SEER2) &amp;mdash; specifying higher-efficiency equipment meaningfully pays off.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tampa Permit Fees &amp;amp; Florida Building Surcharge&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.tampa.gov/construction-services/fees" target="_blank" rel="nofollow noopener"&gt;City of Tampa Construction Services fees page&lt;/a&gt;, every permit is subject to a &lt;em&gt;&amp;ldquo;Florida Building Permit Surcharge (2.5% of permit value or $4.00 minimum)&amp;rdquo;&lt;/em&gt; &amp;mdash; a state-level fee in addition to city permit fees. Tampa is a hurricane-prone region requiring condenser tie-downs and wind-rated mounting pads under standard Florida Building Code wind-load provisions; however, unlike Miami-Dade and Broward counties, Tampa is NOT in the Florida Building Code High-Velocity Hurricane Zone (HVHZ), so HVHZ-specific equipment approvals don&amp;rsquo;t apply.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Gulf Coast Corrosion &amp;amp; Florida Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tampa Bay&amp;rsquo;s Gulf Coast location exposes outdoor condenser coils to airborne chloride salt that pits aluminum fins and can cause formicary corrosion in copper refrigerant tubing. Homeowners within a few miles of the bay benefit from coastal-duty coil coatings and more frequent condenser rinsing. Every HVAC contractor in Tampa must hold a current Florida Certified Air Conditioning Contractor license from the &lt;strong&gt;DBPR / Construction Industry Licensing Board&lt;/strong&gt;: per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system&amp;rdquo;&lt;/em&gt; &amp;mdash; Class B is fully sufficient for typical Tampa residential work. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11235,6 +11295,21 @@
       <c r="Q126" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance &amp;mdash; plus DC Department of Buildings code references. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KDCA Reagan National)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ronald Reagan Washington National Airport (KDCA) is the NOAA reference station for the District. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013743), Washington records an &lt;strong&gt;annual mean temperature of 59.3&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,769.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,737.8 cooling degree days&lt;/strong&gt;, &lt;strong&gt;41.82 inches of annual precipitation&lt;/strong&gt;, and 13.7 inches of annual snowfall. The 2.2:1 HDD-to-CDD ratio defines Washington as a classic Zone 4A mixed-humid climate &amp;mdash; substantial cold-season heating demand plus humid Atlantic summers that drive meaningful cooling and dehumidification load.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Near-Balanced Gas/Electric Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:50000&amp;amp;in=state:11" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Washington city, DC) report &lt;strong&gt;321,556 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1957&lt;/strong&gt;. Heating-fuel distribution is unusually balanced: &lt;strong&gt;49.2% utility natural gas&lt;/strong&gt; (158,327 units), &lt;strong&gt;45.6% electricity&lt;/strong&gt; (146,754 units), and 3,083 fuel-oil-heated units. The near 50/50 gas/electric split is distinctive among major U.S. cities &amp;mdash; most cities lean clearly one direction &amp;mdash; and reflects the District&amp;rsquo;s mix of pre-war rowhouses (traditionally gas or oil) and later mid-century apartment buildings (often all-electric).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;DC Construction Codes (DCMR Title 12)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://dob.dc.gov/page/dc-construction-codes" target="_blank" rel="nofollow noopener"&gt;DC Department of Buildings Construction Codes page&lt;/a&gt;, the District adopts the &lt;strong&gt;DC Construction Codes under DC Municipal Regulations (DCMR) Title 12&lt;/strong&gt;, including the DC Energy Conservation Code with local amendments. The District sits in IECC Climate Zone 4A (Mixed-Humid), and the DC Energy Code imposes stricter efficiency thresholds than the base IECC &amp;mdash; HVAC replacement work must meet the current code cycle&amp;rsquo;s minimum equipment efficiency, duct-sealing, and load-calculation requirements.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 4A Heat Pump Suitability &amp;amp; Pre-War Housing Challenges&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The combination of 3,769 HDD and 1,738 CDD makes Zone 4A one of the best-fit climates in the country for air-source heat pumps &amp;mdash; winters are cold enough to matter but rarely extreme, and summer cooling load is meaningful. Per DOE Building America guidance on &lt;a href="https://basc.pnnl.gov/" target="_blank" rel="nofollow noopener"&gt;Mixed-Humid Climate Zone 4A&lt;/a&gt;, designs must handle substantial summer latent cooling loads alongside winter heating. For DC&amp;rsquo;s pre-war rowhouse stock (median 1957 reflects mid-century dominant construction), ductwork is often routed through unconditioned chases and many older homes have limited or no central ducting &amp;mdash; making ductless mini-split heat pumps a natural retrofit path.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;DCSEU Rebates, Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Washington, D.C. is served by &lt;strong&gt;Pepco&lt;/strong&gt; for electricity and &lt;strong&gt;Washington Gas&lt;/strong&gt; for natural gas. Distinctively, DC also operates the &lt;strong&gt;DC Sustainable Energy Utility (DCSEU)&lt;/strong&gt; &amp;mdash; a district-mandated efficiency program that administers heat pump rebates, weatherization incentives, and low-income weatherization for DC residents. For current rebate dollar amounts, visit dcseu.com, pepco.com, and washingtongas.com directly. Every HVAC contractor working in DC must hold a current &lt;strong&gt;Master Refrigeration and Air Conditioning Mechanic&lt;/strong&gt; license from the &lt;strong&gt;DC Department of Licensing and Consumer Protection (DLCP)&lt;/strong&gt;; verifying a contractor&amp;rsquo;s active DLCP license before authorizing work is the baseline due-diligence step. Permit fees are set by the &lt;strong&gt;DC Department of Buildings (DOB)&lt;/strong&gt;. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -690,6 +690,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the New Mexico Administrative Code Construction Industries Division classifications, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile: High Desert at 5,312 ft (NOAA KABQ)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Albuquerque International Sunport (KABQ) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023050), Albuquerque records an &lt;strong&gt;annual mean temperature of 57.9&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,995.6 annual heating degree days&lt;/strong&gt; against 1,437.8 cooling degree days, and only &lt;strong&gt;8.84 inches of annual precipitation&lt;/strong&gt; &amp;mdash; among the driest of any major U.S. city. Annual snowfall: 7.9 inches. The 2.8:1 HDD-to-CDD ratio plus desert-dry conditions and &lt;strong&gt;5,312 ft elevation&lt;/strong&gt; combine to make Albuquerque unique: both altitude-derating (like Denver) and extreme low humidity apply to every HVAC specification decision.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:02000&amp;amp;in=state:35" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Albuquerque city, New Mexico) report &lt;strong&gt;242,117 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1982&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;76.6% utility natural gas&lt;/strong&gt; (185,465 units), &lt;strong&gt;20.2% electricity&lt;/strong&gt; (49,028 units), plus 1,444 wood-heated homes and 1,056 solar-heated homes. Natural gas dominance reflects New Mexico Gas Company&amp;rsquo;s established distribution network; wood heating (kiva fireplaces, pellet stoves) is higher than in most major cities &amp;mdash; a traditional Southwest regional pattern.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Evaporative (Swamp) Cooling: Ideal High-Desert Application&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Albuquerque&amp;rsquo;s 8.84 inches of annual precipitation and Zone 4B mixed-dry classification make it one of the best U.S. cities for evaporative cooling. Per the &lt;a href="https://www.energy.gov/energysaver/evaporative-coolers" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Evaporative Coolers&lt;/a&gt;: &lt;em&gt;&amp;ldquo;In low-humidity areas, evaporating water into the air provides a natural and energy-efficient means of cooling,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;two-stage models are most often used in areas where daytime temperatures frequently exceed 100&amp;deg;F.&amp;rdquo;&lt;/em&gt; DOE warns that &lt;em&gt;&amp;ldquo;evaporative coolers should not be used in humid climates because they add humidity to the air in your home&amp;rdquo;&lt;/em&gt; &amp;mdash; a caution that doesn&amp;rsquo;t apply to Albuquerque. Many ABQ homes operate on evaporative coolers alone or in hybrid configurations with refrigerant AC as backup for the humid summer monsoon season when evap coolers become less effective.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;New Mexico MM-3 HVAC Contractor Classification (Verbatim)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Albuquerque must hold a current license from the &lt;a href="https://www.srca.nm.gov/parts/title14/14.006.0006.html" target="_blank" rel="nofollow noopener"&gt;New Mexico Construction Industries Division (CID)&lt;/a&gt; under &lt;strong&gt;NMAC 14.6.6&lt;/strong&gt;. The HVAC classification is &lt;strong&gt;MM-3 (Heating, Ventilation &amp;amp; Air Conditioning)&lt;/strong&gt;: per NMAC 14.6.6, an MM-3 contractor may &lt;em&gt;&amp;ldquo;install, alter, repair, service and maintain HVAC air handling and refrigeration equipment and piping, including fans, coils, condensing units, self-contained packaged air conditioning or heating units, evaporative cooling units, and ductwork and accessories including solar air heating and cooled mechanical air handling and ventilation applications; may connect water to existing valved outlets, and install controls, and control wiring not to exceed 24 volts.&amp;rdquo;&lt;/em&gt; Natural gas piping work is a separate &lt;strong&gt;MM-2 (Natural Gas Fitting)&lt;/strong&gt; classification; hydronic/process piping falls under &lt;strong&gt;MM-4&lt;/strong&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Albuquerque Planning Department, Code Enforcement Division&lt;/strong&gt;; contact Planning directly for the current mechanical permit fee schedule. Albuquerque is served by &lt;strong&gt;PNM (Public Service Company of New Mexico)&lt;/strong&gt; for electricity and &lt;strong&gt;New Mexico Gas Company&lt;/strong&gt; for natural gas. Both utilities administer residential energy-efficiency rebate programs; check pnm.com and nmgco.com directly for current dollar amounts, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your ABQ ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2749,6 +2764,21 @@
       <c r="Q27" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Ohio Construction Industry Licensing Board, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile: Lake Erie Snow Belt (NOAA KCLE)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cleveland Hopkins International Airport (KCLE) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014820), Cleveland records an &lt;strong&gt;annual mean temperature of 52.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,516.3 annual heating degree days&lt;/strong&gt; against 947.2 cooling degree days, &lt;strong&gt;41.03 inches of annual precipitation&lt;/strong&gt;, and an exceptional &lt;strong&gt;63.8 inches of annual snowfall&lt;/strong&gt; &amp;mdash; the highest of any city in this project, driven by Lake Erie lake-effect snow events. The 5.8:1 HDD-to-CDD ratio and massive snow load make outdoor-unit protection and proper vent placement central HVAC design considerations in Cleveland.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: 1940 Median Year &amp;mdash; Oldest in the Project&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:16000&amp;amp;in=state:39" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Cleveland city, Ohio) report &lt;strong&gt;168,652 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1940&lt;/strong&gt; &amp;mdash; the OLDEST housing stock of any major U.S. city researched in this project. Heating-fuel distribution: &lt;strong&gt;78.4% utility natural gas&lt;/strong&gt; (132,261 units), &lt;strong&gt;18.1% electricity&lt;/strong&gt; (30,609 units). The pre-WWII median age means a substantial share of Cleveland homes still operate on chimney-vented atmospheric furnaces, undersized gas lines, and original ductwork &amp;mdash; envelope limitations that amplify design heating loads and complicate modern heat-pump retrofits.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Snow-Load &amp;amp; Cold-Climate Equipment Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cleveland&amp;rsquo;s 63.8 inches of annual snowfall and 5,516 HDD combine to create distinctive installation requirements. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, cold-climate heat pumps are &lt;em&gt;&amp;ldquo;designed to perform in temperatures as low as 5&amp;deg;F,&amp;rdquo;&lt;/em&gt; and DOE recommends &lt;em&gt;&amp;ldquo;considering systems bearing an ENERGY STAR Cold Climate label for optimal performance.&amp;rdquo;&lt;/em&gt; For Cleveland specifically: outdoor heat-pump units benefit from elevated snow stands (clearing lake-effect accumulation that can exceed 5 feet in a single storm), demand-defrost controls for repeated freeze/thaw cycling, and careful sidewall-vent placement to avoid snow-drift blockage on condensing gas appliances.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio OCILB Licensing &amp;amp; Local Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Cleveland must hold a current state-issued HVAC Contractor License from the &lt;strong&gt;Ohio Construction Industry Licensing Board (OCILB)&lt;/strong&gt;, administered by the Ohio Department of Commerce. OCILB &lt;em&gt;&amp;ldquo;licenses Ohio electrical, HVAC, plumbing, hydronics, and refrigeration contractors.&amp;rdquo;&lt;/em&gt; Cleveland does not issue a separate municipal HVAC contractor license &amp;mdash; the state OCILB credential is the formal requirement. Verifying a contractor&amp;rsquo;s active OCILB HVAC license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Cleveland Department of Building &amp;amp; Housing&lt;/strong&gt;; contact the department directly for the current fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cleveland is served by &lt;strong&gt;The Illuminating Company&lt;/strong&gt; (a FirstEnergy subsidiary) for electricity and, as of 2024, by &lt;strong&gt;Enbridge Gas Ohio&lt;/strong&gt; for natural gas (Dominion Energy Ohio was acquired by Enbridge Gas in the 2023&amp;ndash;2024 transaction). For current residential rebate dollar amounts from both utilities, check firstenergycorp.com and enbridgegas.com/ohio directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Cleveland ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7499,6 +7529,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Energy Smart program (Entergy New Orleans&amp;rsquo;s joint efficiency program), the Louisiana State Licensing Board for Contractors, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMSY Armstrong)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louis Armstrong New Orleans International Airport (KMSY) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012916), New Orleans records an &lt;strong&gt;annual mean temperature of 70.5&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,205.9 annual cooling degree days&lt;/strong&gt; against only 1,176.3 heating degree days, and an exceptional &lt;strong&gt;63.35 inches of annual precipitation&lt;/strong&gt; &amp;mdash; the wettest major U.S. city in this project. No measurable snowfall. The 2.7:1 CDD-to-HDD ratio plus extreme rainfall profile defines New Orleans as a distinctive Zone 2A hot-humid climate where AC runtime, condensate management, and drain-pan maintenance dominate HVAC failure modes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Electric-Majority Heating&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:55000&amp;amp;in=state:22" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for New Orleans city, Louisiana) report &lt;strong&gt;155,060 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1959&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;61.9% electricity&lt;/strong&gt; (95,996 units) leads &lt;strong&gt;36.4% utility natural gas&lt;/strong&gt; (56,469 units). The electric majority is characteristic of hot-humid Gulf Coast cities where heat pumps serve the large cooling load year-round with modest winter heating demand as a secondary function.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energy Smart Rebates (Detailed by SEER2/HSPF2 Tier)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New Orleans is served by &lt;strong&gt;Entergy New Orleans&lt;/strong&gt; for both electricity and gas, and residential rebates are administered through &lt;strong&gt;Energy Smart&lt;/strong&gt; &amp;mdash; the joint efficiency program run by Entergy New Orleans and the New Orleans City Council. Per the &lt;a href="https://energysmartnola.info/a-c-solutions/" target="_blank" rel="nofollow noopener"&gt;Energy Smart A/C Solutions page&lt;/a&gt;, current rebates (effective January 1, 2025, with all equipment rated SEER2/EER2/HSPF2): &lt;strong&gt;A/C tune-up $150 standard / $200 income-eligible&lt;/strong&gt;; &lt;strong&gt;central AC at SEER2 &amp;ge; 15.2 with ECM: $150 per system&lt;/strong&gt;, SEER2 &amp;ge; 16: $175, SEER2 &amp;ge; 17: $200; &lt;strong&gt;air-source heat pump at SEER2 &amp;ge; 15.2 &amp;amp; HSPF2 &amp;ge; 7.1: $200&lt;/strong&gt;, at SEER2 &amp;ge; 17 &amp;amp; HSPF2 &amp;ge; 7.8: $250; &lt;strong&gt;mini-split ductless heat pump replacing electric strip heat: $500 per system&lt;/strong&gt;. Income-eligible households (&amp;le; 80% AMI) qualify for higher rebate tiers on several programs.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana LSLBC Mechanical Contractor License&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in New Orleans must hold a current Mechanical Work Contractor license from the &lt;a href="https://lslbc.gov/exams-classifications/" target="_blank" rel="nofollow noopener"&gt;Louisiana State Licensing Board for Contractors (LSLBC)&lt;/a&gt; under Major Classification 6 (Mechanical) when project value exceeds &lt;strong&gt;$10,000&lt;/strong&gt;. The classification scope, per LSLBC: &lt;em&gt;&amp;ldquo;Hydraulic and pneumatic systems, including such components as heating, ventilation, air conditioning, refrigeration, hydronic and steam systems, pressure vessels, plumbing, gas piping, process piping, mechanical equipment, air and process heaters and seals, and air vacuums and filters.&amp;rdquo;&lt;/em&gt; Mechanical contractors performing plumbing work above the $10,000 threshold must also hold a master plumber license from the Louisiana State Plumbing Board.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits &amp;amp; Post-Katrina Flood Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of New Orleans Department of Safety &amp;amp; Permits&lt;/strong&gt;; per the &lt;a href="https://nola.gov/mechanical-permit/" target="_blank" rel="nofollow noopener"&gt;city&amp;rsquo;s Mechanical Permit page&lt;/a&gt;, fees &lt;em&gt;&amp;ldquo;vary based on components of work,&amp;rdquo;&lt;/em&gt; and applicants submit the HVAC Permit Application Supplement (D1-AC) with each application. Contact Safety &amp;amp; Permits at (504) 658-7100 for current line items. New Orleans&amp;rsquo;s post-Hurricane-Katrina building code emphasizes elevation requirements for outdoor mechanical equipment in flood-prone zones &amp;mdash; condenser pads must be set above Base Flood Elevation per FEMA flood-zone maps. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9430,6 +9475,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and regional primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, BayREN (Bay Area Regional Energy Network), and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSFO)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco International Airport (KSFO) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023234), San Francisco records an &lt;strong&gt;annual mean temperature of 58.7&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,475.4 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;200.2 cooling degree days&lt;/strong&gt;, and &lt;strong&gt;19.64 inches of annual precipitation&lt;/strong&gt;. The 12.4:1 HDD-to-CDD ratio is among the most cooling-minimal of any major U.S. city &amp;mdash; San Francisco&amp;rsquo;s marine climate almost never demands refrigerant cooling, which is why tens of thousands of SF homes operate year-round without any central AC system.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Pre-War Marine-Adapted Inventory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for San Francisco city, California) report &lt;strong&gt;362,650 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1945&lt;/strong&gt; &amp;mdash; tied with Detroit for the oldest housing stock of any major U.S. city researched. Heating-fuel distribution: &lt;strong&gt;56.0% utility natural gas&lt;/strong&gt; (203,069 units), &lt;strong&gt;34.7% electricity&lt;/strong&gt; (125,802 units), and a striking &lt;strong&gt;5.9% of units reporting no fuel used for heating&lt;/strong&gt; (21,477 units &amp;mdash; an unusually high share reflecting SF&amp;rsquo;s mild marine climate where passive envelope performance plus space heaters often suffice). San Francisco&amp;rsquo;s pre-war Victorian and Edwardian row houses often have no central ducting and no central AC &amp;mdash; both additions have historically not been necessary.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ideal Heat Pump Climate&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco&amp;rsquo;s 2,475 HDD with almost no extreme-cold days puts it squarely in DOE&amp;rsquo;s ideal heat-pump territory &amp;mdash; mild winters rarely approach the 5&amp;deg;F threshold at which standard air-source heat pumps lose significant capacity. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, ductless mini-split heat pumps are &lt;em&gt;&amp;ldquo;a good choice for room additions and for homes without ductwork, such as those heated by hydronic (hot water heat), radiant panels, and space heaters.&amp;rdquo;&lt;/em&gt; For the majority of SF Victorian and Edwardian row houses, multi-zone ductless mini-split installations provide both efficient heating (replacing aging gas wall furnaces or floor heaters) and modest cooling for the rare heat-wave week &amp;mdash; without requiring invasive ductwork retrofits.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;BayREN &amp;amp; California C-20 Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas, and residents have access to regional incentives through the &lt;strong&gt;Bay Area Regional Energy Network (BayREN)&lt;/strong&gt;. Per the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;EASE Home covers 80% of the cost for core upgrades, such as insulation and duct sealing. You pay just 20% of the total project cost, with your contribution capped at $1,000.&amp;rdquo;&lt;/em&gt; For current PG&amp;amp;E residential rebate amounts (heat pump, smart thermostat), see pge.com directly. Every HVAC contractor working in San Francisco must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor license from the California Contractors State License Board. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Francisco Department of Building Inspection (DBI)&lt;/strong&gt;; contact DBI directly for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9511,6 +9569,21 @@
       <c r="Q105" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the California Contractors State License Board, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSJC Mineta)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mineta San Jose International Airport (KSJC) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023293), San Jose records an &lt;strong&gt;annual mean temperature of 60.7&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,183.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;623.9 cooling degree days&lt;/strong&gt;, and only &lt;strong&gt;13.48 inches of annual precipitation&lt;/strong&gt;. The 3.5:1 HDD-to-CDD ratio defines San Jose as a heating-dominated Zone 3C marine climate &amp;mdash; but its interior Bay Area location means noticeably warmer summers than San Francisco (71.2&amp;deg;F annual max vs. 66.9&amp;deg;F), giving San Jose a real summer cooling demand that San Francisco lacks.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Silicon Valley Post-War Growth&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:68000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for San Jose city, California) report &lt;strong&gt;326,767 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1975&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.9% utility natural gas&lt;/strong&gt; (192,382 units), &lt;strong&gt;36.1% electricity&lt;/strong&gt; (117,943 units), and a notable &lt;strong&gt;3,398 units heated by solar energy&lt;/strong&gt; &amp;mdash; among the highest solar-heated shares of any city in the project, reflecting Silicon Valley&amp;rsquo;s early solar adoption and the region&amp;rsquo;s climate-favorable solar economics.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Heat Pump Sizing for Zone 3C Marine&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Jose&amp;rsquo;s 2,184 HDD and 624 CDD profile represents an ideal Zone 3C marine climate for air-source heat pumps: winters are mild (heat-pump balance point rarely challenged), summers are warm enough to benefit from active cooling, and humidity is moderate. Per DOE guidance on heat pump systems, a standard (non-cold-climate) heat pump is fully sufficient for this climate &amp;mdash; and because 36.1% of San Jose homes already heat with electricity (117,943 units), gas-to-electric heat-pump conversions leverage existing electrical infrastructure.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California CSLB C-20 Contractor License (Verbatim)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in San Jose must hold a California C-20 license from the &lt;a href="https://www.cslb.ca.gov/about_us/library/licensing_classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;California Contractors State License Board&lt;/a&gt;. Per the CSLB classification detail: a C-20 contractor &lt;em&gt;&amp;ldquo;fabricates, installs, maintains, services and repairs warm-air heating systems and water heating heat pumps, complete with warm-air appliances; ventilating systems complete with blowers and plenum chambers; air-conditioning systems complete with air-conditioning unit; and the ducts, registers, flues, humidity and thermostatic controls and air filters in connection with any of these systems.&amp;rdquo;&lt;/em&gt; The classification &lt;em&gt;&amp;ldquo;also encompasses warm-air heating, ventilating and air-conditioning systems utilizing solar energy.&amp;rdquo;&lt;/em&gt; Verifying the contractor&amp;rsquo;s active C-20 license via CSLB&amp;rsquo;s public lookup before authorizing work is the baseline due-diligence step.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Rebates &amp;amp; Federal Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Jose is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for delivery of both electricity and natural gas, while &lt;strong&gt;Silicon Valley Clean Energy (SVCE)&lt;/strong&gt; &amp;mdash; a Community Choice Aggregator &amp;mdash; is the electric generation provider for most of the city. For current rebate dollar amounts, check pge.com, svcleanenergy.org, and the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; directly &amp;mdash; SVCE runs its own heat pump incentive programs separate from PG&amp;amp;E. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Jose Planning, Building and Code Enforcement Building Division&lt;/strong&gt;; contact the division directly for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -1656,6 +1656,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, Alabama Power&amp;rsquo;s residential rebate catalog, the Alabama Board of Heating, Air Conditioning and Refrigeration Contractors, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBHM Shuttlesworth)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Birmingham-Shuttlesworth International Airport (KBHM) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013876), Birmingham records an &lt;strong&gt;annual mean temperature of 63.9&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,533.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,177.0 cooling degree days&lt;/strong&gt;, a striking &lt;strong&gt;56.62 inches of annual precipitation&lt;/strong&gt;, and only 1.4 inches of snowfall. The near-balanced 1.16:1 HDD-to-CDD ratio defines Birmingham as a dual-need Zone 3A warm-humid climate, and its 56+ inches of rainfall drive substantial summer latent (humidity) load.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:07000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Birmingham city, Alabama) report &lt;strong&gt;88,527 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1965&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;53.8% electricity&lt;/strong&gt; (47,633 units) and &lt;strong&gt;43.7% utility natural gas&lt;/strong&gt; (38,665 units). Birmingham&amp;rsquo;s electric majority reflects Alabama Power&amp;rsquo;s historically competitive rates plus widespread heat-pump adoption across post-1960s housing growth.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama Power Residential Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.alabamapower.com/residential/save-money-and-energy/demand-side-management-programs/high-seer-heat-pump-rebate.html" target="_blank" rel="nofollow noopener"&gt;Alabama Power Demand Side Management Programs &amp;mdash; High SEER Heat Pump Rebate page&lt;/a&gt;: &lt;strong&gt;&amp;ldquo;Get $1,000 Back When You Switch From Gas to a High Efficiency Heat Pump.&amp;rdquo;&lt;/strong&gt; For smart thermostats, Alabama Power offers &lt;strong&gt;up to $200 back on qualifying smart thermostat purchases&lt;/strong&gt;. For Birmingham homeowners, the $1,000 gas-to-heat-pump conversion rebate is especially valuable given the city&amp;rsquo;s near-balanced HDD/CDD profile &amp;mdash; a heat pump handles both seasons efficiently. Spire Alabama administers rebates for the 43.7% of Birmingham homes on natural gas; check spireenergy.com for current amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HACR Board Licensing (Detailed)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Birmingham must hold a current license from the &lt;a href="https://hacr.alabama.gov/how-to-get-licensed/" target="_blank" rel="nofollow noopener"&gt;Alabama Board of Heating, Air Conditioning and Refrigeration Contractors (HACR)&lt;/a&gt;. Per the HACR licensing page: &lt;em&gt;&amp;ldquo;Active Status: Contractors who perform HVAC or Refrigeration installation, service or repair&amp;rdquo;&lt;/em&gt; must pass the Heating &amp;amp; Air Conditioning Contractors Examination (reciprocity requires a 70% score on an equivalent exam). HACR fees: &lt;strong&gt;Examination $175.00&lt;/strong&gt;; &lt;strong&gt;Active status $220.00 annually&lt;/strong&gt;; &lt;strong&gt;Inactive status $110.00 annually&lt;/strong&gt;. Active contractors must also carry &lt;strong&gt;a performance bond in the amount of $20,000&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active HACR license AND $20,000 performance bond before authorizing work is the baseline due-diligence step for every Birmingham homeowner.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Incentives&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Birmingham Department of Planning, Engineering &amp;amp; Permits&lt;/strong&gt;; the city directs applicants to the Online Permit Center and Birmingham Permit Guide. Contact Permitting &amp;amp; Inspection at 205-254-2904 or OnlinePermitCenter@birminghamal.gov for the current fee schedule. Per &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;DOE Energy Saver guidance on hot-humid climate sizing&lt;/a&gt;: oversized AC equipment in Birmingham&amp;rsquo;s 56+ inch rainfall climate will short-cycle before pulling humidity, leaving homes clammy even at 72&amp;deg;F. Correct Manual J sizing (not bigger-is-better) is essential. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4411,6 +4426,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFAT Yosemite)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fresno Yosemite International Airport (KFAT) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093193), Fresno records an &lt;strong&gt;annual mean temperature of 65.0&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,186.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,209.3 cooling degree days&lt;/strong&gt; &amp;mdash; a near-perfect 1:1 balance &amp;mdash; with only &lt;strong&gt;10.99 inches of annual precipitation&lt;/strong&gt; and no measurable snowfall. The heating and cooling loads are almost identical magnitudes, creating unusual dual-design demands: both winter heating and summer cooling are substantial, and neither dominates. This balance, combined with dry Central Valley summers, makes Fresno one of the best U.S. climates for two-stage or variable-capacity heat pumps that run efficiently in both modes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: High Solar Adoption&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:27000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fresno city, California) report &lt;strong&gt;179,684 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1979&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;54.9% utility natural gas&lt;/strong&gt; (98,594 units), &lt;strong&gt;39.0% electricity&lt;/strong&gt; (70,013 units), and a remarkable &lt;strong&gt;5,038 solar-heated homes (2.8%)&lt;/strong&gt; &amp;mdash; the highest solar share of any city in this project. Central Valley solar economics (long sun-hours, dry climate, abundant rooftop space) drive adoption well above national averages.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dry-Climate Cooling: Whole-House Fans &amp;amp; Evap Coolers&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fresno&amp;rsquo;s dry summers with cool overnight lows make passive cooling strategies realistic supplements or replacements for refrigerant cooling. Per the &lt;a href="https://www.energy.gov/energysaver/cooling-whole-house-fan" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Whole House Fans&lt;/a&gt;: &lt;em&gt;&amp;ldquo;They are most effective when outdoor temperatures are lower than indoor temperatures, as they quickly draw in the cooler outdoor air while exhausting warmer indoor air,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;whole house fans do not dehumidify air like air conditioners and heat pumps, making them less suitable for high-humidity climates.&amp;rdquo;&lt;/em&gt; For Fresno homeowners, running a whole-house fan for 60&amp;ndash;90 minutes after sunset can drop indoor temperatures 15&amp;ndash;20&amp;deg;F using a fraction of the energy refrigerant AC would consume. Evaporative (swamp) coolers are also viable in Fresno&amp;rsquo;s dry summer profile.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Fresno must hold a California C-20 Warm-Air Heating, Ventilating and Air-Conditioning contractor license from the California Contractors State License Board. Verifying the contractor&amp;rsquo;s active C-20 license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Fresno Department of Planning &amp;amp; Development, Building and Safety Services&lt;/strong&gt;; contact Building and Safety directly for the current fee schedule. Fresno is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas; for current residential rebate dollar amounts, visit pge.com or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Fresno ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6874,6 +6902,19 @@
       <c r="Q75" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Arizona Registrar of Contractors, the Mesa City Code, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KIWA Phoenix-Mesa Gateway)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Phoenix-Mesa Gateway Airport (KIWA) is the NOAA reference station closest to Mesa. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003192), Mesa records an &lt;strong&gt;annual mean temperature of 73.2&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,169.5 annual cooling degree days&lt;/strong&gt; against 1,139.1 heating degree days, and only &lt;strong&gt;8.73 inches of annual precipitation&lt;/strong&gt;. The 3.7:1 CDD-to-HDD ratio defines Mesa as a strongly cooling-dominated Zone 2B hot-dry desert climate &amp;mdash; similar to Phoenix but slightly cooler (Mesa&amp;rsquo;s 85.0&amp;deg;F annual max vs Phoenix&amp;rsquo;s 87.1&amp;deg;F at Sky Harbor), reflecting its location further from the urban heat island.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Overwhelmingly Electric Heating (SRP Territory)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:46000&amp;amp;in=state:04" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Mesa city, Arizona) report &lt;strong&gt;196,065 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1988&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;77.8% electricity&lt;/strong&gt; (152,610 units) overwhelmingly dominates, with only &lt;strong&gt;19.6% utility natural gas&lt;/strong&gt; (38,511 units). Mesa&amp;rsquo;s electric share is even higher than Phoenix&amp;rsquo;s 74.6% &amp;mdash; reflecting Mesa&amp;rsquo;s post-1980 growth within SRP&amp;rsquo;s service territory, where competitive electric rates and heat-pump-standard new construction made gas furnaces a minority even in the gas-capable neighborhoods.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal SEER2 Minimum &amp;amp; Attic-Duct Efficiency&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Central Air Conditioning&lt;/a&gt;, federal DOE rulemaking under 10 CFR Part 430 (effective January 1, 2023) requires Southern-region central air conditioners &amp;mdash; which includes Arizona &amp;mdash; to meet a minimum &lt;strong&gt;SEER2 14.3 rating&lt;/strong&gt; for split-system units under 45,000 BTU/hr (equivalent to SEER 15, higher than the Northern-region SEER2 13.4 floor). For Mesa homeowners replacing equipment, that&amp;rsquo;s the regulatory minimum, not a recommendation. DOE further advises that &lt;em&gt;&amp;ldquo;duct losses can account for more than 30% of energy consumption for space conditioning, especially if the ducts are in an unconditioned space such as an attic&amp;rdquo;&lt;/em&gt; &amp;mdash; directly relevant to Mesa&amp;rsquo;s 1988-median housing stock where most supply ducts run through vented attics that exceed 140&amp;deg;F during summer afternoons.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mesa City Code &amp;amp; Arizona ROC Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://library.municode.com/az/mesa/codes/code_of_ordinances" target="_blank" rel="nofollow noopener"&gt;Mesa City Code via Municode&lt;/a&gt;, the City of Mesa adopts the International Residential Code (IRC) and International Mechanical Code (IMC) via Title 4 (Buildings) with Mesa-specific amendments. Every HVAC contractor must hold a current license from the &lt;strong&gt;Arizona Registrar of Contractors (ROC)&lt;/strong&gt;: the residential classification is &lt;strong&gt;R-39 Air Conditioning and Refrigeration, Including Solar&lt;/strong&gt;; commercial work requires the &lt;strong&gt;C-39&lt;/strong&gt; classification. Dual-scope &lt;strong&gt;CR-39&lt;/strong&gt; covers both. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Mesa Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule. Mesa is served by &lt;strong&gt;Salt River Project (SRP)&lt;/strong&gt; for electricity and &lt;strong&gt;Southwest Gas&lt;/strong&gt; for natural gas; for current SRP rebate dollar amounts (heat pump, smart thermostat, duct sealing, pool pump), see srpnet.com/energy-savings directly.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7808,6 +7849,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the California Contractors State License Board, BayREN, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KOAK)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oakland International Airport (KOAK) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023230), Oakland records an &lt;strong&gt;annual mean temperature of 58.1&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,690.4 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;175.2 cooling degree days&lt;/strong&gt;, and &lt;strong&gt;18.68 inches of annual precipitation&lt;/strong&gt;. The 15:1 HDD-to-CDD ratio is the most extreme heating-dominated marine profile of any major U.S. city researched in this project &amp;mdash; even more extreme than San Francisco&amp;rsquo;s 12:1 &amp;mdash; confirming that central air conditioning is rarely the primary HVAC need in Oakland.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Pre-War Bay Area Inventory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:53000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Oakland city, California) report &lt;strong&gt;173,179 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1953&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;62.9% utility natural gas&lt;/strong&gt; (108,914 units), &lt;strong&gt;30.2% electricity&lt;/strong&gt; (52,380 units), and a notable &lt;strong&gt;6,705 occupied units (3.9%) reporting no fuel used for heating&lt;/strong&gt; &amp;mdash; similar to San Francisco&amp;rsquo;s 5.9% no-heat share, reflecting the East Bay&amp;rsquo;s mild marine climate. Oakland&amp;rsquo;s pre-WWII housing stock often has minimal central ducting, knob-and-tube wiring, and single-wall construction &amp;mdash; conditions that constrain modern HVAC retrofit options.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Marine Climate Heat Pump Suitability&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oakland&amp;rsquo;s 2,690 HDD and virtually negligible cooling load make it an exceptional climate for air-source heat pumps &amp;mdash; winters are mild (standard heat pumps never approach their 5&amp;deg;F lower limit), and summer cooling runtime is modest. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, ductless mini-splits are &lt;em&gt;&amp;ldquo;a good choice for room additions and for homes without ductwork, such as those heated by hydronic (hot water heat), radiant panels, and space heaters.&amp;rdquo;&lt;/em&gt; For Oakland&amp;rsquo;s pre-war single-family homes and three-unit apartment buildings, multi-zone ductless mini-splits are the natural heat-pump retrofit path.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California C-20 Contractor License &amp;amp; BayREN&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Oakland must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; license from the &lt;a href="https://www.cslb.ca.gov/About_Us/Library/Licensing_Classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;California Contractors State License Board&lt;/a&gt;, per California Code of Regulations Title 16 Division 8 Article 3. C-20 scope covers &lt;em&gt;&amp;ldquo;warm-air heating systems and water heating heat pumps&amp;hellip;ventilating systems&amp;hellip;air-conditioning systems&amp;hellip;and the ducts, registers, flues, humidity and thermostatic controls and air filters in connection with any of these systems,&amp;rdquo;&lt;/em&gt; including solar-energy HVAC systems.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates, Permits &amp;amp; Federal Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oakland is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for electricity delivery and natural gas, while &lt;strong&gt;Ava Community Energy&lt;/strong&gt; (formerly East Bay Community Energy / EBCE) is the Community Choice Aggregator for electric generation. Oakland residents have access to &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; (80% cost share on core upgrades, homeowner capped at $1,000) plus PG&amp;amp;E and Ava-specific rebates. For current dollar amounts, visit bayren.org, pge.com, and avaenergy.org directly &amp;mdash; Ava&amp;rsquo;s incentive tool routes households through an eligibility filter (ZIP + income + household size) for the most current offers. Permit fees for residential mechanical work are set by the &lt;strong&gt;Oakland Planning &amp;amp; Building Department&lt;/strong&gt;; contact the department directly for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8687,6 +8743,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance &amp;mdash; plus state licensing authority. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KRDU)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Raleigh-Durham International Airport (KRDU) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013722), Raleigh records an &lt;strong&gt;annual mean temperature of 61.2&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,153.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,804.5 cooling degree days&lt;/strong&gt;, &lt;strong&gt;46.07 inches of annual precipitation&lt;/strong&gt;, and 5.2 inches of snowfall. The 1.75:1 HDD-to-CDD ratio defines Raleigh as a classic Zone 4A mixed-humid climate where near-balanced heating and cooling loads make Raleigh an ideal climate for air-source heat pumps.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Newer Research-Triangle Growth&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:55000&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Raleigh city, North Carolina) report &lt;strong&gt;196,924 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1996&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.7% electricity&lt;/strong&gt; (115,536 units) leads &lt;strong&gt;39.1% utility natural gas&lt;/strong&gt; (77,066 units). Raleigh&amp;rsquo;s electric-heat share is higher than Charlotte&amp;rsquo;s 53.3% and its median year built (1996) is two years newer &amp;mdash; reflecting the Research Triangle&amp;rsquo;s post-1990s tech-driven growth into master-planned subdivisions that default to central heat pumps.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Heat Pump Efficiency in Zone 4A&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Today&amp;rsquo;s heat pump can reduce your electricity use for heating by up to 75%&amp;rdquo;&lt;/em&gt; compared to electric resistance. DOE notes that &lt;em&gt;&amp;ldquo;in warmer climates (zones 1&amp;ndash;4), about 60% of homes rely on furnaces, while heat pumps are used in 15%&amp;ndash;25% of homes&amp;rdquo;&lt;/em&gt; &amp;mdash; meaning Raleigh&amp;rsquo;s 58.7% electric-heat share significantly exceeds the DOE-documented Zone 4 average, reflecting North Carolina&amp;rsquo;s long-standing heat-pump adoption driven by Duke Energy&amp;rsquo;s competitive electric rates.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NC Board Licensing (H-1 / H-2 / H-3)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Raleigh must hold a current state-issued Heating &amp;amp; Cooling Contractor License from the &lt;a href="https://www.nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating &amp;amp; Fire Sprinkler Contractors&lt;/a&gt;. NC issues three heating-license classifications &amp;mdash; &lt;strong&gt;H-1&lt;/strong&gt; (unlimited scope), &lt;strong&gt;H-2&lt;/strong&gt; (limited to specified tonnage/BTU thresholds), and &lt;strong&gt;H-3&lt;/strong&gt; (packaged-unit specialty). For typical residential work in Raleigh, any of the three classifications can be sufficient depending on the job scope. The Board&amp;rsquo;s phone number is 919-875-3612; verifying a contractor&amp;rsquo;s active license before authorizing work is the baseline due-diligence step.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Raleigh is served by &lt;strong&gt;Duke Energy Progress&lt;/strong&gt; for electricity and &lt;strong&gt;Dominion Energy North Carolina&lt;/strong&gt; (formerly PSNC Energy) for natural gas. For current Duke Energy Progress &lt;strong&gt;Smart Saver&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat, duct sealing), visit duke-energy.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Raleigh ZIP. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Raleigh Planning and Development Department&lt;/strong&gt; per the FY26 Development Fee Guide; contact the Planning &amp;amp; Development Customer Service Center at 919-996-2500 (One Exchange Plaza, Suite 400) for current line-item amounts. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -2879,6 +2879,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile at 6,035 ft (NOAA Station KCOS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs Municipal Airport (KCOS) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093037), Colorado Springs records an &lt;strong&gt;annual mean temperature of 50.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,888.5 annual heating degree days&lt;/strong&gt; against 607.5 cooling degree days, &lt;strong&gt;15.91 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;32.5 inches of annual snowfall&lt;/strong&gt;. The city sits at &lt;strong&gt;6,035 ft elevation &amp;mdash; the highest elevation of any major U.S. city in this project&lt;/strong&gt;, even higher than Denver&amp;rsquo;s 5,280 ft. That altitude imposes more severe derating on combustion furnaces, refrigerant-charge sizing, and heat-pump output compared to sea-level nameplate capacity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Gas-Dominant Front Range&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:16000&amp;amp;in=state:08" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Colorado Springs city, Colorado) report &lt;strong&gt;198,070 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1986&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.8% utility natural gas&lt;/strong&gt; (138,249 units), &lt;strong&gt;27.2% electricity&lt;/strong&gt; (53,893 units). Unlike Denver&amp;rsquo;s near-50/50 electric-leaning split, Colorado Springs is gas-dominant &amp;mdash; reflecting its later post-1980 suburban growth where gas forced-air furnaces were the default in master-planned subdivisions.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Altitude + Cold-Climate Heat Pump Selection&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;if you live in a region where temperatures regularly dip below freezing in winter months, consider looking for a system with an ENERGY STAR Cold Climate label.&amp;rdquo;&lt;/em&gt; For Colorado Springs specifically, that recommendation stacks on top of altitude derating: a heat pump rated X BTU/hr at sea level will produce meaningfully less at 6,035 ft, so manufacturers&amp;rsquo; altitude-derating tables should be applied during Manual J load calculation. The 5,888 HDD heating season combined with altitude make proper sizing (not simple nameplate replacement) essential.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pikes Peak Regional Building Department (Unique Structure)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs operates under a distinctive permitting and licensing structure: permits and contractor licenses are administered by the &lt;a href="https://www.pprbd.org/" target="_blank" rel="nofollow noopener"&gt;Pikes Peak Regional Building Department (PPRBD)&lt;/a&gt; &amp;mdash; a joint regional authority covering Colorado Springs, El Paso County, and surrounding jurisdictions, rather than city-specific departments. Colorado does not issue a statewide HVAC contractor license; PPRBD handles mechanical contractor licensing for the region. Verifying a contractor&amp;rsquo;s active PPRBD license before authorizing work is the baseline due-diligence step. Contact PPRBD directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Colorado Springs Utilities (Four-Service Municipal) &amp;amp; Federal Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs is served by &lt;strong&gt;Colorado Springs Utilities (CSU)&lt;/strong&gt; &amp;mdash; a rare four-service municipal utility providing electricity, natural gas, water, and wastewater under a single entity owned by the City. For current CSU residential rebate dollar amounts (heat pump, smart thermostat, insulation, solar), visit csu.org directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year total, with $2,000/year cap for heat pumps and $1,200/year for other efficient property).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3684,6 +3699,21 @@
       <c r="Q37" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Texas Department of Licensing and Regulation, El Paso Electric&amp;rsquo;s Texas Residential Solutions Program, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KELP)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;El Paso International Airport (KELP) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023044), El Paso records an &lt;strong&gt;annual mean temperature of 66.2&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;2,661.9 annual cooling degree days&lt;/strong&gt; against 2,206.2 heating degree days, and only &lt;strong&gt;8.78 inches of annual precipitation&lt;/strong&gt; (tied with Albuquerque for among the driest major U.S. cities). Annual snowfall: 2.8 inches. El Paso sits at ~3,700 ft elevation in the Chihuahuan Desert; the 1.2:1 CDD-to-HDD ratio reflects mild winters and hot dry summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Unusual Gas-Majority for a Texas City&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:24000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for El Paso city, Texas) report &lt;strong&gt;242,482 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1983&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;71.2% utility natural gas&lt;/strong&gt; (172,703 units), &lt;strong&gt;26.7% electricity&lt;/strong&gt; (64,819 units). El Paso&amp;rsquo;s gas share is the HIGHEST of any major Texas city in this project &amp;mdash; Dallas, Houston, Austin, and San Antonio are all electric-majority. El Paso&amp;rsquo;s profile reflects cooler high-desert winters, extensive Texas Gas Service distribution, and older housing stock that defaulted to gas furnaces.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Evaporative Cooling: El Paso&amp;rsquo;s Dominant Summer Mode&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;El Paso has one of the highest evaporative-cooling adoption rates in the U.S., driven by exceptional climate fit. Per the &lt;a href="https://www.energy.gov/energysaver/evaporative-coolers" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Evaporative Coolers&lt;/a&gt;: &lt;em&gt;&amp;ldquo;In low-humidity areas, evaporating water into the air provides a natural and energy-efficient means of cooling,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;two-stage evaporative coolers are most often used in areas where daytime temperatures frequently exceed 100&amp;deg;F.&amp;rdquo;&lt;/em&gt; DOE also cautions that &lt;em&gt;&amp;ldquo;evaporative coolers should not be used in humid climates because they add humidity to the air in your home&amp;rdquo;&lt;/em&gt; &amp;mdash; a caution that doesn&amp;rsquo;t apply to El Paso. Many El Paso homes run evaporative coolers as the primary summer cooling mode, with refrigerant AC as backup during the brief monsoon season when humidity spikes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;El Paso Electric Residential Rebates (2025)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.epelectric.com/energy-efficiency/texas-residential-energy-efficiency-programs/texas-residential-energy-rebates-and-incentives" target="_blank" rel="nofollow noopener"&gt;El Paso Electric Texas Residential Solutions Program catalog&lt;/a&gt;, current 2025 rebate programs include: &lt;strong&gt;Smart Thermostat Rebate&lt;/strong&gt; (ENERGY STAR Certified models, through December 31, 2025), &lt;strong&gt;Evaporative/Refrigerated Cooling Rebate&lt;/strong&gt;, &lt;strong&gt;Heat Pump Water Heater Rebate&lt;/strong&gt;, and &lt;strong&gt;Direct Install Measures Rebate&lt;/strong&gt; &amp;mdash; each with its own application form. Program contact: &lt;em&gt;&amp;ldquo;(915) 255-4300 or epe.residential@clearesult.com.&amp;rdquo;&lt;/em&gt; Dollar amounts for each tier are published in the individual rebate application PDFs; visit the EPE rebates page directly for current figures.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in El Paso must hold a current Air Conditioning and Refrigeration (ACR) Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by Texas Occupations Code Chapter 1302 and 16 TAC Chapter 75. Per TDLR: &lt;em&gt;&amp;ldquo;Contractors who install, repair, or maintain systems related to air conditioning, refrigeration, or heating must have a TDLR license and ACR companies must employ an ACR contractor in each permanent location.&amp;rdquo;&lt;/em&gt; Class A covers any size unit; Class B is limited to 25 tons cooling / 1.5 million Btu heating. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of El Paso Development Services Department&lt;/strong&gt;; contact the One-Stop Shop at (915) 212-0104 for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8049,6 +8079,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KOMA Eppley)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Eppley Airfield (KOMA) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014942), Omaha records an &lt;strong&gt;annual mean temperature of 52.4&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,833.1 annual heating degree days&lt;/strong&gt; against 1,293.6 cooling degree days, &lt;strong&gt;31.86 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;27.1 inches of annual snowfall&lt;/strong&gt;. The 4.5:1 HDD-to-CDD ratio defines Omaha as a heating-dominated Zone 5A cool-humid climate &amp;mdash; but with meaningful summer cooling demand too, driven by hot and humid Great Plains summers. Tornado Alley exposure adds severe-weather risk during April&amp;ndash;June.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Gas-Dominant Midwest&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:31" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Omaha city, Nebraska) report &lt;strong&gt;199,926 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1972&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.0% utility natural gas&lt;/strong&gt; (145,987 units), &lt;strong&gt;24.6% electricity&lt;/strong&gt; (49,208 units). Omaha&amp;rsquo;s gas dominance reflects both Black Hills Energy&amp;rsquo;s established distribution network and the Great Plains preference for gas forced-air furnaces in the mid-century subdivisions that dominate the city.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pumps in Zone 5A&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Omaha&amp;rsquo;s 5,833 HDD and routine sub-zero winter temperatures put it at the demanding edge of cold-climate heat pump operation. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F,&amp;rdquo;&lt;/em&gt; and for regions with regular sub-freezing winters, DOE recommends &lt;em&gt;&amp;ldquo;considering systems bearing an ENERGY STAR Cold Climate label.&amp;rdquo;&lt;/em&gt; For Omaha installations, the 27.1-inch annual snowfall also means outdoor units need elevated snow stands and demand-defrost controls to maintain capacity through prolonged cold spells.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing &amp;amp; Local Permits (No Statewide HVAC License)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nebraska does not issue a statewide HVAC contractor license. Instead, HVAC contractor registration and permitting in Omaha are handled locally through the &lt;strong&gt;City of Omaha Permits and Inspections Division&lt;/strong&gt;. Verifying that a contractor is registered with the city before authorizing any HVAC work is the critical due-diligence step &amp;mdash; more important than in states with a statewide board, because the local registration is the only formal credential. Contact Permits and Inspections directly for the current fee schedule and contractor-verification tools.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Omaha&amp;rsquo;s electricity is served by &lt;strong&gt;Omaha Public Power District (OPPD)&lt;/strong&gt; &amp;mdash; a customer-owned public power district &amp;mdash; and natural gas by &lt;strong&gt;Black Hills Energy&lt;/strong&gt;. For current residential rebate dollar amounts from OPPD (heat pump, smart thermostat, weatherization), visit oppd.com; for Black Hills Energy gas-equipment rebates, visit blackhillsenergy.com directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;: &lt;strong&gt;$2,000/year for qualified heat pumps, heat pump water heaters, biomass stoves, or biomass boilers&lt;/strong&gt;; &lt;strong&gt;$1,200/year for other energy-efficient property and home improvements&lt;/strong&gt;; &lt;strong&gt;up to $600 per item&lt;/strong&gt; for central AC and gas/propane/oil furnaces meeting the CEE highest efficiency tier.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8421,6 +8466,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPIT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pittsburgh International Airport (KPIT) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094823), Pittsburgh records an &lt;strong&gt;annual mean temperature of 51.8&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,571.8 annual heating degree days&lt;/strong&gt; against 796.9 cooling degree days, &lt;strong&gt;39.61 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;44.1 inches of annual snowfall&lt;/strong&gt;. The 7:1 HDD-to-CDD ratio defines Pittsburgh as a heating-dominated Zone 5A cool-humid climate &amp;mdash; with Allegheny River valley topography that can trap cold air and elevated snowfall from lake-effect storms off Lake Erie.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Second-Oldest Housing Stock in Project&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:61000&amp;amp;in=state:42" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Pittsburgh city, Pennsylvania) report &lt;strong&gt;137,593 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1942&lt;/strong&gt; &amp;mdash; the second-oldest housing stock of any city in this project, behind only Cleveland&amp;rsquo;s 1940. Heating-fuel distribution: &lt;strong&gt;75.4% utility natural gas&lt;/strong&gt; (103,812 units), &lt;strong&gt;20.3% electricity&lt;/strong&gt; (27,957 units), and a notable &lt;strong&gt;978 fuel oil-heated units&lt;/strong&gt; (0.7%) &amp;mdash; a Northeast Rust Belt legacy. Pittsburgh&amp;rsquo;s pre-WWII brick rowhomes and steel-era housing stock typically have undersized duct chases, limited envelope insulation, and original gas forced-air or hydronic heating systems.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pumps &amp;amp; Dual-Fuel for Aging Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pittsburgh&amp;rsquo;s 5,572 HDD heating season combined with pre-WWII housing creates distinctive HVAC retrofit challenges. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F,&amp;rdquo;&lt;/em&gt; and in dual-fuel configurations &lt;em&gt;&amp;ldquo;during warmer months, the heat pump efficiently heats and cools your home. When temperatures drop, the system automatically switches to the gas furnace, which is better suited for cold weather.&amp;rdquo;&lt;/em&gt; For Pittsburgh homeowners replacing an aging gas furnace, dual-fuel (hybrid heat pump + gas furnace) captures the efficiency gains during milder months while preserving gas backup for the coldest spells. The 44.1-inch annual snowfall also means outdoor units need elevated snow stands and demand-defrost controls.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing: PA HICPA &amp;amp; Pittsburgh Local Registration&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pennsylvania does not issue a statewide HVAC contractor license. Instead, Pennsylvania requires home-improvement contractors performing more than &lt;strong&gt;$5,000 of work per year&lt;/strong&gt; to register with the Office of Attorney General under the &lt;strong&gt;Home Improvement Consumer Protection Act (HICPA)&lt;/strong&gt;. Additionally, the &lt;strong&gt;City of Pittsburgh Department of Permits, Licenses &amp;amp; Inspections (PLI)&lt;/strong&gt; requires local contractor registration for work within city limits. Verifying BOTH the HICPA registration AND Pittsburgh PLI registration before authorizing work is the baseline due-diligence step. Contact PLI directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pittsburgh is served by &lt;strong&gt;Duquesne Light Company&lt;/strong&gt; for electricity (with the &lt;strong&gt;Watt Choices&lt;/strong&gt; residential efficiency program) and &lt;strong&gt;Peoples Natural Gas&lt;/strong&gt; for natural gas. For current rebate dollar amounts, visit duquesnelight.com (Watt Choices) and peoples-gas.com directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year total, with $2,000/year cap for heat pumps and $1,200/year for other energy-efficient property).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11358,6 +11418,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Code of Virginia, the Virginia Department of Professional and Occupational Regulation, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station at Norfolk NAS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Norfolk Naval Air Station (KNGU) is the nearest NOAA long-period reference station, representing Hampton Roads/Virginia Beach coastal climate. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013737), Virginia Beach records an &lt;strong&gt;annual mean temperature of 61.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;3,069.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,872.6 cooling degree days&lt;/strong&gt;, &lt;strong&gt;49.18 inches of annual precipitation&lt;/strong&gt;, and 6.2 inches of snowfall. The 1.6:1 HDD-to-CDD ratio defines Virginia Beach as a classic Zone 4A mixed-humid climate &amp;mdash; plus Atlantic Ocean coastal exposure that accelerates salt-air corrosion on outdoor HVAC equipment and adds hurricane wind-load considerations.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Electric-Majority Heat Pump Market&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:82000&amp;amp;in=state:51" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Virginia Beach city, Virginia) report &lt;strong&gt;179,800 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;62.4% electricity&lt;/strong&gt; (112,232 units), &lt;strong&gt;33.9% utility natural gas&lt;/strong&gt; (61,020 units), and a notable &lt;strong&gt;1.4% fuel oil&lt;/strong&gt; (2,459 units). Virginia Beach&amp;rsquo;s electric majority reflects Dominion Energy&amp;rsquo;s established service area plus widespread heat-pump adoption in post-1980s suburban growth.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Virginia Contractor Licensing: Class A/B/C Monetary Thresholds (Verbatim)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Virginia uses a distinctive three-class contractor licensing structure tied to dollar thresholds. Per &lt;a href="https://law.lis.virginia.gov/vacode/title54.1/chapter11/section54.1-1100/" target="_blank" rel="nofollow noopener"&gt;Code of Virginia Section 54.1-1100&lt;/a&gt;: &lt;strong&gt;Class A&lt;/strong&gt; applies when &lt;em&gt;&amp;ldquo;the total value referred to in a single contract or project is $150,000 or more, or&amp;hellip;the total value of all such construction, removal, repair, or improvements undertaken by such person within any 12-month period is $1 million or more.&amp;rdquo;&lt;/em&gt; &lt;strong&gt;Class B&lt;/strong&gt; applies when &lt;em&gt;&amp;ldquo;the total value referred to in a single contract or project is $30,000 or more, but less than $150,000, or&amp;hellip;the total value&amp;hellip;within any 12-month period is $250,000 or more, but less than $1 million.&amp;rdquo;&lt;/em&gt; &lt;strong&gt;Class C&lt;/strong&gt; applies when &lt;em&gt;&amp;ldquo;the total value referred to in a single contract or project is over $1,000 but less than $30,000, or&amp;hellip;the total value&amp;hellip;within any 12-month period is less than $250,000.&amp;rdquo;&lt;/em&gt; For typical residential HVAC work, a Class C license is sufficient; larger commercial projects may require Class B or A.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;VA DPOR HVAC Specialty (HVA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Virginia Beach must also hold the &lt;strong&gt;HVA (Heating, Ventilation and Air Conditioning)&lt;/strong&gt; specialty classification from the &lt;a href="https://www.dpor.virginia.gov/Boards/Contractors/" target="_blank" rel="nofollow noopener"&gt;Virginia Department of Professional and Occupational Regulation (DPOR), Board for Contractors&lt;/a&gt;. Per DPOR: &lt;em&gt;&amp;ldquo;The class of license (A, B, or C)&amp;hellip;determines the monetary value of contracts/projects that may be performed, and the classification/specialty&amp;hellip;determines what type of work is allowed.&amp;rdquo;&lt;/em&gt; Contact DPOR at (804) 367-8511 or contractors@dpor.virginia.gov. Verifying both the monetary class AND the HVA specialty on a contractor&amp;rsquo;s active license is the baseline due-diligence step for Virginia Beach homeowners.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Coastal Corrosion, Rebates &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Virginia Beach&amp;rsquo;s Atlantic coastal exposure imposes the same salt-air corrosion concern found in Miami, Jacksonville, and Tampa &amp;mdash; outdoor condensers benefit from coastal-duty coil coatings and more frequent rinsing. For current &lt;strong&gt;Dominion Energy Virginia&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat), visit dominionenergy.com directly; &lt;strong&gt;Virginia Natural Gas&lt;/strong&gt; administers separate gas-equipment rebates. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Virginia Beach Permits &amp;amp; Inspections Division&lt;/strong&gt;; contact the division for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -871,6 +871,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Alaska Division of Corporations, Business and Professional Licensing, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile: Subarctic Extreme (NOAA Station KANC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ted Stevens Anchorage International Airport (KANC) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00026451), Anchorage records an &lt;strong&gt;annual mean temperature of 37.6&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;9,978.6 annual heating degree days&lt;/strong&gt; &amp;mdash; the HIGHEST of any city in this project, nearly double Minneapolis&amp;rsquo;s 7,399 HDD &amp;mdash; against only &lt;strong&gt;7.6 cooling degree days&lt;/strong&gt;, &lt;strong&gt;77.9 inches of annual snowfall&lt;/strong&gt;, and 16.42 inches of total precipitation. The 1,313:1 HDD-to-CDD ratio defines Anchorage as a Zone 7 very-cold subarctic climate where heating-system reliability is the single dominant HVAC priority &amp;mdash; and historically, where standard air-source heat pumps were considered impractical due to capacity loss below their balance point.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: Gas-Dominant Subarctic Inventory&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:03000&amp;amp;in=state:02" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Anchorage municipality, Alaska) report &lt;strong&gt;107,868 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1982&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;79.3% utility natural gas&lt;/strong&gt; (85,509 units, Enstar Natural Gas service territory), &lt;strong&gt;15.6% electricity&lt;/strong&gt; (16,853 units), plus 1,969 fuel-oil homes (1.8%) and 420 wood-heated homes. Anchorage is a consolidated city-borough; the Census entity is Anchorage municipality.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Modern Cold-Climate Heat Pumps Change the Math&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Until recently, air-source heat pumps were dismissed for Anchorage-scale heating loads. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, &lt;em&gt;&amp;ldquo;cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F,&amp;rdquo;&lt;/em&gt; and for subarctic regions DOE recommends &lt;em&gt;&amp;ldquo;looking for a system with an ENERGY STAR Cold Climate label.&amp;rdquo;&lt;/em&gt; Cold-climate heat pumps (ccASHP) paired with Enstar Natural Gas furnace backup &amp;mdash; a dual-fuel configuration &amp;mdash; are increasingly specified for Anchorage retrofits: the heat pump handles the milder months efficiently, and the gas furnace takes over below the heat pump&amp;rsquo;s balance point. Outdoor units need elevated snow stands sufficient to clear 77.9 inches of annual snowfall.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alaska Mechanical Administrator License (Three Classes)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Anchorage must hold a current Mechanical Administrator license from the &lt;a href="https://www.commerce.alaska.gov/web/cbpl/professionallicensing/mechanicaladministrators.aspx" target="_blank" rel="nofollow noopener"&gt;Alaska Department of Commerce, Division of Corporations, Business and Professional Licensing (DCBPL)&lt;/a&gt;. The Board issues three relevant HVAC license classes: &lt;strong&gt;Residential HVAC (RHVC)&lt;/strong&gt;, &lt;strong&gt;Unlimited HVAC/Sheet Metal (UHVCS)&lt;/strong&gt;, and &lt;strong&gt;Heating, Cooling, and Process Piping (HCPP)&lt;/strong&gt;. Board contact: (907) 465-2050 or MechanicalAdministrators@Alaska.gov. For Anchorage homeowners, verifying that a contractor holds the appropriate class (most residential work falls under RHVC) is the baseline due-diligence step.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Rebates &amp;amp; Federal Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;Municipality of Anchorage Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule. Anchorage is served by &lt;strong&gt;Chugach Electric Association&lt;/strong&gt; &amp;mdash; a member-owned cooperative utility &amp;mdash; for electricity, and &lt;strong&gt;Enstar Natural Gas&lt;/strong&gt; for the dominant residential heating fuel. For current rebate dollar amounts, visit chugachelectric.com and enstarnaturalgas.com directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps including cold-climate models).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2179,6 +2194,21 @@
       <c r="Q20" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, and U.S. Department of Energy guidance. Every numerical claim in this section links to the source document that contains the underlying value.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile: Lake Erie Snow Belt (NOAA KBUF)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Buffalo Niagara International Airport (KBUF) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014733), Buffalo records an &lt;strong&gt;annual mean temperature of 48.8&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;6,465.9 annual heating degree days&lt;/strong&gt; against 607.8 cooling degree days, &lt;strong&gt;40.68 inches of annual precipitation&lt;/strong&gt;, and a remarkable &lt;strong&gt;95.4 inches of annual snowfall&lt;/strong&gt; &amp;mdash; the HIGHEST of any major U.S. city in this project, driven by Lake Erie lake-effect storms that can dump several feet of snow in a single event. The 10.6:1 HDD-to-CDD ratio and extreme snow load dominate every HVAC design decision for Buffalo homes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: 86% Gas, Pre-WWII Median&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:11000&amp;amp;in=state:36" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Buffalo city, New York) report &lt;strong&gt;119,548 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1938&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;85.97% utility natural gas&lt;/strong&gt; (102,778 units) &amp;mdash; the HIGHEST gas-heating share of any city in this project &amp;mdash; &lt;strong&gt;9.45% electricity&lt;/strong&gt; (11,295 units), and 1,163 fuel-oil homes (0.97%). The 1938 median year built ties with Detroit and is close to Cleveland&amp;rsquo;s 1940 among the oldest housing stocks in the country: Buffalo&amp;rsquo;s dense inventory of pre-WWII brick two-families, Victorian houses, and early-20th-century neighborhoods was overwhelmingly built around gas forced-air or radiator heating.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Designing for 95 Inches of Lake-Effect Snow&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Buffalo&amp;rsquo;s 95.4 inches of annual snowfall isn&amp;rsquo;t a uniform light dusting &amp;mdash; it arrives in intense lake-effect bands that can deposit 2&amp;ndash;5 feet of snow in 24&amp;ndash;48 hours. For outdoor HVAC equipment, that requires &lt;strong&gt;elevated snow stands&lt;/strong&gt; (typically 24+ inches above grade for heat-pump condensers), careful sidewall-vent placement for condensing gas appliances to avoid drift blockage, and robust defrost controls. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, DOE recommends &lt;em&gt;&amp;ldquo;looking for a system with an ENERGY STAR Cold Climate label&amp;rdquo;&lt;/em&gt; for regions experiencing regular sub-freezing winters &amp;mdash; non-negotiable for Buffalo installations where winter low averages well below 0&amp;deg;F during polar vortex events.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing: No NY State License + Buffalo Local Registration&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York State does not issue a statewide HVAC contractor license. Instead, Buffalo requires a local &lt;strong&gt;Heating Contractor License&lt;/strong&gt; administered by the &lt;strong&gt;City of Buffalo Department of Permit &amp;amp; Inspection Services (DPIS)&lt;/strong&gt;. Verifying that a contractor holds the city-issued Heating Contractor License before authorizing any HVAC work is the critical due-diligence step &amp;mdash; more important than in states with a statewide board, because the municipal license is the only formal credential. Contact DPIS at 65 Niagara Square for the current mechanical permit fee schedule and contractor-verification tools.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; NYSERDA Clean Heat&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Buffalo is served by &lt;strong&gt;National Grid&lt;/strong&gt; for both electricity and natural gas. National Grid runs Upstate NY residential efficiency programs covering Gas Heating &amp;amp; Water Heating and Electric Heating &amp;amp; Cooling. Buffalo residents are also eligible for the statewide &lt;strong&gt;NYSERDA NY Clean Heat&lt;/strong&gt; program &amp;mdash; among the most generous heat-pump incentive programs in the country for cold-climate air-source and ground-source systems. For current National Grid and NYSERDA Clean Heat dollar amounts, visit nationalgridus.com and nyserda.ny.gov directly &amp;mdash; both sites use interactive address-lookup tools rather than static dollar lists. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7796,6 +7826,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and state primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the New Jersey State Board of Examiners of HVACR Contractors, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KEWR Newark Liberty)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Newark Liberty International Airport (KEWR) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014734), Newark records an &lt;strong&gt;annual mean temperature of 55.5&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,700.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,269.5 cooling degree days&lt;/strong&gt;, &lt;strong&gt;46.60 inches of annual precipitation&lt;/strong&gt;, and 31.5 inches of annual snowfall. The 3.7:1 HDD-to-CDD ratio defines Newark as a classic Zone 4A mixed-humid climate where both heating and cooling matter meaningfully &amp;mdash; ideal heat-pump territory.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Fuel-Oil Legacy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:51000&amp;amp;in=state:34" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Newark city, New Jersey) report &lt;strong&gt;113,748 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1966&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;70.7% utility natural gas&lt;/strong&gt; (80,434 units), &lt;strong&gt;19.9% electricity&lt;/strong&gt; (22,655 units), and a notable &lt;strong&gt;2.9% fuel oil&lt;/strong&gt; (3,281 units) &amp;mdash; a Northeast urban legacy similar to Philadelphia (3.0%), Boston (7.2%), and NYC (12.5%). Newark also has 3,252 occupied units (2.9%) reporting no fuel used.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 4A Heat Pump &amp;amp; Mini-Split Suitability&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Newark&amp;rsquo;s Zone 4A mixed-humid climate makes it well-suited to air-source heat pumps in both dual-fuel and single-fuel configurations. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, modern cold-climate heat pumps maintain capacity at low temperatures, making them suitable for moderate northern climates such as the Mid-Atlantic. For Newark&amp;rsquo;s dense pre-1966 multi-family housing stock, ductless mini-splits provide a retrofit path that doesn&amp;rsquo;t require invasive ductwork &amp;mdash; particularly relevant for the 5-plus-story walk-ups and triple-decker buildings common in the city&amp;rsquo;s older neighborhoods.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NJ HVACR Contractor License (State Board)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Newark must hold a current license from the &lt;a href="https://www.njconsumeraffairs.gov/hvacr/Pages/default.aspx" target="_blank" rel="nofollow noopener"&gt;New Jersey State Board of Examiners of Heating, Ventilating, Air Conditioning and Refrigeration (HVACR) Contractors&lt;/a&gt;, administered by the NJ Division of Consumer Affairs. New Jersey is one of the few states with a dedicated HVACR-specific licensing board (separate from general contractor licensing). Per the Board: &lt;em&gt;&amp;ldquo;All heating, ventilating, air conditioning and refrigeration contractors must be licensed by the state and renew their licenses every two years,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;The Board ensures contractors meet all educational requirements for licensure.&amp;rdquo;&lt;/em&gt; Board contact: HVACR@dca.njoag.gov / (973) 504-6250 / P.O. Box 47031, Newark, NJ 07101 (the Board itself is headquartered in Newark).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Rebates &amp;amp; Federal Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work in Newark are set by the &lt;strong&gt;Newark Office of Uniform Construction Code (UCC)&lt;/strong&gt;, which administers the New Jersey Uniform Construction Code (NJUCC); contact the UCC office at 920 Mayor Kenneth A. Gibson Blvd, 973-733-4311, for the current fee schedule. Newark is served by &lt;strong&gt;PSE&amp;amp;G&lt;/strong&gt; (Public Service Enterprise Group) for both electricity and natural gas; PSE&amp;amp;G runs the Home Energy Solutions program, and residents are eligible for the statewide &lt;a href="https://www.njcleanenergy.com/residential/home/home" target="_blank" rel="nofollow noopener"&gt;NJ Clean Energy Program&lt;/a&gt; which administers heat pump and other efficiency incentives. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9321,6 +9366,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal and municipal primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Salt Lake City Consolidated Fee Schedule, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSLC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Salt Lake City International Airport (KSLC) is the NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024127), Salt Lake City records an &lt;strong&gt;annual mean temperature of 54.7&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;5,153.9 annual heating degree days&lt;/strong&gt; against 1,419.7 cooling degree days, &lt;strong&gt;15.52 inches of annual precipitation&lt;/strong&gt;, and &lt;strong&gt;51.9 inches of annual snowfall&lt;/strong&gt;. The 3.6:1 HDD-to-CDD ratio, 4,226 ft elevation (altitude derating on combustion equipment and heat-pump capacity), and well-known Wasatch Front winter inversions (which trap valley air pollution for days at a time) combine to make Salt Lake City&amp;rsquo;s HVAC design considerations distinctive among Western cities.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:49" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Salt Lake City city, Utah) report &lt;strong&gt;88,932 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1963&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.3% utility natural gas&lt;/strong&gt; (65,185 units), &lt;strong&gt;23.1% electricity&lt;/strong&gt; (20,513 units), and 1,840 bottled/LP gas homes. The gas dominance reflects Dominion Energy Utah&amp;rsquo;s mature distribution network, though the mid-1960s median year means a significant share of stock predates modern duct-sealing and envelope standards.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Winter Inversions: A Distinctive SLC HVAC Consideration&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Salt Lake City&amp;rsquo;s Wasatch Front valley regularly experiences wintertime temperature inversions that trap PM2.5 and NOx from combustion sources &amp;mdash; including residential gas furnaces &amp;mdash; at ground level for days at a time. This is the single strongest air-quality argument for accelerated heat-pump adoption in the Salt Lake Valley: electric heat pumps (powered by Rocky Mountain Power generation outside the valley) don&amp;rsquo;t contribute to valley-floor combustion emissions during inversion episodes. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, modern cold-climate heat pumps work down to 5&amp;deg;F ambient &amp;mdash; at the boundary of SLC&amp;rsquo;s coldest winter mornings, making ccASHP selection meaningful for Wasatch Front installations. Altitude derating per manufacturer tables applies on top of cold-climate selection.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Salt Lake City Mechanical Permit Fees (Verbatim)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://tools.slc.gov/feeschedule/" target="_blank" rel="nofollow noopener"&gt;Salt Lake City Consolidated Fee Schedule&lt;/a&gt; (Building Services Division, Section 18.52.050 mechanical permits), current mechanical permit fees include: &lt;strong&gt;base fee $57&lt;/strong&gt;; &lt;strong&gt;forced-air furnace or burner up to 200,000 BTU/h $29&lt;/strong&gt;, 200,000&amp;ndash;300,000 BTU/h $41, 300,000&amp;ndash;1,000,000 BTU/h $65; &lt;strong&gt;floor furnace $18&lt;/strong&gt;; &lt;strong&gt;appliance vent $18&lt;/strong&gt;; &lt;strong&gt;heating appliance repair/alteration $41 (up to $1,000 contract value) or $100 (greater than $1,000)&lt;/strong&gt;; &lt;strong&gt;boiler/compressor up to 3 hp $29&lt;/strong&gt;. For a typical residential furnace replacement, expect a $57 base + $29&amp;ndash;$65 per-appliance fee depending on capacity &amp;mdash; among the more transparent municipal fee schedules in this project.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utah DOPL S350 License &amp;amp; Utility Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Salt Lake City must hold a current &lt;strong&gt;S350 HVAC Contractor&lt;/strong&gt; license from the &lt;strong&gt;Utah Division of Occupational and Professional Licensing (DOPL)&lt;/strong&gt;. The S350 classification covers heating, ventilating, and air conditioning contracting statewide. Verifying a contractor&amp;rsquo;s active S350 license via DOPL&amp;rsquo;s online lookup before authorizing work is the baseline due-diligence step. Salt Lake City is served by &lt;strong&gt;Rocky Mountain Power&lt;/strong&gt; (PacifiCorp) for electricity, running the &lt;strong&gt;wattsmart&lt;/strong&gt; residential efficiency program, and by &lt;strong&gt;Dominion Energy Utah&lt;/strong&gt; for natural gas with its &lt;strong&gt;ThermWise&lt;/strong&gt; rebate program. For current wattsmart and ThermWise rebate dollar amounts, visit rockymountainpower.net/wattsmart and dominionenergy.com/utah directly &amp;mdash; both sites route through interactive lookup tools rather than static dollar lists. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11945,6 +12005,21 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below are drawn from federal, state, and utility primary sources &amp;mdash; NOAA climate normals, U.S. Census ACS estimates, the Hawaii DCCA Contractors License Board, Hawaii Energy&amp;rsquo;s HVAC rebate catalog, and U.S. Department of Energy guidance. Every claim in this section links to the source document that contains the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile: Zero Heating Demand (NOAA Station KHNL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Daniel K. Inouye International Airport (KHNL, formerly Honolulu Intl) is the NOAA reference station for Oahu. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00022521), Honolulu records an &lt;strong&gt;annual mean temperature of 78.0&amp;deg;F&lt;/strong&gt;, approximately &lt;strong&gt;4,767.1 annual cooling degree days&lt;/strong&gt; against &lt;strong&gt;0.0 heating degree days&lt;/strong&gt; &amp;mdash; yes, literally zero &amp;mdash; &lt;strong&gt;16.41 inches of annual precipitation&lt;/strong&gt;, and no measurable snowfall. Honolulu&amp;rsquo;s tropical Zone 1A climate has no heating demand whatsoever under the standard 65&amp;deg;F degree-day baseline. This is the only city in this project where HDD is effectively zero.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock: 45% of Homes Have No Heating Fuel&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:71550&amp;amp;in=state:15" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Urban Honolulu CDP, Hawaii) report &lt;strong&gt;136,228 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1973&lt;/strong&gt;. Heating-fuel distribution is unlike anywhere else in the project: &lt;strong&gt;44.97% of occupied units report NO fuel used for heating&lt;/strong&gt; (61,258 units) &amp;mdash; because in Honolulu&amp;rsquo;s tropical climate central heating is simply unnecessary. &lt;strong&gt;46.42% use electricity&lt;/strong&gt; (63,239 units, primarily for occasional warming of bathrooms and unusual cool nights), only &lt;strong&gt;4.79% use utility gas&lt;/strong&gt; (6,521 units), and a notable &lt;strong&gt;2.78% (3,792 units) use solar energy&lt;/strong&gt; &amp;mdash; an unusually high solar-heating share reflecting Hawaii&amp;rsquo;s abundant sun plus high electricity costs driving rooftop solar adoption.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hawaii Energy HVAC Rebates (Statewide Program)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Hawaii&amp;rsquo;s ratepayer-funded efficiency program, &lt;a href="https://hawaiienergy.com/for-homes/rebates/hvac" target="_blank" rel="nofollow noopener"&gt;Hawaii Energy&lt;/a&gt;, administers HVAC rebates for Hawaiian Electric (HECO) customers on Oahu (plus Maui County and Hawaii Island). Current instant rebate amounts verbatim: &lt;strong&gt;central air conditioner retrofit: $1,250 instant rebate&lt;/strong&gt;; &lt;strong&gt;air conditioner tune-up: $75&lt;/strong&gt;; &lt;strong&gt;window air conditioner: up to $45&lt;/strong&gt; ($25 standard / $45 dual inverter); &lt;strong&gt;mini-split VRF air conditioner: up to $550 per unit&lt;/strong&gt;; &lt;strong&gt;whole house fan: $100&lt;/strong&gt;; &lt;strong&gt;solar attic fan: $75&lt;/strong&gt;. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Salt-Air Corrosion &amp;amp; Trade-Wind Ventilation&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Honolulu&amp;rsquo;s coastal Pacific location subjects outdoor HVAC equipment to continuous salt-laden trade winds that accelerate condenser-coil corrosion. Per DOE guidance on &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;hot-humid-climate energy efficiency&lt;/a&gt;, coastal installations benefit from corrosion-resistant coil coatings (&amp;ldquo;sea-coast&amp;rdquo; or &amp;ldquo;anti-corrosion&amp;rdquo; factory options), more frequent rinsing of outdoor units, and stainless or coated hardware. Meanwhile, Honolulu&amp;rsquo;s famous trade winds provide natural ventilation that many older homes use instead of mechanical cooling &amp;mdash; which explains both the 45% no-fuel share and the relatively modest penetration of whole-house central AC compared to mainland tropical cities like Miami.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hawaii DCCA C-52 Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Honolulu must hold a current &lt;strong&gt;C-52 Ventilating and Air Conditioning Contractor&lt;/strong&gt; license from the &lt;a href="https://cca.hawaii.gov/pvl/boards/contractor/" target="_blank" rel="nofollow noopener"&gt;Hawaii Department of Commerce and Consumer Affairs (DCCA) Professional and Vocational Licensing Division Contractors License Board&lt;/a&gt;. The C-52 classification covers ventilating and air conditioning contracting statewide. Verifying a contractor&amp;rsquo;s active C-52 license via DCCA&amp;rsquo;s online lookup before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City and County of Honolulu Department of Planning and Permitting (DPP)&lt;/strong&gt; under the Revised Ordinances of Honolulu; contact DPP Building Division at (808) 768-8242 for the current fee schedule. Note: Honolulu is a Census Designated Place within the consolidated City and County of Honolulu &amp;mdash; permitting is handled at the county level.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -1769,6 +1769,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the Idaho Power Heating &amp;amp; Cooling Efficiency Program rebate catalog, and U.S. Department of Energy climate-zone guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBOI)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Boise Air Terminal (KBOI) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024131), Boise records an &lt;strong&gt;annual mean temperature of 53.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 64.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 42.0&amp;deg;F, approximately &lt;strong&gt;5,320.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,045.0 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;11.51 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;17.6 inches&lt;/strong&gt;. Boise sits in DOE Climate Zone 5B (cool-dry) at roughly 2,700 ft elevation in the Snake River Plain. The roughly 5:1 HDD-to-CDD ratio establishes Boise as a heating-dominant market, but the meaningful summer cooling load (1,000+ CDD) means properly sized cooling capacity remains essential.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:08830&amp;amp;in=state:16" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Boise City city, Idaho) report &lt;strong&gt;99,616 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1985&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;62.3% utility natural gas&lt;/strong&gt; (62,027 units), &lt;strong&gt;34.0% electricity&lt;/strong&gt; (33,838 units), 1,326 units on bottled/tank/LP gas, 940 on wood, and 392 on fuel oil. The relatively young housing stock (median 1985) reflects Boise&amp;rsquo;s post-1980s growth trajectory and means most homes were built under more modern envelope standards than older Mountain West cities &amp;mdash; a factor that improves heat-pump conversion economics.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cool-Dry Climate Considerations (Zone 5B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/eere/buildings/building-america" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Building America climate-zone guidance&lt;/a&gt;, Zone 5B (cool-dry) climates like Boise produce two HVAC-relevant patterns: low indoor relative humidity during the heating season (driven by 11.51 inches of annual precipitation and cold dry winter air at 5,320.5 HDD), and meaningful but not extreme cooling demand. Whole-house humidification is more commonly specified here than in humid eastern cities, and Snake River Valley cold-air inversions during winter mean outdoor heat-pump units benefit from elevated mounting and clear defrost drainage.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Idaho Power Residential Rebates (Heating &amp;amp; Cooling Efficiency Program)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Idaho Power administers a residential &lt;a href="https://www.idahopower.com/energy-environment/ways-to-save/savings-for-your-home/rebates-and-offers/heating-and-cooling-efficiency-program/" target="_blank" rel="nofollow noopener"&gt;Heating &amp;amp; Cooling Efficiency Program&lt;/a&gt; for its Boise service territory. Current rebates for existing homes include: &lt;strong&gt;$800 for a qualifying ducted air-source heat pump&lt;/strong&gt; when replacing an electric forced-air furnace, electric baseboards/ceiling cable/wall units, propane forced-air furnace, or oil forced-air furnace; &lt;strong&gt;$400 for a qualifying ductless heat pump&lt;/strong&gt; meeting the 9 HSPF / 7.6 HSPF2 efficiency requirement; and &lt;strong&gt;$50 for a qualifying smart thermostat&lt;/strong&gt;. Intermountain Gas administers separate gas-side incentives; contact Intermountain Gas directly for current natural-gas furnace rebate amounts. Idaho Power rebates pair with the federal IRS Section 25C Energy Efficient Home Improvement Credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Idaho HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC contractors operating in Idaho are regulated by the Idaho Division of Occupational and Professional Licenses (DOPL) under Idaho Statute Title 54, Chapter 50 (Heating, Ventilation and Air Conditioning Act). Verify a specific contractor&amp;rsquo;s current license status on the DOPL public lookup before contracting. Idaho HVAC license requirements include passing a written examination and meeting documented experience requirements; permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest efficiency tier set by the Consortium for Energy Efficiency (CEE) in effect at the start of the calendar year of installation. The credit is non-refundable and stacks with Idaho Power and Intermountain Gas rebates.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6781,6 +6798,25 @@
       <c r="Q73" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the Wisconsin Focus on Energy statewide rebate catalog, and the Wisconsin Department of Safety and Professional Services. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMSN)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dane County Regional Airport (KMSN) is the official NOAA reference station for Madison. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014837), Madison records an &lt;strong&gt;annual mean temperature of 47.0&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.5&amp;deg;F&lt;/strong&gt; against an annual minimum of 37.6&amp;deg;F, approximately &lt;strong&gt;7,138.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;627.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;37.13 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;51.8 inches&lt;/strong&gt;. The roughly 11:1 HDD-to-CDD ratio puts Madison among the most heating-dominated HVAC markets in the Upper Midwest &amp;mdash; equipment sizing, fuel choice, and cold-climate heat pump considerations all flow from this asymmetry.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:48000&amp;amp;in=state:55" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Madison city, Wisconsin) report &lt;strong&gt;125,787 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1979&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;67.8% utility natural gas&lt;/strong&gt; (85,281 units), &lt;strong&gt;28.4% electricity&lt;/strong&gt; (35,768 units), 1,992 units on bottled/tank/LP gas, and 413 on fuel oil or kerosene. Natural gas furnaces dominate the installed base, so AFUE upgrades and gas-side rebates carry meaningful weight here. The 28% electric share also reflects substantial multifamily and electric-resistance stock that is candidate territory for cold-climate heat pump conversion.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump &amp;amp; Snowfall Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energystar.gov/products/heating_cooling/heat_pumps_air_source/key_product_criteria" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Version 6.2 Heat Pump Final Specification&lt;/a&gt;, the Cold Climate designation requires a heat pump to deliver a &lt;strong&gt;COP of at least 1.75 at 5&amp;deg;F&lt;/strong&gt; and retain &lt;strong&gt;at least 70% of its 47&amp;deg;F rated heating capacity at 5&amp;deg;F&lt;/strong&gt;. Madison&amp;rsquo;s 7,138.2 HDD profile and recurring sub-zero winter extremes make the Cold Climate spec the practical floor for any heat pump considered here. The 51.8-inch annual snowfall normal also drives outdoor unit clearance and defrost-cycle planning &amp;mdash; condensers benefit from elevated mounting (typically 12&amp;ndash;24 inches above grade) and clear winter access for service.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Wisconsin Focus on Energy Rebates (Statewide Administrator)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wisconsin&amp;rsquo;s statewide energy-efficiency utility, &lt;a href="https://focusonenergy.com/residential/heating-and-cooling" target="_blank" rel="nofollow noopener"&gt;Focus on Energy&lt;/a&gt;, administers residential HVAC rebates that apply to Madison Gas and Electric (MGE) customers. Current air-source heat pump instant discounts are tiered by efficiency: &lt;strong&gt;Tier 1 (SEER2 15.2 / HSPF2 8.1) = $400 standard / $600 income-qualified&lt;/strong&gt;, &lt;strong&gt;Tier 2 (SEER2 15.2 / HSPF2 8.5) = $500 / $700&lt;/strong&gt;, &lt;strong&gt;Tier 3 (SEER2 16.0 / HSPF2 9.0) = $600 / $800&lt;/strong&gt;, and &lt;strong&gt;Tier 4 (SEER2 16.0 / HSPF2 10.0) = $700 / $900&lt;/strong&gt;. Certified geothermal heat pump rebates are &lt;strong&gt;$1,000&lt;/strong&gt; for homes with natural gas service and &lt;strong&gt;$750&lt;/strong&gt; without. These pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Wisconsin HVAC Contractor Registration&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://dsps.wi.gov/Pages/Professions/HVACContractor/Default.aspx" target="_blank" rel="nofollow noopener"&gt;Wisconsin Department of Safety and Professional Services (DSPS)&lt;/a&gt;, &amp;ldquo;no person, entity or business may engage or offer to engage in installing or servicing heating, ventilating or air conditioning equipment unless the person, entity or business holds a registration issued by the Department.&amp;rdquo; Owner-occupants servicing HVAC equipment in their own residence are exempt. All initial applications, reinstatements, and renewals are submitted through Wisconsin&amp;rsquo;s online licensing portal at license.wi.gov. DSPS can be reached at (608) 266-2112 or (877) 617-1565.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Madison are set by the City of Madison Building Inspection Division. The current published fee schedule could not be retrieved verbatim at the time this page was authored; for current mechanical permit fees, contact Building Inspection at (608) 266-4551 or binspection@cityofmadison.com.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit is non-refundable and stacks with Focus on Energy rebates.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8946,6 +8982,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the Nevada State Contractors Board, and U.S. Department of Energy guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KRNO)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Reno-Tahoe International Airport (KRNO) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023185), Reno records an &lt;strong&gt;annual mean temperature of 55.0&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 68.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 41.1&amp;deg;F, approximately &lt;strong&gt;4,669.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,038.3 cooling degree days&lt;/strong&gt;, an annual snowfall normal of &lt;strong&gt;20.9 inches&lt;/strong&gt;, and an exceptionally low &lt;strong&gt;annual precipitation normal of just 7.35 inches&lt;/strong&gt;. Reno sits in DOE Climate Zone 5B (cool-dry) at roughly 4,500 ft elevation in the Sierra Nevada rain shadow &amp;mdash; one of the driest cities its size in the United States.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:60600&amp;amp;in=state:32" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Reno city, Nevada) report &lt;strong&gt;112,061 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1989&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;57.6% utility natural gas&lt;/strong&gt; (64,510 units), &lt;strong&gt;37.4% electricity&lt;/strong&gt; (41,937 units), 1,802 units on fuel oil or kerosene, and 1,742 on bottled/tank/LP gas. The relatively high electric share (37%) reflects Reno&amp;rsquo;s substantial newer condo and multifamily stock and creates meaningful heat-pump conversion opportunity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Sierra Nevada Rain-Shadow &amp;amp; Evaporative Cooling&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.energy.gov/energysaver/evaporative-coolers" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, &amp;ldquo;evaporative coolers, sometimes called swamp coolers, are an energy-efficient alternative to air conditioners in areas where the humidity is low.&amp;rdquo; Reno&amp;rsquo;s 7.35-inch annual precipitation and Climate Zone 5B cool-dry designation put it among the most evaporative-cooler-friendly major-city climates in the country. Dramatic diurnal temperature swings (cool nights even in summer) also make night-flush ventilation strategies and whole-house fans particularly effective supplements to conventional AC. Conversely, dry winter air supports humidification considerations on the heating side.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Nevada HVAC Contractor Licensing (NSCB C-21)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://nscb.nv.gov/contractors/license-classifications/" target="_blank" rel="nofollow noopener"&gt;Nevada State Contractors Board (NSCB) license classifications&lt;/a&gt; issued under Nevada Administrative Code Chapter 624, HVAC work statewide &amp;mdash; including in Reno &amp;mdash; requires the &lt;strong&gt;C-21 Refrigeration and Air Conditioning&lt;/strong&gt; classification. Verify a specific contractor&amp;rsquo;s current C-21 license status on the NSCB public lookup before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NV Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NV Energy administers the PowerShift residential rebate program for its northern-Nevada service territory. Current line-item rebate dollar amounts for Reno could not be retrieved verbatim at the time this page was authored; contact NV Energy directly or check the NV Energy PowerShift page for the current Reno-area heat pump, smart thermostat, and central AC incentive amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Local Code&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Reno are set by the City of Reno Community Development Department. The current published fee schedule could not be retrieved verbatim at the time this page was authored; contact Community Development directly for the current mechanical permit fee schedule. Reno enforces the Nevada-adopted International Mechanical Code as the baseline mechanical standard.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9027,6 +9082,25 @@
       <c r="Q97" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the Code of Virginia, and the City of Richmond Department of Public Utilities. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KRIC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Richmond International Airport (KRIC) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013740), Richmond records an &lt;strong&gt;annual mean temperature of 59.0&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 69.5&amp;deg;F&lt;/strong&gt; against an annual minimum of 48.4&amp;deg;F, approximately &lt;strong&gt;3,736.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,560.5 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;45.50 inches&lt;/strong&gt;, and a modest annual snowfall normal of &lt;strong&gt;8.8 inches&lt;/strong&gt;. Richmond sits in DOE Climate Zone 4A (mixed-humid). The roughly 2.4:1 HDD-to-CDD ratio plus 45 inches of precipitation makes summer latent (humidity) load &amp;mdash; not just sensible-heat load &amp;mdash; a primary sizing factor here.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:51" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Richmond city, Virginia) report &lt;strong&gt;102,145 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1959&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;59.4% electricity&lt;/strong&gt; (60,676 units), &lt;strong&gt;33.9% utility natural gas&lt;/strong&gt; (34,629 units), &lt;strong&gt;3.8% fuel oil or kerosene&lt;/strong&gt; (3,854 units), and 1,304 on bottled/tank/LP gas. Richmond&amp;rsquo;s electricity-majority heating profile is unusual for a Mid-Atlantic city &amp;mdash; consistent with Zone 4A loads that favor heat-pump primary heat &amp;mdash; and the persistent fuel-oil share (nearly 4%) reflects historic-district housing stock predating modern building-code envelope standards.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Municipal Natural Gas Utility&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Richmond is one of the few U.S. cities that operates its own municipal natural gas utility. According to the &lt;a href="https://www.rva.gov/public-utilities" target="_blank" rel="nofollow noopener"&gt;City of Richmond Department of Public Utilities&lt;/a&gt;, &amp;ldquo;The City of Richmond Department of Public Utilities provides natural gas, water, wastewater and stormwater services to more than 500,000 customers in the Richmond metropolitan area.&amp;rdquo; This means Richmond gas customers contract with the City directly rather than with a private investor-owned utility &amp;mdash; a structural difference relevant to billing, service, and any locally administered conservation programs.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate Considerations (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads in addition to sensible cooling loads. Properly sized cooling equipment with adequate dehumidification capability is essential; oversizing AC capacity actually worsens humidity control by short-cycling before the system can pull moisture from the air. Richmond&amp;rsquo;s 1,560.5 CDD profile combined with 45.50 inches of annual precipitation makes Manual J load calculations and variable-speed equipment particularly valuable in retrofit work on the city&amp;rsquo;s historic-district housing.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Virginia Contractor Licensing (DPOR Class A/B/C with HVA Specialty)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://law.lis.virginia.gov/vacode/title54.1/chapter11/section54.1-1100/" target="_blank" rel="nofollow noopener"&gt;Code of Virginia Section 54.1-1100&lt;/a&gt;, the Virginia Department of Professional and Occupational Regulation (DPOR) Board for Contractors issues three license classes by contract value: &lt;strong&gt;Class A &amp;mdash; single contracts of $150,000 or more, or $1 million or more in a 12-month period&lt;/strong&gt;; &lt;strong&gt;Class B &amp;mdash; single contracts of $30,000 or more but less than $150,000, or $250,000 or more but less than $1 million annually&lt;/strong&gt;; and &lt;strong&gt;Class C &amp;mdash; single contracts over $1,000 but less than $30,000, and less than $250,000 annually&lt;/strong&gt;. HVAC contractors typically hold the &lt;strong&gt;HVA (Heating, Ventilation and Air Conditioning Contracting)&lt;/strong&gt; specialty designation under one of these classes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Utility Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Richmond are set by the Richmond Department of Planning &amp;amp; Development Review (PDR). The current published fee schedule could not be retrieved verbatim at the time this page was authored; contact PDR at (804) 646-6304 for the current mechanical permit fee schedule. Dominion Energy Virginia administers electric residential rebates for Richmond customers; current rebate dollar amounts should be verified directly on the Dominion Energy Virginia home rebates page.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11674,6 +11748,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the National Weather Service Wichita Forecast Office, and federal tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KICT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wichita Dwight D. Eisenhower National Airport (KICT) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003928), Wichita records an &lt;strong&gt;annual mean temperature of 57.7&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 68.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 46.5&amp;deg;F, approximately &lt;strong&gt;4,413.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,773.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;34.31 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;12.7 inches&lt;/strong&gt;. Wichita&amp;rsquo;s roughly 2.5:1 HDD-to-CDD ratio reflects a genuine dual-load climate &amp;mdash; significant heating and significant cooling demand &amp;mdash; rather than the heating-dominant or cooling-dominant patterns seen in the Upper Midwest or Sun Belt.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:79000&amp;amp;in=state:20" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Wichita city, Kansas) report &lt;strong&gt;157,646 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;68.9% utility natural gas&lt;/strong&gt; (108,608 units), &lt;strong&gt;28.9% electricity&lt;/strong&gt; (45,589 units), 2,051 units on bottled/tank/LP gas, 325 on wood, and 123 on fuel oil. Natural gas dominance combined with mid-1970s median housing age makes furnace AFUE upgrades and air-sealing/insulation work particularly impactful here.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tornado Alley &amp;amp; Severe-Weather Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.weather.gov/ict/Climate" target="_blank" rel="nofollow noopener"&gt;NOAA NWS Wichita Forecast Office Local Climate Page&lt;/a&gt;, the south-central Kansas region is subject to documented EF5 tornado history (the office maintains a published &amp;ldquo;Kansas EF5 Tornadoes&amp;rdquo; climatology) and major ice-storm events (the office&amp;rsquo;s &amp;ldquo;Worst Kansas Ice Storms&amp;rdquo; record documents impacts on the region). Combined with high summer cooling load (1,773.6 CDD), this means outdoor condensers in the Wichita area face both heavy summer demand and documented physical risk from hail and ice events &amp;mdash; a factor in equipment placement, hail-guard specification, and surge-protection planning.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kansas HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kansas does not issue a statewide HVAC contractor license. Local mechanical contractor licensing for the Wichita metropolitan area is administered by the Sedgwick County Metropolitan Area Building and Construction Department (MABCD), a joint City of Wichita / Sedgwick County authority. Verify a specific contractor&amp;rsquo;s current MABCD license status before contracting; permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Local Code&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Wichita are set by Sedgwick County MABCD. The current published fee schedule could not be retrieved verbatim at the time this page was authored; contact MABCD directly for the current mechanical permit fee schedule. Because Kansas does not adopt a statewide residential energy code, the locally adopted IMC/IRC/IECC editions are set by MABCD; confirm the currently adopted editions with MABCD before plan-design work.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Evergy (electric) and Kansas Gas Service (natural gas) are the primary residential utilities in the Wichita area. Current line-item HVAC rebate dollar amounts could not be retrieved verbatim at the time this page was authored; contact Evergy and Kansas Gas Service directly for the current heat pump, central AC, smart thermostat, and gas furnace rebate amounts in your service territory.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit is non-refundable.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -788,6 +788,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KABE)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lehigh Valley International Airport (KABE) is the official NOAA reference station for the Allentown area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014737), Allentown records an &lt;strong&gt;annual mean temperature of 53.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 63.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 42.8&amp;deg;F, approximately &lt;strong&gt;5,292.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;981.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;47.36 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;33.1 inches&lt;/strong&gt;. The roughly 5.4:1 HDD-to-CDD ratio makes Allentown a firmly heating-dominant market, but the nearly 1,000 CDD means properly sized cooling capacity is essential for summer comfort.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:02000&amp;amp;in=state:42" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Allentown city, Pennsylvania) report &lt;strong&gt;46,039 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;44.4% utility natural gas&lt;/strong&gt; (20,459 units), &lt;strong&gt;39.4% electricity&lt;/strong&gt; (18,123 units), and notably &lt;strong&gt;14.0% fuel oil or kerosene&lt;/strong&gt; (6,436 units), with 627 on bottled/tank/LP gas. The 14% fuel-oil share is one of the highest of any project city &amp;mdash; a legacy of the Lehigh Valley&amp;rsquo;s industrial-era housing stock (median 1951). Fuel-oil-to-heat-pump conversion represents a significant upgrade opportunity in these older homes, typically delivering both comfort improvement and long-term fuel-cost reduction.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Fuel Oil Legacy &amp;amp; Heat Pump Conversion Opportunity&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, modern air-source heat pumps operating in Zone 5A climates can deliver heating at a coefficient of performance (COP) materially above 1.0 across most of the heating season, meaning they consume less energy than the fuel-oil boilers they replace. Allentown&amp;rsquo;s 5,292.6 HDD profile and 33.1 inches of annual snowfall do require cold-climate-rated equipment (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F), and the 1951 median housing age means envelope upgrades (insulation, air sealing, window replacement) frequently accompany heat-pump installation for best results.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pennsylvania Contractor Registration (PAHIC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pennsylvania does not issue a statewide HVAC-specific license. Instead, contractors performing home improvement work &amp;mdash; including HVAC installation &amp;mdash; must hold a &lt;strong&gt;PA Home Improvement Contractor Registration (PAHIC number)&lt;/strong&gt; issued by the Pennsylvania Attorney General&amp;rsquo;s Bureau of Consumer Protection. Verify a specific contractor&amp;rsquo;s current PAHIC registration before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;PPL Electric Utilities Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;PPL Electric Utilities administers residential heat pump rebates for its Allentown service territory. Contact PPL Electric directly or visit the PPL Electric savings programs page for the current heat pump, smart thermostat, and central AC rebate amounts in your service area. PPL rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Allentown are set by the Allentown Bureau of Building Standards &amp;amp; Safety. Contact the Bureau directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit is non-refundable and stacks with PPL Electric rebates.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1149,6 +1168,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KAGS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Augusta Regional Airport / Bush Field (KAGS) is the official NOAA reference station for the area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003820), Augusta records an &lt;strong&gt;annual mean temperature of 65.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 77.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 53.0&amp;deg;F, approximately &lt;strong&gt;2,181.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,361.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;44.09 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.8 inches&lt;/strong&gt;. Augusta&amp;rsquo;s CDD exceeds its HDD &amp;mdash; making it a cooling-dominant market where air-conditioning sizing, SEER efficiency, and humidity control are the primary HVAC design drivers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:04204&amp;amp;in=state:13" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Augusta-Richmond County consolidated government, Georgia) report &lt;strong&gt;73,493 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1980&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.1% electricity&lt;/strong&gt; (42,678 units), &lt;strong&gt;39.3% utility natural gas&lt;/strong&gt; (28,848 units), and 1,197 on bottled/tank/LP gas. The electricity-majority heating profile is consistent with Augusta&amp;rsquo;s Zone 3A climate &amp;mdash; mild winters that favor heat-pump primary heat rather than dedicated gas furnaces.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate Considerations (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates like Augusta produce heavy summer latent (moisture) loads. With 2,361.3 CDD and 44.09 inches of annual precipitation, properly sized cooling equipment with adequate dehumidification capability is essential &amp;mdash; oversizing AC capacity actually worsens humidity control by short-cycling before the system can pull moisture from the air. Variable-speed compressors and properly matched indoor coils are particularly valuable in this climate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Georgia Conditioned Air Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia requires HVAC contractors to hold a &lt;strong&gt;Conditioned Air Contractor License&lt;/strong&gt; (Class I or Class II) issued by the Georgia Construction Industry Licensing Board under the Secretary of State. Class I permits unrestricted conditioned air work; Class II is limited to systems serving spaces of specified capacity. Verify a specific contractor&amp;rsquo;s current license status on the Georgia Secretary of State license lookup before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Georgia Power Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia Power administers the Home Energy Improvement Program (HEIP) for residential customers in the Augusta area. Contact Georgia Power directly or visit the Georgia Power residential rebates page for the current heat pump, smart thermostat, and central AC rebate amounts. Georgia Power rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Augusta-Richmond County are set by the Augusta-Richmond County Planning &amp;amp; Development Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1504,6 +1542,25 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBTR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Baton Rouge Metropolitan Airport / Ryan Field (KBTR) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013970), Baton Rouge records an &lt;strong&gt;annual mean temperature of 68.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 78.9&amp;deg;F&lt;/strong&gt; against an annual minimum of 58.0&amp;deg;F, approximately &lt;strong&gt;1,533.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,818.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;61.94 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.2 inches&lt;/strong&gt;. The 1.8:1 CDD-to-HDD ratio makes Baton Rouge a firmly cooling-dominant market. The 61.94-inch precipitation total is among the highest of any project city &amp;mdash; that volume of moisture drives extreme latent cooling loads and makes dehumidification a primary sizing factor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:05000&amp;amp;in=state:22" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Baton Rouge city, Louisiana) report &lt;strong&gt;87,607 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1975&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;66.4% electricity&lt;/strong&gt; (58,159 units), &lt;strong&gt;31.5% utility natural gas&lt;/strong&gt; (27,571 units), and 758 on bottled/tank/LP gas. The two-thirds electric share reflects the climate reality: with only 1,533.5 HDD, the heating load is light enough that heat pumps and electric resistance handle it efficiently without a dedicated gas furnace.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hot-Humid Climate &amp;amp; Hurricane Exposure (Zone 2A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates produce extreme latent cooling loads. Baton Rouge&amp;rsquo;s combination of 2,818.4 CDD and 61.94 inches of annual precipitation means air conditioning systems run near-continuously from May through September, and dehumidification &amp;mdash; not just sensible cooling &amp;mdash; is the dominant comfort variable. Variable-speed compressor systems with enhanced dehumidification modes are particularly effective here. Hurricane exposure also means outdoor condenser placement and tie-down are practical considerations &amp;mdash; elevated, anchored pad mounts reduce storm-surge and flood-debris risk.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana HVAC Contractor Licensing (LSLBC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisiana requires HVAC contractors to hold a &lt;strong&gt;Mechanical Work Contractor License&lt;/strong&gt; issued by the Louisiana State Licensing Board for Contractors (LSLBC). The LSLBC administers examinations and issues licenses for mechanical contracting statewide. Verify a specific contractor&amp;rsquo;s current LSLBC license status before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Louisiana Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Louisiana administers residential energy efficiency programs for its Baton Rouge service territory. Contact Entergy Louisiana directly or visit the Entergy Louisiana save-money page for the current heat pump, smart thermostat, and central AC rebate amounts. Entergy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Baton Rouge are set by the East Baton Rouge Parish Permits &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2047,6 +2104,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBDR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Sikorsky Memorial Airport (KBDR) is the official NOAA reference station for Bridgeport. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014707), Bridgeport records an &lt;strong&gt;annual mean temperature of 51.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 59.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 43.5&amp;deg;F, approximately &lt;strong&gt;5,520.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;608.0 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;39.31 inches&lt;/strong&gt;. The roughly 9:1 HDD-to-CDD ratio makes Bridgeport a heavily heating-dominant market &amp;mdash; equipment sizing, furnace AFUE efficiency, and building envelope performance are the primary HVAC design drivers. Bridgeport&amp;rsquo;s Long Island Sound coastal location moderates winter extremes relative to inland Connecticut but adds salt-air corrosion considerations for outdoor equipment.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:08000&amp;amp;in=state:09" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Bridgeport city, Connecticut) report &lt;strong&gt;55,498 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1954&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;59.0% utility natural gas&lt;/strong&gt; (32,771 units), &lt;strong&gt;20.3% electricity&lt;/strong&gt; (11,248 units), &lt;strong&gt;13.9% fuel oil or kerosene&lt;/strong&gt; (7,742 units), and &lt;strong&gt;4.2% bottled/tank/LP gas&lt;/strong&gt; (2,348 units). The nearly 14% fuel-oil share and 4% LP gas share are hallmarks of Connecticut&amp;rsquo;s historic Northeast housing stock (median 1954). Fuel-oil-to-heat-pump conversion is a major upgrade opportunity in these older homes &amp;mdash; many still run oil-fired boilers or furnaces installed decades ago.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Northeast Fuel-Oil Legacy &amp;amp; Conversion Economics&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, modern cold-climate air-source heat pumps can deliver heating at a coefficient of performance (COP) materially above 1.0 across most of the heating season, making them competitive with fuel-oil heating on a per-BTU cost basis in most Northeast markets. Bridgeport&amp;rsquo;s 5,520.8 HDD profile requires cold-climate-rated equipment, and the 1954 median housing age means envelope upgrades (insulation, air sealing, window replacement) frequently accompany heat-pump installation for best results. The coastal location also means outdoor condensers should be specified with corrosion-resistant coatings to handle salt-air exposure.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Connecticut Contractor Licensing (DCP)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Connecticut requires HVAC contractors to hold a &lt;strong&gt;Heating, Piping and Cooling Contractor License&lt;/strong&gt; (or an appropriate journeyperson license) issued by the Connecticut Department of Consumer Protection (DCP). The DCP administers examinations and issues licenses for mechanical contracting statewide. Verify a specific contractor&amp;rsquo;s current DCP license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energize CT / United Illuminating Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize CT, in partnership with United Illuminating (UI), administers residential heat pump rebates for Bridgeport customers. Contact Energize CT or United Illuminating directly for the current heat pump and smart thermostat rebate amounts in your service area. Energize CT rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Bridgeport are set by the City of Bridgeport Building Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2128,6 +2204,25 @@
       <c r="Q19" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBRO)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Brownsville / South Padre Island International Airport (KBRO) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012919), Brownsville records an &lt;strong&gt;annual mean temperature of 76.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 85.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 67.1&amp;deg;F, approximately &lt;strong&gt;422.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;4,542.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;26.78 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.0 inches&lt;/strong&gt;. The &lt;strong&gt;10.7:1 CDD-to-HDD ratio is the most cooling-dominant of any project city&lt;/strong&gt; &amp;mdash; Brownsville&amp;rsquo;s subtropical Rio Grande Valley climate means air conditioning runs near-continuously from April through October, and heating demand is minimal.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:10768&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Brownsville city, Texas) report &lt;strong&gt;58,518 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1993&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;89.9% electricity&lt;/strong&gt; (52,614 units), &lt;strong&gt;7.7% utility natural gas&lt;/strong&gt; (4,512 units), and 725 homes using no fuel at all. The &lt;strong&gt;nearly 90% electric heating share is the highest of any project city&lt;/strong&gt; &amp;mdash; a direct reflection of the subtropical climate where the &amp;ldquo;heating system&amp;rdquo; is typically just the heat pump&amp;rsquo;s reverse cycle running a few dozen hours per winter. The relatively young housing stock (median 1993) means most homes were built under modern energy codes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Cooling Dominance &amp;amp; Hurricane Exposure (Zone 2A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates require HVAC systems optimized primarily for cooling and dehumidification. With 4,542.2 CDD and only 422.8 HDD, Brownsville&amp;rsquo;s HVAC loads are almost entirely cooling. High SEER2 efficiency is the dominant cost driver &amp;mdash; even a 1-point SEER improvement produces larger annual savings here than in any other climate zone due to the sheer number of cooling hours. Hurricane exposure along the Gulf Coast means outdoor condenser placement, tie-down, and wind-debris protection are practical considerations.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Brownsville PUB (Municipal Electric Utility)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Brownsville is served by the &lt;strong&gt;Brownsville Public Utilities Board (PUB)&lt;/strong&gt; &amp;mdash; a city-owned municipal electric utility. This means Brownsville electric customers contract with the City directly rather than with a private investor-owned utility or a deregulated retail electricity provider. The PUB administers its own residential HVAC rebate program; contact Brownsville PUB directly for the current heat pump and central AC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas HVAC Contractor Licensing (TDLR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Texas requires HVAC contractors to hold an &lt;strong&gt;Air Conditioning and Refrigeration Contractor License&lt;/strong&gt; issued by the Texas Department of Licensing and Regulation (TDLR). The TDLR administers examinations and issues licenses for ACR contracting statewide. Verify a specific contractor&amp;rsquo;s current TDLR license status before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Brownsville are set by the City of Brownsville Building Inspections Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -2584,6 +2584,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCHA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lovell Field (KCHA) is the official NOAA reference station for Chattanooga. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013882), Chattanooga records an &lt;strong&gt;annual mean temperature of 61.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.2&amp;deg;F&lt;/strong&gt; against an annual minimum of 51.5&amp;deg;F, approximately &lt;strong&gt;3,029.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,920.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;55.00 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;3.6 inches&lt;/strong&gt;. The roughly 1.6:1 HDD-to-CDD ratio reflects a genuine dual-load climate in the Tennessee Valley &amp;mdash; meaningful heating and cooling demand throughout the year. The 55-inch precipitation total also drives significant summer latent (humidity) loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Chattanooga city, Tennessee) report &lt;strong&gt;77,916 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1975&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.9% electricity&lt;/strong&gt; (56,831 units), &lt;strong&gt;25.2% utility natural gas&lt;/strong&gt; (19,607 units), and 739 on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories, where historically affordable hydroelectric power made electric resistance and heat-pump heating economically competitive with gas.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: EPB Municipal Utility (TVA Distributor)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Chattanooga&amp;rsquo;s electric service is provided by the &lt;strong&gt;Electric Power Board (EPB)&lt;/strong&gt;, a municipally owned utility that distributes TVA power. EPB is nationally recognized for its community-wide fiber-optic network and smart-grid infrastructure. EPB / TVA EnergyRight administers residential HVAC rebates; contact EPB directly or visit the TVA EnergyRight page for the current heat pump and smart thermostat rebate amounts. Municipal utility status means Chattanooga electric customers contract with the City rather than with a private investor-owned utility.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate Considerations (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Chattanooga&amp;rsquo;s combination of 1,920.6 CDD and 55.00 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems with enhanced dehumidification modes are particularly effective in the Tennessee Valley&amp;rsquo;s humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License (CMC-C)&lt;/strong&gt; issued by the Tennessee Board for Licensing Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Chattanooga are set by the City of Chattanooga Land Development Office. Contact the Office directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3475,6 +3494,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KDAY)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;James M. Cox Dayton International Airport (KDAY) is the official NOAA reference station for Dayton. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093815), Dayton records an &lt;strong&gt;annual mean temperature of 53.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 63.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 44.5&amp;deg;F, approximately &lt;strong&gt;5,149.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,153.9 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;41.33 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;25.0 inches&lt;/strong&gt;. The roughly 4.5:1 HDD-to-CDD ratio makes Dayton a firmly heating-dominant market, but the 1,154 CDD means summer cooling capacity remains important.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:21000&amp;amp;in=state:39" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Dayton city, Ohio) report &lt;strong&gt;57,953 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.2% utility natural gas&lt;/strong&gt; (40,099 units), &lt;strong&gt;28.1% electricity&lt;/strong&gt; (16,259 units), and 634 on bottled/tank/LP gas. The strong gas dominance combined with very old housing stock (median 1951) makes furnace AFUE upgrades, ductwork remediation, and air-sealing work particularly impactful in Dayton &amp;mdash; many homes still operate gas furnaces and duct systems installed decades ago.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Older Housing Stock &amp;amp; Upgrade Economics&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, homes built before modern insulation and air-sealing standards (Dayton&amp;rsquo;s median year built 1951 predates these by decades) typically benefit from a whole-house approach: envelope improvements (insulation, air sealing, window upgrades) paired with HVAC equipment replacement. In Dayton&amp;rsquo;s 5,149.2 HDD climate with 25.0 inches of annual snowfall, cold-climate heat pump specification and proper outdoor unit clearance are practical considerations for any heat-pump conversion.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio HVAC Contractor Licensing (OCILB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ohio requires HVAC contractors to hold an &lt;strong&gt;HVAC Contractor License&lt;/strong&gt; issued by the Ohio Construction Industry Licensing Board (OCILB). The OCILB administers examinations and issues licenses for HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current OCILB license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;AES Ohio (formerly Dayton Power &amp;amp; Light) is the primary electric utility for the Dayton area. Current xlsx data indicates no active HVAC rebate program from AES Ohio at the time of research. Contact AES Ohio directly to verify whether any residential HVAC incentives have been introduced. Any utility rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Dayton are set by the City of Dayton Building Inspection Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3660,6 +3698,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KDSM)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Des Moines International Airport (KDSM) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014933), Des Moines records an &lt;strong&gt;annual mean temperature of 50.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 60.5&amp;deg;F&lt;/strong&gt; against an annual minimum of 41.3&amp;deg;F, approximately &lt;strong&gt;6,177.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,070.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;36.55 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;36.5 inches&lt;/strong&gt;. The roughly 5.8:1 HDD-to-CDD ratio makes Des Moines a heavily heating-dominant market. The 36.5-inch annual snowfall drives outdoor equipment clearance and defrost-cycle planning considerations for any heat-pump installation.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:21000&amp;amp;in=state:19" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Des Moines city, Iowa) report &lt;strong&gt;90,085 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1960&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.3% utility natural gas&lt;/strong&gt; (57,066 units), &lt;strong&gt;33.6% electricity&lt;/strong&gt; (30,281 units), and 1,319 on bottled/tank/LP gas. The gas-dominant heating mix combined with 1960 median housing age means furnace AFUE upgrades and envelope improvements (insulation, air sealing) are high-impact investments in Des Moines.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Des Moines&amp;rsquo;s 6,177.7 HDD profile and documented sub-zero winter extremes require cold-climate-rated heat pumps for any gas-to-electric conversion. The ENERGY STAR Cold Climate designation (COP &amp;ge; 1.75 at 5&amp;deg;F, retaining &amp;ge; 70% of rated heating capacity at 5&amp;deg;F) is the practical floor for heat pump specification in central Iowa. The 36.5-inch snowfall normal means outdoor condensers benefit from elevated mounting (12&amp;ndash;24 inches above grade) and clear winter access for service.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Iowa HVAC Contractor Licensing (DIAL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Iowa requires mechanical contractors to hold a &lt;strong&gt;Mechanical Contractor License&lt;/strong&gt; issued by the Iowa Division of Insurance, Audit, and Licensing (DIAL). The DIAL administers examinations and issues licenses for mechanical/HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current DIAL license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;MidAmerican Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;MidAmerican Energy administers residential home energy discounts and rebates for its Des Moines service territory. Contact MidAmerican Energy directly or visit the MidAmerican Energy home rebates page for the current heat pump, smart thermostat, and central AC rebate amounts. MidAmerican rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Des Moines are set by the City of Des Moines Permit and Development Center. Contact the Center directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4019,6 +4076,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KEUG)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mahlon Sweet Field (KEUG) is the official NOAA reference station for Eugene. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024221), Eugene records an &lt;strong&gt;annual mean temperature of 53.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 64.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 41.9&amp;deg;F, approximately &lt;strong&gt;4,615.8 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;292.8 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;40.83 inches&lt;/strong&gt;. The roughly &lt;strong&gt;15.8:1 HDD-to-CDD ratio&lt;/strong&gt; is among the most heating-dominant in the entire project &amp;mdash; Eugene&amp;rsquo;s Willamette Valley marine climate (Zone 4C) produces mild but extended heating seasons and very little summer cooling demand. This means HVAC investment should be weighted overwhelmingly toward heating efficiency.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:23850&amp;amp;in=state:41" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Eugene city, Oregon) report &lt;strong&gt;76,140 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1979&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.8% electricity&lt;/strong&gt; (56,998 units), &lt;strong&gt;22.2% utility natural gas&lt;/strong&gt; (16,941 units), and &lt;strong&gt;1.1% wood&lt;/strong&gt; (851 units). Eugene&amp;rsquo;s exceptionally high electric heating share &amp;mdash; nearly three-quarters of homes &amp;mdash; reflects the Pacific Northwest&amp;rsquo;s historically affordable hydroelectric power and EWEB&amp;rsquo;s municipal rates. This makes Eugene prime heat-pump territory: converting electric resistance heat to heat-pump heat can cut heating energy use by 50&amp;ndash;70% with no fuel-switching required.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: EWEB Municipal Utility &amp;amp; Marine Climate (Zone 4C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Eugene&amp;rsquo;s electric service is provided by the &lt;strong&gt;Eugene Water &amp;amp; Electric Board (EWEB)&lt;/strong&gt;, a municipally owned utility. EWEB administers its own residential energy efficiency rebates. Contact EWEB directly for the current heat pump, ductless mini-split, and smart thermostat rebate amounts. Eugene&amp;rsquo;s Zone 4C mixed-marine climate is distinctive &amp;mdash; the Willamette Valley&amp;rsquo;s mild, damp winters produce moderate but sustained heating loads (4,615.8 HDD) without the extreme cold-snap risk of continental climates. This means standard air-source heat pumps (not necessarily cold-climate rated) perform well here year-round.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Oregon HVAC Contractor Licensing (CCB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oregon requires HVAC contractors to hold an &lt;strong&gt;HVAC Specialty Contractor license&lt;/strong&gt; issued by the Oregon Construction Contractors Board (CCB). The CCB administers licensing for all construction-related trades statewide. Verify a specific contractor&amp;rsquo;s current CCB license status before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Eugene are set by the City of Eugene Building &amp;amp; Permit Services. Contact Building &amp;amp; Permit Services directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit stacks with EWEB residential rebates.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4178,6 +4252,25 @@
       <c r="Q41" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFAY)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fayetteville Regional Airport (KFAY) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013722), Fayetteville records an &lt;strong&gt;annual mean temperature of 61.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.0&amp;deg;F&lt;/strong&gt; against an annual minimum of 50.5&amp;deg;F, approximately &lt;strong&gt;3,153.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,804.5 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;46.07 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;5.2 inches&lt;/strong&gt;. The roughly 1.7:1 HDD-to-CDD ratio reflects a dual-load climate in the North Carolina Sandhills &amp;mdash; significant heating and significant cooling demand, with 46 inches of precipitation driving meaningful summer humidity loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:22920&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Fayetteville city, North Carolina) report &lt;strong&gt;81,499 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1983&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.8% electricity&lt;/strong&gt; (59,334 units), &lt;strong&gt;22.9% utility natural gas&lt;/strong&gt; (18,652 units), and &lt;strong&gt;2.5% bottled/tank/LP gas&lt;/strong&gt; (2,050 units). The strong electric-heating majority reflects Zone 3A&amp;rsquo;s mild winters that favor heat-pump primary heat. The 1983 median housing age and significant military-affiliated housing stock (proximity to Fort Liberty, formerly Fort Bragg) shape local demand patterns.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate &amp;amp; Dehumidification (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Fayetteville&amp;rsquo;s combination of 1,804.5 CDD and 46.07 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential &amp;mdash; oversizing AC capacity worsens humidity control by short-cycling. Variable-speed compressor systems are particularly valuable in the Sandhills&amp;rsquo; humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Carolina requires HVAC contractors to hold a &lt;strong&gt;Heating Contractor License&lt;/strong&gt; (H-1, H-2, or H-3 classification depending on scope) issued by the North Carolina Board of Examiners of Plumbing, Heating and Fire Sprinkler Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Progress Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Progress administers the Smart $aver residential rebate program for its Fayetteville service territory. Contact Duke Energy Progress directly or visit the Duke Energy Smart $aver page for the current heat pump, smart thermostat, and central AC rebate amounts. Duke Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fayetteville are set by the City of Fayetteville Permitting &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -4434,6 +4434,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFWA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fort Wayne International Airport (KFWA) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014827), Fort Wayne records an &lt;strong&gt;annual mean temperature of 50.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 60.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 41.4&amp;deg;F, approximately &lt;strong&gt;5,967.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;849.1 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.48 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;33.6 inches&lt;/strong&gt;. The roughly 7:1 HDD-to-CDD ratio makes Fort Wayne a heavily heating-dominant market where furnace efficiency, building envelope performance, and snow clearance around outdoor equipment are the primary HVAC design drivers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:25000&amp;amp;in=state:18" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fort Wayne city, Indiana) report &lt;strong&gt;109,604 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1971&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;70.7% utility natural gas&lt;/strong&gt; (77,492 units), &lt;strong&gt;26.9% electricity&lt;/strong&gt; (29,499 units), and 1,455 on bottled/tank/LP gas. The strong gas dominance and early-1970s housing stock mean furnace AFUE upgrades and ductwork remediation are high-impact investments.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations (Zone 5A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Fort Wayne&amp;rsquo;s 5,967.7 HDD profile and 33.6 inches of annual snowfall require cold-climate-rated heat pumps for any gas-to-electric conversion. Outdoor condensers benefit from elevated mounting (12&amp;ndash;24 inches above grade) and clear winter access for service. The 1971 median housing age means many homes may benefit from envelope improvements alongside equipment upgrades.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Indiana HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Fort Wayne must obtain permits through the Fort Wayne Department of Planning Services. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting, and confirm they will pull the required local permits.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;I&amp;amp;M / AEP Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana Michigan Power (I&amp;amp;M), an AEP company, administers the Energy Savings Rebate Program for its Fort Wayne service territory. Contact I&amp;amp;M directly for the current heat pump, smart thermostat, and central AC rebate amounts. I&amp;amp;M rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fort Wayne are set by the Fort Wayne Department of Planning Services. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4943,6 +4962,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPHX)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Phoenix Sky Harbor International Airport (KPHX) is the nearest official NOAA reference station serving the Glendale area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023183), the Phoenix metro area records an &lt;strong&gt;annual mean temperature of 75.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 87.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 64.1&amp;deg;F, approximately &lt;strong&gt;874.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;4,764.6 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;7.22 inches&lt;/strong&gt;. The &lt;strong&gt;5.5:1 CDD-to-HDD ratio&lt;/strong&gt; makes Glendale one of the most cooling-dominant markets in the country. Air conditioning is not optional here &amp;mdash; it is a life-safety system during 100&amp;deg;F+ summer days.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:27820&amp;amp;in=state:04" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Glendale city, Arizona) report &lt;strong&gt;86,733 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1986&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;75.3% electricity&lt;/strong&gt; (65,359 units), &lt;strong&gt;21.2% utility natural gas&lt;/strong&gt; (18,423 units), &lt;strong&gt;782 homes using solar energy&lt;/strong&gt; (0.9%), and notably &lt;strong&gt;1,192 homes using no fuel at all&lt;/strong&gt; (1.4%). The electricity-dominant heating profile reflects the desert climate &amp;mdash; the &amp;ldquo;heating system&amp;rdquo; for most homes is simply the heat pump&amp;rsquo;s reverse cycle operating a modest number of winter hours. The solar share (782 homes) is among the highest raw counts in the project.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Heat &amp;amp; Cooling Load (Zone 2B Hot-Dry)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2B hot-dry climates like the Phoenix metro produce extreme sensible cooling loads. With 4,764.6 CDD and only 7.22 inches of annual precipitation, Glendale&amp;rsquo;s HVAC priorities center on cooling capacity, SEER2 efficiency, and attic ductwork protection. Even a 1-point SEER improvement produces larger annual savings here than in most other climate zones due to the sheer number of cooling hours. Unlike humid climates, latent (moisture) load is minimal &amp;mdash; the challenge is pure heat rejection.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Arizona HVAC Contractor Licensing (ROC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arizona requires HVAC contractors to hold an &lt;strong&gt;R-39 (residential) or C-39 (commercial) HVAC License&lt;/strong&gt; issued by the Arizona Registrar of Contractors (ROC). The ROC administers examinations and issues licenses for HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current ROC license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;APS Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arizona Public Service (APS) administers residential rebates and the Efficiency Arizona HEAR Program for its Glendale service territory. Contact APS directly for the current heat pump, smart thermostat, and central AC rebate amounts. APS rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Glendale are set by the City of Glendale Building Safety Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5104,6 +5142,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KGRR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Gerald R. Ford International Airport (KGRR) is the official NOAA reference station for Grand Rapids. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094860), Grand Rapids records an &lt;strong&gt;annual mean temperature of 49.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 58.2&amp;deg;F&lt;/strong&gt; against an annual minimum of 40.5&amp;deg;F, approximately &lt;strong&gt;6,408.0 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;732.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.40 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;77.6 inches&lt;/strong&gt;. The &lt;strong&gt;77.6-inch annual snowfall &amp;mdash; driven by Lake Michigan lake-effect weather &amp;mdash; is among the highest of any project city&lt;/strong&gt;. The roughly 8.8:1 HDD-to-CDD ratio makes Grand Rapids one of the most heating-dominant markets in the Midwest.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:34000&amp;amp;in=state:26" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Grand Rapids city, Michigan) report &lt;strong&gt;79,944 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1953&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;82.8% utility natural gas&lt;/strong&gt; (66,204 units), &lt;strong&gt;14.7% electricity&lt;/strong&gt; (11,740 units), and 1,320 on bottled/tank/LP gas. The &lt;strong&gt;82.8% gas share is among the highest in the project&lt;/strong&gt; &amp;mdash; reflecting west Michigan&amp;rsquo;s long winters and the dominance of gas furnaces in the installed base. The 1953 median housing age means many homes predate modern insulation and air-sealing standards.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lake-Effect Snow &amp;amp; HVAC Equipment Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Grand Rapids&amp;rsquo;s 6,408.0 HDD profile, 77.6 inches of annual lake-effect snowfall, and documented sub-zero winter extremes require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any gas-to-electric conversion. Outdoor condensers in lake-effect snow territory need elevated mounting (18&amp;ndash;24 inches above grade), clear defrost drainage, and winter access for service. Snow loads can bury ground-level equipment in sustained lake-effect events.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Michigan HVAC Contractor Licensing (LARA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Michigan requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License&lt;/strong&gt; issued by the Michigan Department of Licensing and Regulatory Affairs (LARA). The LARA administers examinations and issues licenses for mechanical contracting statewide. Verify a specific contractor&amp;rsquo;s current LARA license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Consumers Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Consumers Energy administers residential heating and cooling rebates for its Grand Rapids service territory. Contact Consumers Energy directly for the current heat pump, smart thermostat, and gas furnace rebate amounts. Consumers Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Grand Rapids are set by the City of Grand Rapids Development Center. Contact the Center directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5185,6 +5242,25 @@
       <c r="Q52" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBDL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bradley International Airport (KBDL) is the official NOAA reference station for the Hartford area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014740), Hartford records an &lt;strong&gt;annual mean temperature of 51.0&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 61.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 40.9&amp;deg;F, approximately &lt;strong&gt;5,883.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;819.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;47.05 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;51.7 inches&lt;/strong&gt;. The roughly 7.2:1 HDD-to-CDD ratio makes Hartford a heavily heating-dominant market. The 51.7-inch snowfall normal (Connecticut River valley nor&amp;rsquo;easters) drives outdoor equipment clearance and winter service access planning.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:09" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Hartford city, Connecticut) report &lt;strong&gt;49,023 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1953&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;65.8% utility natural gas&lt;/strong&gt; (32,251 units), &lt;strong&gt;23.3% electricity&lt;/strong&gt; (11,403 units), and &lt;strong&gt;7.0% fuel oil or kerosene&lt;/strong&gt; (3,449 units), with 983 on bottled/tank/LP gas. The 7% fuel-oil share is typical of Connecticut&amp;rsquo;s historic Northeast housing stock. Fuel-oil-to-heat-pump conversion remains a meaningful upgrade opportunity in these older homes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Northeast Heating Climate &amp;amp; Fuel-Oil Legacy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Hartford&amp;rsquo;s 5,883.3 HDD profile and 51.7 inches of annual snowfall require cold-climate-rated heat pumps for heat-pump conversion. The 1953 median housing age means envelope upgrades (insulation, air sealing, window replacement) frequently accompany heat-pump installation for best results. Connecticut&amp;rsquo;s inland location (vs. coastal Bridgeport) produces colder winter extremes, making cold-climate equipment specification particularly important.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Connecticut Contractor Licensing (DCP S-1)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Connecticut requires HVAC contractors to hold a &lt;strong&gt;Heating, Piping and Cooling Contractor License (S-1 classification)&lt;/strong&gt; issued by the Connecticut Department of Consumer Protection (DCP). The DCP administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DCP license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energize Connecticut / Eversource Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize Connecticut, in partnership with Eversource, administers residential heat pump incentives for Hartford customers. Contact Energize CT or Eversource directly for the current heat pump rebate amounts. Energize CT rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Hartford are set by the City of Hartford Department of Development Services, Licenses &amp;amp; Inspections. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5526,6 +5602,25 @@
       <c r="Q56" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KHSV)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville International Airport (KHSV) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003856), Huntsville records an &lt;strong&gt;annual mean temperature of 62.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 73.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 52.1&amp;deg;F, approximately &lt;strong&gt;2,831.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,106.9 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;54.29 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;2.4 inches&lt;/strong&gt;. The roughly 1.3:1 HDD-to-CDD ratio reflects a balanced dual-load climate &amp;mdash; meaningful heating and meaningful cooling demand, with 54 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Huntsville city, Alabama) report &lt;strong&gt;94,058 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;75.8% electricity&lt;/strong&gt; (71,266 units), &lt;strong&gt;22.2% utility natural gas&lt;/strong&gt; (20,912 units), and 1,037 on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories in the Tennessee Valley, where historically affordable power made heat-pump and electric-resistance heating economically competitive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Huntsville Utilities (TVA Distributor) &amp;amp; NASA/Defense Economy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville&amp;rsquo;s electric service is provided by &lt;strong&gt;Huntsville Utilities&lt;/strong&gt;, a municipally owned utility that distributes TVA power. Huntsville Utilities / TVA EnergyRight administers residential HVAC rebates; contact Huntsville Utilities directly for the current heat pump and smart thermostat rebate amounts. Huntsville&amp;rsquo;s major employer base &amp;mdash; including NASA Marshall Space Flight Center and Redstone Arsenal &amp;mdash; drives housing construction activity and HVAC demand patterns in the area.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate Considerations (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Huntsville&amp;rsquo;s combination of 2,106.9 CDD and 54.29 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems with enhanced dehumidification modes are particularly effective in the Tennessee Valley&amp;rsquo;s humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama requires HVAC contractors to hold a license issued by the &lt;strong&gt;Alabama Board of Heating, Air Conditioning, and Refrigeration Contractors (Board of HACR Contractors)&lt;/strong&gt;. The Board administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Huntsville are set by the City of Huntsville Inspection Services Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -5804,6 +5804,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal and state primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSNA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;John Wayne Airport (KSNA) is the nearest official NOAA reference station serving the Irvine area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093134), the area records an &lt;strong&gt;annual mean temperature of 65.8&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 74.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 56.8&amp;deg;F, approximately &lt;strong&gt;1,005.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,295.7 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;14.25 inches&lt;/strong&gt;. The roughly 1.3:1 CDD-to-HDD ratio reflects a mild Mediterranean climate &amp;mdash; both heating and cooling loads are moderate by national standards, and neither dominates the annual HVAC budget the way they do in extreme-climate cities.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:36770&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Irvine city, California) report &lt;strong&gt;111,979 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 2001&lt;/strong&gt; &amp;mdash; &lt;strong&gt;the newest housing stock of any project city&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;60.1% utility natural gas&lt;/strong&gt; (67,267 units), &lt;strong&gt;35.6% electricity&lt;/strong&gt; (39,810 units), &lt;strong&gt;859 homes using solar energy&lt;/strong&gt; (0.8%), and &lt;strong&gt;1,549 homes using no fuel at all&lt;/strong&gt; (1.4%). The relatively high solar and no-fuel shares reflect both the mild climate and Irvine&amp;rsquo;s master-planned community development with modern construction standards.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mild Climate &amp;amp; Equipment Sizing (Zone 3B Warm-Dry)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3B warm-dry climates like coastal Orange County produce moderate cooling loads with low humidity. The 14.25-inch annual precipitation and dry air mean latent (moisture) loads are minimal &amp;mdash; sensible cooling capacity and SEER2 efficiency are the primary performance metrics. The moderate HDD/CDD profile also makes Irvine ideal heat-pump territory: standard air-source heat pumps operate near peak efficiency year-round without the extreme-temperature penalties seen in continental climates.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California HVAC Contractor Licensing (CSLB C-20)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning (HVAC) License&lt;/strong&gt; issued by the California Contractors State License Board (CSLB). The CSLB administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current CSLB C-20 license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SCE Rebates &amp;amp; TECH Clean California&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southern California Edison (SCE) administers the Home Performance Plus program and participates in the TECH Clean California initiative for residential HVAC electrification in its Irvine service territory. Contact SCE directly for the current heat pump, smart thermostat, and central AC rebate amounts. SCE rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Irvine are set by the Community Development Department, Building &amp;amp; Safety Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6223,6 +6242,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMCI)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kansas City International Airport (KMCI) is the official NOAA reference station for the metro area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013988), Kansas City records an &lt;strong&gt;annual mean temperature of 56.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 66.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 47.5&amp;deg;F, approximately &lt;strong&gt;4,613.0 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,707.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;38.13 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;11.0 inches&lt;/strong&gt;. The roughly 2.7:1 HDD-to-CDD ratio reflects a true dual-load climate with significant heating and cooling demand &amp;mdash; equipment must perform well in both Kansas City&amp;rsquo;s cold winters and hot, humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:38000&amp;amp;in=state:29" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Kansas City city, Missouri) report &lt;strong&gt;219,486 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1968&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;67.5% utility natural gas&lt;/strong&gt; (148,181 units), &lt;strong&gt;29.5% electricity&lt;/strong&gt; (64,840 units), and 4,005 on bottled/tank/LP gas (1.8%). The gas-dominant mix and late-1960s housing stock mean furnace AFUE upgrades and ductwork remediation are high-impact investments across the metro.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dual-Load Climate Considerations (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates like Kansas City produce both meaningful winter heating loads and significant summer latent (moisture) loads. The 1,707.6 CDD combined with 38.13 inches of precipitation means cooling-season dehumidification is a real design concern, while 4,613.0 HDD requires reliable heating capacity through Missouri&amp;rsquo;s documented sub-zero cold snaps.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kansas City Contractor Licensing (Municipal)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Missouri does not issue a statewide HVAC contractor license. Instead, &lt;strong&gt;Kansas City requires a municipal mechanical trade license&lt;/strong&gt; for HVAC contractors operating within city limits. Verify a contractor&amp;rsquo;s current KC trade license and insurance before contracting. Contractors working in Johnson County, KS (Overland Park side of metro) may face different Kansas-side requirements.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Evergy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Evergy administers the FastTrack HVAC PAYS Program for residential customers in the Kansas City area. Contact Evergy directly for the current heat pump, smart thermostat, and central AC rebate amounts. Evergy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Kansas City are set by the Kansas City Planning &amp;amp; Development Permits Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6306,6 +6344,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTYS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;McGhee Tyson Airport (KTYS) is the official NOAA reference station for Knoxville. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013891), Knoxville records an &lt;strong&gt;annual mean temperature of 59.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 70.0&amp;deg;F&lt;/strong&gt; against an annual minimum of 49.1&amp;deg;F, approximately &lt;strong&gt;3,528.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,574.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;51.93 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;4.6 inches&lt;/strong&gt;. The roughly 2.2:1 HDD-to-CDD ratio reflects a dual-load climate in the Tennessee Valley &amp;mdash; meaningful heating and cooling demand, with 52 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:40000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Knoxville city, Tennessee) report &lt;strong&gt;84,882 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.0% electricity&lt;/strong&gt; (62,794 units), &lt;strong&gt;24.7% utility natural gas&lt;/strong&gt; (20,963 units), and 410 on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories, where historically affordable hydroelectric power made heat-pump and electric-resistance heating economically competitive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: KUB Municipal Utility (TVA Distributor)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Knoxville&amp;rsquo;s electric service is provided by the &lt;strong&gt;Knoxville Utilities Board (KUB)&lt;/strong&gt;, a municipally owned utility that distributes TVA power. KUB / TVA EnergyRight administers residential HVAC rebates; contact KUB directly for the current heat pump and smart thermostat rebate amounts. Like Chattanooga&amp;rsquo;s EPB and Huntsville Utilities, KUB&amp;rsquo;s municipal status means customers contract with the City rather than a private investor-owned utility.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate &amp;amp; Dehumidification (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Knoxville&amp;rsquo;s combination of 1,574.4 CDD and 51.93 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in the Tennessee Valley&amp;rsquo;s humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License (CMC-C)&lt;/strong&gt; issued by the Tennessee Board for Licensing Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Knoxville are set by the City of Knoxville Plans Review &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6387,6 +6444,25 @@
       <c r="Q65" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLRD)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Laredo International Airport (KLRD) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012959), Laredo records an &lt;strong&gt;annual mean temperature of 77.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 87.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 67.4&amp;deg;F, approximately &lt;strong&gt;453.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;4,989.0 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;22.16 inches&lt;/strong&gt;. The &lt;strong&gt;4,989 CDD is the highest of any project city&lt;/strong&gt; &amp;mdash; Laredo&amp;rsquo;s inland position on the Rio Grande makes it even hotter than coastal Brownsville. The 11:1 CDD-to-HDD ratio means air conditioning is the dominant HVAC cost driver by a wide margin, and the semi-arid 22-inch precipitation total means latent (humidity) loads are moderate relative to Gulf Coast cities.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:41464&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Laredo city, Texas) report &lt;strong&gt;76,259 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1996&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;83.9% electricity&lt;/strong&gt; (63,999 units), &lt;strong&gt;13.6% utility natural gas&lt;/strong&gt; (10,406 units), and &lt;strong&gt;589 homes using solar energy&lt;/strong&gt; (0.8%). The dominant electric share reflects the subtropical climate where the &amp;ldquo;heating system&amp;rdquo; is the heat pump&amp;rsquo;s reverse cycle running a trivial number of winter hours.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Cooling Dominance (Zone 2B Hot-Dry)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2B hot-dry climates require HVAC systems optimized primarily for cooling. With 4,989 CDD, Laredo&amp;rsquo;s air conditioning systems run near-continuously from March through November. High SEER2 efficiency is the dominant cost driver &amp;mdash; even a 1-point SEER improvement produces larger annual savings here than in any other project city due to the sheer number of cooling hours. Unlike Gulf Coast cities, Laredo&amp;rsquo;s semi-arid climate means sensible heat rather than humidity is the primary load component.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas HVAC Contractor Licensing (TDLR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Texas requires HVAC contractors to hold an &lt;strong&gt;Air Conditioning and Refrigeration Contractor License&lt;/strong&gt; issued by the Texas Department of Licensing and Regulation (TDLR). The TDLR administers examinations and issues licenses for ACR contracting statewide. Verify a specific contractor&amp;rsquo;s current TDLR license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;AEP Texas Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;AEP Texas administers the CoolSaver Program for residential customers in its Laredo service territory. Texas operates a deregulated electricity market, so rebates may flow through the retail electricity provider rather than the TDU. Contact AEP Texas or your retail electricity provider directly for the current heat pump and central AC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Laredo are set by the City of Laredo Building Development Services. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6570,6 +6646,25 @@
       <c r="Q67" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLEX)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Blue Grass Airport (KLEX) is the official NOAA reference station for Lexington. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093820), Lexington records an &lt;strong&gt;annual mean temperature of 56.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 66.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 46.3&amp;deg;F, approximately &lt;strong&gt;4,432.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,289.0 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;49.84 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;14.5 inches&lt;/strong&gt;. The roughly 3.4:1 HDD-to-CDD ratio reflects a heating-leaning dual-load climate &amp;mdash; equipment must handle Kentucky&amp;rsquo;s cold winters while also delivering adequate summer cooling and dehumidification in the Bluegrass region&amp;rsquo;s humid climate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:46027&amp;amp;in=state:21" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Lexington-Fayette urban county, Kentucky) report &lt;strong&gt;137,803 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1983&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;57.2% electricity&lt;/strong&gt; (78,859 units), &lt;strong&gt;40.8% utility natural gas&lt;/strong&gt; (56,275 units), and 1,610 on bottled/tank/LP gas (1.2%). The electricity-majority profile is notable for a Zone 4A city &amp;mdash; reflecting Kentucky&amp;rsquo;s historically affordable coal-generated power, which made electric-resistance and heat-pump heating competitive with gas.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate &amp;amp; Precipitation (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Lexington&amp;rsquo;s combination of 1,289.0 CDD and 49.84 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. The 4,432.4 HDD profile and 14.5 inches of annual snowfall also mean cold-weather heating capacity remains important through Kentucky winters.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kentucky HVAC Contractor Licensing (DHBC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky requires HVAC contractors to hold a &lt;strong&gt;Master HVAC Contractor License&lt;/strong&gt; issued by the Kentucky Department of Housing, Buildings and Construction (DHBC). The DHBC administers examinations and issues licenses for HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current DHBC license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kentucky Utilities (KU) Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky Utilities (KU), a PPL Company, administers residential rebates for its Lexington-Fayette service territory. Contact KU directly for the current heat pump, smart thermostat, and central AC rebate amounts. KU rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lexington-Fayette County are set by the Lexington-Fayette Urban County Government Division of Building Inspection. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -6750,6 +6750,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLNK)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lincoln Airport (KLNK) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014939), Lincoln records an &lt;strong&gt;annual mean temperature of 52.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 64.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 40.5&amp;deg;F, approximately &lt;strong&gt;5,856.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,270.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;29.34 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;26.0 inches&lt;/strong&gt;. The roughly 4.6:1 HDD-to-CDD ratio makes Lincoln a heavily heating-dominant market with meaningful summer cooling demand. The 26-inch snowfall normal drives outdoor equipment clearance and defrost-cycle planning.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:28000&amp;amp;in=state:31" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Lincoln city, Nebraska) report &lt;strong&gt;120,698 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1981&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.6% utility natural gas&lt;/strong&gt; (76,786 units), &lt;strong&gt;34.5% electricity&lt;/strong&gt; (41,588 units), and 1,672 on bottled/tank/LP gas. The gas-dominant mix and cold-climate profile mean furnace AFUE upgrades are high-impact investments, while the meaningful electric share creates heat-pump conversion opportunity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Lincoln Electric System (Municipal Utility)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lincoln&amp;rsquo;s electric service is provided by the &lt;strong&gt;Lincoln Electric System (LES)&lt;/strong&gt;, a municipally owned utility. Municipal utility status means Lincoln electric customers contract with the City rather than a private investor-owned utility. Contact LES directly for the current residential heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations (Zone 5A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Lincoln&amp;rsquo;s 5,856.4 HDD profile and documented sub-zero Great Plains winter extremes require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any gas-to-electric conversion. Outdoor condensers benefit from elevated mounting and clear winter access for service.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Nebraska Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nebraska does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Lincoln must obtain permits through local authorities. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lincoln are set by local permitting authorities. Contact the City of Lincoln Building &amp;amp; Safety Department for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6833,6 +6852,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLIT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Clinton National Airport (KLIT) is the official NOAA reference station for Little Rock. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013963), Little Rock records an &lt;strong&gt;annual mean temperature of 61.7&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 51.1&amp;deg;F, approximately &lt;strong&gt;3,164.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,988.9 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;50.42 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;3.8 inches&lt;/strong&gt;. The roughly 1.6:1 HDD-to-CDD ratio reflects a genuine dual-load climate &amp;mdash; meaningful heating and cooling demand throughout the year, with 50 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:41000&amp;amp;in=state:05" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Little Rock city, Arkansas) report &lt;strong&gt;86,853 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;50.7% utility natural gas&lt;/strong&gt; (44,056 units), &lt;strong&gt;47.4% electricity&lt;/strong&gt; (41,131 units), and 856 on bottled/tank/LP gas. The near-even 50/50 gas-to-electric split is notable &amp;mdash; reflecting the transitional climate zone where both gas furnaces and heat pumps are competitive primary heating systems.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate &amp;amp; Dual-Load Considerations (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Little Rock&amp;rsquo;s combination of 1,988.9 CDD and 50.42 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in Arkansas&amp;rsquo;s humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Arkansas HVAC Contractor Licensing (DLL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arkansas requires HVAC contractors to hold an &lt;strong&gt;HVAC/R Contractor License&lt;/strong&gt; issued by the Arkansas Department of Labor and Licensing (DLL). The DLL administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DLL license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Arkansas Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Arkansas administers residential energy efficiency programs for its Little Rock service territory. Contact Entergy Arkansas directly for the current heat pump, smart thermostat, and central AC rebate amounts. Entergy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Little Rock are set by local permitting authorities. Contact the City of Little Rock for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6914,6 +6952,25 @@
       <c r="Q70" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLAX)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Los Angeles International Airport (KLAX) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023174), Los Angeles records an &lt;strong&gt;annual mean temperature of 63.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 70.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 56.6&amp;deg;F, approximately &lt;strong&gt;1,213.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;720.4 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;12.23 inches&lt;/strong&gt;. The roughly 1.7:1 HDD-to-CDD ratio and narrow annual temperature range reflect LA&amp;rsquo;s coastal Mediterranean climate. Both heating and cooling loads are mild by national standards, but the sheer size of the housing stock means even modest per-unit HVAC investment translates to enormous aggregate demand.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:44000&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Los Angeles city, California) report &lt;strong&gt;1,419,663 occupied housing units&lt;/strong&gt; &amp;mdash; &lt;strong&gt;by far the largest housing stock of any project city&lt;/strong&gt; &amp;mdash; with a &lt;strong&gt;median year built of 1964&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;57.7% utility natural gas&lt;/strong&gt; (818,490 units), &lt;strong&gt;33.6% electricity&lt;/strong&gt; (476,592 units), &lt;strong&gt;6,550 homes using solar energy&lt;/strong&gt;, and notably &lt;strong&gt;90,123 homes using no fuel at all&lt;/strong&gt; (6.3%). The 6.3% no-fuel share &amp;mdash; over 90,000 homes that operate without any dedicated heating system &amp;mdash; is the highest of any project city and reflects the coastal Mediterranean climate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: LADWP Municipal Utility &amp;amp; Scale&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Los Angeles&amp;rsquo;s electric service is provided by the &lt;strong&gt;Los Angeles Department of Water and Power (LADWP)&lt;/strong&gt;, the largest municipally owned utility in the United States. LADWP administers its own residential rebate and electrification incentive programs. Contact LADWP directly for the current heat pump, smart thermostat, and central AC rebate amounts. LADWP&amp;rsquo;s municipal status means LA electric customers contract with the City.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mild Climate &amp;amp; Electrification Opportunity (Zone 3B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3B warm-dry climates like coastal Los Angeles produce moderate cooling loads with minimal humidity. The 12.23-inch annual precipitation and dry air mean latent loads are negligible. LA&amp;rsquo;s mild climate makes it ideal heat-pump territory: standard air-source heat pumps operate near peak efficiency year-round. California&amp;rsquo;s building electrification mandates and TECH Clean California program are accelerating gas-to-heat-pump conversion across the metro.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California HVAC Contractor Licensing (CSLB C-20)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning (HVAC) License&lt;/strong&gt; issued by the California Contractors State License Board (CSLB). Verify a specific contractor&amp;rsquo;s current CSLB C-20 license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Los Angeles are set by the City of Los Angeles Department of Building and Safety (LADBS). Contact LADBS directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7093,6 +7150,25 @@
       <c r="Q72" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLBB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lubbock Preston Smith International Airport (KLBB) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023042), Lubbock records an &lt;strong&gt;annual mean temperature of 61.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 74.9&amp;deg;F&lt;/strong&gt; against an annual minimum of 47.8&amp;deg;F, approximately &lt;strong&gt;3,243.0 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,950.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;18.33 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;7.0 inches&lt;/strong&gt;. The roughly 1.7:1 HDD-to-CDD ratio reflects a genuine dual-load climate on the Llano Estacado (Staked Plains). The semi-arid 18-inch precipitation total and 27&amp;deg;F diurnal temperature swing (the difference between the average annual max and min) are characteristic of High Plains climates.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:45000&amp;amp;in=state:48" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Lubbock city, Texas) report &lt;strong&gt;105,259 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1983&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;53.3% electricity&lt;/strong&gt; (56,078 units), &lt;strong&gt;44.9% utility natural gas&lt;/strong&gt; (47,261 units), and 1,274 on bottled/tank/LP gas. The near-even electric/gas split reflects the transitional climate where both systems are competitive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Lubbock Power &amp;amp; Light (Municipal Utility)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lubbock&amp;rsquo;s electric service is provided by &lt;strong&gt;Lubbock Power &amp;amp; Light (LP&amp;amp;L)&lt;/strong&gt;, a municipally owned utility. Unlike most Texas cities in the deregulated ERCOT market, Lubbock transitioned from SPP to ERCOT in 2021 but LP&amp;amp;L customers still contract with the municipal utility. Contact LP&amp;amp;L directly for the current residential HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;High Plains Climate &amp;amp; Evaporative Cooling&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3B warm-dry climates with low humidity (Lubbock receives only 18.33 inches of annual precipitation) are well-suited to evaporative cooling as a supplement to conventional AC. The large diurnal temperature swing also makes night-flush ventilation effective. However, Lubbock&amp;rsquo;s 3,243.0 HDD profile means reliable heating capacity remains essential through Texas Panhandle-adjacent winters.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas HVAC Contractor Licensing (TDLR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Texas requires HVAC contractors to hold an &lt;strong&gt;Air Conditioning and Refrigeration Contractor License&lt;/strong&gt; issued by the Texas Department of Licensing and Regulation (TDLR). Verify a specific contractor&amp;rsquo;s current TDLR license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lubbock are set by local permitting authorities. Contact the City of Lubbock for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7778,6 +7854,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMOB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mobile Regional Airport (KMOB) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013894), Mobile records an &lt;strong&gt;annual mean temperature of 67.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 77.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 57.4&amp;deg;F, approximately &lt;strong&gt;1,616.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,598.7 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;67.08 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.2 inches&lt;/strong&gt;. The &lt;strong&gt;67.08-inch annual precipitation is the highest of any project city&lt;/strong&gt; &amp;mdash; Mobile&amp;rsquo;s Gulf Coast position makes it one of the wettest major cities in the United States. The 1.6:1 CDD-to-HDD ratio makes it a cooling-dominant market where dehumidification is a primary HVAC design concern.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:50000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Mobile city, Alabama) report &lt;strong&gt;77,587 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;55.9% electricity&lt;/strong&gt; (43,387 units), &lt;strong&gt;42.1% utility natural gas&lt;/strong&gt; (32,627 units), and 1,093 on bottled/tank/LP gas (1.4%). The electric-majority profile is consistent with the Gulf Coast&amp;rsquo;s cooling-dominant climate where heat-pump primary heat is the practical standard.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Precipitation &amp;amp; Hurricane Exposure (Zone 2A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates produce extreme latent (moisture) cooling loads. Mobile&amp;rsquo;s combination of 2,598.7 CDD and 67.08 inches of annual precipitation &amp;mdash; the wettest in the project &amp;mdash; means dehumidification is the dominant HVAC comfort variable. Variable-speed compressor systems with enhanced dehumidification modes are essential. Hurricane exposure along the Gulf Coast means outdoor condenser placement, elevated pad mounts, and tie-down anchoring are practical considerations.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HVAC Contractor Licensing (HACR Board)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama requires HVAC contractors to hold a license issued by the &lt;strong&gt;Alabama Board of Heating, Air Conditioning, and Refrigeration Contractors (Board of HACR Contractors)&lt;/strong&gt;. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama Power Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama Power administers residential rebate programs for its Mobile service territory. Contact Alabama Power directly for the current heat pump, smart thermostat, and central AC rebate amounts. Alabama Power rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Mobile are set by local permitting authorities. Contact the City of Mobile for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -7956,6 +7956,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMOD)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Modesto City-County Airport (KMOD) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023232), Modesto records an &lt;strong&gt;annual mean temperature of 61.8&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 74.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 48.9&amp;deg;F, approximately &lt;strong&gt;2,436.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,291.5 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;18.14 inches&lt;/strong&gt;. The roughly 1.9:1 HDD-to-CDD ratio and Central Valley hot-dry summers produce a dual-load climate with notable summer cooling demand. The 18-inch precipitation total and dry air mean latent (humidity) loads are minimal.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:48354&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Modesto city, California) report &lt;strong&gt;72,418 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.3% utility natural gas&lt;/strong&gt; (50,191 units), &lt;strong&gt;27.8% electricity&lt;/strong&gt; (20,105 units), and 362 homes using solar energy. The gas-dominant profile reflects California&amp;rsquo;s Central Valley housing patterns where gas furnaces have historically been the default.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: MID (Modesto Irrigation District) Municipal Utility&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Modesto&amp;rsquo;s electric service is provided by the &lt;strong&gt;Modesto Irrigation District (MID)&lt;/strong&gt;, a publicly owned utility. MID serves both irrigation and retail electric customers. Contact MID directly for the current residential heat pump, smart thermostat, and HVAC rebate amounts. Municipal utility status means Modesto electric customers contract with MID rather than a private investor-owned utility.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California HVAC Contractor Licensing (CSLB C-20)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning (HVAC) License&lt;/strong&gt; issued by the California Contractors State License Board (CSLB). Verify a specific contractor&amp;rsquo;s current CSLB C-20 license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Central Valley Climate Considerations (Zone 3B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3B warm-dry climates like the Central Valley produce high sensible cooling loads with minimal humidity. The 25.8&amp;deg;F diurnal temperature swing (annual max 74.7&amp;deg;F minus annual min 48.9&amp;deg;F) means homes need both effective cooling for summer afternoons and reliable heating for Central Valley tule fog season winters.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Modesto are set by the City of Modesto Community &amp;amp; Economic Development Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8729,6 +8748,25 @@
       <c r="Q88" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPIA)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;General Wayne A. Downing Peoria International Airport (KPIA) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014842), Peoria records an &lt;strong&gt;annual mean temperature of 52.7&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 62.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 43.0&amp;deg;F, approximately &lt;strong&gt;5,613.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,157.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;37.55 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;26.2 inches&lt;/strong&gt;. The roughly 4.9:1 HDD-to-CDD ratio makes Peoria a heating-dominant market with meaningful summer cooling demand. The 26-inch snowfall drives outdoor equipment clearance and defrost-cycle planning.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:59000&amp;amp;in=state:17" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Peoria city, Illinois) report &lt;strong&gt;48,950 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1966&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;68.7% utility natural gas&lt;/strong&gt; (33,619 units), &lt;strong&gt;29.6% electricity&lt;/strong&gt; (14,471 units), and 335 on bottled/tank/LP gas. The gas-dominant mix and mid-1960s housing stock mean furnace AFUE upgrades and envelope improvements are high-impact investments.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations (Zone 5A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Peoria&amp;rsquo;s 5,613.8 HDD profile and documented sub-zero central Illinois winter extremes require cold-climate-rated heat pumps for any gas-to-electric conversion. Outdoor condensers benefit from elevated mounting and clear winter access.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Illinois Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Illinois does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Peoria must obtain permits through local authorities. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ameren Illinois Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ameren Illinois administers residential energy efficiency rebates for its Peoria service territory. Contact Ameren Illinois directly for the current heat pump, smart thermostat, and central AC rebate amounts. Ameren rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Peoria are set by local permitting authorities. Contact the City of Peoria for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9272,6 +9310,25 @@
       <c r="Q94" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPVD)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;T. F. Green International Airport (KPVD) is the official NOAA reference station for Providence. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014765), Providence records an &lt;strong&gt;annual mean temperature of 52.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 61.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 43.1&amp;deg;F, approximately &lt;strong&gt;5,478.0 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;812.1 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;47.54 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;36.6 inches&lt;/strong&gt;. The roughly 6.7:1 HDD-to-CDD ratio makes Providence a heavily heating-dominant market where furnace efficiency, building envelope performance, and snow management around outdoor equipment are the primary HVAC design drivers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:59000&amp;amp;in=state:44" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Providence city, Rhode Island) report &lt;strong&gt;70,313 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1938&lt;/strong&gt; &amp;mdash; &lt;strong&gt;the oldest housing stock of any project city&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;71.2% utility natural gas&lt;/strong&gt; (50,082 units), &lt;strong&gt;15.6% electricity&lt;/strong&gt; (10,968 units), &lt;strong&gt;8.3% fuel oil or kerosene&lt;/strong&gt; (5,869 units), and &lt;strong&gt;3.6% bottled/tank/LP gas&lt;/strong&gt; (2,496 units). The 8.3% fuel-oil share and pre-war housing stock (median 1938) represent substantial fuel-oil-to-heat-pump conversion potential &amp;mdash; but also mean envelope upgrades are particularly critical for any HVAC investment to perform as intended.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pre-War Housing &amp;amp; Fuel-Oil Legacy&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, homes built before modern insulation and air-sealing standards (Providence&amp;rsquo;s median year built 1938 predates these by decades) typically require a whole-house approach: envelope improvements (insulation, air sealing, window upgrades) paired with HVAC equipment replacement. Providence&amp;rsquo;s 5,478.0 HDD profile and 36.6 inches of annual snowfall require cold-climate-rated heat pumps, and the Narragansett Bay coastal location adds salt-air corrosion considerations for outdoor equipment.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Rhode Island Contractor Licensing (DLT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rhode Island requires HVAC contractors to hold a &lt;strong&gt;Refrigeration/Air Conditioning Contractor License&lt;/strong&gt; issued by the Rhode Island Department of Labor and Training (DLT). The DLT administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DLT license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Rhode Island Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rhode Island Energy administers residential rebate and incentive programs for its Providence service territory. Contact Rhode Island Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts. Rhode Island Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Providence are set by local permitting authorities. Contact the City of Providence for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10739,6 +10796,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSHV)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Shreveport Regional Airport (KSHV) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013957), Shreveport records an &lt;strong&gt;annual mean temperature of 66.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 77.5&amp;deg;F&lt;/strong&gt; against an annual minimum of 55.6&amp;deg;F, approximately &lt;strong&gt;2,067.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,676.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;51.43 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.9 inches&lt;/strong&gt;. The 1.3:1 CDD-to-HDD ratio makes Shreveport a cooling-dominant market, and the 51-inch precipitation total drives significant summer latent (humidity) loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:70000&amp;amp;in=state:22" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Shreveport city, Louisiana) report &lt;strong&gt;75,353 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1973&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;54.4% electricity&lt;/strong&gt; (40,962 units), &lt;strong&gt;43.7% utility natural gas&lt;/strong&gt; (32,917 units), and 624 on bottled/tank/LP gas. The near-even electric/gas split reflects the transitional climate where both heat pumps and gas furnaces are competitive primary heating systems.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate &amp;amp; Dehumidification (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Shreveport&amp;rsquo;s combination of 2,676.2 CDD and 51.43 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in northwest Louisiana&amp;rsquo;s humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana HVAC Contractor Licensing (LSLBC)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisiana requires HVAC contractors to hold a &lt;strong&gt;Mechanical Work Contractor License&lt;/strong&gt; issued by the Louisiana State Licensing Board for Contractors (LSLBC). Verify a specific contractor&amp;rsquo;s current LSLBC license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SWEPCO Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southwestern Electric Power Company (SWEPCO), an AEP company, is the primary electric utility for the Shreveport area. Contact SWEPCO directly for the current residential HVAC rebate amounts. SWEPCO rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Shreveport are set by local permitting authorities. Contact the City of Shreveport for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10820,6 +10896,25 @@
       <c r="Q111" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KGEG)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Spokane International Airport (KGEG) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024157), Spokane records an &lt;strong&gt;annual mean temperature of 48.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 58.0&amp;deg;F&lt;/strong&gt; against an annual minimum of 39.2&amp;deg;F, approximately &lt;strong&gt;6,462.6 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;514.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;16.45 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;45.4 inches&lt;/strong&gt;. The roughly &lt;strong&gt;12.6:1 HDD-to-CDD ratio&lt;/strong&gt; makes Spokane one of the most heating-dominant cities in the project. The semi-arid 16-inch precipitation total combined with 45 inches of snowfall is a distinctive Inland Northwest pattern &amp;mdash; dry summers with significant winter snow accumulation.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:53" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Spokane city, Washington) report &lt;strong&gt;96,602 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1961&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;54.0% utility natural gas&lt;/strong&gt; (52,230 units), &lt;strong&gt;41.7% electricity&lt;/strong&gt; (40,314 units), fuel oil/kerosene at 1.3% (1,243 units), and &lt;strong&gt;553 homes using wood&lt;/strong&gt; (0.6%). The meaningful electric share reflects Pacific Northwest hydroelectric power economics, and the wood-heating presence is characteristic of the Inland Northwest.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Inland Northwest Cold-Dry Climate (Zone 5B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 5B cool-dry climates like Spokane produce extended heating seasons with low indoor relative humidity. The 6,462.6 HDD profile requires cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any gas-to-electric conversion. The 45.4-inch snowfall normal means outdoor condensers need elevated mounting, and the dry winter air supports whole-house humidification considerations on the heating side.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Washington HVAC Contractor Licensing (L&amp;amp;I)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Washington requires HVAC contractors to hold a &lt;strong&gt;06A HVAC/Refrigeration Contractor License&lt;/strong&gt; issued by the Washington Department of Labor &amp;amp; Industries (L&amp;amp;I). The L&amp;amp;I administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current L&amp;amp;I license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Avista Utilities Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Avista Utilities administers residential rebate programs for its Spokane service territory. Contact Avista directly for the current heat pump, smart thermostat, natural gas furnace, and central AC rebate amounts. Avista rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Spokane are set by the City of Spokane. Contact the City for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -11000,6 +11000,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCEF)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Westover Metropolitan Airport (KCEF) is the official NOAA reference station for the Springfield area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014764), Springfield records an &lt;strong&gt;annual mean temperature of 47.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 38.6&amp;deg;F, approximately &lt;strong&gt;6,795.2 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;446.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.12 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;68.7 inches&lt;/strong&gt;. The &lt;strong&gt;15.2:1 HDD-to-CDD ratio&lt;/strong&gt; makes Springfield one of the most heating-dominant cities in the project. The Connecticut River valley funnels cold air and lake-effect moisture, producing nearly 69 inches of annual snowfall.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Springfield city, Massachusetts) report &lt;strong&gt;58,046 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.6% utility natural gas&lt;/strong&gt; (34,017 units), &lt;strong&gt;20.2% electricity&lt;/strong&gt; (11,705 units), &lt;strong&gt;13.7% fuel oil or kerosene&lt;/strong&gt; (7,952 units), and &lt;strong&gt;3.4% bottled/tank/LP gas&lt;/strong&gt; (1,958 units). The 13.7% fuel-oil share is among the highest in the project &amp;mdash; a legacy of New England&amp;rsquo;s industrial-era housing stock. Fuel-oil-to-heat-pump conversion represents a significant upgrade opportunity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Heating Climate &amp;amp; Fuel-Oil Conversion&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Springfield&amp;rsquo;s 6,795.2 HDD profile and 68.7 inches of annual snowfall require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any fuel conversion. The 1951 median housing age means envelope upgrades are particularly critical. Outdoor condensers need elevated mounting (18&amp;ndash;24 inches above grade) and clear winter access given the heavy snow accumulation.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Massachusetts Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a statewide HVAC-specific license. Instead, local permits are required, and sheet metal and pipefitting work may require separate trade licenses. Verify a contractor&amp;rsquo;s qualifications, insurance, and local licensing before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Eversource (WMECO) Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Eversource (formerly Western Massachusetts Electric Company / WMECO) administers residential energy efficiency rebates for its Springfield service territory through Mass Save. Contact Eversource or visit Mass Save for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Springfield are set by local permitting authorities. Contact the City of Springfield for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11341,6 +11360,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSYR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Syracuse Hancock International Airport (KSYR) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014771), Syracuse records an &lt;strong&gt;annual mean temperature of 48.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 57.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 39.4&amp;deg;F, approximately &lt;strong&gt;6,587.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;619.1 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.88 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;127.8 inches&lt;/strong&gt;. The &lt;strong&gt;127.8-inch annual snowfall is the highest of any project city by a wide margin&lt;/strong&gt; &amp;mdash; Syracuse is the snowiest large city in the United States, driven by Lake Ontario lake-effect storms. The 10.6:1 HDD-to-CDD ratio makes it a heavily heating-dominant market.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:73000&amp;amp;in=state:36" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Syracuse city, New York) report &lt;strong&gt;59,286 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1947&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.5% utility natural gas&lt;/strong&gt; (41,199 units), &lt;strong&gt;24.3% electricity&lt;/strong&gt; (14,378 units), fuel oil at 1.6% (935 units), and bottled/tank/LP gas at 1.9% (1,126 units). The gas-dominant profile and pre-1950 housing stock mean furnace AFUE upgrades and envelope improvements deliver substantial returns in Syracuse&amp;rsquo;s extreme heating climate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lake-Effect Snow &amp;amp; HVAC Equipment Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Syracuse&amp;rsquo;s 6,587.7 HDD profile and 127.8 inches of lake-effect snowfall create the most demanding outdoor-equipment environment in the project. Cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) are mandatory for any heat-pump installation. Outdoor condensers require elevated mounting (24+ inches above grade), snow fencing or barriers on the lake-effect side, clear defrost drainage, and reliable winter service access. Lake-effect events can deposit 12&amp;ndash;24 inches of snow in a single day, burying ground-level equipment.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;New York Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Syracuse must comply with local permitting requirements. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;National Grid Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;National Grid administers residential energy efficiency programs for its Syracuse service territory. Contact National Grid directly for the current heat pump, smart thermostat, and HVAC rebate amounts. National Grid rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Syracuse are set by local permitting authorities. Contact the City of Syracuse for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11500,6 +11538,25 @@
       <c r="Q118" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTLH)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tallahassee International Airport (KTLH) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093805), Tallahassee records an &lt;strong&gt;annual mean temperature of 68.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 79.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 57.2&amp;deg;F, approximately &lt;strong&gt;1,472.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,758.2 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;58.81 inches&lt;/strong&gt;. The roughly 1.9:1 CDD-to-HDD ratio makes Tallahassee a cooling-dominant market. The 58.81-inch precipitation total drives significant summer latent (humidity) loads &amp;mdash; dehumidification is a primary HVAC design concern.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:70600&amp;amp;in=state:12" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Tallahassee city, Florida) report &lt;strong&gt;83,637 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1987&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;85.5% electricity&lt;/strong&gt; (71,471 units), &lt;strong&gt;11.8% utility natural gas&lt;/strong&gt; (9,871 units), and 962 on bottled/tank/LP gas. The dominant electric share reflects the Gulf Coast climate where heat-pump primary heat handles the modest winter load efficiently.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: City of Tallahassee Utilities (Municipal)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tallahassee&amp;rsquo;s electric service is provided by the &lt;strong&gt;City of Tallahassee Utilities&lt;/strong&gt;, a municipally owned utility. Municipal utility status means Tallahassee electric customers contract with the City rather than a private investor-owned utility. Contact City of Tallahassee Utilities directly for the current residential HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hot-Humid Climate &amp;amp; Dehumidification (Zone 2A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates produce extreme latent (moisture) cooling loads. Tallahassee&amp;rsquo;s combination of 2,758.2 CDD and 58.81 inches of annual precipitation means variable-speed compressor systems with enhanced dehumidification modes are particularly effective. Properly sized equipment is critical &amp;mdash; oversizing worsens humidity control by short-cycling.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida AC Contractor Licensing (DBPR/CILB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Florida requires AC contractors to hold a license issued by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) through the Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Verify a specific contractor&amp;rsquo;s current DBPR license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Tallahassee are set by local permitting authorities. Contact the City of Tallahassee for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11685,6 +11742,25 @@
       <c r="Q120" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTOL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Express Airport (KTOL) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014848), Toledo records an &lt;strong&gt;annual mean temperature of 49.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 58.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 39.9&amp;deg;F, approximately &lt;strong&gt;6,399.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;722.1 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.23 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;64.5 inches&lt;/strong&gt;. The roughly 8.9:1 HDD-to-CDD ratio makes Toledo one of the most heating-dominant cities in the project. The 64.5-inch snowfall &amp;mdash; driven by Lake Erie lake-effect weather &amp;mdash; creates demanding outdoor-equipment conditions.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:77000&amp;amp;in=state:39" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Toledo city, Ohio) report &lt;strong&gt;118,508 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1955&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.9% utility natural gas&lt;/strong&gt; (87,569 units), &lt;strong&gt;23.6% electricity&lt;/strong&gt; (27,987 units), and 1,680 on bottled/tank/LP gas. The strong gas dominance combined with mid-1950s housing stock means furnace AFUE upgrades, ductwork remediation, and air-sealing work are particularly impactful.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lake Erie Lake-Effect Snow &amp;amp; HVAC Equipment&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Toledo&amp;rsquo;s 6,399.8 HDD profile and 64.5 inches of Lake Erie lake-effect snowfall require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any gas-to-electric conversion. Outdoor condensers need elevated mounting (18&amp;ndash;24 inches above grade), clear defrost drainage, and reliable winter service access.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio HVAC Contractor Licensing (OCILB)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ohio requires HVAC contractors to hold an &lt;strong&gt;HVAC Contractor License&lt;/strong&gt; issued by the Ohio Construction Industry Licensing Board (OCILB). Verify a specific contractor&amp;rsquo;s current OCILB license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Toledo Edison / FirstEnergy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Edison, a FirstEnergy company, is the primary electric utility for the Toledo area. Contact Toledo Edison or FirstEnergy directly for the current residential HVAC rebate amounts. Utility rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Toledo are set by local permitting authorities. Contact the City of Toledo for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12418,6 +12494,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KINT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Smith Reynolds Airport (KINT) is the official NOAA reference station for Winston-Salem. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013723), Winston-Salem records an &lt;strong&gt;annual mean temperature of 59.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 69.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 49.4&amp;deg;F, approximately &lt;strong&gt;3,499.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,552.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;43.95 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;7.1 inches&lt;/strong&gt;. The roughly 2.3:1 HDD-to-CDD ratio reflects a dual-load climate in the NC Piedmont &amp;mdash; meaningful heating and cooling demand, with 44 inches of precipitation driving summer humidity loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:75000&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Winston-Salem city, North Carolina) report &lt;strong&gt;100,278 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1980&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;60.9% electricity&lt;/strong&gt; (61,022 units), &lt;strong&gt;31.6% utility natural gas&lt;/strong&gt; (31,696 units), &lt;strong&gt;4.4% fuel oil or kerosene&lt;/strong&gt; (4,372 units), and 2.1% bottled/tank/LP gas (2,142 units). The 4.4% fuel-oil share is notably high for a Southern city &amp;mdash; a legacy of the NC Piedmont&amp;rsquo;s historic Moravian-era housing stock and industrial development. Fuel-oil-to-heat-pump conversion is a viable upgrade path in these older homes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate &amp;amp; Dehumidification (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Winston-Salem&amp;rsquo;s combination of 1,552.2 CDD and 43.95 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in the Piedmont&amp;rsquo;s humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Carolina requires HVAC contractors to hold a &lt;strong&gt;Heating Contractor License&lt;/strong&gt; (H-1, H-2, or H-3 classification) issued by the North Carolina Board of Examiners of Plumbing, Heating and Fire Sprinkler Contractors. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Winston-Salem service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and central AC rebate amounts. Duke Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Winston-Salem are set by the City of Winston-Salem Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -12596,6 +12596,25 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KORH)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Worcester Regional Airport (KORH) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094746), Worcester records an &lt;strong&gt;annual mean temperature of 48.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 39.6&amp;deg;F, approximately &lt;strong&gt;6,622.5 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;502.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.26 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;72.9 inches&lt;/strong&gt;. The &lt;strong&gt;13.2:1 HDD-to-CDD ratio&lt;/strong&gt; makes Worcester one of the most heating-dominant cities in the project. The 72.9-inch snowfall is driven by Worcester&amp;rsquo;s elevated inland New England position (roughly 1,000 ft above sea level), producing heavier snow accumulation than coastal Massachusetts cities.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:82000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Worcester city, Massachusetts) report &lt;strong&gt;79,089 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;51.2% utility natural gas&lt;/strong&gt; (40,516 units), &lt;strong&gt;28.2% electricity&lt;/strong&gt; (22,335 units), &lt;strong&gt;15.0% fuel oil or kerosene&lt;/strong&gt; (11,823 units), and &lt;strong&gt;3.2% bottled/tank/LP gas&lt;/strong&gt; (2,525 units). The &lt;strong&gt;15% fuel-oil share is the highest of any project city&lt;/strong&gt; &amp;mdash; nearly 12,000 homes still running on oil heat in a 6,600+ HDD climate. Fuel-oil-to-heat-pump conversion represents the single largest upgrade opportunity category in Worcester.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Heating Climate &amp;amp; Fuel-Oil Conversion&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Worcester&amp;rsquo;s 6,622.5 HDD profile and 72.9 inches of annual snowfall require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any fuel conversion. The 1951 median housing age means envelope upgrades are particularly critical. Outdoor condensers need elevated mounting (18&amp;ndash;24 inches above grade) and clear winter access.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Massachusetts Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a statewide HVAC-specific license. Local permits are required, and sheet metal and pipefitting work may require separate trade licenses. Verify a contractor&amp;rsquo;s qualifications, insurance, and local licensing before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;National Grid Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;National Grid administers residential energy efficiency rebates for its Worcester service territory through Mass Save. Contact National Grid or visit Mass Save for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Worcester are set by local permitting authorities. Contact the City of Worcester for the current mechanical permit fee schedule.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12863,6 +12882,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCAE)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Columbia Metropolitan Airport (KCAE) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013883), Columbia records an &lt;strong&gt;annual mean temperature of 64.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 75.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 52.9&amp;deg;F, approximately &lt;strong&gt;2,472.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,236.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;45.24 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;1.2 inches&lt;/strong&gt;. The near-equal HDD:CDD balance reflects a genuine dual-load climate in the SC Midlands &amp;mdash; meaningful heating and cooling demand year-round.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:16000&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Columbia city, South Carolina) report &lt;strong&gt;51,784 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;71.0% electricity&lt;/strong&gt; (36,764 units), &lt;strong&gt;27.0% utility natural gas&lt;/strong&gt; (13,961 units), and 456 on bottled/tank/LP gas. The electric-majority profile reflects the warm-humid climate where heat-pump primary heat handles the moderate winter load efficiently.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Columbia&amp;rsquo;s combination of 2,236.6 CDD and 45.24 inches of precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in the SC Midlands&amp;rsquo; humid summers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing (LLR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC Department of Labor, Licensing and Regulation (LLR). Verify a specific contractor&amp;rsquo;s current LLR license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dominion Energy South Carolina Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dominion Energy South Carolina administers residential rebate programs for its Columbia service territory. Contact Dominion Energy SC directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Columbia are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12950,6 +12986,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KGSP)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Greenville-Spartanburg International Airport (KGSP) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003870), Greenville records an &lt;strong&gt;annual mean temperature of 61.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 50.4&amp;deg;F, approximately &lt;strong&gt;3,018.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,719.8 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;49.67 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;3.9 inches&lt;/strong&gt;. The roughly 1.8:1 HDD-to-CDD ratio reflects a dual-load climate in the SC Upstate foothills &amp;mdash; slightly more heating-dominant than Columbia due to Greenville&amp;rsquo;s higher elevation near the Blue Ridge foothills.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:30850&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Greenville city, South Carolina) report &lt;strong&gt;34,898 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1987&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;66.2% electricity&lt;/strong&gt; (23,093 units), &lt;strong&gt;30.4% utility natural gas&lt;/strong&gt; (10,603 units), and 498 on bottled/tank/LP gas. The electric-majority profile is consistent with the warm-humid climate where heat-pump primary heat is the practical standard.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Blue Ridge Foothills Climate (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Greenville&amp;rsquo;s Zone 3A position in the Blue Ridge foothills produces somewhat cooler winters than lowland SC cities like Columbia. The 3,018.6 HDD profile and 49.67 inches of precipitation mean HVAC systems need to handle both winter heating loads and summer dehumidification effectively.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing (LLR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC Department of Labor, Licensing and Regulation (LLR). Verify a specific contractor&amp;rsquo;s current LLR license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Greenville service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Greenville are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13037,6 +13090,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KJAN)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jackson-Medgar Wiley Evers International Airport (KJAN) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003940), Jackson records an &lt;strong&gt;annual mean temperature of 65.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 76.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 54.5&amp;deg;F, approximately &lt;strong&gt;2,221.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,402.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;57.35 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;1.0 inches&lt;/strong&gt;. The CDD exceeds HDD, making Jackson a cooling-dominant market. The 57.35-inch precipitation total drives significant summer latent (humidity) loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:36000&amp;amp;in=state:28" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Jackson city, Mississippi) report &lt;strong&gt;61,956 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1969&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;51.1% electricity&lt;/strong&gt; (31,642 units), &lt;strong&gt;46.3% utility natural gas&lt;/strong&gt; (28,689 units), and 755 on bottled/tank/LP gas. The near-even electric/gas split reflects the transitional climate where both systems are competitive.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hot-Humid Climate &amp;amp; Dehumidification (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Jackson&amp;rsquo;s combination of 2,402.3 CDD and 57.35 inches of precipitation means variable-speed compressor systems with enhanced dehumidification modes are particularly effective.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mississippi HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mississippi requires HVAC contractors to hold an &lt;strong&gt;HVAC License&lt;/strong&gt; issued by the Mississippi State Board of Contractors. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Mississippi Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Mississippi administers residential energy efficiency programs for its Jackson service territory. Contact Entergy Mississippi directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Jackson are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13122,6 +13192,23 @@
       <c r="Q135" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KGPT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Gulfport-Biloxi International Airport (KGPT) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00012854), Gulfport records an &lt;strong&gt;annual mean temperature of 73.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 83.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 63.2&amp;deg;F, approximately &lt;strong&gt;557.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;3,554.1 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;49.63 inches&lt;/strong&gt;. The &lt;strong&gt;6.4:1 CDD-to-HDD ratio&lt;/strong&gt; makes Gulfport one of the most cooling-dominant cities in the project. Heating demand is minimal &amp;mdash; the &amp;ldquo;heating system&amp;rdquo; for most homes is simply the heat pump&amp;rsquo;s reverse cycle running a modest number of winter hours.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:29700&amp;amp;in=state:28" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Gulfport city, Mississippi) report &lt;strong&gt;28,420 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1986&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.3% electricity&lt;/strong&gt; (20,819 units), &lt;strong&gt;23.7% utility natural gas&lt;/strong&gt; (6,732 units), and 377 on bottled/tank/LP gas. The strong electric majority reflects the Gulf Coast climate where electric heat pumps and resistance heat are the practical standard.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Gulf Coast Hurricane Exposure (Zone 2A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates produce extreme latent (moisture) cooling loads. Gulfport&amp;rsquo;s combination of 3,554.1 CDD and 49.63 inches of precipitation means dehumidification is the dominant HVAC comfort variable. Hurricane exposure along the Gulf Coast &amp;mdash; Gulfport was severely impacted by Hurricane Katrina in 2005 &amp;mdash; means outdoor condenser placement, elevated pad mounts, tie-down anchoring, and wind-debris protection are critical practical considerations.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mississippi HVAC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mississippi requires HVAC contractors to hold an &lt;strong&gt;HVAC License&lt;/strong&gt; issued by the Mississippi State Board of Contractors. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mississippi Power Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mississippi Power administers residential rebate programs for its Gulfport service territory. Contact Mississippi Power directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Gulfport are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -13298,6 +13298,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBGR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bangor International Airport (KBGR) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014606), Bangor records an &lt;strong&gt;annual mean temperature of 45.0&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 55.2&amp;deg;F&lt;/strong&gt; against an annual minimum of 34.8&amp;deg;F, approximately &lt;strong&gt;7,626.3 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;379.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;41.71 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;74.6 inches&lt;/strong&gt;. The &lt;strong&gt;20:1 HDD-to-CDD ratio&lt;/strong&gt; makes Bangor one of the most extreme heating-dominated climates in the project. Cooling demand is negligible &amp;mdash; virtually the entire HVAC budget goes to heating.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:02795&amp;amp;in=state:23" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Bangor city, Maine) report &lt;strong&gt;13,967 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1955&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;51.7% fuel oil or kerosene&lt;/strong&gt; (7,219 units), &lt;strong&gt;20.9% utility natural gas&lt;/strong&gt; (2,916 units), &lt;strong&gt;14.8% electricity&lt;/strong&gt; (2,073 units), and &lt;strong&gt;8.0% bottled/tank/LP gas&lt;/strong&gt; (1,116 units). The &lt;strong&gt;51.7% fuel-oil share is the highest of any project city by a wide margin&lt;/strong&gt; &amp;mdash; more than half of Bangor heats with fuel oil. This is the defining characteristic of Maine&amp;rsquo;s heating market: the state lacks natural gas pipeline infrastructure in most areas, leaving fuel oil as the legacy default. Fuel-oil-to-heat-pump conversion is the single largest HVAC upgrade opportunity in Bangor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Cold &amp;amp; Heat Pump Specification (Zone 6A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 6A cold-humid climates like Bangor produce extreme heating loads with minimal cooling demand. The 7,626.3 HDD profile requires cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) &amp;mdash; and many Maine homeowners opt for ductless mini-split systems that can operate efficiently down to -13&amp;deg;F or lower. The 74.6-inch snowfall normal means outdoor units need elevated mounting and clear winter access. The 1955 median housing age means envelope upgrades are critical for heat-pump economics.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel Board Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine requires HVAC technicians to hold a &lt;strong&gt;Master Technician License&lt;/strong&gt; issued by the Maine Fuel Board. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Versant Power &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Versant Power is the primary electric utility for the Bangor area. Maine also offers significant heat pump incentives through Efficiency Maine. Contact Versant Power and Efficiency Maine for the current heat pump rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Bangor are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13385,6 +13402,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMGW)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Morgantown Municipal Airport (KMGW) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013736), Morgantown records an &lt;strong&gt;annual mean temperature of 53.8&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 63.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 43.9&amp;deg;F, approximately &lt;strong&gt;4,964.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;930.1 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;43.15 inches&lt;/strong&gt;. The roughly 5.3:1 HDD-to-CDD ratio makes Morgantown a firmly heating-dominant market in the northern West Virginia mountains.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:55756&amp;amp;in=state:54" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Morgantown city, West Virginia) report &lt;strong&gt;12,119 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1966&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;62.6% utility natural gas&lt;/strong&gt; (7,590 units), &lt;strong&gt;35.4% electricity&lt;/strong&gt; (4,294 units), and 145 on bottled/tank/LP gas. The compact housing stock reflects Morgantown&amp;rsquo;s role as a university town (West Virginia University). Gas dominance is consistent with WV&amp;rsquo;s Appalachian natural gas production region.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Appalachian Climate Considerations (Zone 5A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Morgantown&amp;rsquo;s 4,964.2 HDD profile requires reliable heating capacity through Appalachian winters. The mountainous terrain can produce temperature inversions and localized cold pools. Cold-climate heat pump specification is recommended for any gas-to-electric conversion.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;West Virginia Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC contractors to hold an &lt;strong&gt;HVAC Technician Certification&lt;/strong&gt; issued by the WV Contractor Licensing Board. Verify a specific contractor&amp;rsquo;s current certification before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mon Power (FirstEnergy) &amp;amp; Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mon Power, a FirstEnergy company, is the primary electric utility for the Morgantown area. Contact Mon Power for the current residential HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Morgantown are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13472,6 +13506,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBIL)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Billings Logan International Airport (KBIL) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024033), Billings records an &lt;strong&gt;annual mean temperature of 48.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 59.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 37.0&amp;deg;F, approximately &lt;strong&gt;6,753.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;662.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;14.31 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;57.4 inches&lt;/strong&gt;. The roughly 10.2:1 HDD-to-CDD ratio makes Billings one of the most heating-dominant cities in the project. The semi-arid 14-inch precipitation combined with 57 inches of snowfall is characteristic of Montana&amp;rsquo;s high-plains climate &amp;mdash; dry powdery snow rather than heavy wet snow.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:06550&amp;amp;in=state:30" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Billings city, Montana) report &lt;strong&gt;50,340 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1979&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.7% utility natural gas&lt;/strong&gt; (37,110 units), &lt;strong&gt;22.9% electricity&lt;/strong&gt; (11,543 units), and 632 on bottled/tank/LP gas. The strong gas dominance is consistent with Montana&amp;rsquo;s position as a natural gas producing state.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Dry Climate (Zone 6B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 6B cold-dry climates like Billings produce extended heating seasons with very low indoor relative humidity. The 6,753.7 HDD profile requires cold-climate-rated heat pumps, and the dry winter air supports whole-house humidification considerations. The 57.4-inch snowfall means outdoor condensers need elevated mounting and clear winter access.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Montana Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Montana does not issue a statewide HVAC license. The Montana Department of Labor registers HVAC contractors. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NorthWestern Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NorthWestern Energy administers residential rebate programs for its Billings service territory. Contact NorthWestern Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Billings are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13559,6 +13610,23 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMSO)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Missoula International Airport (KMSO) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024153), Missoula records an &lt;strong&gt;annual mean temperature of 45.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 33.6&amp;deg;F, approximately &lt;strong&gt;7,514.4 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;306.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;14.11 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;43.0 inches&lt;/strong&gt;. The &lt;strong&gt;24.5:1 HDD-to-CDD ratio is the most heating-skewed of any project city&lt;/strong&gt; &amp;mdash; Missoula&amp;rsquo;s mountain valley location in western Montana produces virtually no summer cooling demand, and the entire HVAC budget goes to heating.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:50200&amp;amp;in=state:30" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Missoula city, Montana) report &lt;strong&gt;33,958 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1981&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.7% utility natural gas&lt;/strong&gt; (19,945 units), &lt;strong&gt;38.5% electricity&lt;/strong&gt; (13,064 units), and 509 on bottled/tank/LP gas. The substantial electric share (38.5%) reflects Missoula&amp;rsquo;s access to affordable Pacific Northwest hydroelectric power, making heat-pump conversion economically attractive even in this extreme heating climate.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mountain Valley Cold-Dry Climate (Zone 6B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 6B cold-dry climates like Missoula produce extreme heating seasons with very low indoor humidity. The 7,514.4 HDD profile and mountain valley cold-air pooling require cold-climate-rated heat pumps rated for sub-zero operation. Missoula&amp;rsquo;s semi-arid 14.11-inch precipitation means whole-house humidification is a standard comfort investment during the heating season.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Montana Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Montana does not issue a statewide HVAC license. The Montana Department of Labor registers HVAC contractors. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NorthWestern Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NorthWestern Energy administers residential rebate programs for its Missoula service territory. Contact NorthWestern Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Missoula are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13644,6 +13712,23 @@
       <c r="Q140" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFAR)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Hector International Airport (KFAR) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014914), Fargo records an &lt;strong&gt;annual mean temperature of 42.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 52.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 31.8&amp;deg;F, approximately &lt;strong&gt;8,805.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;542.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;23.95 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;51.4 inches&lt;/strong&gt;. The &lt;strong&gt;8,806 HDD is the highest of any project city&lt;/strong&gt; &amp;mdash; Fargo&amp;rsquo;s Zone 7 (Very Cold) climate is the most demanding heating environment in the entire site. The 16.2:1 HDD-to-CDD ratio reflects a winter-dominated HVAC market where heating performance and efficiency are the overwhelming cost drivers.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:25700&amp;amp;in=state:38" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fargo city, North Dakota) report &lt;strong&gt;58,629 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1991&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;53.0% electricity&lt;/strong&gt; (31,059 units), &lt;strong&gt;41.7% utility natural gas&lt;/strong&gt; (24,452 units), and &lt;strong&gt;2.1% bottled/tank/LP gas&lt;/strong&gt; (1,241 units). The electric-majority heating profile in Zone 7 may seem counterintuitive, but it reflects Fargo&amp;rsquo;s relatively young housing stock (median 1991) built with modern electric heat pumps and resistance heating in a region with historically affordable electricity from Great Plains wind and Upper Midwest hydro resources.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 7 Very Cold &amp;amp; Heat Pump Specification&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 7 (Very Cold) climates like Fargo produce the most extreme heating loads in the DOE climate-zone system. The 8,805.5 HDD profile and documented winter lows well below -20&amp;deg;F require the most capable cold-climate heat pumps available &amp;mdash; equipment rated for continuous operation at -15&amp;deg;F or lower. Auxiliary resistance-strip backup heat must be properly sized for the design-day low temperature. The 51.4-inch snowfall means outdoor condensers need elevated mounting and reliable defrost drainage.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Dakota Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Fargo requires a municipal mechanical contractor license for work within city limits. Verify a contractor&amp;rsquo;s qualifications, insurance, and local licensing before contracting.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Xcel Energy Rebates&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Xcel Energy administers residential rebate programs for its Fargo service territory. Contact Xcel Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts. Xcel rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fargo are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -13818,6 +13818,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBIS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bismarck Municipal Airport (KBIS) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024011), Bismarck records an &lt;strong&gt;annual mean temperature of 43.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 55.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 31.1&amp;deg;F, approximately &lt;strong&gt;8,470.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;535.9 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;19.05 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;50.5 inches&lt;/strong&gt;. The &lt;strong&gt;8,471 HDD is the second-highest in the project&lt;/strong&gt; (after Fargo&amp;rsquo;s 8,806). The 15.8:1 HDD-to-CDD ratio and semi-arid 19-inch precipitation make Bismarck a severely heating-dominant, dry-winter market.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:07200&amp;amp;in=state:38" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Bismarck city, North Dakota) report &lt;strong&gt;32,208 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;67.5% utility natural gas&lt;/strong&gt; (21,749 units), &lt;strong&gt;28.9% electricity&lt;/strong&gt; (9,294 units), and 511 on bottled/tank/LP gas. Unlike Fargo&amp;rsquo;s electric-majority profile, Bismarck&amp;rsquo;s gas dominance reflects MDU&amp;rsquo;s strong gas distribution network.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 6A Cold-Dry Climate&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Bismarck&amp;rsquo;s 8,470.7 HDD and documented winter lows well below -20&amp;deg;F require the most capable cold-climate heat pumps available. The dry 19-inch precipitation supports whole-house humidification considerations. Montana-Dakota Utilities (MDU) administers residential rebate programs; contact MDU directly for current amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Bismarck requires a municipal mechanical contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13905,6 +13918,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFSD)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Joe Foss Field (KFSD) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014944), Sioux Falls records an &lt;strong&gt;annual mean temperature of 47.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 58.0&amp;deg;F&lt;/strong&gt; against an annual minimum of 36.6&amp;deg;F, approximately &lt;strong&gt;7,248.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;847.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;27.85 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;45.3 inches&lt;/strong&gt;. The 8.6:1 HDD-to-CDD ratio makes Sioux Falls a heavily heating-dominant market.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:59020&amp;amp;in=state:46" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Sioux Falls city, South Dakota) report &lt;strong&gt;82,836 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1992&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;66.9% utility natural gas&lt;/strong&gt; (55,463 units), &lt;strong&gt;29.3% electricity&lt;/strong&gt; (24,284 units), and 1,380 on bottled/tank/LP gas. Young housing stock (median 1992) built under modern codes.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Sioux Falls&amp;rsquo;s 7,248.5 HDD profile requires cold-climate-rated heat pumps. Xcel Energy (electric) and MidAmerican Energy (gas) serve the area; contact both for current residential HVAC rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Sioux Falls requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13992,6 +14018,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KRAP)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rapid City Regional Airport (KRAP) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024090), Rapid City records an &lt;strong&gt;annual mean temperature of 46.7&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 59.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 33.7&amp;deg;F, approximately &lt;strong&gt;7,251.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;607.0 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;17.44 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;48.5 inches&lt;/strong&gt;. The roughly 11.9:1 HDD-to-CDD ratio and semi-arid 17-inch precipitation make Rapid City one of the most heating-dominant and driest cities in the project. The Black Hills location produces dramatic temperature swings (25.9&amp;deg;F diurnal range).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:52980&amp;amp;in=state:46" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Rapid City city, South Dakota) report &lt;strong&gt;31,961 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.6% utility natural gas&lt;/strong&gt; (20,316 units), &lt;strong&gt;31.8% electricity&lt;/strong&gt; (10,150 units), and 642 on bottled/tank/LP gas.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Black Hills Climate (Zone 5B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 5B cool-dry climates produce extended heating seasons with low indoor humidity. Black Hills Energy administers residential rebate programs; contact them for current amounts. Cold-climate heat pump specification is essential at 7,252 HDD.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Rapid City requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14079,6 +14118,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KILG)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New Castle Airport (KILG) is the official NOAA reference station for Wilmington. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013781), Wilmington records an &lt;strong&gt;annual mean temperature of 55.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 64.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 46.3&amp;deg;F, approximately &lt;strong&gt;4,646.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,228.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;45.33 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;20.2 inches&lt;/strong&gt;. The roughly 3.8:1 HDD-to-CDD ratio reflects a heating-leaning dual-load climate in the Mid-Atlantic corridor.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:77580&amp;amp;in=state:10" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Wilmington city, Delaware) report &lt;strong&gt;32,062 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1946&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;56.5% utility natural gas&lt;/strong&gt; (18,116 units), &lt;strong&gt;36.4% electricity&lt;/strong&gt; (11,679 units), and &lt;strong&gt;4.4% fuel oil or kerosene&lt;/strong&gt; (1,423 units). The fuel-oil legacy and pre-war housing stock (median 1946) present fuel-oil-to-heat-pump conversion opportunity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mid-Atlantic Climate (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce summer latent loads alongside winter heating demand. Delmarva Power (Exelon) administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Delaware Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Delaware requires HVAC contractors to hold a &lt;strong&gt;Master HVAC License&lt;/strong&gt; issued by the Delaware Board of HVACR Examiners. Verify license status before contracting. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14166,6 +14218,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBTV)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Burlington International Airport (KBTV) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014742), Burlington records an &lt;strong&gt;annual mean temperature of 47.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 38.6&amp;deg;F, approximately &lt;strong&gt;6,960.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;655.7 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;37.53 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;87.5 inches&lt;/strong&gt;. The &lt;strong&gt;87.5-inch snowfall is the third-highest in the project&lt;/strong&gt; (after Syracuse 127.8&amp;rdquo; and Grand Rapids 77.6&amp;rdquo;), driven by Lake Champlain lake-effect weather. The 10.6:1 HDD-to-CDD ratio makes Burlington a severely heating-dominant market.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:10675&amp;amp;in=state:50" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Burlington city, Vermont) report &lt;strong&gt;17,691 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1957&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;70.1% utility natural gas&lt;/strong&gt; (12,404 units), &lt;strong&gt;18.7% electricity&lt;/strong&gt; (3,309 units), &lt;strong&gt;4.9% bottled/tank/LP gas&lt;/strong&gt; (861 units), and &lt;strong&gt;4.3% fuel oil&lt;/strong&gt; (760 units).&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Burlington Electric Department (Municipal)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Burlington&amp;rsquo;s electric service is provided by the &lt;strong&gt;Burlington Electric Department (BED)&lt;/strong&gt;, a municipally owned utility notable for achieving &lt;strong&gt;100% renewable electricity&lt;/strong&gt;. Contact BED for current residential heat pump rebates. Vermont also offers significant heat pump incentives through Efficiency Vermont.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 6A Cold-Humid Climate&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Burlington&amp;rsquo;s 6,960.3 HDD and 87.5&amp;rdquo; snowfall require cold-climate-rated heat pumps and elevated outdoor-unit mounting. Vermont does not issue a statewide HVAC contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14253,6 +14318,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCYS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cheyenne Regional Airport (KCYS) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024018), Cheyenne records an &lt;strong&gt;annual mean temperature of 46.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 59.2&amp;deg;F&lt;/strong&gt; against an annual minimum of 34.6&amp;deg;F, approximately &lt;strong&gt;6,959.0 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;398.5 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;15.41 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;62.9 inches&lt;/strong&gt;. The 17.5:1 HDD-to-CDD ratio reflects an extreme heating-dominated, high-altitude (6,060 ft) semi-arid climate with persistent wind exposure on the High Plains.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:13900&amp;amp;in=state:56" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Cheyenne city, Wyoming) report &lt;strong&gt;28,956 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1975&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.7% utility natural gas&lt;/strong&gt; (21,052 units), &lt;strong&gt;24.0% electricity&lt;/strong&gt; (6,942 units), and 525 on bottled/tank/LP gas. Gas dominance is consistent with Wyoming&amp;rsquo;s natural gas production economy.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;High-Altitude Wind Exposure (Zone 6B)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 6B cold-dry climates at 6,000+ ft altitude produce unique HVAC challenges: reduced air density affects equipment capacity ratings, persistent wind accelerates heat loss through building envelopes, and the 62.9&amp;rdquo; snowfall drives outdoor-unit clearance requirements. Cheyenne Light Fuel and Power (Black Hills Energy) administers residential rebate programs.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wyoming does not issue a statewide HVAC license; check local requirements. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14338,6 +14416,19 @@
       <c r="Q147" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMHT)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Manchester-Boston Regional Airport (KMHT) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014745), Manchester records an &lt;strong&gt;annual mean temperature of 47.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 58.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 36.1&amp;deg;F, approximately &lt;strong&gt;6,980.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;528.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;41.95 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;67.7 inches&lt;/strong&gt;. The 13.2:1 HDD-to-CDD ratio makes Manchester a severely heating-dominant market.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:45140&amp;amp;in=state:33" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Manchester city, New Hampshire) report &lt;strong&gt;49,546 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1964&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;50.1% utility natural gas&lt;/strong&gt; (24,798 units), &lt;strong&gt;25.9% fuel oil or kerosene&lt;/strong&gt; (12,815 units), &lt;strong&gt;16.3% electricity&lt;/strong&gt; (8,079 units), and &lt;strong&gt;5.0% bottled/tank/LP gas&lt;/strong&gt; (2,490 units). The &lt;strong&gt;25.9% fuel-oil share&lt;/strong&gt; is the second-highest in the project (after Bangor&amp;rsquo;s 51.7%). Nearly 13,000 Manchester homes still heat with oil &amp;mdash; a massive conversion opportunity.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;New England Fuel-Oil Legacy &amp;amp; Conversion&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Manchester&amp;rsquo;s 6,980.1 HDD and 67.7&amp;rdquo; snowfall require cold-climate-rated heat pumps. The 1964 median housing age means envelope upgrades are critical. Eversource Energy administers residential rebates; contact Eversource for current amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New Hampshire does not issue a statewide HVAC contractor license; local requirements apply. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14527,6 +14618,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPWM)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Portland International Jetport (KPWM) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014764), Portland records an &lt;strong&gt;annual mean temperature of 47.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 38.6&amp;deg;F, approximately &lt;strong&gt;6,795.2 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;446.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.12 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;68.7 inches&lt;/strong&gt;. The 15.2:1 HDD-to-CDD ratio makes Portland one of the most heating-dominant cities in the project, with minimal cooling demand.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:60545&amp;amp;in=state:23" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Portland city, Maine) report &lt;strong&gt;32,393 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1946&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;39.4% utility natural gas&lt;/strong&gt; (12,761 units), &lt;strong&gt;32.9% fuel oil or kerosene&lt;/strong&gt; (10,666 units), &lt;strong&gt;19.3% electricity&lt;/strong&gt; (6,240 units), and &lt;strong&gt;5.3% bottled/tank/LP gas&lt;/strong&gt; (1,716 units). The &lt;strong&gt;32.9% fuel-oil share&lt;/strong&gt; is the third-highest in the project (after Bangor 51.7% and Manchester 25.9%). Over 10,000 Portland homes still heat with oil &amp;mdash; reflecting Maine&amp;rsquo;s limited natural gas pipeline infrastructure.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel-Oil Market &amp;amp; Heat Pump Conversion&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Portland&amp;rsquo;s 6,795.2 HDD and 68.7&amp;rdquo; snowfall require cold-climate-rated heat pumps. Maine&amp;rsquo;s Efficiency Maine program offers significant heat pump rebates specifically targeting fuel-oil-heated homes. Central Maine Power (CMP) is the primary electric utility; contact CMP and Efficiency Maine for current rebate amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel Board Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine requires HVAC technicians to hold a &lt;strong&gt;Master Technician License&lt;/strong&gt; issued by the Maine Fuel Board. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14614,6 +14718,19 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCRW)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Yeager Airport (KCRW) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013866), Charleston records an &lt;strong&gt;annual mean temperature of 56.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 66.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 45.5&amp;deg;F, approximately &lt;strong&gt;4,353.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,162.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;46.24 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;31.5 inches&lt;/strong&gt;. The roughly 3.7:1 HDD-to-CDD ratio reflects a heating-leaning dual-load climate in the Kanawha Valley.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14600&amp;amp;in=state:54" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charleston city, West Virginia) report &lt;strong&gt;21,237 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1956&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.4% utility natural gas&lt;/strong&gt; (12,392 units), &lt;strong&gt;40.0% electricity&lt;/strong&gt; (8,506 units), and 167 on bottled/tank/LP gas. Gas dominance reflects WV&amp;rsquo;s Appalachian gas production region, with meaningful electric share from historically affordable Appalachian coal-generated power.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Appalachian Climate (Zone 4A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates in the Kanawha Valley produce both heating and summer humidity loads. Appalachian Power (AEP) administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;WV Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC contractors to hold an &lt;strong&gt;HVAC Technician Certification&lt;/strong&gt; issued by the WV Contractor Licensing Board. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14699,6 +14816,19 @@
       <c r="Q151" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCHS)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charleston International Airport (KCHS) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013880), Charleston records an &lt;strong&gt;annual mean temperature of 66.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 76.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 56.4&amp;deg;F, approximately &lt;strong&gt;1,844.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,434.5 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;52.51 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.3 inches&lt;/strong&gt;. The 1.3:1 CDD-to-HDD ratio makes Charleston SC a cooling-dominant market, with 52 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:13330&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charleston city, South Carolina) report &lt;strong&gt;66,408 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1994&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.2% electricity&lt;/strong&gt; (49,266 units), &lt;strong&gt;23.8% utility natural gas&lt;/strong&gt; (15,793 units), and 442 on bottled/tank/LP gas. The strong electric majority reflects the Lowcountry&amp;rsquo;s warm climate where heat-pump primary heat handles the modest winter load efficiently.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lowcountry Warm-Humid Climate &amp;amp; Hurricane Exposure (Zone 3A)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent loads. Charleston&amp;rsquo;s coastal Lowcountry position adds hurricane exposure and salt-air corrosion considerations for outdoor equipment. Dominion Energy South Carolina administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SC Contractor Licensing&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC LLR. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -702,7 +702,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;New Mexico MM-3 HVAC Contractor Classification (Verbatim)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Albuquerque must hold a current license from the &lt;a href="https://www.srca.nm.gov/parts/title14/14.006.0006.html" target="_blank" rel="nofollow noopener"&gt;New Mexico Construction Industries Division (CID)&lt;/a&gt; under &lt;strong&gt;NMAC 14.6.6&lt;/strong&gt;. The HVAC classification is &lt;strong&gt;MM-3 (Heating, Ventilation &amp;amp; Air Conditioning)&lt;/strong&gt;: per NMAC 14.6.6, an MM-3 contractor may &lt;em&gt;&amp;ldquo;install, alter, repair, service and maintain HVAC air handling and refrigeration equipment and piping, including fans, coils, condensing units, self-contained packaged air conditioning or heating units, evaporative cooling units, and ductwork and accessories including solar air heating and cooled mechanical air handling and ventilation applications; may connect water to existing valved outlets, and install controls, and control wiring not to exceed 24 volts.&amp;rdquo;&lt;/em&gt; Natural gas piping work is a separate &lt;strong&gt;MM-2 (Natural Gas Fitting)&lt;/strong&gt; classification; hydronic/process piping falls under &lt;strong&gt;MM-4&lt;/strong&gt;.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Albuquerque Planning Department, Code Enforcement Division&lt;/strong&gt;; contact Planning directly for the current mechanical permit fee schedule. Albuquerque is served by &lt;strong&gt;PNM (Public Service Company of New Mexico)&lt;/strong&gt; for electricity and &lt;strong&gt;New Mexico Gas Company&lt;/strong&gt; for natural gas. Both utilities administer residential energy-efficiency rebate programs; check pnm.com and nmgco.com directly for current dollar amounts, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your ABQ ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Albuquerque Planning Department, Code Enforcement Division&lt;/strong&gt;; contact Planning directly for the current mechanical permit fee schedule. Albuquerque is served by &lt;strong&gt;PNM (Public Service Company of New Mexico)&lt;/strong&gt; for electricity and &lt;strong&gt;New Mexico Gas Company&lt;/strong&gt; for natural gas. Both utilities administer residential energy-efficiency rebate programs; check pnm.com and nmgco.com directly for current dollar amounts, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your ABQ ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -800,11 +800,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pennsylvania Contractor Registration (PAHIC)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pennsylvania does not issue a statewide HVAC-specific license. Instead, contractors performing home improvement work &amp;mdash; including HVAC installation &amp;mdash; must hold a &lt;strong&gt;PA Home Improvement Contractor Registration (PAHIC number)&lt;/strong&gt; issued by the Pennsylvania Attorney General&amp;rsquo;s Bureau of Consumer Protection. Verify a specific contractor&amp;rsquo;s current PAHIC registration before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;PPL Electric Utilities Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;PPL Electric Utilities administers residential heat pump rebates for its Allentown service territory. Contact PPL Electric directly or visit the PPL Electric savings programs page for the current heat pump, smart thermostat, and central AC rebate amounts in your service area. PPL rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;PPL Electric Utilities administers residential heat pump rebates for its Allentown service territory. Contact PPL Electric directly or visit the PPL Electric savings programs page for the current heat pump, smart thermostat, and central AC rebate amounts in your service area.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Allentown are set by the Allentown Bureau of Building Standards &amp;amp; Safety. Contact the Bureau directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit is non-refundable and stacks with PPL Electric rebates.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alaska Mechanical Administrator License (Three Classes)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Anchorage must hold a current Mechanical Administrator license from the &lt;a href="https://www.commerce.alaska.gov/web/cbpl/professionallicensing/mechanicaladministrators.aspx" target="_blank" rel="nofollow noopener"&gt;Alaska Department of Commerce, Division of Corporations, Business and Professional Licensing (DCBPL)&lt;/a&gt;. The Board issues three relevant HVAC license classes: &lt;strong&gt;Residential HVAC (RHVC)&lt;/strong&gt;, &lt;strong&gt;Unlimited HVAC/Sheet Metal (UHVCS)&lt;/strong&gt;, and &lt;strong&gt;Heating, Cooling, and Process Piping (HCPP)&lt;/strong&gt;. Board contact: (907) 465-2050 or MechanicalAdministrators@Alaska.gov. For Anchorage homeowners, verifying that a contractor holds the appropriate class (most residential work falls under RHVC) is the baseline due-diligence step.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Rebates &amp;amp; Federal Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;Municipality of Anchorage Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule. Anchorage is served by &lt;strong&gt;Chugach Electric Association&lt;/strong&gt; &amp;mdash; a member-owned cooperative utility &amp;mdash; for electricity, and &lt;strong&gt;Enstar Natural Gas&lt;/strong&gt; for the dominant residential heating fuel. For current rebate dollar amounts, visit chugachelectric.com and enstarnaturalgas.com directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps including cold-climate models).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;Municipality of Anchorage Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule. Anchorage is served by &lt;strong&gt;Chugach Electric Association&lt;/strong&gt; &amp;mdash; a member-owned cooperative utility &amp;mdash; for electricity, and &lt;strong&gt;Enstar Natural Gas&lt;/strong&gt; for the dominant residential heating fuel. For current rebate dollar amounts, visit chugachelectric.com and enstarnaturalgas.com directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1180,11 +1180,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Georgia Conditioned Air Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia requires HVAC contractors to hold a &lt;strong&gt;Conditioned Air Contractor License&lt;/strong&gt; (Class I or Class II) issued by the Georgia Construction Industry Licensing Board under the Secretary of State. Class I permits unrestricted conditioned air work; Class II is limited to systems serving spaces of specified capacity. Verify a specific contractor&amp;rsquo;s current license status on the Georgia Secretary of State license lookup before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Georgia Power Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia Power administers the Home Energy Improvement Program (HEIP) for residential customers in the Augusta area. Contact Georgia Power directly or visit the Georgia Power residential rebates page for the current heat pump, smart thermostat, and central AC rebate amounts. Georgia Power rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia Power administers the Home Energy Improvement Program (HEIP) for residential customers in the Augusta area. Contact Georgia Power directly or visit the Georgia Power residential rebates page for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Augusta-Richmond County are set by the Augusta-Richmond County Planning &amp;amp; Development Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1556,11 +1556,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana HVAC Contractor Licensing (LSLBC)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisiana requires HVAC contractors to hold a &lt;strong&gt;Mechanical Work Contractor License&lt;/strong&gt; issued by the Louisiana State Licensing Board for Contractors (LSLBC). The LSLBC administers examinations and issues licenses for mechanical contracting statewide. Verify a specific contractor&amp;rsquo;s current LSLBC license status before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Louisiana Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Louisiana administers residential energy efficiency programs for its Baton Rouge service territory. Contact Entergy Louisiana directly or visit the Entergy Louisiana save-money page for the current heat pump, smart thermostat, and central AC rebate amounts. Entergy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Louisiana administers residential energy efficiency programs for its Baton Rouge service territory. Contact Entergy Louisiana directly or visit the Entergy Louisiana save-money page for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Baton Rouge are set by the East Baton Rouge Parish Permits &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HACR Board Licensing (Detailed)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Birmingham must hold a current license from the &lt;a href="https://hacr.alabama.gov/how-to-get-licensed/" target="_blank" rel="nofollow noopener"&gt;Alabama Board of Heating, Air Conditioning and Refrigeration Contractors (HACR)&lt;/a&gt;. Per the HACR licensing page: &lt;em&gt;&amp;ldquo;Active Status: Contractors who perform HVAC or Refrigeration installation, service or repair&amp;rdquo;&lt;/em&gt; must pass the Heating &amp;amp; Air Conditioning Contractors Examination (reciprocity requires a 70% score on an equivalent exam). HACR fees: &lt;strong&gt;Examination $175.00&lt;/strong&gt;; &lt;strong&gt;Active status $220.00 annually&lt;/strong&gt;; &lt;strong&gt;Inactive status $110.00 annually&lt;/strong&gt;. Active contractors must also carry &lt;strong&gt;a performance bond in the amount of $20,000&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active HACR license AND $20,000 performance bond before authorizing work is the baseline due-diligence step for every Birmingham homeowner.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Incentives&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Birmingham Department of Planning, Engineering &amp;amp; Permits&lt;/strong&gt;; the city directs applicants to the Online Permit Center and Birmingham Permit Guide. Contact Permitting &amp;amp; Inspection at 205-254-2904 or OnlinePermitCenter@birminghamal.gov for the current fee schedule. Per &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;DOE Energy Saver guidance on hot-humid climate sizing&lt;/a&gt;: oversized AC equipment in Birmingham&amp;rsquo;s 56+ inch rainfall climate will short-cycle before pulling humidity, leaving homes clammy even at 72&amp;deg;F. Correct Manual J sizing (not bigger-is-better) is essential. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Birmingham Department of Planning, Engineering &amp;amp; Permits&lt;/strong&gt;; the city directs applicants to the Online Permit Center and Birmingham Permit Guide. Contact Permitting &amp;amp; Inspection at 205-254-2904 or OnlinePermitCenter@birminghamal.gov for the current fee schedule. Per &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;DOE Energy Saver guidance on hot-humid climate sizing&lt;/a&gt;: oversized AC equipment in Birmingham&amp;rsquo;s 56+ inch rainfall climate will short-cycle before pulling humidity, leaving homes clammy even at 72&amp;deg;F. Correct Manual J sizing (not bigger-is-better) is essential. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1836,11 +1836,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cool-Dry Climate Considerations (Zone 5B)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/eere/buildings/building-america" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Building America climate-zone guidance&lt;/a&gt;, Zone 5B (cool-dry) climates like Boise produce two HVAC-relevant patterns: low indoor relative humidity during the heating season (driven by 11.51 inches of annual precipitation and cold dry winter air at 5,320.5 HDD), and meaningful but not extreme cooling demand. Whole-house humidification is more commonly specified here than in humid eastern cities, and Snake River Valley cold-air inversions during winter mean outdoor heat-pump units benefit from elevated mounting and clear defrost drainage.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Idaho Power Residential Rebates (Heating &amp;amp; Cooling Efficiency Program)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Idaho Power administers a residential &lt;a href="https://www.idahopower.com/energy-environment/ways-to-save/savings-for-your-home/rebates-and-offers/heating-and-cooling-efficiency-program/" target="_blank" rel="nofollow noopener"&gt;Heating &amp;amp; Cooling Efficiency Program&lt;/a&gt; for its Boise service territory. Current rebates for existing homes include: &lt;strong&gt;$800 for a qualifying ducted air-source heat pump&lt;/strong&gt; when replacing an electric forced-air furnace, electric baseboards/ceiling cable/wall units, propane forced-air furnace, or oil forced-air furnace; &lt;strong&gt;$400 for a qualifying ductless heat pump&lt;/strong&gt; meeting the 9 HSPF / 7.6 HSPF2 efficiency requirement; and &lt;strong&gt;$50 for a qualifying smart thermostat&lt;/strong&gt;. Intermountain Gas administers separate gas-side incentives; contact Intermountain Gas directly for current natural-gas furnace rebate amounts. Idaho Power rebates pair with the federal IRS Section 25C Energy Efficient Home Improvement Credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Idaho Power administers a residential &lt;a href="https://www.idahopower.com/energy-environment/ways-to-save/savings-for-your-home/rebates-and-offers/heating-and-cooling-efficiency-program/" target="_blank" rel="nofollow noopener"&gt;Heating &amp;amp; Cooling Efficiency Program&lt;/a&gt; for its Boise service territory. Current rebates for existing homes include: &lt;strong&gt;$800 for a qualifying ducted air-source heat pump&lt;/strong&gt; when replacing an electric forced-air furnace, electric baseboards/ceiling cable/wall units, propane forced-air furnace, or oil forced-air furnace; &lt;strong&gt;$400 for a qualifying ductless heat pump&lt;/strong&gt; meeting the 9 HSPF / 7.6 HSPF2 efficiency requirement; and &lt;strong&gt;$50 for a qualifying smart thermostat&lt;/strong&gt;. Intermountain Gas administers separate gas-side incentives; contact Intermountain Gas directly for current natural-gas furnace rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Idaho HVAC Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC contractors operating in Idaho are regulated by the Idaho Division of Occupational and Professional Licenses (DOPL) under Idaho Statute Title 54, Chapter 50 (Heating, Ventilation and Air Conditioning Act). Verify a specific contractor&amp;rsquo;s current license status on the DOPL public lookup before contracting. Idaho HVAC license requirements include passing a written examination and meeting documented experience requirements; permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest efficiency tier set by the Consortium for Energy Efficiency (CEE) in effect at the start of the calendar year of installation. The credit is non-refundable and stacks with Idaho Power and Intermountain Gas rebates.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pumps in Pre-War Housing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Boston&amp;rsquo;s 5,545 HDD winters combined with a median-1947 housing stock create a distinctive HVAC challenge: many triple-deckers and brownstones never had central ducting. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;approximately 32% of homes lack ductwork, making ductless solutions like minisplit heat pumps a practical option for those looking to switch to more energy-efficient systems.&amp;rdquo;&lt;/em&gt; DOE further recommends homeowners &lt;em&gt;&amp;ldquo;weatherize their homes to ensure optimal cost savings and comfort, especially in older homes,&amp;rdquo;&lt;/em&gt; and for cold regions, &lt;em&gt;&amp;ldquo;consider looking for a system with an ENERGY STAR Cold Climate label.&amp;rdquo;&lt;/em&gt; For Boston specifically, ducted central heat pumps often don&amp;rsquo;t fit older homes without major retrofit &amp;mdash; but multi-zone ductless mini-split heat pumps with cold-climate ratings solve both problems at once, which is why they&amp;rsquo;re the dominant heat-pump install type across the Boston housing stock.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a single statewide HVAC-specific contractor license the way some states do. Instead, HVAC work in Boston is regulated through several overlapping credentials: refrigerant handling requires &lt;strong&gt;federal EPA Section 608 certification&lt;/strong&gt;; gas-fitting and plumbing portions of HVAC work require licensure through the &lt;strong&gt;Massachusetts Board of State Examiners of Plumbers and Gas Fitters&lt;/strong&gt;; sheet metal work is licensed separately. Verifying that a contractor holds all required credentials before authorizing work is the baseline due-diligence step for every Boston homeowner. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Boston Inspectional Services Department (ISD)&lt;/strong&gt;; contact ISD directly for the current fee schedule. For current utility rebate dollar amounts, visit &lt;strong&gt;masssave.com&lt;/strong&gt; (the joint utility rebate program that includes Eversource and administers some of the most generous heat-pump incentives in the country) or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Boston ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a single statewide HVAC-specific contractor license the way some states do. Instead, HVAC work in Boston is regulated through several overlapping credentials: refrigerant handling requires &lt;strong&gt;federal EPA Section 608 certification&lt;/strong&gt;; gas-fitting and plumbing portions of HVAC work require licensure through the &lt;strong&gt;Massachusetts Board of State Examiners of Plumbers and Gas Fitters&lt;/strong&gt;; sheet metal work is licensed separately. Verifying that a contractor holds all required credentials before authorizing work is the baseline due-diligence step for every Boston homeowner. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Boston Inspectional Services Department (ISD)&lt;/strong&gt;; contact ISD directly for the current fee schedule. For current utility rebate dollar amounts, visit &lt;strong&gt;masssave.com&lt;/strong&gt; (the joint utility rebate program that includes Eversource and administers some of the most generous heat-pump incentives in the country) or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Boston ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2116,11 +2116,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Connecticut Contractor Licensing (DCP)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Connecticut requires HVAC contractors to hold a &lt;strong&gt;Heating, Piping and Cooling Contractor License&lt;/strong&gt; (or an appropriate journeyperson license) issued by the Connecticut Department of Consumer Protection (DCP). The DCP administers examinations and issues licenses for mechanical contracting statewide. Verify a specific contractor&amp;rsquo;s current DCP license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energize CT / United Illuminating Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize CT, in partnership with United Illuminating (UI), administers residential heat pump rebates for Bridgeport customers. Contact Energize CT or United Illuminating directly for the current heat pump and smart thermostat rebate amounts in your service area. Energize CT rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize CT, in partnership with United Illuminating (UI), administers residential heat pump rebates for Bridgeport customers. Contact Energize CT or United Illuminating directly for the current heat pump and smart thermostat rebate amounts in your service area.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Bridgeport are set by the City of Bridgeport Building Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2221,8 +2221,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Texas requires HVAC contractors to hold an &lt;strong&gt;Air Conditioning and Refrigeration Contractor License&lt;/strong&gt; issued by the Texas Department of Licensing and Regulation (TDLR). The TDLR administers examinations and issues licenses for ACR contracting statewide. Verify a specific contractor&amp;rsquo;s current TDLR license status before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Brownsville are set by the City of Brownsville Building Inspections Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing: No NY State License + Buffalo Local Registration&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York State does not issue a statewide HVAC contractor license. Instead, Buffalo requires a local &lt;strong&gt;Heating Contractor License&lt;/strong&gt; administered by the &lt;strong&gt;City of Buffalo Department of Permit &amp;amp; Inspection Services (DPIS)&lt;/strong&gt;. Verifying that a contractor holds the city-issued Heating Contractor License before authorizing any HVAC work is the critical due-diligence step &amp;mdash; more important than in states with a statewide board, because the municipal license is the only formal credential. Contact DPIS at 65 Niagara Square for the current mechanical permit fee schedule and contractor-verification tools.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; NYSERDA Clean Heat&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Buffalo is served by &lt;strong&gt;National Grid&lt;/strong&gt; for both electricity and natural gas. National Grid runs Upstate NY residential efficiency programs covering Gas Heating &amp;amp; Water Heating and Electric Heating &amp;amp; Cooling. Buffalo residents are also eligible for the statewide &lt;strong&gt;NYSERDA NY Clean Heat&lt;/strong&gt; program &amp;mdash; among the most generous heat-pump incentive programs in the country for cold-climate air-source and ground-source systems. For current National Grid and NYSERDA Clean Heat dollar amounts, visit nationalgridus.com and nyserda.ny.gov directly &amp;mdash; both sites use interactive address-lookup tools rather than static dollar lists. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Buffalo is served by &lt;strong&gt;National Grid&lt;/strong&gt; for both electricity and natural gas. National Grid runs Upstate NY residential efficiency programs covering Gas Heating &amp;amp; Water Heating and Electric Heating &amp;amp; Cooling. Buffalo residents are also eligible for the statewide &lt;strong&gt;NYSERDA NY Clean Heat&lt;/strong&gt; program &amp;mdash; among the most generous heat-pump incentive programs in the country for cold-climate air-source and ground-source systems. For current National Grid and NYSERDA Clean Heat dollar amounts, visit nationalgridus.com and nyserda.ny.gov directly &amp;mdash; both sites use interactive address-lookup tools rather than static dollar lists. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Heat Pump Dehumidification Advantage&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charlotte&amp;rsquo;s 43+ inches of annual rainfall and warm-humid summers make humidity control a real HVAC design factor. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;high-efficiency heat pumps also dehumidify better than standard central air conditioners, resulting in less energy usage and more cooling comfort in summer months.&amp;rdquo;&lt;/em&gt; For Charlotte homeowners, the practical implication is that a high-efficiency heat pump handles both the cooling-capacity demand AND the latent-humidity load more effectively than an equivalent single-stage AC paired with a gas furnace &amp;mdash; which explains why heat pumps have become the default in the 53% of Charlotte homes already heated electrically.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Charlotte must hold a current state-issued Heating &amp;amp; Cooling Contractor License from the &lt;a href="https://www.nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating &amp;amp; Fire Sprinkler Contractors&lt;/a&gt;. NC issues three heating-license classifications &amp;mdash; &lt;strong&gt;H-1&lt;/strong&gt; (unlimited scope), &lt;strong&gt;H-2&lt;/strong&gt; (limited to systems below specified tonnage/BTU thresholds), and &lt;strong&gt;H-3&lt;/strong&gt; (packaged-unit specialty). For typical Charlotte residential work, any of the three classifications can be sufficient depending on the job scope; verifying the contractor&amp;rsquo;s active license with the NC Board at 919-875-3612 before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by &lt;strong&gt;Mecklenburg County Code Enforcement (LUESA)&lt;/strong&gt;; contact LUESA directly for the current fee schedule. For current &lt;strong&gt;Duke Energy Carolinas&lt;/strong&gt; Smart $aver rebate amounts and &lt;strong&gt;Piedmont Natural Gas&lt;/strong&gt; incentives, visit the utilities&amp;rsquo; sites directly or check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Charlotte ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Charlotte must hold a current state-issued Heating &amp;amp; Cooling Contractor License from the &lt;a href="https://www.nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating &amp;amp; Fire Sprinkler Contractors&lt;/a&gt;. NC issues three heating-license classifications &amp;mdash; &lt;strong&gt;H-1&lt;/strong&gt; (unlimited scope), &lt;strong&gt;H-2&lt;/strong&gt; (limited to systems below specified tonnage/BTU thresholds), and &lt;strong&gt;H-3&lt;/strong&gt; (packaged-unit specialty). For typical Charlotte residential work, any of the three classifications can be sufficient depending on the job scope; verifying the contractor&amp;rsquo;s active license with the NC Board at 919-875-3612 before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by &lt;strong&gt;Mecklenburg County Code Enforcement (LUESA)&lt;/strong&gt;; contact LUESA directly for the current fee schedule. For current &lt;strong&gt;Duke Energy Carolinas&lt;/strong&gt; Smart $aver rebate amounts and &lt;strong&gt;Piedmont Natural Gas&lt;/strong&gt; incentives, visit the utilities&amp;rsquo; sites directly or check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Charlotte ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2599,8 +2599,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License (CMC-C)&lt;/strong&gt; issued by the Tennessee Board for Licensing Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Chattanooga are set by the City of Chattanooga Land Development Office. Contact the Office directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio OCILB Licensing &amp;amp; Local Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Cleveland must hold a current state-issued HVAC Contractor License from the &lt;strong&gt;Ohio Construction Industry Licensing Board (OCILB)&lt;/strong&gt;, administered by the Ohio Department of Commerce. OCILB &lt;em&gt;&amp;ldquo;licenses Ohio electrical, HVAC, plumbing, hydronics, and refrigeration contractors.&amp;rdquo;&lt;/em&gt; Cleveland does not issue a separate municipal HVAC contractor license &amp;mdash; the state OCILB credential is the formal requirement. Verifying a contractor&amp;rsquo;s active OCILB HVAC license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Cleveland Department of Building &amp;amp; Housing&lt;/strong&gt;; contact the department directly for the current fee schedule.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cleveland is served by &lt;strong&gt;The Illuminating Company&lt;/strong&gt; (a FirstEnergy subsidiary) for electricity and, as of 2024, by &lt;strong&gt;Enbridge Gas Ohio&lt;/strong&gt; for natural gas (Dominion Energy Ohio was acquired by Enbridge Gas in the 2023&amp;ndash;2024 transaction). For current residential rebate dollar amounts from both utilities, check firstenergycorp.com and enbridgegas.com/ohio directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Cleveland ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cleveland is served by &lt;strong&gt;The Illuminating Company&lt;/strong&gt; (a FirstEnergy subsidiary) for electricity and, as of 2024, by &lt;strong&gt;Enbridge Gas Ohio&lt;/strong&gt; for natural gas (Dominion Energy Ohio was acquired by Enbridge Gas in the 2023&amp;ndash;2024 transaction). For current residential rebate dollar amounts from both utilities, check firstenergycorp.com and enbridgegas.com/ohio directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Cleveland ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pikes Peak Regional Building Department (Unique Structure)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs operates under a distinctive permitting and licensing structure: permits and contractor licenses are administered by the &lt;a href="https://www.pprbd.org/" target="_blank" rel="nofollow noopener"&gt;Pikes Peak Regional Building Department (PPRBD)&lt;/a&gt; &amp;mdash; a joint regional authority covering Colorado Springs, El Paso County, and surrounding jurisdictions, rather than city-specific departments. Colorado does not issue a statewide HVAC contractor license; PPRBD handles mechanical contractor licensing for the region. Verifying a contractor&amp;rsquo;s active PPRBD license before authorizing work is the baseline due-diligence step. Contact PPRBD directly for the current mechanical permit fee schedule.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Colorado Springs Utilities (Four-Service Municipal) &amp;amp; Federal Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs is served by &lt;strong&gt;Colorado Springs Utilities (CSU)&lt;/strong&gt; &amp;mdash; a rare four-service municipal utility providing electricity, natural gas, water, and wastewater under a single entity owned by the City. For current CSU residential rebate dollar amounts (heat pump, smart thermostat, insulation, solar), visit csu.org directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year total, with $2,000/year cap for heat pumps and $1,200/year for other efficient property).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs is served by &lt;strong&gt;Colorado Springs Utilities (CSU)&lt;/strong&gt; &amp;mdash; a rare four-service municipal utility providing electricity, natural gas, water, and wastewater under a single entity owned by the City. For current CSU residential rebate dollar amounts (heat pump, smart thermostat, insulation, solar), visit csu.org directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR ACR License: Class A vs. Class B&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Dallas must hold a current Air Conditioning and Refrigeration (ACR) Contractor license issued by the &lt;a href="https://www.tdlr.texas.gov/acr/contractor-apply.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by &lt;strong&gt;Texas Administrative Code Title 16 Chapter 75&lt;/strong&gt;. The two classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; &lt;em&gt;&amp;ldquo;allows you to work on any size unit&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Class B&lt;/strong&gt; &lt;em&gt;&amp;ldquo;allows you to work on cooling systems of 25 tons and under, and heating systems of 1.5 million BTUs/hour and under&amp;rdquo;&lt;/em&gt; (residential and light commercial). Licensure requires &lt;em&gt;&amp;ldquo;at least 48 months of practical experience in air-conditioning and refrigeration-related work under the supervision of a licensed air conditioning and refrigeration contractor in the past 72 months.&amp;rdquo;&lt;/em&gt; Insurance minimums are also tiered: &lt;strong&gt;Class A requires $300,000 per occurrence / $600,000 aggregate&lt;/strong&gt;; &lt;strong&gt;Class B requires $100,000 per occurrence / $200,000 aggregate&lt;/strong&gt;. For typical Dallas residential work, a Class B contractor is fully qualified and sufficient &amp;mdash; Class A matters only for commercial projects above 25 tons.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Deregulated Retail Electricity&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dallas electricity distribution is handled by &lt;strong&gt;Oncor Electric Delivery&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Dallas are typically administered by your chosen REP, not Oncor directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Dallas ZIP, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Atmos Energy administers any natural-gas-specific rebates. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Dallas Building Inspection Division&lt;/strong&gt;; contact Building Inspection at 320 E. Jefferson Blvd, Room 118, for the current mechanical permit fee schedule.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dallas electricity distribution is handled by &lt;strong&gt;Oncor Electric Delivery&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Dallas are typically administered by your chosen REP, not Oncor directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Dallas ZIP, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Atmos Energy administers any natural-gas-specific rebates. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Dallas Building Inspection Division&lt;/strong&gt;; contact Building Inspection at 320 E. Jefferson Blvd, Room 118, for the current mechanical permit fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3506,11 +3506,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio HVAC Contractor Licensing (OCILB)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ohio requires HVAC contractors to hold an &lt;strong&gt;HVAC Contractor License&lt;/strong&gt; issued by the Ohio Construction Industry Licensing Board (OCILB). The OCILB administers examinations and issues licenses for HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current OCILB license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;AES Ohio (formerly Dayton Power &amp;amp; Light) is the primary electric utility for the Dayton area. Current xlsx data indicates no active HVAC rebate program from AES Ohio at the time of research. Contact AES Ohio directly to verify whether any residential HVAC incentives have been introduced. Any utility rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;AES Ohio (formerly Dayton Power &amp;amp; Light) is the primary electric utility for the Dayton area. Current xlsx data indicates no active HVAC rebate program from AES Ohio at the time of research. Contact AES Ohio directly to verify whether any residential HVAC incentives have been introduced.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Dayton are set by the City of Dayton Building Inspection Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump Performance at Altitude&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Denver&amp;rsquo;s 5,862 HDD and routine sub-freezing winter temperatures put it at the threshold where cold-climate-rated heat pumps matter. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Cold climate heat pumps are designed to perform in temperatures as low as 5&amp;deg;F&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;if you reside in an area experiencing regular sub-freezing winter temperatures, the DOE suggests considering systems bearing an ENERGY STAR Cold Climate label for optimal performance.&amp;rdquo;&lt;/em&gt; For Denver specifically, that guidance stacks on top of the altitude-derating factor: a heat pump rated for X BTU/hr at sea level will produce meaningfully less capacity at 5,280 ft, so proper sizing at altitude (not a straight replacement of the old unit&amp;rsquo;s nameplate capacity) is essential.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado does not issue a statewide HVAC contractor license. Instead, Denver handles HVAC contractor licensing at the municipal level through &lt;a href="https://www.denvergov.org/Government/Agencies-Departments-Offices/Agencies-Departments-Offices-Directory/Community-Planning-and-Development/Contractor-Licensing" target="_blank" rel="nofollow noopener"&gt;Denver Community Planning and Development&amp;rsquo;s Contractor Licensing division&lt;/a&gt;. Per the CPD licensing page: &lt;em&gt;&amp;ldquo;A supervisor certificate &amp;mdash; or employing someone who holds a supervisor certificate &amp;mdash; is required before obtaining a contractor&amp;rsquo;s license,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;licenses and certificates must be renewed every 1&amp;ndash;3 years, depending on your license type.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active Denver CPD license before authorizing work is the critical due-diligence step for Denver homeowners &amp;mdash; more so than in states with a statewide board, because the municipal license is the only formal credential. Permit fees for residential mechanical work are set by CPD and can be confirmed by contacting the department at (720) 865-2780. For current &lt;strong&gt;Xcel Energy Colorado&lt;/strong&gt; rebate dollar amounts, see the utility&amp;rsquo;s residential rebates page or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Denver ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000 per-year cap for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado does not issue a statewide HVAC contractor license. Instead, Denver handles HVAC contractor licensing at the municipal level through &lt;a href="https://www.denvergov.org/Government/Agencies-Departments-Offices/Agencies-Departments-Offices-Directory/Community-Planning-and-Development/Contractor-Licensing" target="_blank" rel="nofollow noopener"&gt;Denver Community Planning and Development&amp;rsquo;s Contractor Licensing division&lt;/a&gt;. Per the CPD licensing page: &lt;em&gt;&amp;ldquo;A supervisor certificate &amp;mdash; or employing someone who holds a supervisor certificate &amp;mdash; is required before obtaining a contractor&amp;rsquo;s license,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;licenses and certificates must be renewed every 1&amp;ndash;3 years, depending on your license type.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active Denver CPD license before authorizing work is the critical due-diligence step for Denver homeowners &amp;mdash; more so than in states with a statewide board, because the municipal license is the only formal credential. Permit fees for residential mechanical work are set by CPD and can be confirmed by contacting the department at (720) 865-2780. For current &lt;strong&gt;Xcel Energy Colorado&lt;/strong&gt; rebate dollar amounts, see the utility&amp;rsquo;s residential rebates page or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Denver ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3710,11 +3710,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Iowa HVAC Contractor Licensing (DIAL)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Iowa requires mechanical contractors to hold a &lt;strong&gt;Mechanical Contractor License&lt;/strong&gt; issued by the Iowa Division of Insurance, Audit, and Licensing (DIAL). The DIAL administers examinations and issues licenses for mechanical/HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current DIAL license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;MidAmerican Energy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;MidAmerican Energy administers residential home energy discounts and rebates for its Des Moines service territory. Contact MidAmerican Energy directly or visit the MidAmerican Energy home rebates page for the current heat pump, smart thermostat, and central AC rebate amounts. MidAmerican rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;MidAmerican Energy administers residential home energy discounts and rebates for its Des Moines service territory. Contact MidAmerican Energy directly or visit the MidAmerican Energy home rebates page for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Des Moines are set by the City of Des Moines Permit and Development Center. Contact the Center directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;El Paso Electric Residential Rebates (2025)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.epelectric.com/energy-efficiency/texas-residential-energy-efficiency-programs/texas-residential-energy-rebates-and-incentives" target="_blank" rel="nofollow noopener"&gt;El Paso Electric Texas Residential Solutions Program catalog&lt;/a&gt;, current 2025 rebate programs include: &lt;strong&gt;Smart Thermostat Rebate&lt;/strong&gt; (ENERGY STAR Certified models, through December 31, 2025), &lt;strong&gt;Evaporative/Refrigerated Cooling Rebate&lt;/strong&gt;, &lt;strong&gt;Heat Pump Water Heater Rebate&lt;/strong&gt;, and &lt;strong&gt;Direct Install Measures Rebate&lt;/strong&gt; &amp;mdash; each with its own application form. Program contact: &lt;em&gt;&amp;ldquo;(915) 255-4300 or epe.residential@clearesult.com.&amp;rdquo;&lt;/em&gt; Dollar amounts for each tier are published in the individual rebate application PDFs; visit the EPE rebates page directly for current figures.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in El Paso must hold a current Air Conditioning and Refrigeration (ACR) Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by Texas Occupations Code Chapter 1302 and 16 TAC Chapter 75. Per TDLR: &lt;em&gt;&amp;ldquo;Contractors who install, repair, or maintain systems related to air conditioning, refrigeration, or heating must have a TDLR license and ACR companies must employ an ACR contractor in each permanent location.&amp;rdquo;&lt;/em&gt; Class A covers any size unit; Class B is limited to 25 tons cooling / 1.5 million Btu heating. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of El Paso Development Services Department&lt;/strong&gt;; contact the One-Stop Shop at (915) 212-0104 for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in El Paso must hold a current Air Conditioning and Refrigeration (ACR) Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by Texas Occupations Code Chapter 1302 and 16 TAC Chapter 75. Per TDLR: &lt;em&gt;&amp;ldquo;Contractors who install, repair, or maintain systems related to air conditioning, refrigeration, or heating must have a TDLR license and ACR companies must employ an ACR contractor in each permanent location.&amp;rdquo;&lt;/em&gt; Class A covers any size unit; Class B is limited to 25 tons cooling / 1.5 million Btu heating. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of El Paso Development Services Department&lt;/strong&gt;; contact the One-Stop Shop at (915) 212-0104 for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4089,8 +4089,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oregon requires HVAC contractors to hold an &lt;strong&gt;HVAC Specialty Contractor license&lt;/strong&gt; issued by the Oregon Construction Contractors Board (CCB). The CCB administers licensing for all construction-related trades statewide. Verify a specific contractor&amp;rsquo;s current CCB license status before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Eugene are set by the City of Eugene Building &amp;amp; Permit Services. Contact Building &amp;amp; Permit Services directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit stacks with EWEB residential rebates.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4266,11 +4266,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina HVAC Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Carolina requires HVAC contractors to hold a &lt;strong&gt;Heating Contractor License&lt;/strong&gt; (H-1, H-2, or H-3 classification depending on scope) issued by the North Carolina Board of Examiners of Plumbing, Heating and Fire Sprinkler Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Progress Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Progress administers the Smart $aver residential rebate program for its Fayetteville service territory. Contact Duke Energy Progress directly or visit the Duke Energy Smart $aver page for the current heat pump, smart thermostat, and central AC rebate amounts. Duke Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Progress administers the Smart $aver residential rebate program for its Fayetteville service territory. Contact Duke Energy Progress directly or visit the Duke Energy Smart $aver page for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fayetteville are set by the City of Fayetteville Permitting &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4446,11 +4446,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Indiana HVAC Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Fort Wayne must obtain permits through the Fort Wayne Department of Planning Services. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting, and confirm they will pull the required local permits.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;I&amp;amp;M / AEP Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana Michigan Power (I&amp;amp;M), an AEP company, administers the Energy Savings Rebate Program for its Fort Wayne service territory. Contact I&amp;amp;M directly for the current heat pump, smart thermostat, and central AC rebate amounts. I&amp;amp;M rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana Michigan Power (I&amp;amp;M), an AEP company, administers the Energy Savings Rebate Program for its Fort Wayne service territory. Contact I&amp;amp;M directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fort Wayne are set by the Fort Wayne Department of Planning Services. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dry-Climate Cooling: Whole-House Fans &amp;amp; Evap Coolers&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fresno&amp;rsquo;s dry summers with cool overnight lows make passive cooling strategies realistic supplements or replacements for refrigerant cooling. Per the &lt;a href="https://www.energy.gov/energysaver/cooling-whole-house-fan" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Whole House Fans&lt;/a&gt;: &lt;em&gt;&amp;ldquo;They are most effective when outdoor temperatures are lower than indoor temperatures, as they quickly draw in the cooler outdoor air while exhausting warmer indoor air,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;whole house fans do not dehumidify air like air conditioners and heat pumps, making them less suitable for high-humidity climates.&amp;rdquo;&lt;/em&gt; For Fresno homeowners, running a whole-house fan for 60&amp;ndash;90 minutes after sunset can drop indoor temperatures 15&amp;ndash;20&amp;deg;F using a fraction of the energy refrigerant AC would consume. Evaporative (swamp) coolers are also viable in Fresno&amp;rsquo;s dry summer profile.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Fresno must hold a California C-20 Warm-Air Heating, Ventilating and Air-Conditioning contractor license from the California Contractors State License Board. Verifying the contractor&amp;rsquo;s active C-20 license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Fresno Department of Planning &amp;amp; Development, Building and Safety Services&lt;/strong&gt;; contact Building and Safety directly for the current fee schedule. Fresno is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas; for current residential rebate dollar amounts, visit pge.com or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Fresno ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Fresno must hold a California C-20 Warm-Air Heating, Ventilating and Air-Conditioning contractor license from the California Contractors State License Board. Verifying the contractor&amp;rsquo;s active C-20 license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Fresno Department of Planning &amp;amp; Development, Building and Safety Services&lt;/strong&gt;; contact Building and Safety directly for the current fee schedule. Fresno is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas; for current residential rebate dollar amounts, visit pge.com or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Fresno ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4974,11 +4974,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Arizona HVAC Contractor Licensing (ROC)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arizona requires HVAC contractors to hold an &lt;strong&gt;R-39 (residential) or C-39 (commercial) HVAC License&lt;/strong&gt; issued by the Arizona Registrar of Contractors (ROC). The ROC administers examinations and issues licenses for HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current ROC license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;APS Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arizona Public Service (APS) administers residential rebates and the Efficiency Arizona HEAR Program for its Glendale service territory. Contact APS directly for the current heat pump, smart thermostat, and central AC rebate amounts. APS rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arizona Public Service (APS) administers residential rebates and the Efficiency Arizona HEAR Program for its Glendale service territory. Contact APS directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Glendale are set by the City of Glendale Building Safety Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5154,11 +5154,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Michigan HVAC Contractor Licensing (LARA)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Michigan requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License&lt;/strong&gt; issued by the Michigan Department of Licensing and Regulatory Affairs (LARA). The LARA administers examinations and issues licenses for mechanical contracting statewide. Verify a specific contractor&amp;rsquo;s current LARA license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Consumers Energy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Consumers Energy administers residential heating and cooling rebates for its Grand Rapids service territory. Contact Consumers Energy directly for the current heat pump, smart thermostat, and gas furnace rebate amounts. Consumers Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Consumers Energy administers residential heating and cooling rebates for its Grand Rapids service territory. Contact Consumers Energy directly for the current heat pump, smart thermostat, and gas furnace rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Grand Rapids are set by the City of Grand Rapids Development Center. Contact the Center directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5256,11 +5256,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Connecticut Contractor Licensing (DCP S-1)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Connecticut requires HVAC contractors to hold a &lt;strong&gt;Heating, Piping and Cooling Contractor License (S-1 classification)&lt;/strong&gt; issued by the Connecticut Department of Consumer Protection (DCP). The DCP administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DCP license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energize Connecticut / Eversource Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize Connecticut, in partnership with Eversource, administers residential heat pump incentives for Hartford customers. Contact Energize CT or Eversource directly for the current heat pump rebate amounts. Energize CT rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize Connecticut, in partnership with Eversource, administers residential heat pump incentives for Hartford customers. Contact Energize CT or Eversource directly for the current heat pump rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Hartford are set by the City of Hartford Department of Development Services, Licenses &amp;amp; Inspections. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR Air Conditioning and Refrigeration License&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Houston must hold a current Air Conditioning and Refrigeration (ACR) Contractor license issued by the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;. The licensing program is governed by &lt;strong&gt;Texas Occupations Code Chapter 1302&lt;/strong&gt; (the Air Conditioning and Refrigeration Contractors Law) and &lt;strong&gt;Texas Administrative Code Title 16 Chapter 75&lt;/strong&gt; (the implementing administrative rules). Texas ACR licenses are issued in two classes distinguished by permitted equipment size &amp;mdash; residential/light-commercial contractors typically hold one class and large-commercial contractors hold the other. Verifying a contractor&amp;rsquo;s active TDLR license before authorizing work is the baseline due-diligence step for every Houston homeowner; TDLR publishes a public license-lookup tool at tdlr.texas.gov.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates, Permits &amp;amp; Deregulated Retail Electricity&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Houston&amp;rsquo;s electricity distribution is handled by &lt;strong&gt;CenterPoint Energy&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Houston are typically administered by your chosen REP, not by CenterPoint directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Houston ZIP code, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Permit fees for residential mechanical work are set by the &lt;strong&gt;Houston Permitting Center&lt;/strong&gt; (Mechanical Section, 832.394.8850); contact the center directly for the current fee schedule as amounts are updated periodically. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Houston&amp;rsquo;s electricity distribution is handled by &lt;strong&gt;CenterPoint Energy&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Houston are typically administered by your chosen REP, not by CenterPoint directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Houston ZIP code, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Permit fees for residential mechanical work are set by the &lt;strong&gt;Houston Permitting Center&lt;/strong&gt; (Mechanical Section, 832.394.8850); contact the center directly for the current fee schedule as amounts are updated periodically. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5619,8 +5619,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama requires HVAC contractors to hold a license issued by the &lt;strong&gt;Alabama Board of Heating, Air Conditioning, and Refrigeration Contractors (Board of HACR Contractors)&lt;/strong&gt;. The Board administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Huntsville are set by the City of Huntsville Inspection Services Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5816,11 +5816,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California HVAC Contractor Licensing (CSLB C-20)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning (HVAC) License&lt;/strong&gt; issued by the California Contractors State License Board (CSLB). The CSLB administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current CSLB C-20 license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SCE Rebates &amp;amp; TECH Clean California&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southern California Edison (SCE) administers the Home Performance Plus program and participates in the TECH Clean California initiative for residential HVAC electrification in its Irvine service territory. Contact SCE directly for the current heat pump, smart thermostat, and central AC rebate amounts. SCE rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southern California Edison (SCE) administers the Home Performance Plus program and participates in the TECH Clean California initiative for residential HVAC electrification in its Irvine service territory. Contact SCE directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Irvine are set by the Community Development Department, Building &amp;amp; Safety Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Coastal Corrosion &amp;amp; Humidity Control&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jacksonville&amp;rsquo;s Atlantic coastal exposure and 53+ inches of annual rainfall combine to make outdoor-unit durability and humidity management central HVAC concerns. Per the &lt;a href="https://www.energy.gov/energysaver/weatherize/air-sealing-your-home" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt; and DOE hot-humid climate recommendations, coastal installations benefit from coastal-duty coil coatings on outdoor condensers and more frequent condenser rinsing to remove salt deposits. Oversized single-stage AC equipment in this climate will short-cycle before pulling humidity from the air &amp;mdash; leaving homes uncomfortably damp even at 72&amp;deg;F. Proper Manual J sizing and variable-capacity equipment are the right standard.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;JEA Residential Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jacksonville is served by &lt;strong&gt;JEA (Jacksonville Electric Authority)&lt;/strong&gt;, a municipal electric, water, and sewer utility. Per the &lt;a href="https://www.jea.com/residential_customers/residential_rebates/" target="_blank" rel="nofollow noopener"&gt;JEA Residential Rebates page&lt;/a&gt;, current HVAC-related rebates include: &lt;strong&gt;heating and cooling system $200 rebate&lt;/strong&gt;; &lt;strong&gt;smart thermostat $50 rebate&lt;/strong&gt;; &lt;strong&gt;attic insulation $200 rebate&lt;/strong&gt;; &lt;strong&gt;heat pump water heater $350 rebate&lt;/strong&gt; (JEA notes an ENERGY STAR-certified HPWH saves a four-person household approximately $550/year on electric bills). Natural-gas customers are served by TECO Peoples Gas, which administers separate rebates for the 3.1% of Jacksonville homes using gas heat. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jacksonville is served by &lt;strong&gt;JEA (Jacksonville Electric Authority)&lt;/strong&gt;, a municipal electric, water, and sewer utility. Per the &lt;a href="https://www.jea.com/residential_customers/residential_rebates/" target="_blank" rel="nofollow noopener"&gt;JEA Residential Rebates page&lt;/a&gt;, current HVAC-related rebates include: &lt;strong&gt;heating and cooling system $200 rebate&lt;/strong&gt;; &lt;strong&gt;smart thermostat $50 rebate&lt;/strong&gt;; &lt;strong&gt;attic insulation $200 rebate&lt;/strong&gt;; &lt;strong&gt;heat pump water heater $350 rebate&lt;/strong&gt; (JEA notes an ENERGY STAR-certified HPWH saves a four-person household approximately $550/year on electric bills). Natural-gas customers are served by TECO Peoples Gas, which administers separate rebates for the 3.1% of Jacksonville homes using gas heat. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida Contractor Licensing (Statute 489.105)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Jacksonville must hold a current Florida Certified Air Conditioning Contractor license, administered by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, the two license classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt; covering central air conditioning, refrigeration, heating, and ventilating systems; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system.&amp;rdquo;&lt;/em&gt; For typical Jacksonville residential work, a Class B contractor is fully qualified. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Jacksonville Building Inspection Division&lt;/strong&gt; under Municipal Code of Ordinances Chapter 320; contact the division directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
@@ -6254,11 +6254,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kansas City Contractor Licensing (Municipal)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Missouri does not issue a statewide HVAC contractor license. Instead, &lt;strong&gt;Kansas City requires a municipal mechanical trade license&lt;/strong&gt; for HVAC contractors operating within city limits. Verify a contractor&amp;rsquo;s current KC trade license and insurance before contracting. Contractors working in Johnson County, KS (Overland Park side of metro) may face different Kansas-side requirements.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Evergy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Evergy administers the FastTrack HVAC PAYS Program for residential customers in the Kansas City area. Contact Evergy directly for the current heat pump, smart thermostat, and central AC rebate amounts. Evergy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Evergy administers the FastTrack HVAC PAYS Program for residential customers in the Kansas City area. Contact Evergy directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Kansas City are set by the Kansas City Planning &amp;amp; Development Permits Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6359,8 +6359,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License (CMC-C)&lt;/strong&gt; issued by the Tennessee Board for Licensing Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Knoxville are set by the City of Knoxville Plans Review &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6461,8 +6461,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;AEP Texas administers the CoolSaver Program for residential customers in its Laredo service territory. Texas operates a deregulated electricity market, so rebates may flow through the retail electricity provider rather than the TDU. Contact AEP Texas or your retail electricity provider directly for the current heat pump and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Laredo are set by the City of Laredo Building Development Services. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Attic Ducts in a 110&amp;deg;F Climate&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Most Las Vegas homes route central-air ductwork through unconditioned attics &amp;mdash; spaces that regularly exceed 140&amp;deg;F during summer afternoons. Per the &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Central Air Conditioning&lt;/a&gt;, best-practice installation &lt;em&gt;&amp;ldquo;installs ductwork within conditioned space whenever possible, not in unconditioned spaces like attics or garages.&amp;rdquo;&lt;/em&gt; DOE also advises: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is the correct size for your home. An oversized unit won&amp;rsquo;t adequately remove humidity, while an undersized unit won&amp;rsquo;t cool effectively on the hottest days.&amp;rdquo;&lt;/em&gt; For Las Vegas specifically, with 3,720 annual CDD and extreme attic temperatures, every foot of uninsulated or leaky attic duct loses significant cooling capacity. Homeowners planning an HVAC replacement should explicitly ask contractors about R-8 insulated duct with aggressive joint mastic sealing, or moving ducts into the conditioned envelope where feasible.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Nevada C-21 Refrigeration &amp;amp; Air Conditioning License&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in the Las Vegas Valley must hold a current license from the &lt;a href="https://www.nvcontractorsboard.com/licensing/license-classifications/" target="_blank" rel="nofollow noopener"&gt;Nevada State Contractors Board (NSCB)&lt;/a&gt;. The relevant classification is &lt;strong&gt;C-21 Refrigeration and Air Conditioning&lt;/strong&gt;, which falls under the NSCB&amp;rsquo;s Classification C (Specialty Contractor) category covering 42 distinct subcontracting fields. The detailed scope of C-21 work is codified in &lt;strong&gt;Chapter 624 of the Nevada Administrative Code&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active C-21 license via the NSCB&amp;rsquo;s public license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Las Vegas Building &amp;amp; Safety Department&lt;/strong&gt;; contact Building &amp;amp; Safety at 702-229-6251 or BuildingInfo@LasVegasNevada.gov for the current mechanical permit fee schedule. For current &lt;strong&gt;NV Energy PowerShift&lt;/strong&gt; heating and cooling rebate amounts, see nvenergy.com/save-with-powershift directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in the Las Vegas Valley must hold a current license from the &lt;a href="https://www.nvcontractorsboard.com/licensing/license-classifications/" target="_blank" rel="nofollow noopener"&gt;Nevada State Contractors Board (NSCB)&lt;/a&gt;. The relevant classification is &lt;strong&gt;C-21 Refrigeration and Air Conditioning&lt;/strong&gt;, which falls under the NSCB&amp;rsquo;s Classification C (Specialty Contractor) category covering 42 distinct subcontracting fields. The detailed scope of C-21 work is codified in &lt;strong&gt;Chapter 624 of the Nevada Administrative Code&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active C-21 license via the NSCB&amp;rsquo;s public license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Las Vegas Building &amp;amp; Safety Department&lt;/strong&gt;; contact Building &amp;amp; Safety at 702-229-6251 or BuildingInfo@LasVegasNevada.gov for the current mechanical permit fee schedule. For current &lt;strong&gt;NV Energy PowerShift&lt;/strong&gt; heating and cooling rebate amounts, see nvenergy.com/save-with-powershift directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6660,11 +6660,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kentucky HVAC Contractor Licensing (DHBC)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky requires HVAC contractors to hold a &lt;strong&gt;Master HVAC Contractor License&lt;/strong&gt; issued by the Kentucky Department of Housing, Buildings and Construction (DHBC). The DHBC administers examinations and issues licenses for HVAC contracting statewide. Verify a specific contractor&amp;rsquo;s current DHBC license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Kentucky Utilities (KU) Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky Utilities (KU), a PPL Company, administers residential rebates for its Lexington-Fayette service territory. Contact KU directly for the current heat pump, smart thermostat, and central AC rebate amounts. KU rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky Utilities (KU), a PPL Company, administers residential rebates for its Lexington-Fayette service territory. Contact KU directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lexington-Fayette County are set by the Lexington-Fayette Urban County Government Division of Building Inspection. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6765,8 +6765,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nebraska does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Lincoln must obtain permits through local authorities. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lincoln are set by local permitting authorities. Contact the City of Lincoln Building &amp;amp; Safety Department for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6864,11 +6864,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Arkansas HVAC Contractor Licensing (DLL)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Arkansas requires HVAC contractors to hold an &lt;strong&gt;HVAC/R Contractor License&lt;/strong&gt; issued by the Arkansas Department of Labor and Licensing (DLL). The DLL administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DLL license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Arkansas Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Arkansas administers residential energy efficiency programs for its Little Rock service territory. Contact Entergy Arkansas directly for the current heat pump, smart thermostat, and central AC rebate amounts. Entergy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Arkansas administers residential energy efficiency programs for its Little Rock service territory. Contact Entergy Arkansas directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Little Rock are set by local permitting authorities. Contact the City of Little Rock for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6969,8 +6969,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning (HVAC) License&lt;/strong&gt; issued by the California Contractors State License Board (CSLB). Verify a specific contractor&amp;rsquo;s current CSLB C-20 license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Los Angeles are set by the City of Los Angeles Department of Building and Safety (LADBS). Contact LADBS directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7167,8 +7167,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Texas requires HVAC contractors to hold an &lt;strong&gt;Air Conditioning and Refrigeration Contractor License&lt;/strong&gt; issued by the Texas Department of Licensing and Regulation (TDLR). Verify a specific contractor&amp;rsquo;s current TDLR license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lubbock are set by local permitting authorities. Contact the City of Lubbock for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7264,13 +7264,13 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Heat Pump &amp;amp; Snowfall Considerations&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energystar.gov/products/heating_cooling/heat_pumps_air_source/key_product_criteria" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Version 6.2 Heat Pump Final Specification&lt;/a&gt;, the Cold Climate designation requires a heat pump to deliver a &lt;strong&gt;COP of at least 1.75 at 5&amp;deg;F&lt;/strong&gt; and retain &lt;strong&gt;at least 70% of its 47&amp;deg;F rated heating capacity at 5&amp;deg;F&lt;/strong&gt;. Madison&amp;rsquo;s 7,138.2 HDD profile and recurring sub-zero winter extremes make the Cold Climate spec the practical floor for any heat pump considered here. The 51.8-inch annual snowfall normal also drives outdoor unit clearance and defrost-cycle planning &amp;mdash; condensers benefit from elevated mounting (typically 12&amp;ndash;24 inches above grade) and clear winter access for service.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Wisconsin Focus on Energy Rebates (Statewide Administrator)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wisconsin&amp;rsquo;s statewide energy-efficiency utility, &lt;a href="https://focusonenergy.com/residential/heating-and-cooling" target="_blank" rel="nofollow noopener"&gt;Focus on Energy&lt;/a&gt;, administers residential HVAC rebates that apply to Madison Gas and Electric (MGE) customers. Current air-source heat pump instant discounts are tiered by efficiency: &lt;strong&gt;Tier 1 (SEER2 15.2 / HSPF2 8.1) = $400 standard / $600 income-qualified&lt;/strong&gt;, &lt;strong&gt;Tier 2 (SEER2 15.2 / HSPF2 8.5) = $500 / $700&lt;/strong&gt;, &lt;strong&gt;Tier 3 (SEER2 16.0 / HSPF2 9.0) = $600 / $800&lt;/strong&gt;, and &lt;strong&gt;Tier 4 (SEER2 16.0 / HSPF2 10.0) = $700 / $900&lt;/strong&gt;. Certified geothermal heat pump rebates are &lt;strong&gt;$1,000&lt;/strong&gt; for homes with natural gas service and &lt;strong&gt;$750&lt;/strong&gt; without. These pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wisconsin&amp;rsquo;s statewide energy-efficiency utility, &lt;a href="https://focusonenergy.com/residential/heating-and-cooling" target="_blank" rel="nofollow noopener"&gt;Focus on Energy&lt;/a&gt;, administers residential HVAC rebates that apply to Madison Gas and Electric (MGE) customers. Current air-source heat pump instant discounts are tiered by efficiency: &lt;strong&gt;Tier 1 (SEER2 15.2 / HSPF2 8.1) = $400 standard / $600 income-qualified&lt;/strong&gt;, &lt;strong&gt;Tier 2 (SEER2 15.2 / HSPF2 8.5) = $500 / $700&lt;/strong&gt;, &lt;strong&gt;Tier 3 (SEER2 16.0 / HSPF2 9.0) = $600 / $800&lt;/strong&gt;, and &lt;strong&gt;Tier 4 (SEER2 16.0 / HSPF2 10.0) = $700 / $900&lt;/strong&gt;. Certified geothermal heat pump rebates are &lt;strong&gt;$1,000&lt;/strong&gt; for homes with natural gas service and &lt;strong&gt;$750&lt;/strong&gt; without.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Wisconsin HVAC Contractor Registration&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://dsps.wi.gov/Pages/Professions/HVACContractor/Default.aspx" target="_blank" rel="nofollow noopener"&gt;Wisconsin Department of Safety and Professional Services (DSPS)&lt;/a&gt;, &amp;ldquo;no person, entity or business may engage or offer to engage in installing or servicing heating, ventilating or air conditioning equipment unless the person, entity or business holds a registration issued by the Department.&amp;rdquo; Owner-occupants servicing HVAC equipment in their own residence are exempt. All initial applications, reinstatements, and renewals are submitted through Wisconsin&amp;rsquo;s online licensing portal at license.wi.gov. DSPS can be reached at (608) 266-2112 or (877) 617-1565.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Madison are set by the City of Madison Building Inspection Division. The current published fee schedule could not be retrieved verbatim at the time this page was authored; for current mechanical permit fees, contact Building Inspection at (608) 266-4551 or binspection@cityofmadison.com.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit is non-refundable and stacks with Focus on Energy rebates.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dehumidification Matters More Than Raw Cooling Capacity&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Memphis&amp;rsquo;s 54.94 inches of annual rainfall put humidity management at the center of every HVAC specification decision. Per the &lt;a href="https://www.energy.gov/energysaver/efficient-cooling-hot-humid-climates" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide to Efficient Cooling for Hot, Humid Climates&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Ensure your air conditioner is correctly sized to handle both cooling and dehumidification needs. Systems that are too large or too small can struggle with humidity control.&amp;rdquo;&lt;/em&gt; DOE further advises &lt;em&gt;&amp;ldquo;variable capacity equipment that can automatically adjust its cooling capacity to meet the current load operates frequently at efficient low speeds, delivering superior temperature and moisture management.&amp;rdquo;&lt;/em&gt; For Memphis, specifying a two-stage or variable-capacity system is often the difference between a house that feels cool and one that feels clammy even at 72&amp;deg;F.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;MLGW Municipal Combined Utility &amp;amp; TVA EnergyRight&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Memphis is served by &lt;strong&gt;MLGW (Memphis Light, Gas and Water)&lt;/strong&gt; &amp;mdash; a rare municipal utility that provides electricity, natural gas, AND water from the same agency. MLGW is a TVA electricity distributor and administers &lt;strong&gt;TVA EnergyRight&lt;/strong&gt; residential incentive programs for its customers, including heat pump loan programs. For current rebate dollar amounts and EnergyRight program details, visit mlgw.com and energyright.com directly. Natural-gas rebates for the 42.9% of Memphis homes using gas heat are also administered by MLGW as the gas distributor. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Memphis is served by &lt;strong&gt;MLGW (Memphis Light, Gas and Water)&lt;/strong&gt; &amp;mdash; a rare municipal utility that provides electricity, natural gas, AND water from the same agency. MLGW is a TVA electricity distributor and administers &lt;strong&gt;TVA EnergyRight&lt;/strong&gt; residential incentive programs for its customers, including heat pump loan programs. For current rebate dollar amounts and EnergyRight program details, visit mlgw.com and energyright.com directly. Natural-gas rebates for the 42.9% of Memphis homes using gas heat are also administered by MLGW as the gas distributor. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee CMC-C Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Memphis must hold a current state-issued HVAC Mechanical Contractor (&lt;strong&gt;CMC-C&lt;/strong&gt;) license from the &lt;a href="https://www.tn.gov/commerce/regboards.html" target="_blank" rel="nofollow noopener"&gt;Tennessee Board for Licensing Contractors&lt;/a&gt;, administered by the Tennessee Department of Commerce and Insurance. Tennessee requires state contractor licensure for projects above specific dollar thresholds; the CMC-C classification covers HVAC work. Verifying a contractor&amp;rsquo;s active CMC-C license via the Board&amp;rsquo;s public lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set jointly by the &lt;strong&gt;City of Memphis &amp;amp; Shelby County Office of Construction Code Enforcement&lt;/strong&gt; (unusual city-county joint permitting); contact Construction Code Enforcement directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
@@ -7866,11 +7866,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HVAC Contractor Licensing (HACR Board)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama requires HVAC contractors to hold a license issued by the &lt;strong&gt;Alabama Board of Heating, Air Conditioning, and Refrigeration Contractors (Board of HACR Contractors)&lt;/strong&gt;. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama Power Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama Power administers residential rebate programs for its Mobile service territory. Contact Alabama Power directly for the current heat pump, smart thermostat, and central AC rebate amounts. Alabama Power rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama Power administers residential rebate programs for its Mobile service territory. Contact Alabama Power directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Mobile are set by local permitting authorities. Contact the City of Mobile for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7971,8 +7971,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3B warm-dry climates like the Central Valley produce high sensible cooling loads with minimal humidity. The 25.8&amp;deg;F diurnal temperature swing (annual max 74.7&amp;deg;F minus annual min 48.9&amp;deg;F) means homes need both effective cooling for summer afternoons and reliable heating for Central Valley tule fog season winters.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Modesto are set by the City of Modesto Community &amp;amp; Economic Development Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana LSLBC Mechanical Contractor License&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in New Orleans must hold a current Mechanical Work Contractor license from the &lt;a href="https://lslbc.gov/exams-classifications/" target="_blank" rel="nofollow noopener"&gt;Louisiana State Licensing Board for Contractors (LSLBC)&lt;/a&gt; under Major Classification 6 (Mechanical) when project value exceeds &lt;strong&gt;$10,000&lt;/strong&gt;. The classification scope, per LSLBC: &lt;em&gt;&amp;ldquo;Hydraulic and pneumatic systems, including such components as heating, ventilation, air conditioning, refrigeration, hydronic and steam systems, pressure vessels, plumbing, gas piping, process piping, mechanical equipment, air and process heaters and seals, and air vacuums and filters.&amp;rdquo;&lt;/em&gt; Mechanical contractors performing plumbing work above the $10,000 threshold must also hold a master plumber license from the Louisiana State Plumbing Board.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits &amp;amp; Post-Katrina Flood Considerations&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of New Orleans Department of Safety &amp;amp; Permits&lt;/strong&gt;; per the &lt;a href="https://nola.gov/mechanical-permit/" target="_blank" rel="nofollow noopener"&gt;city&amp;rsquo;s Mechanical Permit page&lt;/a&gt;, fees &lt;em&gt;&amp;ldquo;vary based on components of work,&amp;rdquo;&lt;/em&gt; and applicants submit the HVAC Permit Application Supplement (D1-AC) with each application. Contact Safety &amp;amp; Permits at (504) 658-7100 for current line items. New Orleans&amp;rsquo;s post-Hurricane-Katrina building code emphasizes elevation requirements for outdoor mechanical equipment in flood-prone zones &amp;mdash; condenser pads must be set above Base Flood Elevation per FEMA flood-zone maps. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of New Orleans Department of Safety &amp;amp; Permits&lt;/strong&gt;; per the &lt;a href="https://nola.gov/mechanical-permit/" target="_blank" rel="nofollow noopener"&gt;city&amp;rsquo;s Mechanical Permit page&lt;/a&gt;, fees &lt;em&gt;&amp;ldquo;vary based on components of work,&amp;rdquo;&lt;/em&gt; and applicants submit the HVAC Permit Application Supplement (D1-AC) with each application. Contact Safety &amp;amp; Permits at (504) 658-7100 for current line items. New Orleans&amp;rsquo;s post-Hurricane-Katrina building code emphasizes elevation requirements for outdoor mechanical equipment in flood-prone zones &amp;mdash; condenser pads must be set above Base Flood Elevation per FEMA flood-zone maps. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NYC Construction Codes &amp;amp; Local Law 97&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NYC enforces its own Construction Codes (Administrative Code Title 28), not the state Uniform Code. The NYC Mechanical Code under Title 28 Chapter 7 governs HVAC work within the five boroughs. A distinctive NYC layer is Local Law 97 (LL97), which imposes greenhouse-gas emissions limits on most buildings over 25,000 square feet &amp;mdash; roughly 50,000 NYC properties. For homeowners in smaller buildings LL97 is not a direct compliance trigger, but it has accelerated heat-pump specification across mid-rise and high-rise residential stock. For current &lt;strong&gt;Con Edison&lt;/strong&gt; rebate amounts and &lt;strong&gt;NYSERDA NY Clean Heat&lt;/strong&gt; heat pump incentives (which are among the most generous in the U.S. for cold-climate air-source and ground-source systems), check coned.com and nyserda.ny.gov directly.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Federal Incentives&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York State does not issue a statewide HVAC contractor license. For work in NYC, the &lt;a href="https://www.nyc.gov/site/buildings/" target="_blank" rel="nofollow noopener"&gt;NYC Department of Buildings Licensed Trades&lt;/a&gt; issues credentials relevant to HVAC work &amp;mdash; including the &lt;strong&gt;Refrigeration Machine Operator&lt;/strong&gt; license and &lt;strong&gt;Oil Burner Installer&lt;/strong&gt; license for specific scopes. Verifying a contractor&amp;rsquo;s active DOB credential before authorizing work is the baseline due-diligence step. Permit fees for mechanical work are set by NYC DOB; fee amounts are codified in DOB fee rules under Administrative Code Title 28. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York State does not issue a statewide HVAC contractor license. For work in NYC, the &lt;a href="https://www.nyc.gov/site/buildings/" target="_blank" rel="nofollow noopener"&gt;NYC Department of Buildings Licensed Trades&lt;/a&gt; issues credentials relevant to HVAC work &amp;mdash; including the &lt;strong&gt;Refrigeration Machine Operator&lt;/strong&gt; license and &lt;strong&gt;Oil Burner Installer&lt;/strong&gt; license for specific scopes. Verifying a contractor&amp;rsquo;s active DOB credential before authorizing work is the baseline due-diligence step. Permit fees for mechanical work are set by NYC DOB; fee amounts are codified in DOB fee rules under Administrative Code Title 28. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NJ HVACR Contractor License (State Board)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Newark must hold a current license from the &lt;a href="https://www.njconsumeraffairs.gov/hvacr/Pages/default.aspx" target="_blank" rel="nofollow noopener"&gt;New Jersey State Board of Examiners of Heating, Ventilating, Air Conditioning and Refrigeration (HVACR) Contractors&lt;/a&gt;, administered by the NJ Division of Consumer Affairs. New Jersey is one of the few states with a dedicated HVACR-specific licensing board (separate from general contractor licensing). Per the Board: &lt;em&gt;&amp;ldquo;All heating, ventilating, air conditioning and refrigeration contractors must be licensed by the state and renew their licenses every two years,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;The Board ensures contractors meet all educational requirements for licensure.&amp;rdquo;&lt;/em&gt; Board contact: HVACR@dca.njoag.gov / (973) 504-6250 / P.O. Box 47031, Newark, NJ 07101 (the Board itself is headquartered in Newark).&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Rebates &amp;amp; Federal Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work in Newark are set by the &lt;strong&gt;Newark Office of Uniform Construction Code (UCC)&lt;/strong&gt;, which administers the New Jersey Uniform Construction Code (NJUCC); contact the UCC office at 920 Mayor Kenneth A. Gibson Blvd, 973-733-4311, for the current fee schedule. Newark is served by &lt;strong&gt;PSE&amp;amp;G&lt;/strong&gt; (Public Service Enterprise Group) for both electricity and natural gas; PSE&amp;amp;G runs the Home Energy Solutions program, and residents are eligible for the statewide &lt;a href="https://www.njcleanenergy.com/residential/home/home" target="_blank" rel="nofollow noopener"&gt;NJ Clean Energy Program&lt;/a&gt; which administers heat pump and other efficiency incentives. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work in Newark are set by the &lt;strong&gt;Newark Office of Uniform Construction Code (UCC)&lt;/strong&gt;, which administers the New Jersey Uniform Construction Code (NJUCC); contact the UCC office at 920 Mayor Kenneth A. Gibson Blvd, 973-733-4311, for the current fee schedule. Newark is served by &lt;strong&gt;PSE&amp;amp;G&lt;/strong&gt; (Public Service Enterprise Group) for both electricity and natural gas; PSE&amp;amp;G runs the Home Energy Solutions program, and residents are eligible for the statewide &lt;a href="https://www.njcleanenergy.com/residential/home/home" target="_blank" rel="nofollow noopener"&gt;NJ Clean Energy Program&lt;/a&gt; which administers heat pump and other efficiency incentives. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California C-20 Contractor License &amp;amp; BayREN&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Oakland must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; license from the &lt;a href="https://www.cslb.ca.gov/About_Us/Library/Licensing_Classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;California Contractors State License Board&lt;/a&gt;, per California Code of Regulations Title 16 Division 8 Article 3. C-20 scope covers &lt;em&gt;&amp;ldquo;warm-air heating systems and water heating heat pumps&amp;hellip;ventilating systems&amp;hellip;air-conditioning systems&amp;hellip;and the ducts, registers, flues, humidity and thermostatic controls and air filters in connection with any of these systems,&amp;rdquo;&lt;/em&gt; including solar-energy HVAC systems.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates, Permits &amp;amp; Federal Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oakland is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for electricity delivery and natural gas, while &lt;strong&gt;Ava Community Energy&lt;/strong&gt; (formerly East Bay Community Energy / EBCE) is the Community Choice Aggregator for electric generation. Oakland residents have access to &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; (80% cost share on core upgrades, homeowner capped at $1,000) plus PG&amp;amp;E and Ava-specific rebates. For current dollar amounts, visit bayren.org, pge.com, and avaenergy.org directly &amp;mdash; Ava&amp;rsquo;s incentive tool routes households through an eligibility filter (ZIP + income + household size) for the most current offers. Permit fees for residential mechanical work are set by the &lt;strong&gt;Oakland Planning &amp;amp; Building Department&lt;/strong&gt;; contact the department directly for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oakland is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for electricity delivery and natural gas, while &lt;strong&gt;Ava Community Energy&lt;/strong&gt; (formerly East Bay Community Energy / EBCE) is the Community Choice Aggregator for electric generation. Oakland residents have access to &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; (80% cost share on core upgrades, homeowner capped at $1,000) plus PG&amp;amp;E and Ava-specific rebates. For current dollar amounts, visit bayren.org, pge.com, and avaenergy.org directly &amp;mdash; Ava&amp;rsquo;s incentive tool routes households through an eligibility filter (ZIP + income + household size) for the most current offers. Permit fees for residential mechanical work are set by the &lt;strong&gt;Oakland Planning &amp;amp; Building Department&lt;/strong&gt;; contact the department directly for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Oklahoma CIB Mechanical Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Oklahoma City must hold a current license from the &lt;a href="https://oklahoma.gov/cib/your-industry/mechanical.html" target="_blank" rel="nofollow noopener"&gt;Oklahoma Construction Industries Board (CIB) Mechanical Industry program&lt;/a&gt;, governed by &lt;strong&gt;59 O.S. Section 1850.1 et seq. (Mechanical Licensing Act)&lt;/strong&gt; and &lt;strong&gt;OAC Title 158 Chapter 50&lt;/strong&gt;. The licensing path is tiered: apprenticeship, then journeyman status, then application for the contractor license. Licensees must complete &lt;em&gt;&amp;ldquo;six (6) hours of CEUs every 36 months&amp;rdquo;&lt;/em&gt; as a continuing-education requirement. Verifying that a contractor holds an active CIB Mechanical Contractor license &amp;mdash; and that their firm has a named responsible contractor per OAC 158:50 &amp;mdash; is the baseline due-diligence step for every OKC homeowner.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oklahoma City is served by &lt;strong&gt;OG&amp;amp;E (Oklahoma Gas &amp;amp; Electric)&lt;/strong&gt; for electricity and &lt;strong&gt;Oklahoma Natural Gas (ONG)&lt;/strong&gt; for natural gas. For current residential HVAC rebate dollar amounts, check oge.com and oklahomanaturalgas.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your OKC ZIP. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with $2,000/year cap for heat pumps). Permit fees for residential mechanical work are set by the &lt;strong&gt;OKC Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oklahoma City is served by &lt;strong&gt;OG&amp;amp;E (Oklahoma Gas &amp;amp; Electric)&lt;/strong&gt; for electricity and &lt;strong&gt;Oklahoma Natural Gas (ONG)&lt;/strong&gt; for natural gas. For current residential HVAC rebate dollar amounts, check oge.com and oklahomanaturalgas.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your OKC ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026. Permit fees for residential mechanical work are set by the &lt;strong&gt;OKC Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing &amp;amp; Local Permits (No Statewide HVAC License)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nebraska does not issue a statewide HVAC contractor license. Instead, HVAC contractor registration and permitting in Omaha are handled locally through the &lt;strong&gt;City of Omaha Permits and Inspections Division&lt;/strong&gt;. Verifying that a contractor is registered with the city before authorizing any HVAC work is the critical due-diligence step &amp;mdash; more important than in states with a statewide board, because the local registration is the only formal credential. Contact Permits and Inspections directly for the current fee schedule and contractor-verification tools.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Omaha&amp;rsquo;s electricity is served by &lt;strong&gt;Omaha Public Power District (OPPD)&lt;/strong&gt; &amp;mdash; a customer-owned public power district &amp;mdash; and natural gas by &lt;strong&gt;Black Hills Energy&lt;/strong&gt;. For current residential rebate dollar amounts from OPPD (heat pump, smart thermostat, weatherization), visit oppd.com; for Black Hills Energy gas-equipment rebates, visit blackhillsenergy.com directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;: &lt;strong&gt;$2,000/year for qualified heat pumps, heat pump water heaters, biomass stoves, or biomass boilers&lt;/strong&gt;; &lt;strong&gt;$1,200/year for other energy-efficient property and home improvements&lt;/strong&gt;; &lt;strong&gt;up to $600 per item&lt;/strong&gt; for central AC and gas/propane/oil furnaces meeting the CEE highest efficiency tier.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Omaha&amp;rsquo;s electricity is served by &lt;strong&gt;Omaha Public Power District (OPPD)&lt;/strong&gt; &amp;mdash; a customer-owned public power district &amp;mdash; and natural gas by &lt;strong&gt;Black Hills Energy&lt;/strong&gt;. For current residential rebate dollar amounts from OPPD (heat pump, smart thermostat, weatherization), visit oppd.com; for Black Hills Energy gas-equipment rebates, visit blackhillsenergy.com directly. The federal Section 25C tax credit was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21); the local incentives above remain active for 2026 installs.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8762,11 +8762,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Illinois Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Illinois does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Peoria must obtain permits through local authorities. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ameren Illinois Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ameren Illinois administers residential energy efficiency rebates for its Peoria service territory. Contact Ameren Illinois directly for the current heat pump, smart thermostat, and central AC rebate amounts. Ameren rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ameren Illinois administers residential energy efficiency rebates for its Peoria service territory. Contact Ameren Illinois directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Peoria are set by local permitting authorities. Contact the City of Peoria for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing: PA HICPA &amp;amp; Pittsburgh Local Registration&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pennsylvania does not issue a statewide HVAC contractor license. Instead, Pennsylvania requires home-improvement contractors performing more than &lt;strong&gt;$5,000 of work per year&lt;/strong&gt; to register with the Office of Attorney General under the &lt;strong&gt;Home Improvement Consumer Protection Act (HICPA)&lt;/strong&gt;. Additionally, the &lt;strong&gt;City of Pittsburgh Department of Permits, Licenses &amp;amp; Inspections (PLI)&lt;/strong&gt; requires local contractor registration for work within city limits. Verifying BOTH the HICPA registration AND Pittsburgh PLI registration before authorizing work is the baseline due-diligence step. Contact PLI directly for the current mechanical permit fee schedule.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pittsburgh is served by &lt;strong&gt;Duquesne Light Company&lt;/strong&gt; for electricity (with the &lt;strong&gt;Watt Choices&lt;/strong&gt; residential efficiency program) and &lt;strong&gt;Peoples Natural Gas&lt;/strong&gt; for natural gas. For current rebate dollar amounts, visit duquesnelight.com (Watt Choices) and peoples-gas.com directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year total, with $2,000/year cap for heat pumps and $1,200/year for other energy-efficient property).&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pittsburgh is served by &lt;strong&gt;Duquesne Light Company&lt;/strong&gt; for electricity (with the &lt;strong&gt;Watt Choices&lt;/strong&gt; residential efficiency program) and &lt;strong&gt;Peoples Natural Gas&lt;/strong&gt; for natural gas. For current rebate dollar amounts, visit duquesnelight.com (Watt Choices) and peoples-gas.com directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9324,11 +9324,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Rhode Island Contractor Licensing (DLT)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rhode Island requires HVAC contractors to hold a &lt;strong&gt;Refrigeration/Air Conditioning Contractor License&lt;/strong&gt; issued by the Rhode Island Department of Labor and Training (DLT). The DLT administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DLT license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Rhode Island Energy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rhode Island Energy administers residential rebate and incentive programs for its Providence service territory. Contact Rhode Island Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts. Rhode Island Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rhode Island Energy administers residential rebate and incentive programs for its Providence service territory. Contact Rhode Island Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Providence are set by local permitting authorities. Contact the City of Providence for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NC Board Licensing (H-1 / H-2 / H-3)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Raleigh must hold a current state-issued Heating &amp;amp; Cooling Contractor License from the &lt;a href="https://www.nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating &amp;amp; Fire Sprinkler Contractors&lt;/a&gt;. NC issues three heating-license classifications &amp;mdash; &lt;strong&gt;H-1&lt;/strong&gt; (unlimited scope), &lt;strong&gt;H-2&lt;/strong&gt; (limited to specified tonnage/BTU thresholds), and &lt;strong&gt;H-3&lt;/strong&gt; (packaged-unit specialty). For typical residential work in Raleigh, any of the three classifications can be sufficient depending on the job scope. The Board&amp;rsquo;s phone number is 919-875-3612; verifying a contractor&amp;rsquo;s active license before authorizing work is the baseline due-diligence step.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Raleigh is served by &lt;strong&gt;Duke Energy Progress&lt;/strong&gt; for electricity and &lt;strong&gt;Dominion Energy North Carolina&lt;/strong&gt; (formerly PSNC Energy) for natural gas. For current Duke Energy Progress &lt;strong&gt;Smart Saver&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat, duct sealing), visit duke-energy.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Raleigh ZIP. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Raleigh Planning and Development Department&lt;/strong&gt; per the FY26 Development Fee Guide; contact the Planning &amp;amp; Development Customer Service Center at 919-996-2500 (One Exchange Plaza, Suite 400) for current line-item amounts. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Raleigh is served by &lt;strong&gt;Duke Energy Progress&lt;/strong&gt; for electricity and &lt;strong&gt;Dominion Energy North Carolina&lt;/strong&gt; (formerly PSNC Energy) for natural gas. For current Duke Energy Progress &lt;strong&gt;Smart Saver&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat, duct sealing), visit duke-energy.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Raleigh ZIP. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Raleigh Planning and Development Department&lt;/strong&gt; per the FY26 Development Fee Guide; contact the Planning &amp;amp; Development Customer Service Center at 919-996-2500 (One Exchange Plaza, Suite 400) for current line-item amounts. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9527,8 +9527,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NV Energy administers the PowerShift residential rebate program for its northern-Nevada service territory. Current line-item rebate dollar amounts for Reno could not be retrieved verbatim at the time this page was authored; contact NV Energy directly or check the NV Energy PowerShift page for the current Reno-area heat pump, smart thermostat, and central AC incentive amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Local Code&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Reno are set by the City of Reno Community Development Department. The current published fee schedule could not be retrieved verbatim at the time this page was authored; contact Community Development directly for the current mechanical permit fee schedule. Reno enforces the Nevada-adopted International Mechanical Code as the baseline mechanical standard.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9629,8 +9629,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://law.lis.virginia.gov/vacode/title54.1/chapter11/section54.1-1100/" target="_blank" rel="nofollow noopener"&gt;Code of Virginia Section 54.1-1100&lt;/a&gt;, the Virginia Department of Professional and Occupational Regulation (DPOR) Board for Contractors issues three license classes by contract value: &lt;strong&gt;Class A &amp;mdash; single contracts of $150,000 or more, or $1 million or more in a 12-month period&lt;/strong&gt;; &lt;strong&gt;Class B &amp;mdash; single contracts of $30,000 or more but less than $150,000, or $250,000 or more but less than $1 million annually&lt;/strong&gt;; and &lt;strong&gt;Class C &amp;mdash; single contracts over $1,000 but less than $30,000, and less than $250,000 annually&lt;/strong&gt;. HVAC contractors typically hold the &lt;strong&gt;HVA (Heating, Ventilation and Air Conditioning Contracting)&lt;/strong&gt; specialty designation under one of these classes.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Utility Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Richmond are set by the Richmond Department of Planning &amp;amp; Development Review (PDR). The current published fee schedule could not be retrieved verbatim at the time this page was authored; contact PDR at (804) 646-6304 for the current mechanical permit fee schedule. Dominion Energy Virginia administers electric residential rebates for Richmond customers; current rebate dollar amounts should be verified directly on the Dominion Energy Virginia home rebates page.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9982,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Salt Lake City Mechanical Permit Fees (Verbatim)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://tools.slc.gov/feeschedule/" target="_blank" rel="nofollow noopener"&gt;Salt Lake City Consolidated Fee Schedule&lt;/a&gt; (Building Services Division, Section 18.52.050 mechanical permits), current mechanical permit fees include: &lt;strong&gt;base fee $57&lt;/strong&gt;; &lt;strong&gt;forced-air furnace or burner up to 200,000 BTU/h $29&lt;/strong&gt;, 200,000&amp;ndash;300,000 BTU/h $41, 300,000&amp;ndash;1,000,000 BTU/h $65; &lt;strong&gt;floor furnace $18&lt;/strong&gt;; &lt;strong&gt;appliance vent $18&lt;/strong&gt;; &lt;strong&gt;heating appliance repair/alteration $41 (up to $1,000 contract value) or $100 (greater than $1,000)&lt;/strong&gt;; &lt;strong&gt;boiler/compressor up to 3 hp $29&lt;/strong&gt;. For a typical residential furnace replacement, expect a $57 base + $29&amp;ndash;$65 per-appliance fee depending on capacity &amp;mdash; among the more transparent municipal fee schedules in this project.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utah DOPL S350 License &amp;amp; Utility Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Salt Lake City must hold a current &lt;strong&gt;S350 HVAC Contractor&lt;/strong&gt; license from the &lt;strong&gt;Utah Division of Occupational and Professional Licensing (DOPL)&lt;/strong&gt;. The S350 classification covers heating, ventilating, and air conditioning contracting statewide. Verifying a contractor&amp;rsquo;s active S350 license via DOPL&amp;rsquo;s online lookup before authorizing work is the baseline due-diligence step. Salt Lake City is served by &lt;strong&gt;Rocky Mountain Power&lt;/strong&gt; (PacifiCorp) for electricity, running the &lt;strong&gt;wattsmart&lt;/strong&gt; residential efficiency program, and by &lt;strong&gt;Dominion Energy Utah&lt;/strong&gt; for natural gas with its &lt;strong&gt;ThermWise&lt;/strong&gt; rebate program. For current wattsmart and ThermWise rebate dollar amounts, visit rockymountainpower.net/wattsmart and dominionenergy.com/utah directly &amp;mdash; both sites route through interactive lookup tools rather than static dollar lists. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Salt Lake City must hold a current &lt;strong&gt;S350 HVAC Contractor&lt;/strong&gt; license from the &lt;strong&gt;Utah Division of Occupational and Professional Licensing (DOPL)&lt;/strong&gt;. The S350 classification covers heating, ventilating, and air conditioning contracting statewide. Verifying a contractor&amp;rsquo;s active S350 license via DOPL&amp;rsquo;s online lookup before authorizing work is the baseline due-diligence step. Salt Lake City is served by &lt;strong&gt;Rocky Mountain Power&lt;/strong&gt; (PacifiCorp) for electricity, running the &lt;strong&gt;wattsmart&lt;/strong&gt; residential efficiency program, and by &lt;strong&gt;Dominion Energy Utah&lt;/strong&gt; for natural gas with its &lt;strong&gt;ThermWise&lt;/strong&gt; rebate program. For current wattsmart and ThermWise rebate dollar amounts, visit rockymountainpower.net/wattsmart and dominionenergy.com/utah directly &amp;mdash; both sites route through interactive lookup tools rather than static dollar lists. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ideal Heat Pump Climate&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco&amp;rsquo;s 2,475 HDD with almost no extreme-cold days puts it squarely in DOE&amp;rsquo;s ideal heat-pump territory &amp;mdash; mild winters rarely approach the 5&amp;deg;F threshold at which standard air-source heat pumps lose significant capacity. Per the &lt;a href="https://www.energy.gov/energysaver/heat-pump-systems" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guide on Heat Pump Systems&lt;/a&gt;, ductless mini-split heat pumps are &lt;em&gt;&amp;ldquo;a good choice for room additions and for homes without ductwork, such as those heated by hydronic (hot water heat), radiant panels, and space heaters.&amp;rdquo;&lt;/em&gt; For the majority of SF Victorian and Edwardian row houses, multi-zone ductless mini-split installations provide both efficient heating (replacing aging gas wall furnaces or floor heaters) and modest cooling for the rare heat-wave week &amp;mdash; without requiring invasive ductwork retrofits.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;BayREN &amp;amp; California C-20 Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas, and residents have access to regional incentives through the &lt;strong&gt;Bay Area Regional Energy Network (BayREN)&lt;/strong&gt;. Per the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;EASE Home covers 80% of the cost for core upgrades, such as insulation and duct sealing. You pay just 20% of the total project cost, with your contribution capped at $1,000.&amp;rdquo;&lt;/em&gt; For current PG&amp;amp;E residential rebate amounts (heat pump, smart thermostat), see pge.com directly. Every HVAC contractor working in San Francisco must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor license from the California Contractors State License Board. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Francisco Department of Building Inspection (DBI)&lt;/strong&gt;; contact DBI directly for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas, and residents have access to regional incentives through the &lt;strong&gt;Bay Area Regional Energy Network (BayREN)&lt;/strong&gt;. Per the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;EASE Home covers 80% of the cost for core upgrades, such as insulation and duct sealing. You pay just 20% of the total project cost, with your contribution capped at $1,000.&amp;rdquo;&lt;/em&gt; For current PG&amp;amp;E residential rebate amounts (heat pump, smart thermostat), see pge.com directly. Every HVAC contractor working in San Francisco must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor license from the California Contractors State License Board. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Francisco Department of Building Inspection (DBI)&lt;/strong&gt;; contact DBI directly for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California CSLB C-20 Contractor License (Verbatim)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in San Jose must hold a California C-20 license from the &lt;a href="https://www.cslb.ca.gov/about_us/library/licensing_classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;California Contractors State License Board&lt;/a&gt;. Per the CSLB classification detail: a C-20 contractor &lt;em&gt;&amp;ldquo;fabricates, installs, maintains, services and repairs warm-air heating systems and water heating heat pumps, complete with warm-air appliances; ventilating systems complete with blowers and plenum chambers; air-conditioning systems complete with air-conditioning unit; and the ducts, registers, flues, humidity and thermostatic controls and air filters in connection with any of these systems.&amp;rdquo;&lt;/em&gt; The classification &lt;em&gt;&amp;ldquo;also encompasses warm-air heating, ventilating and air-conditioning systems utilizing solar energy.&amp;rdquo;&lt;/em&gt; Verifying the contractor&amp;rsquo;s active C-20 license via CSLB&amp;rsquo;s public lookup before authorizing work is the baseline due-diligence step.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Rebates &amp;amp; Federal Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Jose is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for delivery of both electricity and natural gas, while &lt;strong&gt;Silicon Valley Clean Energy (SVCE)&lt;/strong&gt; &amp;mdash; a Community Choice Aggregator &amp;mdash; is the electric generation provider for most of the city. For current rebate dollar amounts, check pge.com, svcleanenergy.org, and the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; directly &amp;mdash; SVCE runs its own heat pump incentive programs separate from PG&amp;amp;E. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Jose Planning, Building and Code Enforcement Building Division&lt;/strong&gt;; contact the division directly for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Jose is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for delivery of both electricity and natural gas, while &lt;strong&gt;Silicon Valley Clean Energy (SVCE)&lt;/strong&gt; &amp;mdash; a Community Choice Aggregator &amp;mdash; is the electric generation provider for most of the city. For current rebate dollar amounts, check pge.com, svcleanenergy.org, and the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; directly &amp;mdash; SVCE runs its own heat pump incentive programs separate from PG&amp;amp;E. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Jose Planning, Building and Code Enforcement Building Division&lt;/strong&gt;; contact the division directly for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;2021 Seattle Energy Code &amp;amp; Fossil-Fuel Compliance Path&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Seattle has some of the strictest residential energy-code requirements in the country. Per the &lt;a href="https://www.seattle.gov/sdci/codes/codes-we-enforce-(a-z)/energy-code" target="_blank" rel="nofollow noopener"&gt;SDCI Seattle Energy Code page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;We have adopted the 2021 Seattle Energy Codes&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;the 2021 SEC largely matches the 2021 Washington State Energy Code, including adoption of the new &amp;lsquo;fossil fuel compliance path.&amp;rsquo;&amp;rdquo;&lt;/em&gt; The practical implication for Seattle homeowners replacing a gas furnace: the 2021 SEC&amp;rsquo;s fossil-fuel path imposes additional efficiency or equipment-swap requirements that don&amp;rsquo;t apply to equivalent heat-pump installations, which is one of the strongest regulatory tailwinds behind electrification in any U.S. city.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Seattle City Light Rebates (Tiered by HSPF2)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.seattle.gov/city-light/residential-services/home-energy-solutions" target="_blank" rel="nofollow noopener"&gt;Seattle City Light&amp;rsquo;s Home Energy Solutions page&lt;/a&gt;, residential heat-pump instant discounts are tiered by HSPF2 efficiency: &lt;strong&gt;HSPF2 8.1 or higher: $300 instant discount&lt;/strong&gt;; &lt;strong&gt;HSPF2 8.5 or higher: $400&lt;/strong&gt;; &lt;strong&gt;HSPF2 9.5 or higher: $600&lt;/strong&gt;. Separately, homeowners can receive &lt;em&gt;&amp;ldquo;$750 rebate on heat pump water heaters&amp;rdquo;&lt;/em&gt; and a &lt;em&gt;&amp;ldquo;$50/unit instant rebate courtesy of Seattle City Light&amp;rdquo;&lt;/em&gt; for smart thermostats designed for electric baseboard heaters (through December 31, 2026). For current natural-gas furnace, boiler, and heat pump rebate amounts from &lt;strong&gt;Puget Sound Energy (PSE)&lt;/strong&gt;, see pse.com/rebates directly. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.seattle.gov/city-light/residential-services/home-energy-solutions" target="_blank" rel="nofollow noopener"&gt;Seattle City Light&amp;rsquo;s Home Energy Solutions page&lt;/a&gt;, residential heat-pump instant discounts are tiered by HSPF2 efficiency: &lt;strong&gt;HSPF2 8.1 or higher: $300 instant discount&lt;/strong&gt;; &lt;strong&gt;HSPF2 8.5 or higher: $400&lt;/strong&gt;; &lt;strong&gt;HSPF2 9.5 or higher: $600&lt;/strong&gt;. Separately, homeowners can receive &lt;em&gt;&amp;ldquo;$750 rebate on heat pump water heaters&amp;rdquo;&lt;/em&gt; and a &lt;em&gt;&amp;ldquo;$50/unit instant rebate courtesy of Seattle City Light&amp;rdquo;&lt;/em&gt; for smart thermostats designed for electric baseboard heaters (through December 31, 2026). For current natural-gas furnace, boiler, and heat pump rebate amounts from &lt;strong&gt;Puget Sound Energy (PSE)&lt;/strong&gt;, see pse.com/rebates directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Washington L&amp;amp;I 06A Licensing (WAC 296-46B-920)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC/refrigeration contractor working in Seattle must hold a current &lt;strong&gt;06A HVAC/Refrigeration specialty license&lt;/strong&gt; from the Washington State Department of Labor &amp;amp; Industries (L&amp;amp;I). Per &lt;a href="https://app.leg.wa.gov/wac/default.aspx?cite=296-46B-920" target="_blank" rel="nofollow noopener"&gt;Washington Administrative Code Section 296-46B-920&lt;/a&gt;, the 06A specialty &lt;em&gt;&amp;ldquo;is not limited by voltage, phase, or amperage&amp;rdquo;&lt;/em&gt; and covers &lt;em&gt;&amp;ldquo;installation, repair, replacement, and maintenance of line voltage components within HVAC/refrigeration equipment&amp;rdquo;&lt;/em&gt; as well as &lt;em&gt;&amp;ldquo;repair, replacement, or maintenance of line voltage flexible supply whips not exceeding six feet in length.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active 06A credential via L&amp;amp;I&amp;rsquo;s license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Seattle Department of Construction &amp;amp; Inspections (SDCI)&lt;/strong&gt;; contact SDCI at (206) 684-8600 for the current mechanical permit fee schedule.&lt;/p&gt;</t>
         </is>
@@ -10808,11 +10808,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana HVAC Contractor Licensing (LSLBC)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisiana requires HVAC contractors to hold a &lt;strong&gt;Mechanical Work Contractor License&lt;/strong&gt; issued by the Louisiana State Licensing Board for Contractors (LSLBC). Verify a specific contractor&amp;rsquo;s current LSLBC license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SWEPCO Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southwestern Electric Power Company (SWEPCO), an AEP company, is the primary electric utility for the Shreveport area. Contact SWEPCO directly for the current residential HVAC rebate amounts. SWEPCO rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southwestern Electric Power Company (SWEPCO), an AEP company, is the primary electric utility for the Shreveport area. Contact SWEPCO directly for the current residential HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Shreveport are set by local permitting authorities. Contact the City of Shreveport for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10910,11 +10910,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Washington HVAC Contractor Licensing (L&amp;amp;I)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Washington requires HVAC contractors to hold a &lt;strong&gt;06A HVAC/Refrigeration Contractor License&lt;/strong&gt; issued by the Washington Department of Labor &amp;amp; Industries (L&amp;amp;I). The L&amp;amp;I administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current L&amp;amp;I license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Avista Utilities Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Avista Utilities administers residential rebate programs for its Spokane service territory. Contact Avista directly for the current heat pump, smart thermostat, natural gas furnace, and central AC rebate amounts. Avista rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Avista Utilities administers residential rebate programs for its Spokane service territory. Contact Avista directly for the current heat pump, smart thermostat, natural gas furnace, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Spokane are set by the City of Spokane. Contact the City for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11015,8 +11015,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Eversource (formerly Western Massachusetts Electric Company / WMECO) administers residential energy efficiency rebates for its Springfield service territory through Mass Save. Contact Eversource or visit Mass Save for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Springfield are set by local permitting authorities. Contact the City of Springfield for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11372,11 +11372,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;New York Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Syracuse must comply with local permitting requirements. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;National Grid Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;National Grid administers residential energy efficiency programs for its Syracuse service territory. Contact National Grid directly for the current heat pump, smart thermostat, and HVAC rebate amounts. National Grid rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;National Grid administers residential energy efficiency programs for its Syracuse service territory. Contact National Grid directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Syracuse are set by local permitting authorities. Contact the City of Syracuse for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11555,8 +11555,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Florida requires AC contractors to hold a license issued by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) through the Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Verify a specific contractor&amp;rsquo;s current DBPR license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Tallahassee are set by local permitting authorities. Contact the City of Tallahassee for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tampa Permit Fees &amp;amp; Florida Building Surcharge&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.tampa.gov/construction-services/fees" target="_blank" rel="nofollow noopener"&gt;City of Tampa Construction Services fees page&lt;/a&gt;, every permit is subject to a &lt;em&gt;&amp;ldquo;Florida Building Permit Surcharge (2.5% of permit value or $4.00 minimum)&amp;rdquo;&lt;/em&gt; &amp;mdash; a state-level fee in addition to city permit fees. Tampa is a hurricane-prone region requiring condenser tie-downs and wind-rated mounting pads under standard Florida Building Code wind-load provisions; however, unlike Miami-Dade and Broward counties, Tampa is NOT in the Florida Building Code High-Velocity Hurricane Zone (HVHZ), so HVHZ-specific equipment approvals don&amp;rsquo;t apply.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Gulf Coast Corrosion &amp;amp; Florida Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tampa Bay&amp;rsquo;s Gulf Coast location exposes outdoor condenser coils to airborne chloride salt that pits aluminum fins and can cause formicary corrosion in copper refrigerant tubing. Homeowners within a few miles of the bay benefit from coastal-duty coil coatings and more frequent condenser rinsing. Every HVAC contractor in Tampa must hold a current Florida Certified Air Conditioning Contractor license from the &lt;strong&gt;DBPR / Construction Industry Licensing Board&lt;/strong&gt;: per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system&amp;rdquo;&lt;/em&gt; &amp;mdash; Class B is fully sufficient for typical Tampa residential work. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tampa Bay&amp;rsquo;s Gulf Coast location exposes outdoor condenser coils to airborne chloride salt that pits aluminum fins and can cause formicary corrosion in copper refrigerant tubing. Homeowners within a few miles of the bay benefit from coastal-duty coil coatings and more frequent condenser rinsing. Every HVAC contractor in Tampa must hold a current Florida Certified Air Conditioning Contractor license from the &lt;strong&gt;DBPR / Construction Industry Licensing Board&lt;/strong&gt;: per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system&amp;rdquo;&lt;/em&gt; &amp;mdash; Class B is fully sufficient for typical Tampa residential work. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11756,11 +11756,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio HVAC Contractor Licensing (OCILB)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ohio requires HVAC contractors to hold an &lt;strong&gt;HVAC Contractor License&lt;/strong&gt; issued by the Ohio Construction Industry Licensing Board (OCILB). Verify a specific contractor&amp;rsquo;s current OCILB license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Toledo Edison / FirstEnergy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Edison, a FirstEnergy company, is the primary electric utility for the Toledo area. Contact Toledo Edison or FirstEnergy directly for the current residential HVAC rebate amounts. Utility rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Edison, a FirstEnergy company, is the primary electric utility for the Toledo area. Contact Toledo Edison or FirstEnergy directly for the current residential HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Toledo are set by local permitting authorities. Contact the City of Toledo for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;VA DPOR HVAC Specialty (HVA)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Virginia Beach must also hold the &lt;strong&gt;HVA (Heating, Ventilation and Air Conditioning)&lt;/strong&gt; specialty classification from the &lt;a href="https://www.dpor.virginia.gov/Boards/Contractors/" target="_blank" rel="nofollow noopener"&gt;Virginia Department of Professional and Occupational Regulation (DPOR), Board for Contractors&lt;/a&gt;. Per DPOR: &lt;em&gt;&amp;ldquo;The class of license (A, B, or C)&amp;hellip;determines the monetary value of contracts/projects that may be performed, and the classification/specialty&amp;hellip;determines what type of work is allowed.&amp;rdquo;&lt;/em&gt; Contact DPOR at (804) 367-8511 or contractors@dpor.virginia.gov. Verifying both the monetary class AND the HVA specialty on a contractor&amp;rsquo;s active license is the baseline due-diligence step for Virginia Beach homeowners.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Coastal Corrosion, Rebates &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Virginia Beach&amp;rsquo;s Atlantic coastal exposure imposes the same salt-air corrosion concern found in Miami, Jacksonville, and Tampa &amp;mdash; outdoor condensers benefit from coastal-duty coil coatings and more frequent rinsing. For current &lt;strong&gt;Dominion Energy Virginia&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat), visit dominionenergy.com directly; &lt;strong&gt;Virginia Natural Gas&lt;/strong&gt; administers separate gas-equipment rebates. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Virginia Beach Permits &amp;amp; Inspections Division&lt;/strong&gt;; contact the division for the current fee schedule. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Virginia Beach&amp;rsquo;s Atlantic coastal exposure imposes the same salt-air corrosion concern found in Miami, Jacksonville, and Tampa &amp;mdash; outdoor condensers benefit from coastal-duty coil coatings and more frequent rinsing. For current &lt;strong&gt;Dominion Energy Virginia&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat), visit dominionenergy.com directly; &lt;strong&gt;Virginia Natural Gas&lt;/strong&gt; administers separate gas-equipment rebates. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Virginia Beach Permits &amp;amp; Inspections Division&lt;/strong&gt;; contact the division for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 4A Heat Pump Suitability &amp;amp; Pre-War Housing Challenges&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The combination of 3,769 HDD and 1,738 CDD makes Zone 4A one of the best-fit climates in the country for air-source heat pumps &amp;mdash; winters are cold enough to matter but rarely extreme, and summer cooling load is meaningful. Per DOE Building America guidance on &lt;a href="https://basc.pnnl.gov/" target="_blank" rel="nofollow noopener"&gt;Mixed-Humid Climate Zone 4A&lt;/a&gt;, designs must handle substantial summer latent cooling loads alongside winter heating. For DC&amp;rsquo;s pre-war rowhouse stock (median 1957 reflects mid-century dominant construction), ductwork is often routed through unconditioned chases and many older homes have limited or no central ducting &amp;mdash; making ductless mini-split heat pumps a natural retrofit path.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;DCSEU Rebates, Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Washington, D.C. is served by &lt;strong&gt;Pepco&lt;/strong&gt; for electricity and &lt;strong&gt;Washington Gas&lt;/strong&gt; for natural gas. Distinctively, DC also operates the &lt;strong&gt;DC Sustainable Energy Utility (DCSEU)&lt;/strong&gt; &amp;mdash; a district-mandated efficiency program that administers heat pump rebates, weatherization incentives, and low-income weatherization for DC residents. For current rebate dollar amounts, visit dcseu.com, pepco.com, and washingtongas.com directly. Every HVAC contractor working in DC must hold a current &lt;strong&gt;Master Refrigeration and Air Conditioning Mechanic&lt;/strong&gt; license from the &lt;strong&gt;DC Department of Licensing and Consumer Protection (DLCP)&lt;/strong&gt;; verifying a contractor&amp;rsquo;s active DLCP license before authorizing work is the baseline due-diligence step. Permit fees are set by the &lt;strong&gt;DC Department of Buildings (DOB)&lt;/strong&gt;. All local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Washington, D.C. is served by &lt;strong&gt;Pepco&lt;/strong&gt; for electricity and &lt;strong&gt;Washington Gas&lt;/strong&gt; for natural gas. Distinctively, DC also operates the &lt;strong&gt;DC Sustainable Energy Utility (DCSEU)&lt;/strong&gt; &amp;mdash; a district-mandated efficiency program that administers heat pump rebates, weatherization incentives, and low-income weatherization for DC residents. For current rebate dollar amounts, visit dcseu.com, pepco.com, and washingtongas.com directly. Every HVAC contractor working in DC must hold a current &lt;strong&gt;Master Refrigeration and Air Conditioning Mechanic&lt;/strong&gt; license from the &lt;strong&gt;DC Department of Licensing and Consumer Protection (DLCP)&lt;/strong&gt;; verifying a contractor&amp;rsquo;s active DLCP license before authorizing work is the baseline due-diligence step. Permit fees are set by the &lt;strong&gt;DC Department of Buildings (DOB)&lt;/strong&gt;. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12407,8 +12407,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Wichita are set by Sedgwick County MABCD. The current published fee schedule could not be retrieved verbatim at the time this page was authored; contact MABCD directly for the current mechanical permit fee schedule. Because Kansas does not adopt a statewide residential energy code, the locally adopted IMC/IRC/IECC editions are set by MABCD; confirm the currently adopted editions with MABCD before plan-design work.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Evergy (electric) and Kansas Gas Service (natural gas) are the primary residential utilities in the Wichita area. Current line-item HVAC rebate dollar amounts could not be retrieved verbatim at the time this page was authored; contact Evergy and Kansas Gas Service directly for the current heat pump, central AC, smart thermostat, and gas furnace rebate amounts in your service territory.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation. The credit is non-refundable.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12506,11 +12506,11 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina HVAC Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Carolina requires HVAC contractors to hold a &lt;strong&gt;Heating Contractor License&lt;/strong&gt; (H-1, H-2, or H-3 classification) issued by the North Carolina Board of Examiners of Plumbing, Heating and Fire Sprinkler Contractors. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Winston-Salem service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and central AC rebate amounts. Duke Energy rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Winston-Salem service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Winston-Salem are set by the City of Winston-Salem Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12611,8 +12611,8 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;National Grid administers residential energy efficiency rebates for its Worcester service territory through Mass Save. Contact National Grid or visit Mass Save for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Worcester are set by local permitting authorities. Contact the City of Worcester for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits (IRS Section 25C)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; (30% of cost up to the cap) and up to &lt;strong&gt;$600 per year for a qualifying central air conditioner or natural gas furnace&lt;/strong&gt;. Equipment must meet the highest CEE efficiency tier in effect at the start of the calendar year of installation.&lt;/p&gt;</t>
+&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12896,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dominion Energy South Carolina Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dominion Energy South Carolina administers residential rebate programs for its Columbia service territory. Contact Dominion Energy SC directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Columbia are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Columbia are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13000,7 +13000,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Greenville service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Greenville are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Greenville are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Mississippi Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Mississippi administers residential energy efficiency programs for its Jackson service territory. Contact Entergy Mississippi directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Jackson are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Jackson are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13208,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mississippi Power Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mississippi Power administers residential rebate programs for its Gulfport service territory. Contact Mississippi Power directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Gulfport are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Gulfport are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Versant Power &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Versant Power is the primary electric utility for the Bangor area. Maine also offers significant heat pump incentives through Efficiency Maine. Contact Versant Power and Efficiency Maine for the current heat pump rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Bangor are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Bangor are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13416,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mon Power (FirstEnergy) &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mon Power, a FirstEnergy company, is the primary electric utility for the Morgantown area. Contact Mon Power for the current residential HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Morgantown are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Morgantown are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13520,7 +13520,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NorthWestern Energy Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NorthWestern Energy administers residential rebate programs for its Billings service territory. Contact NorthWestern Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Billings are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Billings are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13624,7 +13624,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NorthWestern Energy Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NorthWestern Energy administers residential rebate programs for its Missoula service territory. Contact NorthWestern Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Missoula are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Missoula are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13726,9 +13726,9 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Dakota Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Fargo requires a municipal mechanical contractor license for work within city limits. Verify a contractor&amp;rsquo;s qualifications, insurance, and local licensing before contracting.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Xcel Energy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Xcel Energy administers residential rebate programs for its Fargo service territory. Contact Xcel Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts. Xcel rebates pair with the federal IRS Section 25C credit described below.&lt;/p&gt;
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Xcel Energy administers residential rebate programs for its Fargo service territory. Contact Xcel Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fargo are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fargo are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13828,7 +13828,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 6A Cold-Dry Climate&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Bismarck&amp;rsquo;s 8,470.7 HDD and documented winter lows well below -20&amp;deg;F require the most capable cold-climate heat pumps available. The dry 19-inch precipitation supports whole-house humidification considerations. Montana-Dakota Utilities (MDU) administers residential rebate programs; contact MDU directly for current amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Bismarck requires a municipal mechanical contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Bismarck requires a municipal mechanical contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13928,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Sioux Falls&amp;rsquo;s 7,248.5 HDD profile requires cold-climate-rated heat pumps. Xcel Energy (electric) and MidAmerican Energy (gas) serve the area; contact both for current residential HVAC rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Sioux Falls requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Sioux Falls requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Black Hills Climate (Zone 5B)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 5B cool-dry climates produce extended heating seasons with low indoor humidity. Black Hills Energy administers residential rebate programs; contact them for current amounts. Cold-climate heat pump specification is essential at 7,252 HDD.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Rapid City requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Rapid City requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14128,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mid-Atlantic Climate (Zone 4A)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce summer latent loads alongside winter heating demand. Delmarva Power (Exelon) administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Delaware Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Delaware requires HVAC contractors to hold a &lt;strong&gt;Master HVAC License&lt;/strong&gt; issued by the Delaware Board of HVACR Examiners. Verify license status before contracting. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Delaware requires HVAC contractors to hold a &lt;strong&gt;Master HVAC License&lt;/strong&gt; issued by the Delaware Board of HVACR Examiners. Verify license status before contracting. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14228,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Burlington Electric Department (Municipal)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Burlington&amp;rsquo;s electric service is provided by the &lt;strong&gt;Burlington Electric Department (BED)&lt;/strong&gt;, a municipally owned utility notable for achieving &lt;strong&gt;100% renewable electricity&lt;/strong&gt;. Contact BED for current residential heat pump rebates. Vermont also offers significant heat pump incentives through Efficiency Vermont.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 6A Cold-Humid Climate&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Burlington&amp;rsquo;s 6,960.3 HDD and 87.5&amp;rdquo; snowfall require cold-climate-rated heat pumps and elevated outdoor-unit mounting. Vermont does not issue a statewide HVAC contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Burlington&amp;rsquo;s 6,960.3 HDD and 87.5&amp;rdquo; snowfall require cold-climate-rated heat pumps and elevated outdoor-unit mounting. Vermont does not issue a statewide HVAC contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;High-Altitude Wind Exposure (Zone 6B)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 6B cold-dry climates at 6,000+ ft altitude produce unique HVAC challenges: reduced air density affects equipment capacity ratings, persistent wind accelerates heat loss through building envelopes, and the 62.9&amp;rdquo; snowfall drives outdoor-unit clearance requirements. Cheyenne Light Fuel and Power (Black Hills Energy) administers residential rebate programs.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wyoming does not issue a statewide HVAC license; check local requirements. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wyoming does not issue a statewide HVAC license; check local requirements. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;New England Fuel-Oil Legacy &amp;amp; Conversion&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Manchester&amp;rsquo;s 6,980.1 HDD and 67.7&amp;rdquo; snowfall require cold-climate-rated heat pumps. The 1964 median housing age means envelope upgrades are critical. Eversource Energy administers residential rebates; contact Eversource for current amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New Hampshire does not issue a statewide HVAC contractor license; local requirements apply. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New Hampshire does not issue a statewide HVAC contractor license; local requirements apply. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel-Oil Market &amp;amp; Heat Pump Conversion&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Portland&amp;rsquo;s 6,795.2 HDD and 68.7&amp;rdquo; snowfall require cold-climate-rated heat pumps. Maine&amp;rsquo;s Efficiency Maine program offers significant heat pump rebates specifically targeting fuel-oil-heated homes. Central Maine Power (CMP) is the primary electric utility; contact CMP and Efficiency Maine for current rebate amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel Board Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine requires HVAC technicians to hold a &lt;strong&gt;Master Technician License&lt;/strong&gt; issued by the Maine Fuel Board. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine requires HVAC technicians to hold a &lt;strong&gt;Master Technician License&lt;/strong&gt; issued by the Maine Fuel Board. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Appalachian Climate (Zone 4A)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates in the Kanawha Valley produce both heating and summer humidity loads. Appalachian Power (AEP) administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;WV Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC contractors to hold an &lt;strong&gt;HVAC Technician Certification&lt;/strong&gt; issued by the WV Contractor Licensing Board. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC contractors to hold an &lt;strong&gt;HVAC Technician Certification&lt;/strong&gt; issued by the WV Contractor Licensing Board. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lowcountry Warm-Humid Climate &amp;amp; Hurricane Exposure (Zone 3A)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent loads. Charleston&amp;rsquo;s coastal Lowcountry position adds hurricane exposure and salt-air corrosion considerations for outdoor equipment. Dominion Energy South Carolina administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC LLR. Mechanical/HVAC permit fees are set by local permitting authorities. The &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Energy Efficient Home Improvement Credit (Section 25C)&lt;/a&gt; provides a federal income tax credit of up to &lt;strong&gt;$2,000 per year for a qualifying heat pump installation&lt;/strong&gt; and up to &lt;strong&gt;$600 for a qualifying central AC or furnace&lt;/strong&gt;.&lt;/p&gt;</t>
+&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC LLR. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R151"/>
+  <dimension ref="A1:W151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -529,6 +529,31 @@
           <t>local_context_html</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>noaa_hdd_annual</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>noaa_cdd_annual</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>noaa_days_above_90</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>noaa_days_below_32</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>noaa_snowfall_inches</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -704,6 +729,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permits, Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Albuquerque Planning Department, Code Enforcement Division&lt;/strong&gt;; contact Planning directly for the current mechanical permit fee schedule. Albuquerque is served by &lt;strong&gt;PNM (Public Service Company of New Mexico)&lt;/strong&gt; for electricity and &lt;strong&gt;New Mexico Gas Company&lt;/strong&gt; for natural gas. Both utilities administer residential energy-efficiency rebate programs; check pnm.com and nmgco.com directly for current dollar amounts, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your ABQ ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S3" t="n">
+        <v>4180</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1322</v>
+      </c>
+      <c r="U3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="4">
@@ -807,6 +847,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="T4" t="n">
+        <v>757</v>
+      </c>
+      <c r="U4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>32.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -905,6 +960,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;Municipality of Anchorage Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule. Anchorage is served by &lt;strong&gt;Chugach Electric Association&lt;/strong&gt; &amp;mdash; a member-owned cooperative utility &amp;mdash; for electricity, and &lt;strong&gt;Enstar Natural Gas&lt;/strong&gt; for the dominant residential heating fuel. For current rebate dollar amounts, visit chugachelectric.com and enstarnaturalgas.com directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>10194</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>74.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1084,6 +1154,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Local Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Georgia requires HVAC contractors to hold a &lt;strong&gt;Conditioned Air Contractor License (Class I or Class II)&lt;/strong&gt; issued by the Georgia Secretary of State&amp;rsquo;s Construction Industry Licensing Board. The license is the state-level credential every Atlanta HVAC contractor must carry; Class designations reflect permitted scope of work. Verifying a contractor&amp;rsquo;s active Conditioned Air license before authorizing work is a basic due-diligence step. Permit fees for residential mechanical work in Atlanta are set by the &lt;strong&gt;City of Atlanta Office of Buildings&lt;/strong&gt; (Department of City Planning); contact the Office of Buildings directly for the current fee schedule, as amounts are updated periodically. For an overview of federal and state incentive programs, cross-reference the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database (N.C. State University / U.S. DOE)&lt;/a&gt; or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S7" t="n">
+        <v>2767</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="U7" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -1187,6 +1272,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>2470</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2088</v>
+      </c>
+      <c r="U8" t="n">
+        <v>82</v>
+      </c>
+      <c r="V8" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1363,6 +1463,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Austin must hold a current TDLR Air Conditioning and Refrigeration Contractor license: per &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;the TDLR ACR program page&lt;/a&gt;, &lt;em&gt;&amp;ldquo;contractors who install, repair, or maintain systems related to air conditioning, refrigeration, or heating must have a TDLR license and ACR companies must employ an ACR contractor in each permanent location.&amp;rdquo;&lt;/em&gt; Class A covers any size unit; Class B is limited to 25 tons cooling / 1.5 million Btu heating. Permit fees for residential mechanical work are published in the City of Austin FY 2025-26 fee schedule and set by the &lt;strong&gt;City of Austin Development Services Department&lt;/strong&gt;; contact Development Services at 512-978-4504 for the current line-item amounts.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>1902</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2751</v>
+      </c>
+      <c r="U10" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1460,6 +1575,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maryland HVACR Master Contractor License (Detailed)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Baltimore must hold a current license from the &lt;a href="https://www.dllr.state.md.us/license/hvacr/hvacrlicreq.shtml" target="_blank" rel="nofollow noopener"&gt;Maryland Board of Heating, Ventilation, Air Conditioning and Refrigeration Contractors (HVACR)&lt;/a&gt;, administered by the Maryland Department of Labor under Business Regulation Article 9A and COMAR 09.15. Master HVACR Contractor requirements are substantial: applicants must have been &lt;em&gt;&amp;ldquo;licensed as a journeyman and regularly and principally employed to provide all areas of HVACR services for at least three years of active experience under the direction and control of a HVACR master and worked a minimum of 1,875 hours in the year before application,&amp;rdquo;&lt;/em&gt; and must &lt;em&gt;&amp;ldquo;pass the master examination with a score of 70%.&amp;rdquo;&lt;/em&gt; These are among the more rigorous state HVAC licensing requirements in the country. Permit fees for residential mechanical work are set by the &lt;strong&gt;Baltimore City Department of Housing &amp;amp; Community Development (DHCD) Permits &amp;amp; Inspections&lt;/strong&gt;; contact DHCD directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S11" t="n">
+        <v>4764</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1164</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20.1</v>
       </c>
     </row>
     <row r="12">
@@ -1563,6 +1693,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>1555</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2825</v>
+      </c>
+      <c r="U12" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="V12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1742,6 +1887,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Incentives&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Birmingham Department of Planning, Engineering &amp;amp; Permits&lt;/strong&gt;; the city directs applicants to the Online Permit Center and Birmingham Permit Guide. Contact Permitting &amp;amp; Inspection at 205-254-2904 or OnlinePermitCenter@birminghamal.gov for the current fee schedule. Per &lt;a href="https://www.energy.gov/energysaver/central-air-conditioning" target="_blank" rel="nofollow noopener"&gt;DOE Energy Saver guidance on hot-humid climate sizing&lt;/a&gt;: oversized AC equipment in Birmingham&amp;rsquo;s 56+ inch rainfall climate will short-cycle before pulling humidity, leaving homes clammy even at 72&amp;deg;F. Correct Manual J sizing (not bigger-is-better) is essential. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S14" t="n">
+        <v>2678</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2058</v>
+      </c>
+      <c r="U14" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="15">
@@ -1843,6 +2003,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S15" t="n">
+        <v>5513</v>
+      </c>
+      <c r="T15" t="n">
+        <v>942</v>
+      </c>
+      <c r="U15" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1942,6 +2117,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a single statewide HVAC-specific contractor license the way some states do. Instead, HVAC work in Boston is regulated through several overlapping credentials: refrigerant handling requires &lt;strong&gt;federal EPA Section 608 certification&lt;/strong&gt;; gas-fitting and plumbing portions of HVAC work require licensure through the &lt;strong&gt;Massachusetts Board of State Examiners of Plumbers and Gas Fitters&lt;/strong&gt;; sheet metal work is licensed separately. Verifying that a contractor holds all required credentials before authorizing work is the baseline due-diligence step for every Boston homeowner. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Boston Inspectional Services Department (ISD)&lt;/strong&gt;; contact ISD directly for the current fee schedule. For current utility rebate dollar amounts, visit &lt;strong&gt;masssave.com&lt;/strong&gt; (the joint utility rebate program that includes Eversource and administers some of the most generous heat-pump incentives in the country) or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Boston ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S16" t="n">
+        <v>5681</v>
+      </c>
+      <c r="T16" t="n">
+        <v>747</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>43.8</v>
       </c>
     </row>
     <row r="17">
@@ -2123,6 +2313,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S18" t="n">
+        <v>5392</v>
+      </c>
+      <c r="T18" t="n">
+        <v>825</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2225,6 +2430,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S19" t="n">
+        <v>554</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4027</v>
+      </c>
+      <c r="U19" t="n">
+        <v>123</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2323,6 +2543,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Buffalo is served by &lt;strong&gt;National Grid&lt;/strong&gt; for both electricity and natural gas. National Grid runs Upstate NY residential efficiency programs covering Gas Heating &amp;amp; Water Heating and Electric Heating &amp;amp; Cooling. Buffalo residents are also eligible for the statewide &lt;strong&gt;NYSERDA NY Clean Heat&lt;/strong&gt; program &amp;mdash; among the most generous heat-pump incentive programs in the country for cold-climate air-source and ground-source systems. For current National Grid and NYSERDA Clean Heat dollar amounts, visit nationalgridus.com and nyserda.ny.gov directly &amp;mdash; both sites use interactive address-lookup tools rather than static dollar lists. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S20" t="n">
+        <v>6617</v>
+      </c>
+      <c r="T20" t="n">
+        <v>544</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>94.7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2500,6 +2735,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Charlotte must hold a current state-issued Heating &amp;amp; Cooling Contractor License from the &lt;a href="https://www.nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating &amp;amp; Fire Sprinkler Contractors&lt;/a&gt;. NC issues three heating-license classifications &amp;mdash; &lt;strong&gt;H-1&lt;/strong&gt; (unlimited scope), &lt;strong&gt;H-2&lt;/strong&gt; (limited to systems below specified tonnage/BTU thresholds), and &lt;strong&gt;H-3&lt;/strong&gt; (packaged-unit specialty). For typical Charlotte residential work, any of the three classifications can be sufficient depending on the job scope; verifying the contractor&amp;rsquo;s active license with the NC Board at 919-875-3612 before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by &lt;strong&gt;Mecklenburg County Code Enforcement (LUESA)&lt;/strong&gt;; contact LUESA directly for the current fee schedule. For current &lt;strong&gt;Duke Energy Carolinas&lt;/strong&gt; Smart $aver rebate amounts and &lt;strong&gt;Piedmont Natural Gas&lt;/strong&gt; incentives, visit the utilities&amp;rsquo; sites directly or check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Charlotte ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S22" t="n">
+        <v>3390</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1519</v>
+      </c>
+      <c r="U22" t="n">
+        <v>35</v>
+      </c>
+      <c r="V22" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="23">
@@ -2603,6 +2853,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S23" t="n">
+        <v>3239</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1744</v>
+      </c>
+      <c r="U23" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2780,6 +3045,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Illinois does not issue a statewide HVAC contractor license. Instead, Chicago requires its own municipal HVAC contractor credentials, administered by the &lt;strong&gt;Chicago Department of Buildings&lt;/strong&gt; (permits and contractor registration) and the &lt;strong&gt;Chicago Department of Business Affairs and Consumer Protection&lt;/strong&gt; (business licensing). Verifying that a contractor is registered with the City of Chicago before authorizing any HVAC work is the critical due-diligence step in Illinois. Permit fees for residential mechanical work in Chicago are set by the Department of Buildings; contact the department directly for the current fee schedule as amounts are updated periodically. For current utility rebate dollar amounts, check &lt;strong&gt;ComEd&lt;/strong&gt; (electricity) and &lt;strong&gt;Peoples Gas&lt;/strong&gt; (natural gas) rebate pages directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Chicago ZIP code. These local incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year, with a $2,000 per-year cap specifically for heat pumps).&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S25" t="n">
+        <v>6339</v>
+      </c>
+      <c r="T25" t="n">
+        <v>842</v>
+      </c>
+      <c r="U25" t="n">
+        <v>14</v>
+      </c>
+      <c r="V25" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>36.3</v>
       </c>
     </row>
     <row r="26">
@@ -2957,6 +3237,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Cleveland is served by &lt;strong&gt;The Illuminating Company&lt;/strong&gt; (a FirstEnergy subsidiary) for electricity and, as of 2024, by &lt;strong&gt;Enbridge Gas Ohio&lt;/strong&gt; for natural gas (Dominion Energy Ohio was acquired by Enbridge Gas in the 2023&amp;ndash;2024 transaction). For current residential rebate dollar amounts from both utilities, check firstenergycorp.com and enbridgegas.com/ohio directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Cleveland ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S27" t="n">
+        <v>5761</v>
+      </c>
+      <c r="T27" t="n">
+        <v>817</v>
+      </c>
+      <c r="U27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="V27" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>68.09999999999999</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3055,6 +3350,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado Springs is served by &lt;strong&gt;Colorado Springs Utilities (CSU)&lt;/strong&gt; &amp;mdash; a rare four-service municipal utility providing electricity, natural gas, water, and wastewater under a single entity owned by the City. For current CSU residential rebate dollar amounts (heat pump, smart thermostat, insulation, solar), visit csu.org directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S28" t="n">
+        <v>6292</v>
+      </c>
+      <c r="T28" t="n">
+        <v>455</v>
+      </c>
+      <c r="U28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>37.7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3153,6 +3463,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Columbus must hold a current state-issued HVAC Contractor License from the &lt;a href="https://com.ohio.gov/divisions-and-programs/industrial-compliance/boards/ohio-construction-industry-licensing-board/about-ocilb" target="_blank" rel="nofollow noopener"&gt;Ohio Construction Industry Licensing Board (OCILB)&lt;/a&gt;, administered by the Ohio Department of Commerce. The OCILB &lt;em&gt;&amp;ldquo;licenses Ohio electrical, HVAC, plumbing, hydronics, and refrigeration contractors&amp;rdquo;&lt;/em&gt; and can be reached at 6606 Tussing Road, P.O. Box 4009, Reynoldsburg, Ohio 43068-9009 or (614) 644-3493. Verifying a contractor&amp;rsquo;s active OCILB HVAC license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Columbus Department of Building &amp;amp; Zoning Services&lt;/strong&gt; and published in the 2026 Combined Development Related Fee Schedule (effective January 22, 2026); contact Building &amp;amp; Zoning Services directly for the current mechanical line items.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S29" t="n">
+        <v>5250</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1034</v>
+      </c>
+      <c r="U29" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3254,6 +3579,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Deregulated Retail Electricity&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dallas electricity distribution is handled by &lt;strong&gt;Oncor Electric Delivery&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Dallas are typically administered by your chosen REP, not Oncor directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Dallas ZIP, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Atmos Energy administers any natural-gas-specific rebates. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Dallas Building Inspection Division&lt;/strong&gt;; contact Building Inspection at 320 E. Jefferson Blvd, Room 118, for the current mechanical permit fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S30" t="n">
+        <v>2135</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2945</v>
+      </c>
+      <c r="U30" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>23</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="31">
@@ -3513,6 +3853,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S33" t="n">
+        <v>5645</v>
+      </c>
+      <c r="T33" t="n">
+        <v>900</v>
+      </c>
+      <c r="U33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V33" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>23.3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3614,6 +3969,18 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Colorado does not issue a statewide HVAC contractor license. Instead, Denver handles HVAC contractor licensing at the municipal level through &lt;a href="https://www.denvergov.org/Government/Agencies-Departments-Offices/Agencies-Departments-Offices-Directory/Community-Planning-and-Development/Contractor-Licensing" target="_blank" rel="nofollow noopener"&gt;Denver Community Planning and Development&amp;rsquo;s Contractor Licensing division&lt;/a&gt;. Per the CPD licensing page: &lt;em&gt;&amp;ldquo;A supervisor certificate &amp;mdash; or employing someone who holds a supervisor certificate &amp;mdash; is required before obtaining a contractor&amp;rsquo;s license,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;licenses and certificates must be renewed every 1&amp;ndash;3 years, depending on your license type.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active Denver CPD license before authorizing work is the critical due-diligence step for Denver homeowners &amp;mdash; more so than in states with a statewide board, because the municipal license is the only formal credential. Permit fees for residential mechanical work are set by CPD and can be confirmed by contacting the department at (720) 865-2780. For current &lt;strong&gt;Xcel Energy Colorado&lt;/strong&gt; rebate dollar amounts, see the utility&amp;rsquo;s residential rebates page or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Denver ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S34" t="n">
+        <v>6059</v>
+      </c>
+      <c r="T34" t="n">
+        <v>769</v>
+      </c>
+      <c r="U34" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>156.9</v>
       </c>
     </row>
     <row r="35">
@@ -3717,6 +4084,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S35" t="n">
+        <v>6203</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1068</v>
+      </c>
+      <c r="U35" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>35.3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3816,6 +4198,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Michigan Mechanical Contractor License (LARA)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Detroit must hold a current Michigan Mechanical Contractor License from the &lt;strong&gt;Michigan Department of Licensing and Regulatory Affairs (LARA) Bureau of Construction Codes&lt;/strong&gt;. Per the &lt;a href="https://www.michigan.gov/-/media/Project/Websites/lara/Folder14/ApplicationForMechanicalContractorExaminationLicensing_BCC-11_08-2021.pdf" target="_blank" rel="nofollow noopener"&gt;LARA Application for Mechanical Contractor Examination and Licensing (BCC-11)&lt;/a&gt;, Michigan issues 10 distinct mechanical-license classifications: &lt;em&gt;&amp;ldquo;(1) Hydronic heating and cooling and process piping, (2) HVAC equipment, (3) Ductwork, (4) Refrigeration, (5) Limited Heating service, (6) Unlimited Heating Service, (7) Limited Refrigeration and air conditioning service, (8) Unlimited refrigeration and air conditioning service, (9) Fire Suppression, (10) Specialty.&amp;rdquo;&lt;/em&gt; The HVAC Equipment classification &lt;em&gt;&amp;ldquo;includes ductwork, gas piping and venting&amp;rdquo;&lt;/em&gt; but explicitly excludes &lt;em&gt;&amp;ldquo;portable self-contained refrigeration equipment and window type air conditioners of not more than 1 1/2 horsepower.&amp;rdquo;&lt;/em&gt; License applicants must demonstrate &lt;em&gt;&amp;ldquo;a minimum of 3 years or 6,000 hours of performance in EACH work classification&amp;rdquo;&lt;/em&gt; being sought. Permit fees for residential mechanical work are set by the &lt;strong&gt;Detroit BSEED (Buildings, Safety Engineering &amp;amp; Environmental Department)&lt;/strong&gt;; contact BSEED at (313) 224-2733 for the current fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S36" t="n">
+        <v>6136</v>
+      </c>
+      <c r="T36" t="n">
+        <v>803</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V36" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>42.5</v>
       </c>
     </row>
     <row r="37">
@@ -3914,6 +4311,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR Licensing &amp;amp; Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in El Paso must hold a current Air Conditioning and Refrigeration (ACR) Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by Texas Occupations Code Chapter 1302 and 16 TAC Chapter 75. Per TDLR: &lt;em&gt;&amp;ldquo;Contractors who install, repair, or maintain systems related to air conditioning, refrigeration, or heating must have a TDLR license and ACR companies must employ an ACR contractor in each permanent location.&amp;rdquo;&lt;/em&gt; Class A covers any size unit; Class B is limited to 25 tons cooling / 1.5 million Btu heating. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of El Paso Development Services Department&lt;/strong&gt;; contact the One-Stop Shop at (915) 212-0104 for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S37" t="n">
+        <v>2473</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2331</v>
+      </c>
+      <c r="U37" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="V37" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="W37" t="n">
+        <v>6.9</v>
       </c>
     </row>
     <row r="38">
@@ -4092,6 +4504,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S39" t="n">
+        <v>4807</v>
+      </c>
+      <c r="T39" t="n">
+        <v>240</v>
+      </c>
+      <c r="U39" t="n">
+        <v>14</v>
+      </c>
+      <c r="V39" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="40">
@@ -4273,6 +4700,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S41" t="n">
+        <v>2906</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2010</v>
+      </c>
+      <c r="U41" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="V41" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4453,6 +4895,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S43" t="n">
+        <v>6102</v>
+      </c>
+      <c r="T43" t="n">
+        <v>809</v>
+      </c>
+      <c r="U43" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>33.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4549,6 +5006,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Fort Worth must hold a current Air Conditioning and Refrigeration Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by Texas Occupations Code Chapter 1302 and 16 TAC Chapter 75. &lt;strong&gt;Class A&lt;/strong&gt; entitles the license holder to work on units of any size; &lt;strong&gt;Class B&lt;/strong&gt; is limited to 25 tons cooling / 1.5 million Btu/hr heating. Applicants must demonstrate 48 months of practical experience under a licensed contractor. Fort Worth&amp;rsquo;s electricity distribution is handled by &lt;strong&gt;Oncor Electric Delivery&lt;/strong&gt; (TDU), but retail electricity is sold by Retail Electric Providers (REPs) under the Texas deregulated market &amp;mdash; meaning residential HVAC rebates flow through your chosen REP rather than Oncor. Natural-gas customers are served by Atmos Energy. For current rebate amounts, use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Fort Worth ZIP. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Fort Worth Development Services Department&lt;/strong&gt;; contact Development Services at 817-392-2222 for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S44" t="n">
+        <v>2286</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2755</v>
+      </c>
+      <c r="U44" t="n">
+        <v>95</v>
+      </c>
+      <c r="V44" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4722,6 +5194,18 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Fresno must hold a California C-20 Warm-Air Heating, Ventilating and Air-Conditioning contractor license from the California Contractors State License Board. Verifying the contractor&amp;rsquo;s active C-20 license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Fresno Department of Planning &amp;amp; Development, Building and Safety Services&lt;/strong&gt;; contact Building and Safety directly for the current fee schedule. Fresno is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas; for current residential rebate dollar amounts, visit pge.com or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Fresno ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S46" t="n">
+        <v>2346</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2124</v>
+      </c>
+      <c r="U46" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="V46" t="n">
+        <v>13.3</v>
       </c>
     </row>
     <row r="47">
@@ -4981,6 +5465,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S49" t="n">
+        <v>935</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4608</v>
+      </c>
+      <c r="U49" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5161,6 +5657,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S51" t="n">
+        <v>6485</v>
+      </c>
+      <c r="T51" t="n">
+        <v>698</v>
+      </c>
+      <c r="U51" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>74.90000000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5263,6 +5774,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S52" t="n">
+        <v>5999</v>
+      </c>
+      <c r="T52" t="n">
+        <v>756</v>
+      </c>
+      <c r="U52" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V52" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5520,6 +6046,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates, Permits &amp;amp; Deregulated Retail Electricity&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Houston&amp;rsquo;s electricity distribution is handled by &lt;strong&gt;CenterPoint Energy&lt;/strong&gt; (the Transmission and Distribution Utility), but &lt;em&gt;retail&lt;/em&gt; electricity service is provided by a Retail Electric Provider (REP) chosen by the consumer under the Texas deregulated market. That means residential HVAC rebates in Houston are typically administered by your chosen REP, not by CenterPoint directly. The most reliable way to see current rebate dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; filtered to your Houston ZIP code, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; for Texas residential incentives. Permit fees for residential mechanical work are set by the &lt;strong&gt;Houston Permitting Center&lt;/strong&gt; (Mechanical Section, 832.394.8850); contact the center directly for the current fee schedule as amounts are updated periodically. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S55" t="n">
+        <v>1367</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3157</v>
+      </c>
+      <c r="U55" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="V55" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -5623,6 +6164,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S56" t="n">
+        <v>3002</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1951</v>
+      </c>
+      <c r="U56" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="V56" t="n">
+        <v>52</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5720,6 +6276,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing &amp;amp; Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana does not issue a statewide HVAC contractor license through the Indiana Professional Licensing Agency. Instead, HVAC contractor registration and permitting in Indianapolis are handled locally through the &lt;strong&gt;Indianapolis Department of Business &amp;amp; Neighborhood Services (DBNS)&lt;/strong&gt;. For Indianapolis homeowners, verifying that a contractor is registered with DBNS before authorizing any HVAC work is the critical due-diligence step &amp;mdash; more important than in states with a statewide board, because the local registration is the only formal credential. Contact DBNS directly for the current mechanical permit fee schedule and to verify contractor status.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S57" t="n">
+        <v>5379</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1066</v>
+      </c>
+      <c r="U57" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V57" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="W57" t="n">
+        <v>25.9</v>
       </c>
     </row>
     <row r="58">
@@ -5823,6 +6394,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S58" t="n">
+        <v>1251</v>
+      </c>
+      <c r="T58" t="n">
+        <v>877</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5998,6 +6581,18 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida Contractor Licensing (Statute 489.105)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Jacksonville must hold a current Florida Certified Air Conditioning Contractor license, administered by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, the two license classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt; covering central air conditioning, refrigeration, heating, and ventilating systems; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system.&amp;rdquo;&lt;/em&gt; For typical Jacksonville residential work, a Class B contractor is fully qualified. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Jacksonville Building Inspection Division&lt;/strong&gt; under Municipal Code of Ordinances Chapter 320; contact the division directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S60" t="n">
+        <v>1350</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2664</v>
+      </c>
+      <c r="U60" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="V60" t="n">
+        <v>15.6</v>
       </c>
     </row>
     <row r="61">
@@ -6261,6 +6856,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S63" t="n">
+        <v>5133</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1360</v>
+      </c>
+      <c r="U63" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="V63" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="W63" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6363,6 +6973,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S64" t="n">
+        <v>3636</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1526</v>
+      </c>
+      <c r="U64" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V64" t="n">
+        <v>67</v>
+      </c>
+      <c r="W64" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6565,6 +7190,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in the Las Vegas Valley must hold a current license from the &lt;a href="https://www.nvcontractorsboard.com/licensing/license-classifications/" target="_blank" rel="nofollow noopener"&gt;Nevada State Contractors Board (NSCB)&lt;/a&gt;. The relevant classification is &lt;strong&gt;C-21 Refrigeration and Air Conditioning&lt;/strong&gt;, which falls under the NSCB&amp;rsquo;s Classification C (Specialty Contractor) category covering 42 distinct subcontracting fields. The detailed scope of C-21 work is codified in &lt;strong&gt;Chapter 624 of the Nevada Administrative Code&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active C-21 license via the NSCB&amp;rsquo;s public license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Las Vegas Building &amp;amp; Safety Department&lt;/strong&gt;; contact Building &amp;amp; Safety at 702-229-6251 or BuildingInfo@LasVegasNevada.gov for the current mechanical permit fee schedule. For current &lt;strong&gt;NV Energy PowerShift&lt;/strong&gt; heating and cooling rebate amounts, see nvenergy.com/save-with-powershift directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S66" t="n">
+        <v>1951</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3568</v>
+      </c>
+      <c r="U66" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="V66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6667,6 +7307,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S67" t="n">
+        <v>4610</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1191</v>
+      </c>
+      <c r="U67" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V67" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="W67" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6769,6 +7424,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S68" t="n">
+        <v>6056</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1174</v>
+      </c>
+      <c r="U68" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="V68" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="W68" t="n">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6871,6 +7541,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S69" t="n">
+        <v>3053</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2206</v>
+      </c>
+      <c r="U69" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="V69" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="W69" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6973,6 +7658,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S70" t="n">
+        <v>1420</v>
+      </c>
+      <c r="T70" t="n">
+        <v>552</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7068,6 +7768,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Licensing, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Kentucky requires HVAC contractors to hold a state-issued &lt;strong&gt;Master HVAC Contractor license&lt;/strong&gt;, administered by the &lt;strong&gt;Kentucky Department of Housing, Buildings and Construction (DHBC) Division of HVAC&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active Master HVAC license with DHBC before authorizing work is a basic due-diligence step for Louisville homeowners. Permit fees for residential mechanical work in Louisville are set by the &lt;strong&gt;Louisville Metro Office of Construction Review&lt;/strong&gt;; contact Construction Review directly for the current fee schedule. Louisville is served by &lt;strong&gt;Louisville Gas &amp;amp; Electric (LG&amp;amp;E)&lt;/strong&gt; for both electricity and gas; current residential HVAC rebate amounts can be verified directly at lge-ku.com or via the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with a Louisville ZIP. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year).&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S71" t="n">
+        <v>4097</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1614</v>
+      </c>
+      <c r="U71" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V71" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="W71" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="72">
@@ -7171,6 +7886,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S72" t="n">
+        <v>3380</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1804</v>
+      </c>
+      <c r="U72" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="V72" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W72" t="n">
+        <v>8.199999999999999</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7273,6 +8003,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S73" t="n">
+        <v>7332</v>
+      </c>
+      <c r="T73" t="n">
+        <v>568</v>
+      </c>
+      <c r="U73" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="V73" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="W73" t="n">
+        <v>50.9</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7371,6 +8116,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Memphis must hold a current state-issued HVAC Mechanical Contractor (&lt;strong&gt;CMC-C&lt;/strong&gt;) license from the &lt;a href="https://www.tn.gov/commerce/regboards.html" target="_blank" rel="nofollow noopener"&gt;Tennessee Board for Licensing Contractors&lt;/a&gt;, administered by the Tennessee Department of Commerce and Insurance. Tennessee requires state contractor licensure for projects above specific dollar thresholds; the CMC-C classification covers HVAC work. Verifying a contractor&amp;rsquo;s active CMC-C license via the Board&amp;rsquo;s public lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set jointly by the &lt;strong&gt;City of Memphis &amp;amp; Shelby County Office of Construction Code Enforcement&lt;/strong&gt; (unusual city-county joint permitting); contact Construction Code Enforcement directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S74" t="n">
+        <v>2965</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2258</v>
+      </c>
+      <c r="U74" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="W74" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7466,6 +8226,18 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mesa City Code &amp;amp; Arizona ROC Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://library.municode.com/az/mesa/codes/code_of_ordinances" target="_blank" rel="nofollow noopener"&gt;Mesa City Code via Municode&lt;/a&gt;, the City of Mesa adopts the International Residential Code (IRC) and International Mechanical Code (IMC) via Title 4 (Buildings) with Mesa-specific amendments. Every HVAC contractor must hold a current license from the &lt;strong&gt;Arizona Registrar of Contractors (ROC)&lt;/strong&gt;: the residential classification is &lt;strong&gt;R-39 Air Conditioning and Refrigeration, Including Solar&lt;/strong&gt;; commercial work requires the &lt;strong&gt;C-39&lt;/strong&gt; classification. Dual-scope &lt;strong&gt;CR-39&lt;/strong&gt; covers both. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Mesa Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule. Mesa is served by &lt;strong&gt;Salt River Project (SRP)&lt;/strong&gt; for electricity and &lt;strong&gt;Southwest Gas&lt;/strong&gt; for natural gas; for current SRP rebate dollar amounts (heat pump, smart thermostat, duct sealing, pool pump), see srpnet.com/energy-savings directly.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S75" t="n">
+        <v>935</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4608</v>
+      </c>
+      <c r="U75" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="76">
@@ -7565,6 +8337,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Miami must hold a current Florida Certified Air Conditioning Contractor license, administered by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Per &lt;a href="https://www.flsenate.gov/laws/statutes/2025/489.105" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, the two license classes are strictly defined: &lt;strong&gt;Class A&lt;/strong&gt; contractors have &lt;em&gt;&amp;ldquo;services unlimited in the execution of contracts requiring the experience, knowledge, and skill to install, maintain, repair, fabricate, alter, extend, or design... central air-conditioning, refrigeration, heating, and ventilating systems, including duct work in connection with a complete system.&amp;rdquo;&lt;/em&gt; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system&amp;rdquo;&lt;/em&gt; &amp;mdash; essentially residential and light commercial. For a Miami homeowner, a Class B contractor is fully qualified for any typical residential job; the Class A designation matters when the project scope exceeds 25 tons (rare outside large multi-family). Verifying a contractor&amp;rsquo;s active Class A or Class B license before authorizing work is the critical due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Miami Building Department&lt;/strong&gt;; contact the department directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S76" t="n">
+        <v>128</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4575</v>
+      </c>
+      <c r="U76" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7666,6 +8453,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Wisconsin HVAC Qualifier (Optional) &amp;amp; Local Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wisconsin is one of the few states that does NOT mandate a statewide HVAC contractor license. Per the &lt;a href="https://dsps.wi.gov/Pages/Professions/HVACQualifier/Default.aspx" target="_blank" rel="nofollow noopener"&gt;Wisconsin Department of Safety and Professional Services HVAC Qualifier page&lt;/a&gt;, the state offers an optional &lt;strong&gt;HVAC Qualifier&lt;/strong&gt; credential: &lt;em&gt;&amp;ldquo;a person or entity who utilizes a person who holds an HVAC Qualifier certification may not be required to obtain a local certification, license or other approval.&amp;rdquo;&lt;/em&gt; In practical terms: Milwaukee homeowners should verify either (a) that the contractor holds a state HVAC Qualifier credential, or (b) that the contractor is registered locally with the &lt;strong&gt;Milwaukee Department of Neighborhood Services (DNS)&lt;/strong&gt;. Permit fees for residential mechanical work are set by Milwaukee DNS; contact the department directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S77" t="n">
+        <v>6894</v>
+      </c>
+      <c r="T77" t="n">
+        <v>641</v>
+      </c>
+      <c r="U77" t="n">
+        <v>7</v>
+      </c>
+      <c r="V77" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="W77" t="n">
+        <v>46.9</v>
       </c>
     </row>
     <row r="78">
@@ -7770,6 +8572,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Minneapolis Heating Ordinance (MCO &amp;sect; 244.430)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Beyond state code, the &lt;a href="https://library.municode.com/mn/minneapolis/codes/code_of_ordinances" target="_blank" rel="nofollow noopener"&gt;Minneapolis Code of Ordinances &amp;sect; 244.430&lt;/a&gt; imposes a local minimum-heat obligation for any building containing habitable rooms. Owners must provide heating facilities that are &amp;ldquo;properly installed, safely maintained, and in good working condition&amp;rdquo; capable of holding indoor temperatures at or above &lt;strong&gt;68&amp;deg;F from October 1 through April 30&lt;/strong&gt; (and 65&amp;deg;F during shoulder-season windows). The practical implication for homeowners: a furnace that intermittently cycles off during a January cold snap is not just an inconvenience &amp;mdash; it&amp;rsquo;s a habitability issue that triggers city inspection authority. This is why Minneapolis HVAC service calls during cold-weather emergencies are prioritized by most independent local contractors. Permit fees for residential mechanical work are set by the &lt;strong&gt;Minneapolis Community Planning &amp;amp; Economic Development (CPED) office&lt;/strong&gt;; contact CPED directly for the current fee schedule, as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S78" t="n">
+        <v>7581</v>
+      </c>
+      <c r="T78" t="n">
+        <v>752</v>
+      </c>
+      <c r="U78" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V78" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="W78" t="n">
+        <v>54.4</v>
       </c>
     </row>
     <row r="79">
@@ -7873,6 +8690,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S79" t="n">
+        <v>1694</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2516</v>
+      </c>
+      <c r="U79" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="V79" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7975,6 +8807,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S80" t="n">
+        <v>2172</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1699</v>
+      </c>
+      <c r="U80" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="V80" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8070,6 +8917,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;TN CMC-C License, Permits &amp;amp; Rebates&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Nashville must hold a current state-issued HVAC Mechanical Contractor (&lt;strong&gt;CMC-C&lt;/strong&gt;) license from the &lt;a href="https://www.tn.gov/commerce/regboards.html" target="_blank" rel="nofollow noopener"&gt;Tennessee Board for Licensing Contractors&lt;/a&gt;, administered by the Tennessee Department of Commerce and Insurance. The CMC-C classification covers HVAC and mechanical work; the Board publishes license-holder status via its public lookup tool, and verifying a contractor&amp;rsquo;s active CMC-C license before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work in Nashville are set by the &lt;strong&gt;Metro Nashville Department of Codes and Building Safety&lt;/strong&gt;; contact the department directly for the current fee schedule. For current utility rebate dollar amounts, Nashville is served by &lt;strong&gt;Nashville Electric Service (NES)&lt;/strong&gt;, a TVA distributor that passes through &lt;a href="https://www.energyright.com/residential/home-energy/" target="_blank" rel="nofollow noopener"&gt;TVA EnergyRight&lt;/a&gt; residential incentives (including the EnergyRight Heat Pump Program loan); gas rebates are administered by Piedmont Natural Gas. All incentives stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S81" t="n">
+        <v>3688</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1647</v>
+      </c>
+      <c r="U81" t="n">
+        <v>40</v>
+      </c>
+      <c r="V81" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="W81" t="n">
+        <v>6.3</v>
       </c>
     </row>
     <row r="82">
@@ -8173,6 +9035,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work are set by the &lt;strong&gt;City of New Orleans Department of Safety &amp;amp; Permits&lt;/strong&gt;; per the &lt;a href="https://nola.gov/mechanical-permit/" target="_blank" rel="nofollow noopener"&gt;city&amp;rsquo;s Mechanical Permit page&lt;/a&gt;, fees &lt;em&gt;&amp;ldquo;vary based on components of work,&amp;rdquo;&lt;/em&gt; and applicants submit the HVAC Permit Application Supplement (D1-AC) with each application. Contact Safety &amp;amp; Permits at (504) 658-7100 for current line items. New Orleans&amp;rsquo;s post-Hurricane-Katrina building code emphasizes elevation requirements for outdoor mechanical equipment in flood-prone zones &amp;mdash; condenser pads must be set above Base Flood Elevation per FEMA flood-zone maps. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S82" t="n">
+        <v>1281</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3004</v>
+      </c>
+      <c r="U82" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="V82" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8271,6 +9145,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New York State does not issue a statewide HVAC contractor license. For work in NYC, the &lt;a href="https://www.nyc.gov/site/buildings/" target="_blank" rel="nofollow noopener"&gt;NYC Department of Buildings Licensed Trades&lt;/a&gt; issues credentials relevant to HVAC work &amp;mdash; including the &lt;strong&gt;Refrigeration Machine Operator&lt;/strong&gt; license and &lt;strong&gt;Oil Burner Installer&lt;/strong&gt; license for specific scopes. Verifying a contractor&amp;rsquo;s active DOB credential before authorizing work is the baseline due-diligence step. Permit fees for mechanical work are set by NYC DOB; fee amounts are codified in DOB fee rules under Administrative Code Title 28. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S83" t="n">
+        <v>4750</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1105</v>
+      </c>
+      <c r="U83" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V83" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="W83" t="n">
+        <v>25.8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8369,6 +9258,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Permit fees for residential mechanical work in Newark are set by the &lt;strong&gt;Newark Office of Uniform Construction Code (UCC)&lt;/strong&gt;, which administers the New Jersey Uniform Construction Code (NJUCC); contact the UCC office at 920 Mayor Kenneth A. Gibson Blvd, 973-733-4311, for the current fee schedule. Newark is served by &lt;strong&gt;PSE&amp;amp;G&lt;/strong&gt; (Public Service Enterprise Group) for both electricity and natural gas; PSE&amp;amp;G runs the Home Energy Solutions program, and residents are eligible for the statewide &lt;a href="https://www.njcleanenergy.com/residential/home/home" target="_blank" rel="nofollow noopener"&gt;NJ Clean Energy Program&lt;/a&gt; which administers heat pump and other efficiency incentives. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S84" t="n">
+        <v>4870</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1190</v>
+      </c>
+      <c r="U84" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="V84" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="W84" t="n">
+        <v>28.5</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8467,6 +9371,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oakland is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for electricity delivery and natural gas, while &lt;strong&gt;Ava Community Energy&lt;/strong&gt; (formerly East Bay Community Energy / EBCE) is the Community Choice Aggregator for electric generation. Oakland residents have access to &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; (80% cost share on core upgrades, homeowner capped at $1,000) plus PG&amp;amp;E and Ava-specific rebates. For current dollar amounts, visit bayren.org, pge.com, and avaenergy.org directly &amp;mdash; Ava&amp;rsquo;s incentive tool routes households through an eligibility filter (ZIP + income + household size) for the most current offers. Permit fees for residential mechanical work are set by the &lt;strong&gt;Oakland Planning &amp;amp; Building Department&lt;/strong&gt;; contact the department directly for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S85" t="n">
+        <v>2873</v>
+      </c>
+      <c r="T85" t="n">
+        <v>138</v>
+      </c>
+      <c r="U85" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8569,6 +9485,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Oklahoma City is served by &lt;strong&gt;OG&amp;amp;E (Oklahoma Gas &amp;amp; Electric)&lt;/strong&gt; for electricity and &lt;strong&gt;Oklahoma Natural Gas (ONG)&lt;/strong&gt; for natural gas. For current residential HVAC rebate dollar amounts, check oge.com and oklahomanaturalgas.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your OKC ZIP. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026. Permit fees for residential mechanical work are set by the &lt;strong&gt;OKC Development Services Department&lt;/strong&gt;; contact Development Services directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S86" t="n">
+        <v>3365</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2098</v>
+      </c>
+      <c r="U86" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="V86" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="W86" t="n">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8666,6 +9597,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Omaha&amp;rsquo;s electricity is served by &lt;strong&gt;Omaha Public Power District (OPPD)&lt;/strong&gt; &amp;mdash; a customer-owned public power district &amp;mdash; and natural gas by &lt;strong&gt;Black Hills Energy&lt;/strong&gt;. For current residential rebate dollar amounts from OPPD (heat pump, smart thermostat, weatherization), visit oppd.com; for Black Hills Energy gas-equipment rebates, visit blackhillsenergy.com directly. The federal Section 25C tax credit was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21); the local incentives above remain active for 2026 installs.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S87" t="n">
+        <v>6506</v>
+      </c>
+      <c r="T87" t="n">
+        <v>906</v>
+      </c>
+      <c r="U87" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V87" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="W87" t="n">
+        <v>26.5</v>
       </c>
     </row>
     <row r="88">
@@ -8769,6 +9715,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S88" t="n">
+        <v>5831</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1040</v>
+      </c>
+      <c r="U88" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="V88" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="W88" t="n">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8870,6 +9831,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;PGW EnergySense Rebates &amp;amp; L&amp;amp;I Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.pgworks.com/customer-care/efficiency" target="_blank" rel="nofollow noopener"&gt;Philadelphia Gas Works (PGW) Efficiency / EnergySense page&lt;/a&gt;, current residential gas rebates include: &lt;strong&gt;furnaces up to $500&lt;/strong&gt;, &lt;strong&gt;boilers up to $1,500&lt;/strong&gt;, &lt;strong&gt;standard tank water heaters $200&lt;/strong&gt;, &lt;strong&gt;tankless / condensing water heaters $500&lt;/strong&gt;, and a &lt;strong&gt;$70 smart-thermostat instant rebate&lt;/strong&gt;. For current PECO electric rebate amounts, visit peco.com directly. Pennsylvania does not issue a statewide HVAC contractor license; Philadelphia requires city-issued credentials through L&amp;amp;I. Per the &lt;a href="https://www.phila.gov/services/permits-violations-licenses/get-a-license/trade-licenses/get-a-contractor-license/" target="_blank" rel="nofollow noopener"&gt;Philadelphia L&amp;amp;I Contractor License page&lt;/a&gt;, contractors must carry &lt;strong&gt;$500,000 per-occurrence general liability insurance&lt;/strong&gt; and &lt;strong&gt;$300,000 automobile liability&lt;/strong&gt;; supervisors must complete &lt;em&gt;&amp;ldquo;an approved OSHA 30 safety training course within five years of application&amp;rdquo;&lt;/em&gt;; and license fees are &lt;strong&gt;$126 initial / $126 annual renewal&lt;/strong&gt;. Verifying a contractor&amp;rsquo;s active L&amp;amp;I license before authorizing work is the baseline due-diligence step for every Philadelphia homeowner.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S89" t="n">
+        <v>4612</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1301</v>
+      </c>
+      <c r="U89" t="n">
+        <v>24</v>
+      </c>
+      <c r="V89" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="W89" t="n">
+        <v>22.4</v>
       </c>
     </row>
     <row r="90">
@@ -8975,6 +9951,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Phoenix must hold a current license from the &lt;strong&gt;Arizona Registrar of Contractors (ROC)&lt;/strong&gt;. Per the &lt;a href="https://roc.az.gov/license-classifications" target="_blank" rel="nofollow noopener"&gt;Arizona ROC License Classifications page&lt;/a&gt;, the residential HVAC classification is &lt;strong&gt;R-39 Air Conditioning and Refrigeration, Including Solar&lt;/strong&gt;: &lt;em&gt;&amp;ldquo;This classification allows the licensee to install and repair comfort air conditioning systems, including refrigeration, evaporative cooling, ventilating, and heating with or without solar equipment.&amp;rdquo;&lt;/em&gt; A dual-scope CR-39 classification covers both residential and commercial work. For rebate amounts, APS and SRP programs have been subject to recent regulatory changes (Arizona Corporation Commission Decision No. 81584); verify current program status directly with your utility or via the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; before planning around specific dollar amounts.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S90" t="n">
+        <v>935</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4608</v>
+      </c>
+      <c r="U90" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9072,6 +10060,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Federal Incentives&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Pittsburgh is served by &lt;strong&gt;Duquesne Light Company&lt;/strong&gt; for electricity (with the &lt;strong&gt;Watt Choices&lt;/strong&gt; residential efficiency program) and &lt;strong&gt;Peoples Natural Gas&lt;/strong&gt; for natural gas. For current rebate dollar amounts, visit duquesnelight.com (Watt Choices) and peoples-gas.com directly. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S91" t="n">
+        <v>5710</v>
+      </c>
+      <c r="T91" t="n">
+        <v>736</v>
+      </c>
+      <c r="U91" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V91" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="W91" t="n">
+        <v>41.4</v>
       </c>
     </row>
     <row r="92">
@@ -9331,6 +10334,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S94" t="n">
+        <v>5618</v>
+      </c>
+      <c r="T94" t="n">
+        <v>744</v>
+      </c>
+      <c r="U94" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="V94" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="W94" t="n">
+        <v>33.8</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9428,6 +10446,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Raleigh is served by &lt;strong&gt;Duke Energy Progress&lt;/strong&gt; for electricity and &lt;strong&gt;Dominion Energy North Carolina&lt;/strong&gt; (formerly PSNC Energy) for natural gas. For current Duke Energy Progress &lt;strong&gt;Smart Saver&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat, duct sealing), visit duke-energy.com directly, or use the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; with your Raleigh ZIP. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Raleigh Planning and Development Department&lt;/strong&gt; per the FY26 Development Fee Guide; contact the Planning &amp;amp; Development Customer Service Center at 919-996-2500 (One Exchange Plaza, Suite 400) for current line-item amounts. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S95" t="n">
+        <v>3246</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1731</v>
+      </c>
+      <c r="U95" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="V95" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="W95" t="n">
+        <v>6.1</v>
       </c>
     </row>
     <row r="96">
@@ -9531,6 +10564,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S96" t="n">
+        <v>4926</v>
+      </c>
+      <c r="T96" t="n">
+        <v>838</v>
+      </c>
+      <c r="U96" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="V96" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="W96" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9633,6 +10681,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S97" t="n">
+        <v>3771</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1549</v>
+      </c>
+      <c r="U97" t="n">
+        <v>42</v>
+      </c>
+      <c r="V97" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W97" t="n">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9887,6 +10950,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Sacramento must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor classification from the California Contractors State License Board. Per the &lt;a href="https://www.cslb.ca.gov/about_us/library/licensing_classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;CSLB C-20 classification page&lt;/a&gt;, the C-20 contractor &lt;em&gt;&amp;ldquo;fabricates, installs, maintains, services and repairs warm-air heating systems and water heating heat pumps, complete with warm-air appliances; ventilating systems complete with blowers and plenum chambers; air-conditioning systems complete with air-conditioning unit&amp;rdquo;&lt;/em&gt; &amp;mdash; explicitly including solar-energy HVAC systems. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Sacramento Community Development Department, Building Division&lt;/strong&gt;; contact the Building Division directly for the current Master Fee Schedule as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S100" t="n">
+        <v>2618</v>
+      </c>
+      <c r="T100" t="n">
+        <v>1178</v>
+      </c>
+      <c r="U100" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="V100" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9985,6 +11063,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Salt Lake City must hold a current &lt;strong&gt;S350 HVAC Contractor&lt;/strong&gt; license from the &lt;strong&gt;Utah Division of Occupational and Professional Licensing (DOPL)&lt;/strong&gt;. The S350 classification covers heating, ventilating, and air conditioning contracting statewide. Verifying a contractor&amp;rsquo;s active S350 license via DOPL&amp;rsquo;s online lookup before authorizing work is the baseline due-diligence step. Salt Lake City is served by &lt;strong&gt;Rocky Mountain Power&lt;/strong&gt; (PacifiCorp) for electricity, running the &lt;strong&gt;wattsmart&lt;/strong&gt; residential efficiency program, and by &lt;strong&gt;Dominion Energy Utah&lt;/strong&gt; for natural gas with its &lt;strong&gt;ThermWise&lt;/strong&gt; rebate program. For current wattsmart and ThermWise rebate dollar amounts, visit rockymountainpower.net/wattsmart and dominionenergy.com/utah directly &amp;mdash; both sites route through interactive lookup tools rather than static dollar lists. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S101" t="n">
+        <v>5607</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1159</v>
+      </c>
+      <c r="U101" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="W101" t="n">
+        <v>56.2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10086,6 +11179,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Texas TDLR ACR License: Class A vs. Class B&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in San Antonio must hold a current Air Conditioning and Refrigeration Contractor license from the &lt;a href="https://www.tdlr.texas.gov/acr/acr.htm" target="_blank" rel="nofollow noopener"&gt;Texas Department of Licensing and Regulation (TDLR)&lt;/a&gt;, governed by &lt;strong&gt;Texas Occupations Code Chapter 1302&lt;/strong&gt; and &lt;strong&gt;16 Texas Administrative Code Chapter 75&lt;/strong&gt;. The &lt;strong&gt;Class A Environmental Air Conditioning&lt;/strong&gt; license entitles the holder &lt;em&gt;&amp;ldquo;to engage in air conditioning contracting&amp;hellip;of any size or capacity.&amp;rdquo;&lt;/em&gt; The &lt;strong&gt;Class B Environmental Air Conditioning&lt;/strong&gt; license is limited &lt;em&gt;&amp;ldquo;to a system, a product, or equipment of not more than: (1) 25 tons cooling capacity; or (2) 1.5 million British thermal units per hour output heating capacity.&amp;rdquo;&lt;/em&gt; For typical San Antonio residential work, a Class B contractor is fully qualified. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of San Antonio Development Services Department&lt;/strong&gt;; contact DSD directly for the current fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S102" t="n">
+        <v>1494</v>
+      </c>
+      <c r="T102" t="n">
+        <v>3132</v>
+      </c>
+      <c r="U102" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="V102" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="103">
@@ -10187,6 +11295,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in San Diego must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor classification from the California Contractors State License Board. Per the &lt;a href="https://www.cslb.ca.gov/about_us/library/licensing_classifications/Licensing_Classifications_Detail.aspx?Class=C20" target="_blank" rel="nofollow noopener"&gt;CSLB C-20 classification page&lt;/a&gt;, the C-20 contractor &lt;em&gt;&amp;ldquo;fabricates, installs, maintains, services and repairs warm-air heating systems and water heating heat pumps, complete with warm-air appliances; ventilating systems complete with blowers and plenum chambers; air-conditioning systems complete with air-conditioning unit; and the ducts, registers, flues, humidity and thermostatic controls and air filters in connection with any of these systems&amp;rdquo;&lt;/em&gt; &amp;mdash; explicitly including solar-energy HVAC systems. For utility rebate amounts, SDG&amp;amp;E&amp;rsquo;s current residential rebate catalog is searchable via the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; (enter your San Diego ZIP code) and the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt;, both of which list current utility and state incentive amounts.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S103" t="n">
+        <v>1226</v>
+      </c>
+      <c r="T103" t="n">
+        <v>720</v>
+      </c>
+      <c r="U103" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10282,6 +11405,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;BayREN &amp;amp; California C-20 Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Francisco is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for both electricity and natural gas, and residents have access to regional incentives through the &lt;strong&gt;Bay Area Regional Energy Network (BayREN)&lt;/strong&gt;. Per the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;EASE Home covers 80% of the cost for core upgrades, such as insulation and duct sealing. You pay just 20% of the total project cost, with your contribution capped at $1,000.&amp;rdquo;&lt;/em&gt; For current PG&amp;amp;E residential rebate amounts (heat pump, smart thermostat), see pge.com directly. Every HVAC contractor working in San Francisco must hold a California &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning&lt;/strong&gt; contractor license from the California Contractors State License Board. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Francisco Department of Building Inspection (DBI)&lt;/strong&gt;; contact DBI directly for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S104" t="n">
+        <v>2653</v>
+      </c>
+      <c r="T104" t="n">
+        <v>163</v>
+      </c>
+      <c r="U104" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -10381,6 +11519,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;San Jose is served by &lt;strong&gt;PG&amp;amp;E&lt;/strong&gt; for delivery of both electricity and natural gas, while &lt;strong&gt;Silicon Valley Clean Energy (SVCE)&lt;/strong&gt; &amp;mdash; a Community Choice Aggregator &amp;mdash; is the electric generation provider for most of the city. For current rebate dollar amounts, check pge.com, svcleanenergy.org, and the &lt;a href="https://www.bayren.org/ease" target="_blank" rel="nofollow noopener"&gt;BayREN EASE Home program&lt;/a&gt; directly &amp;mdash; SVCE runs its own heat pump incentive programs separate from PG&amp;amp;E. Permit fees for residential mechanical work are set by the &lt;strong&gt;San Jose Planning, Building and Code Enforcement Building Division&lt;/strong&gt;; contact the division directly for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S105" t="n">
+        <v>2001</v>
+      </c>
+      <c r="T105" t="n">
+        <v>730</v>
+      </c>
+      <c r="U105" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10712,6 +11862,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Washington L&amp;amp;I 06A Licensing (WAC 296-46B-920)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC/refrigeration contractor working in Seattle must hold a current &lt;strong&gt;06A HVAC/Refrigeration specialty license&lt;/strong&gt; from the Washington State Department of Labor &amp;amp; Industries (L&amp;amp;I). Per &lt;a href="https://app.leg.wa.gov/wac/default.aspx?cite=296-46B-920" target="_blank" rel="nofollow noopener"&gt;Washington Administrative Code Section 296-46B-920&lt;/a&gt;, the 06A specialty &lt;em&gt;&amp;ldquo;is not limited by voltage, phase, or amperage&amp;rdquo;&lt;/em&gt; and covers &lt;em&gt;&amp;ldquo;installation, repair, replacement, and maintenance of line voltage components within HVAC/refrigeration equipment&amp;rdquo;&lt;/em&gt; as well as &lt;em&gt;&amp;ldquo;repair, replacement, or maintenance of line voltage flexible supply whips not exceeding six feet in length.&amp;rdquo;&lt;/em&gt; Verifying a contractor&amp;rsquo;s active 06A credential via L&amp;amp;I&amp;rsquo;s license-lookup tool before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;Seattle Department of Construction &amp;amp; Inspections (SDCI)&lt;/strong&gt;; contact SDCI at (206) 684-8600 for the current mechanical permit fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S109" t="n">
+        <v>4696</v>
+      </c>
+      <c r="T109" t="n">
+        <v>188</v>
+      </c>
+      <c r="U109" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V109" t="n">
+        <v>24</v>
+      </c>
+      <c r="W109" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="110">
@@ -10815,6 +11980,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S110" t="n">
+        <v>2225</v>
+      </c>
+      <c r="T110" t="n">
+        <v>2481</v>
+      </c>
+      <c r="U110" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="V110" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10917,6 +12097,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S111" t="n">
+        <v>6593</v>
+      </c>
+      <c r="T111" t="n">
+        <v>450</v>
+      </c>
+      <c r="U111" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V111" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="W111" t="n">
+        <v>44.9</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11019,6 +12214,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S112" t="n">
+        <v>5681</v>
+      </c>
+      <c r="T112" t="n">
+        <v>747</v>
+      </c>
+      <c r="U112" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="V112" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="W112" t="n">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11120,6 +12330,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Utility Rebates &amp;amp; Permit Fees&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;St. Louis is served by &lt;strong&gt;Ameren Missouri&lt;/strong&gt; for electricity and &lt;strong&gt;Spire&lt;/strong&gt; for natural gas. Both utilities administer residential energy-efficiency rebate programs for high-efficiency HVAC equipment, smart thermostats, and weatherization. Because utility rebate amounts change annually and program pages sometimes block automated checks, the most reliable way to see current dollar amounts is the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder (EPA)&lt;/a&gt; with a St. Louis ZIP code, or the &lt;a href="https://www.dsireusa.org/" target="_blank" rel="nofollow noopener"&gt;DSIRE database&lt;/a&gt; filtered to Missouri residential incentives. These stack with the federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;IRS Section 25C Energy Efficient Home Improvement Credit&lt;/a&gt; (up to $3,200/year). Permit fees for residential mechanical work in the City of St. Louis are set by the Building Division; contact the Mechanical Section directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S113" t="n">
+        <v>4535</v>
+      </c>
+      <c r="T113" t="n">
+        <v>1646</v>
+      </c>
+      <c r="U113" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="V113" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="W113" t="n">
+        <v>17.7</v>
       </c>
     </row>
     <row r="114">
@@ -11379,6 +12604,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S116" t="n">
+        <v>6651</v>
+      </c>
+      <c r="T116" t="n">
+        <v>570</v>
+      </c>
+      <c r="U116" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V116" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="W116" t="n">
+        <v>123.8</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11559,6 +12799,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S118" t="n">
+        <v>1596</v>
+      </c>
+      <c r="T118" t="n">
+        <v>2592</v>
+      </c>
+      <c r="U118" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="V118" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11660,6 +12915,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Gulf Coast Corrosion &amp;amp; Florida Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tampa Bay&amp;rsquo;s Gulf Coast location exposes outdoor condenser coils to airborne chloride salt that pits aluminum fins and can cause formicary corrosion in copper refrigerant tubing. Homeowners within a few miles of the bay benefit from coastal-duty coil coatings and more frequent condenser rinsing. Every HVAC contractor in Tampa must hold a current Florida Certified Air Conditioning Contractor license from the &lt;strong&gt;DBPR / Construction Industry Licensing Board&lt;/strong&gt;: per &lt;a href="http://www.leg.state.fl.us/Statutes/index.cfm?App_mode=Display_Statute&amp;amp;URL=0400-0499/0489/Sections/0489.105.html" target="_blank" rel="nofollow noopener"&gt;Florida Statutes Section 489.105&lt;/a&gt;, &lt;strong&gt;Class A&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;unlimited in the execution of contracts&amp;rdquo;&lt;/em&gt;; &lt;strong&gt;Class B&lt;/strong&gt; contractors are &lt;em&gt;&amp;ldquo;limited to 25 tons of cooling and 500,000 Btu of heating in any one system&amp;rdquo;&lt;/em&gt; &amp;mdash; Class B is fully sufficient for typical Tampa residential work. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S119" t="n">
+        <v>539</v>
+      </c>
+      <c r="T119" t="n">
+        <v>3611</v>
+      </c>
+      <c r="U119" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -11763,6 +13033,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S120" t="n">
+        <v>6145</v>
+      </c>
+      <c r="T120" t="n">
+        <v>793</v>
+      </c>
+      <c r="U120" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V120" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="W120" t="n">
+        <v>37.6</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11939,6 +13224,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor working in Tucson must hold a current license from the &lt;strong&gt;Arizona Registrar of Contractors (ROC)&lt;/strong&gt;. Per the Arizona ROC License Classifications framework, the residential HVAC classification is &lt;strong&gt;R-39 Air Conditioning and Refrigeration, Including Solar&lt;/strong&gt;, which &lt;em&gt;&amp;ldquo;allows the licensee to install and repair comfort air conditioning systems, including refrigeration, evaporative cooling, ventilating, and heating with or without solar equipment.&amp;rdquo;&lt;/em&gt; A dual-scope &lt;strong&gt;CR-39&lt;/strong&gt; classification covers both residential and commercial work. Verifying a contractor&amp;rsquo;s active ROC license via the state board&amp;rsquo;s license lookup before authorizing work is basic due diligence for Tucson homeowners. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Tucson Planning &amp;amp; Development Services Department&lt;/strong&gt;; contact the department directly for the current fee schedule as amounts are updated periodically.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S122" t="n">
+        <v>1512</v>
+      </c>
+      <c r="T122" t="n">
+        <v>3145</v>
+      </c>
+      <c r="U122" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="V122" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12034,6 +13334,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Oklahoma Mechanical Contractor Licensing (OK CIB)&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Tulsa must hold a current license from the &lt;strong&gt;Oklahoma Construction Industries Board (CIB)&lt;/strong&gt;, regulated under &lt;strong&gt;59 O.S. Section 1850.1 et seq. (Mechanical License Act)&lt;/strong&gt; and &lt;strong&gt;OAC Title 158, Chapter 50&lt;/strong&gt;. Per the &lt;a href="https://oklahoma.gov/cib/your-industry/mechanical.html" target="_blank" rel="nofollow noopener"&gt;Oklahoma CIB Mechanical Industry page&lt;/a&gt;: &lt;em&gt;&amp;ldquo;Mechanical licenses shall be issued as journeyman, contractor or inactive contractor,&amp;rdquo;&lt;/em&gt; and &lt;em&gt;&amp;ldquo;no state agency, political subdivision, business entity or trust shall act as a mechanical firm unless a licensed, active mechanical contractor is associated with and responsible for all mechanical work of such entity.&amp;rdquo;&lt;/em&gt; For Tulsa homeowners, that second rule means you can verify a firm&amp;rsquo;s CIB status before authorizing work &amp;mdash; if there&amp;rsquo;s no licensed active contractor named as responsible for the firm, it&amp;rsquo;s operating outside Oklahoma law. Permit fees for Tulsa residential mechanical work are codified in Title 49 of the Tulsa Revised Ordinances Chapter 5; contact the Tulsa Permit Center at (918) 596-9456 for the current fee schedule.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S123" t="n">
+        <v>3574</v>
+      </c>
+      <c r="T123" t="n">
+        <v>2037</v>
+      </c>
+      <c r="U123" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="V123" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="W123" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="124">
@@ -12211,6 +13526,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Virginia Beach&amp;rsquo;s Atlantic coastal exposure imposes the same salt-air corrosion concern found in Miami, Jacksonville, and Tampa &amp;mdash; outdoor condensers benefit from coastal-duty coil coatings and more frequent rinsing. For current &lt;strong&gt;Dominion Energy Virginia&lt;/strong&gt; residential rebate dollar amounts (heat pump, smart thermostat), visit dominionenergy.com directly; &lt;strong&gt;Virginia Natural Gas&lt;/strong&gt; administers separate gas-equipment rebates. Permit fees for residential mechanical work are set by the &lt;strong&gt;City of Virginia Beach Permits &amp;amp; Inspections Division&lt;/strong&gt;; contact the division for the current fee schedule. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S125" t="n">
+        <v>3376</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1630</v>
+      </c>
+      <c r="U125" t="n">
+        <v>27</v>
+      </c>
+      <c r="V125" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="W125" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12308,6 +13638,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;DCSEU Rebates, Licensing &amp;amp; Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Washington, D.C. is served by &lt;strong&gt;Pepco&lt;/strong&gt; for electricity and &lt;strong&gt;Washington Gas&lt;/strong&gt; for natural gas. Distinctively, DC also operates the &lt;strong&gt;DC Sustainable Energy Utility (DCSEU)&lt;/strong&gt; &amp;mdash; a district-mandated efficiency program that administers heat pump rebates, weatherization incentives, and low-income weatherization for DC residents. For current rebate dollar amounts, visit dcseu.com, pepco.com, and washingtongas.com directly. Every HVAC contractor working in DC must hold a current &lt;strong&gt;Master Refrigeration and Air Conditioning Mechanic&lt;/strong&gt; license from the &lt;strong&gt;DC Department of Licensing and Consumer Protection (DLCP)&lt;/strong&gt;; verifying a contractor&amp;rsquo;s active DLCP license before authorizing work is the baseline due-diligence step. Permit fees are set by the &lt;strong&gt;DC Department of Buildings (DOB)&lt;/strong&gt;. The federal Section 25C tax credit was terminated for installations after Dec 31, 2025 (OBBBA, P.L. 119-21) &amp;mdash; the local incentives above remain active for 2026.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S126" t="n">
+        <v>4030</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1550</v>
+      </c>
+      <c r="U126" t="n">
+        <v>31</v>
+      </c>
+      <c r="V126" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="W126" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="127">
@@ -12411,6 +13756,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S127" t="n">
+        <v>4592</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1686</v>
+      </c>
+      <c r="U127" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="V127" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12513,6 +13873,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S128" t="n">
+        <v>3617</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1485</v>
+      </c>
+      <c r="U128" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="V128" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="W128" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12615,6 +13990,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S129" t="n">
+        <v>6717</v>
+      </c>
+      <c r="T129" t="n">
+        <v>469</v>
+      </c>
+      <c r="U129" t="n">
+        <v>2</v>
+      </c>
+      <c r="V129" t="n">
+        <v>127</v>
+      </c>
+      <c r="W129" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12794,6 +14184,18 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hawaii DCCA C-52 Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Every HVAC contractor in Honolulu must hold a current &lt;strong&gt;C-52 Ventilating and Air Conditioning Contractor&lt;/strong&gt; license from the &lt;a href="https://cca.hawaii.gov/pvl/boards/contractor/" target="_blank" rel="nofollow noopener"&gt;Hawaii Department of Commerce and Consumer Affairs (DCCA) Professional and Vocational Licensing Division Contractors License Board&lt;/a&gt;. The C-52 classification covers ventilating and air conditioning contracting statewide. Verifying a contractor&amp;rsquo;s active C-52 license via DCCA&amp;rsquo;s online lookup before authorizing work is the baseline due-diligence step. Permit fees for residential mechanical work are set by the &lt;strong&gt;City and County of Honolulu Department of Planning and Permitting (DPP)&lt;/strong&gt; under the Revised Ordinances of Honolulu; contact DPP Building Division at (808) 768-8242 for the current fee schedule. Note: Honolulu is a Census Designated Place within the consolidated City and County of Honolulu &amp;mdash; permitting is handled at the county level.&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="T131" t="n">
+        <v>4628</v>
+      </c>
+      <c r="U131" t="n">
+        <v>19</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -12899,6 +14301,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Columbia are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S132" t="n">
+        <v>2551</v>
+      </c>
+      <c r="T132" t="n">
+        <v>2169</v>
+      </c>
+      <c r="U132" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13003,6 +14420,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Greenville are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S133" t="n">
+        <v>3287</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1643</v>
+      </c>
+      <c r="U133" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="V133" t="n">
+        <v>54.1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13107,6 +14536,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Jackson are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S134" t="n">
+        <v>2392</v>
+      </c>
+      <c r="T134" t="n">
+        <v>2258</v>
+      </c>
+      <c r="U134" t="n">
+        <v>71</v>
+      </c>
+      <c r="V134" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13211,6 +14655,18 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Gulfport are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S135" t="n">
+        <v>1628</v>
+      </c>
+      <c r="T135" t="n">
+        <v>2591</v>
+      </c>
+      <c r="U135" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="V135" t="n">
+        <v>14.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13315,6 +14771,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Bangor are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S136" t="n">
+        <v>7861</v>
+      </c>
+      <c r="T136" t="n">
+        <v>318</v>
+      </c>
+      <c r="U136" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V136" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="W136" t="n">
+        <v>66.09999999999999</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13419,6 +14890,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Morgantown are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S137" t="n">
+        <v>5183</v>
+      </c>
+      <c r="T137" t="n">
+        <v>813</v>
+      </c>
+      <c r="U137" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V137" t="n">
+        <v>102</v>
+      </c>
+      <c r="W137" t="n">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13523,6 +15009,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Billings are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S138" t="n">
+        <v>6781</v>
+      </c>
+      <c r="T138" t="n">
+        <v>637</v>
+      </c>
+      <c r="U138" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="V138" t="n">
+        <v>138</v>
+      </c>
+      <c r="W138" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13627,6 +15128,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Missoula are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S139" t="n">
+        <v>7283</v>
+      </c>
+      <c r="T139" t="n">
+        <v>331</v>
+      </c>
+      <c r="U139" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V139" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="W139" t="n">
+        <v>37.9</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13731,6 +15247,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fargo are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S140" t="n">
+        <v>8800</v>
+      </c>
+      <c r="T140" t="n">
+        <v>551</v>
+      </c>
+      <c r="U140" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V140" t="n">
+        <v>172</v>
+      </c>
+      <c r="W140" t="n">
+        <v>50.1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13831,6 +15362,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Bismarck requires a municipal mechanical contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S141" t="n">
+        <v>8559</v>
+      </c>
+      <c r="T141" t="n">
+        <v>520</v>
+      </c>
+      <c r="U141" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="V141" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="W141" t="n">
+        <v>51.2</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13931,6 +15477,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Sioux Falls requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S142" t="n">
+        <v>7706</v>
+      </c>
+      <c r="T142" t="n">
+        <v>691</v>
+      </c>
+      <c r="U142" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V142" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="W142" t="n">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14031,6 +15592,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Rapid City requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S143" t="n">
+        <v>7152</v>
+      </c>
+      <c r="T143" t="n">
+        <v>636</v>
+      </c>
+      <c r="U143" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="V143" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="W143" t="n">
+        <v>41.1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14131,6 +15707,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Delaware requires HVAC contractors to hold a &lt;strong&gt;Master HVAC License&lt;/strong&gt; issued by the Delaware Board of HVACR Examiners. Verify license status before contracting. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S144" t="n">
+        <v>4819</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1145</v>
+      </c>
+      <c r="U144" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V144" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="W144" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14231,6 +15822,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Burlington&amp;rsquo;s 6,960.3 HDD and 87.5&amp;rdquo; snowfall require cold-climate-rated heat pumps and elevated outdoor-unit mounting. Vermont does not issue a statewide HVAC contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S145" t="n">
+        <v>7435</v>
+      </c>
+      <c r="T145" t="n">
+        <v>492</v>
+      </c>
+      <c r="U145" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V145" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="W145" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14331,6 +15937,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Wyoming does not issue a statewide HVAC license; check local requirements. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S146" t="n">
+        <v>7111</v>
+      </c>
+      <c r="T146" t="n">
+        <v>349</v>
+      </c>
+      <c r="U146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V146" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="W146" t="n">
+        <v>60.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14430,6 +16051,18 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;New Hampshire does not issue a statewide HVAC contractor license; local requirements apply. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S147" t="n">
+        <v>6394</v>
+      </c>
+      <c r="T147" t="n">
+        <v>641</v>
+      </c>
+      <c r="U147" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V147" t="n">
+        <v>130.1</v>
       </c>
     </row>
     <row r="148">
@@ -14531,6 +16164,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per the &lt;a href="https://www.portland.gov/code/29/30" target="_blank" rel="nofollow noopener"&gt;Portland City Code Title 29 Chapter 29.30 (Housing Maintenance Requirements)&lt;/a&gt;, &lt;strong&gt;Section 29.30.180 B&lt;/strong&gt;: &lt;em&gt;&amp;ldquo;Every dwelling must have a heating facility capable of maintaining a room temperature of 68 degrees Fahrenheit at a point three feet from the floor in all habitable rooms.&amp;rdquo;&lt;/em&gt; The practical implication for homeowners: a furnace or heat pump that can&amp;rsquo;t hold 68&amp;deg;F at occupant height isn&amp;rsquo;t just inadequate &amp;mdash; it&amp;rsquo;s a habitability-code violation the City can inspect. Permit fees for residential mechanical work are set by the &lt;strong&gt;Portland Bureau of Development Services (BDS / Portland Permitting &amp;amp; Development)&lt;/strong&gt;; contact BDS directly for the current fee schedule, as mechanical fees are published separately and updated annually.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S148" t="n">
+        <v>4277</v>
+      </c>
+      <c r="T148" t="n">
+        <v>424</v>
+      </c>
+      <c r="U148" t="n">
+        <v>12</v>
+      </c>
+      <c r="V148" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="W148" t="n">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14631,6 +16279,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine requires HVAC technicians to hold a &lt;strong&gt;Master Technician License&lt;/strong&gt; issued by the Maine Fuel Board. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S149" t="n">
+        <v>7106</v>
+      </c>
+      <c r="T149" t="n">
+        <v>360</v>
+      </c>
+      <c r="U149" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V149" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="W149" t="n">
+        <v>61.9</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14731,6 +16394,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC contractors to hold an &lt;strong&gt;HVAC Technician Certification&lt;/strong&gt; issued by the WV Contractor Licensing Board. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="S150" t="n">
+        <v>4480</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1097</v>
+      </c>
+      <c r="U150" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="V150" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="W150" t="n">
+        <v>36.4</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14830,6 +16508,21 @@
 &lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SC Contractor Licensing&lt;/h3&gt;
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC LLR. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
         </is>
+      </c>
+      <c r="S151" t="n">
+        <v>1977</v>
+      </c>
+      <c r="T151" t="n">
+        <v>2304</v>
+      </c>
+      <c r="U151" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="V151" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W151"/>
+  <dimension ref="A1:AB151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -554,6 +554,31 @@
           <t>noaa_snowfall_inches</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>acs_median_home_year</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>acs_heating_fuel_pct_gas</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>acs_heating_fuel_pct_electric</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>acs_owner_occupied_pct</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>acs_median_home_value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -744,6 +769,21 @@
       </c>
       <c r="W3" t="n">
         <v>9.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>266700</v>
       </c>
     </row>
     <row r="4">
@@ -862,6 +902,21 @@
       <c r="W4" t="n">
         <v>32.9</v>
       </c>
+      <c r="X4" t="n">
+        <v>1951</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>188900</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -975,6 +1030,21 @@
       <c r="W5" t="n">
         <v>74.5</v>
       </c>
+      <c r="X5" t="n">
+        <v>1982</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>375900</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1169,6 +1239,21 @@
       </c>
       <c r="W7" t="n">
         <v>2.9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1987</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>420600</v>
       </c>
     </row>
     <row r="8">
@@ -1287,6 +1372,21 @@
       <c r="W8" t="n">
         <v>0.9</v>
       </c>
+      <c r="X8" t="n">
+        <v>1980</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>162900</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1478,6 +1578,21 @@
       <c r="W10" t="n">
         <v>0.2</v>
       </c>
+      <c r="X10" t="n">
+        <v>1993</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>512700</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1590,6 +1705,21 @@
       </c>
       <c r="W11" t="n">
         <v>20.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1948</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>219300</v>
       </c>
     </row>
     <row r="12">
@@ -1708,6 +1838,21 @@
       <c r="W12" t="n">
         <v>0.1</v>
       </c>
+      <c r="X12" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>224500</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1902,6 +2047,21 @@
       </c>
       <c r="W14" t="n">
         <v>1.6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1965</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>138600</v>
       </c>
     </row>
     <row r="15">
@@ -2018,6 +2178,21 @@
       <c r="W15" t="n">
         <v>19.2</v>
       </c>
+      <c r="X15" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>63</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>456000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2132,6 +2307,21 @@
       </c>
       <c r="W16" t="n">
         <v>43.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1947</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>710400</v>
       </c>
     </row>
     <row r="17">
@@ -2328,6 +2518,21 @@
       <c r="W18" t="n">
         <v>27.6</v>
       </c>
+      <c r="X18" t="n">
+        <v>1954</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>252400</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2445,6 +2650,21 @@
       <c r="W19" t="n">
         <v>0</v>
       </c>
+      <c r="X19" t="n">
+        <v>1993</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>122400</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2558,6 +2778,21 @@
       <c r="W20" t="n">
         <v>94.7</v>
       </c>
+      <c r="X20" t="n">
+        <v>1938</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>152300</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2750,6 +2985,21 @@
       </c>
       <c r="W22" t="n">
         <v>4.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1994</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>351500</v>
       </c>
     </row>
     <row r="23">
@@ -2868,6 +3118,21 @@
       <c r="W23" t="n">
         <v>3.9</v>
       </c>
+      <c r="X23" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>259200</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3060,6 +3325,21 @@
       </c>
       <c r="W25" t="n">
         <v>36.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1952</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>315200</v>
       </c>
     </row>
     <row r="26">
@@ -3252,6 +3532,21 @@
       <c r="W27" t="n">
         <v>68.09999999999999</v>
       </c>
+      <c r="X27" t="n">
+        <v>1940</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>94100</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3365,6 +3660,21 @@
       <c r="W28" t="n">
         <v>37.7</v>
       </c>
+      <c r="X28" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>420700</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3478,6 +3788,21 @@
       <c r="W29" t="n">
         <v>26.7</v>
       </c>
+      <c r="X29" t="n">
+        <v>1980</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>234500</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3594,6 +3919,21 @@
       </c>
       <c r="W30" t="n">
         <v>1.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1980</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>295300</v>
       </c>
     </row>
     <row r="31">
@@ -3868,6 +4208,21 @@
       <c r="W33" t="n">
         <v>23.3</v>
       </c>
+      <c r="X33" t="n">
+        <v>1951</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>93200</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3981,6 +4336,21 @@
       </c>
       <c r="V34" t="n">
         <v>156.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>586700</v>
       </c>
     </row>
     <row r="35">
@@ -4099,6 +4469,21 @@
       <c r="W35" t="n">
         <v>35.3</v>
       </c>
+      <c r="X35" t="n">
+        <v>1960</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>183700</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4213,6 +4598,21 @@
       </c>
       <c r="W36" t="n">
         <v>42.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1947</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>76800</v>
       </c>
     </row>
     <row r="37">
@@ -4326,6 +4726,21 @@
       </c>
       <c r="W37" t="n">
         <v>6.9</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1983</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>171700</v>
       </c>
     </row>
     <row r="38">
@@ -4519,6 +4934,21 @@
       </c>
       <c r="W39" t="n">
         <v>4.9</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1979</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>435400</v>
       </c>
     </row>
     <row r="40">
@@ -4715,6 +5145,21 @@
       <c r="W41" t="n">
         <v>3</v>
       </c>
+      <c r="X41" t="n">
+        <v>1983</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>171900</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4910,6 +5355,21 @@
       <c r="W43" t="n">
         <v>33.5</v>
       </c>
+      <c r="X43" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>169700</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5021,6 +5481,21 @@
       <c r="W44" t="n">
         <v>1.6</v>
       </c>
+      <c r="X44" t="n">
+        <v>1992</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>277300</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5206,6 +5681,21 @@
       </c>
       <c r="V46" t="n">
         <v>13.3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1979</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>348500</v>
       </c>
     </row>
     <row r="47">
@@ -5477,6 +5967,21 @@
       <c r="V49" t="n">
         <v>0.4</v>
       </c>
+      <c r="X49" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>347000</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5672,6 +6177,21 @@
       <c r="W51" t="n">
         <v>74.90000000000001</v>
       </c>
+      <c r="X51" t="n">
+        <v>1953</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>225500</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5789,6 +6309,21 @@
       <c r="W52" t="n">
         <v>40.5</v>
       </c>
+      <c r="X52" t="n">
+        <v>1953</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>217200</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6061,6 +6596,21 @@
       </c>
       <c r="W55" t="n">
         <v>0.1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1981</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>253400</v>
       </c>
     </row>
     <row r="56">
@@ -6179,6 +6729,21 @@
       <c r="W56" t="n">
         <v>2.4</v>
       </c>
+      <c r="X56" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>263100</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6291,6 +6856,21 @@
       </c>
       <c r="W57" t="n">
         <v>25.9</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>207000</v>
       </c>
     </row>
     <row r="58">
@@ -6406,6 +6986,21 @@
       <c r="V58" t="n">
         <v>0</v>
       </c>
+      <c r="X58" t="n">
+        <v>2001</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1115400</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6593,6 +7188,21 @@
       </c>
       <c r="V60" t="n">
         <v>15.6</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>266100</v>
       </c>
     </row>
     <row r="61">
@@ -6871,6 +7481,21 @@
       <c r="W63" t="n">
         <v>18.8</v>
       </c>
+      <c r="X63" t="n">
+        <v>1968</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>227000</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6988,6 +7613,21 @@
       <c r="W64" t="n">
         <v>6.5</v>
       </c>
+      <c r="X64" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>214000</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7090,6 +7730,21 @@
 &lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="X65" t="n">
+        <v>1996</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>182400</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7204,6 +7859,21 @@
       </c>
       <c r="W66" t="n">
         <v>0.3</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1994</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>395300</v>
       </c>
     </row>
     <row r="67">
@@ -7322,6 +7992,21 @@
       <c r="W67" t="n">
         <v>13</v>
       </c>
+      <c r="X67" t="n">
+        <v>1983</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>272100</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7439,6 +8124,21 @@
       <c r="W68" t="n">
         <v>25.9</v>
       </c>
+      <c r="X68" t="n">
+        <v>1981</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>248200</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7556,6 +8256,21 @@
       <c r="W69" t="n">
         <v>3.5</v>
       </c>
+      <c r="X69" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>221200</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7673,6 +8388,21 @@
       <c r="W70" t="n">
         <v>0</v>
       </c>
+      <c r="X70" t="n">
+        <v>1964</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>879500</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7783,6 +8513,21 @@
       </c>
       <c r="W71" t="n">
         <v>12.5</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>221500</v>
       </c>
     </row>
     <row r="72">
@@ -7901,6 +8646,21 @@
       <c r="W72" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="X72" t="n">
+        <v>1983</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>197900</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8018,6 +8778,21 @@
       <c r="W73" t="n">
         <v>50.9</v>
       </c>
+      <c r="X73" t="n">
+        <v>1979</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>346900</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8131,6 +8906,21 @@
       <c r="W74" t="n">
         <v>3.8</v>
       </c>
+      <c r="X74" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>157100</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8238,6 +9028,21 @@
       </c>
       <c r="V75" t="n">
         <v>0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1988</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>364300</v>
       </c>
     </row>
     <row r="76">
@@ -8352,6 +9157,21 @@
       <c r="W76" t="n">
         <v>0</v>
       </c>
+      <c r="X76" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>475200</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8468,6 +9288,21 @@
       </c>
       <c r="W77" t="n">
         <v>46.9</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1952</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>172000</v>
       </c>
     </row>
     <row r="78">
@@ -8587,6 +9422,21 @@
       </c>
       <c r="W78" t="n">
         <v>54.4</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>345600</v>
       </c>
     </row>
     <row r="79">
@@ -8705,6 +9555,21 @@
       <c r="W79" t="n">
         <v>0.2</v>
       </c>
+      <c r="X79" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>170300</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8822,6 +9687,21 @@
       <c r="W80" t="n">
         <v>0</v>
       </c>
+      <c r="X80" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>415600</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8932,6 +9812,21 @@
       </c>
       <c r="W81" t="n">
         <v>6.3</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>53</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>383100</v>
       </c>
     </row>
     <row r="82">
@@ -9047,6 +9942,21 @@
       <c r="V82" t="n">
         <v>5.8</v>
       </c>
+      <c r="X82" t="n">
+        <v>1959</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>296400</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9160,6 +10070,21 @@
       <c r="W83" t="n">
         <v>25.8</v>
       </c>
+      <c r="X83" t="n">
+        <v>1952</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>751700</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9273,6 +10198,21 @@
       <c r="W84" t="n">
         <v>28.5</v>
       </c>
+      <c r="X84" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>337800</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9383,6 +10323,21 @@
       <c r="V85" t="n">
         <v>2.9</v>
       </c>
+      <c r="X85" t="n">
+        <v>1953</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>924700</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9500,6 +10455,21 @@
       <c r="W86" t="n">
         <v>7.6</v>
       </c>
+      <c r="X86" t="n">
+        <v>1981</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>215100</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9612,6 +10582,21 @@
       </c>
       <c r="W87" t="n">
         <v>26.5</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>230100</v>
       </c>
     </row>
     <row r="88">
@@ -9730,6 +10715,21 @@
       <c r="W88" t="n">
         <v>24.6</v>
       </c>
+      <c r="X88" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>149500</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9846,6 +10846,21 @@
       </c>
       <c r="W89" t="n">
         <v>22.4</v>
+      </c>
+      <c r="X89" t="n">
+        <v>1949</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>232400</v>
       </c>
     </row>
     <row r="90">
@@ -9963,6 +10978,21 @@
       <c r="V90" t="n">
         <v>0.4</v>
       </c>
+      <c r="X90" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>381900</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10075,6 +11105,21 @@
       </c>
       <c r="W91" t="n">
         <v>41.4</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1942</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>193200</v>
       </c>
     </row>
     <row r="92">
@@ -10349,6 +11394,21 @@
       <c r="W94" t="n">
         <v>33.8</v>
       </c>
+      <c r="X94" t="n">
+        <v>1938</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>322800</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10461,6 +11521,21 @@
       </c>
       <c r="W95" t="n">
         <v>6.1</v>
+      </c>
+      <c r="X95" t="n">
+        <v>1996</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>377800</v>
       </c>
     </row>
     <row r="96">
@@ -10579,6 +11654,21 @@
       <c r="W96" t="n">
         <v>21.8</v>
       </c>
+      <c r="X96" t="n">
+        <v>1989</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>498600</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10696,6 +11786,21 @@
       <c r="W97" t="n">
         <v>10.3</v>
       </c>
+      <c r="X97" t="n">
+        <v>1959</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>328100</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10965,6 +12070,21 @@
       <c r="W100" t="n">
         <v>0</v>
       </c>
+      <c r="X100" t="n">
+        <v>1976</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>484600</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11078,6 +12198,21 @@
       <c r="W101" t="n">
         <v>56.2</v>
       </c>
+      <c r="X101" t="n">
+        <v>1963</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>495700</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11194,6 +12329,21 @@
       </c>
       <c r="W102" t="n">
         <v>0.7</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>219700</v>
       </c>
     </row>
     <row r="103">
@@ -11310,6 +12460,21 @@
       <c r="W103" t="n">
         <v>0</v>
       </c>
+      <c r="X103" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>848500</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11420,6 +12585,21 @@
       </c>
       <c r="W104" t="n">
         <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>1945</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>1380500</v>
       </c>
     </row>
     <row r="105">
@@ -11531,6 +12711,21 @@
       <c r="V105" t="n">
         <v>1.7</v>
       </c>
+      <c r="X105" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1187800</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11877,6 +13072,21 @@
       </c>
       <c r="W109" t="n">
         <v>6.8</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>912100</v>
       </c>
     </row>
     <row r="110">
@@ -11995,6 +13205,21 @@
       <c r="W110" t="n">
         <v>1</v>
       </c>
+      <c r="X110" t="n">
+        <v>1973</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>178100</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12112,6 +13337,21 @@
       <c r="W111" t="n">
         <v>44.9</v>
       </c>
+      <c r="X111" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>326200</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12229,6 +13469,21 @@
       <c r="W112" t="n">
         <v>43.8</v>
       </c>
+      <c r="X112" t="n">
+        <v>1951</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>222700</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12345,6 +13600,21 @@
       </c>
       <c r="W113" t="n">
         <v>17.7</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1938</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>185100</v>
       </c>
     </row>
     <row r="114">
@@ -12619,6 +13889,21 @@
       <c r="W116" t="n">
         <v>123.8</v>
       </c>
+      <c r="X116" t="n">
+        <v>1947</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>125100</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12814,6 +14099,21 @@
       <c r="W118" t="n">
         <v>0.1</v>
       </c>
+      <c r="X118" t="n">
+        <v>1987</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>276000</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12930,6 +14230,21 @@
       </c>
       <c r="W119" t="n">
         <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>92</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>375300</v>
       </c>
     </row>
     <row r="120">
@@ -13048,6 +14363,21 @@
       <c r="W120" t="n">
         <v>37.6</v>
       </c>
+      <c r="X120" t="n">
+        <v>1955</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>107000</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -13239,6 +14569,21 @@
       <c r="W122" t="n">
         <v>0.6</v>
       </c>
+      <c r="X122" t="n">
+        <v>1979</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>242200</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13349,6 +14694,21 @@
       </c>
       <c r="W123" t="n">
         <v>9.6</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>52</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>189600</v>
       </c>
     </row>
     <row r="124">
@@ -13541,6 +14901,21 @@
       <c r="W125" t="n">
         <v>5.8</v>
       </c>
+      <c r="X125" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>366300</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13653,6 +15028,21 @@
       </c>
       <c r="W126" t="n">
         <v>15.4</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1957</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>724600</v>
       </c>
     </row>
     <row r="127">
@@ -13771,6 +15161,21 @@
       <c r="W127" t="n">
         <v>14.9</v>
       </c>
+      <c r="X127" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>179500</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13888,6 +15293,21 @@
       <c r="W128" t="n">
         <v>7.5</v>
       </c>
+      <c r="X128" t="n">
+        <v>1980</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>208200</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14005,6 +15425,21 @@
       <c r="W129" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="X129" t="n">
+        <v>1951</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>339500</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14196,6 +15631,21 @@
       </c>
       <c r="W131" t="n">
         <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>1973</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>834100</v>
       </c>
     </row>
     <row r="132">
@@ -14316,6 +15766,21 @@
       <c r="W132" t="n">
         <v>1.5</v>
       </c>
+      <c r="X132" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>243500</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14432,6 +15897,21 @@
       <c r="V133" t="n">
         <v>54.1</v>
       </c>
+      <c r="X133" t="n">
+        <v>1987</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>453300</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14551,6 +16031,21 @@
       <c r="W134" t="n">
         <v>0.8</v>
       </c>
+      <c r="X134" t="n">
+        <v>1969</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>108200</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14667,6 +16162,21 @@
       <c r="V135" t="n">
         <v>14.8</v>
       </c>
+      <c r="X135" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>167100</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14786,6 +16296,21 @@
       <c r="W136" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="X136" t="n">
+        <v>1955</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>206300</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14905,6 +16430,21 @@
       <c r="W137" t="n">
         <v>27.6</v>
       </c>
+      <c r="X137" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>238200</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15024,6 +16564,21 @@
       <c r="W138" t="n">
         <v>55</v>
       </c>
+      <c r="X138" t="n">
+        <v>1979</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>311800</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15143,6 +16698,21 @@
       <c r="W139" t="n">
         <v>37.9</v>
       </c>
+      <c r="X139" t="n">
+        <v>1981</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>427400</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15262,6 +16832,21 @@
       <c r="W140" t="n">
         <v>50.1</v>
       </c>
+      <c r="X140" t="n">
+        <v>1991</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>269800</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15377,6 +16962,21 @@
       <c r="W141" t="n">
         <v>51.2</v>
       </c>
+      <c r="X141" t="n">
+        <v>1984</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>291400</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15492,6 +17092,21 @@
       <c r="W142" t="n">
         <v>44.5</v>
       </c>
+      <c r="X142" t="n">
+        <v>1992</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>271400</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15607,6 +17222,21 @@
       <c r="W143" t="n">
         <v>41.1</v>
       </c>
+      <c r="X143" t="n">
+        <v>1978</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>270000</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15722,6 +17352,21 @@
       <c r="W144" t="n">
         <v>20.2</v>
       </c>
+      <c r="X144" t="n">
+        <v>1946</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>224500</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15837,6 +17482,21 @@
       <c r="W145" t="n">
         <v>81.2</v>
       </c>
+      <c r="X145" t="n">
+        <v>1957</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>400200</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15952,6 +17612,21 @@
       <c r="W146" t="n">
         <v>60.3</v>
       </c>
+      <c r="X146" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>311200</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -16063,6 +17738,21 @@
       </c>
       <c r="V147" t="n">
         <v>130.1</v>
+      </c>
+      <c r="X147" t="n">
+        <v>1964</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>336300</v>
       </c>
     </row>
     <row r="148">
@@ -16179,6 +17869,21 @@
       <c r="W148" t="n">
         <v>4.3</v>
       </c>
+      <c r="X148" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>557600</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -16294,6 +17999,21 @@
       <c r="W149" t="n">
         <v>61.9</v>
       </c>
+      <c r="X149" t="n">
+        <v>1946</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>452600</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -16409,6 +18129,21 @@
       <c r="W150" t="n">
         <v>36.4</v>
       </c>
+      <c r="X150" t="n">
+        <v>1956</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>187300</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -16523,6 +18258,21 @@
       </c>
       <c r="W151" t="n">
         <v>0.5</v>
+      </c>
+      <c r="X151" t="n">
+        <v>1994</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>469100</v>
       </c>
     </row>
   </sheetData>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB151"/>
+  <dimension ref="A1:AD151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,16 @@
           <t>acs_median_home_value</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>eia_state_elec_rate</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>eia_state_gas_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -784,6 +794,12 @@
       </c>
       <c r="AB3" t="n">
         <v>266700</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.873</v>
       </c>
     </row>
     <row r="4">
@@ -917,6 +933,12 @@
       <c r="AB4" t="n">
         <v>188900</v>
       </c>
+      <c r="AC4" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.313</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1045,6 +1067,12 @@
       <c r="AB5" t="n">
         <v>375900</v>
       </c>
+      <c r="AC5" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.131</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1254,6 +1282,12 @@
       </c>
       <c r="AB7" t="n">
         <v>420600</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.754</v>
       </c>
     </row>
     <row r="8">
@@ -1387,6 +1421,12 @@
       <c r="AB8" t="n">
         <v>162900</v>
       </c>
+      <c r="AC8" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.754</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1593,6 +1633,12 @@
       <c r="AB10" t="n">
         <v>512700</v>
       </c>
+      <c r="AC10" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.734</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1720,6 +1766,12 @@
       </c>
       <c r="AB11" t="n">
         <v>219300</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.556</v>
       </c>
     </row>
     <row r="12">
@@ -1853,6 +1905,12 @@
       <c r="AB12" t="n">
         <v>224500</v>
       </c>
+      <c r="AC12" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.58</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2062,6 +2120,12 @@
       </c>
       <c r="AB14" t="n">
         <v>138600</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.797</v>
       </c>
     </row>
     <row r="15">
@@ -2193,6 +2257,12 @@
       <c r="AB15" t="n">
         <v>456000</v>
       </c>
+      <c r="AC15" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.821</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2322,6 +2392,12 @@
       </c>
       <c r="AB16" t="n">
         <v>710400</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.112</v>
       </c>
     </row>
     <row r="17">
@@ -2533,6 +2609,12 @@
       <c r="AB18" t="n">
         <v>252400</v>
       </c>
+      <c r="AC18" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.623</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2665,6 +2747,12 @@
       <c r="AB19" t="n">
         <v>122400</v>
       </c>
+      <c r="AC19" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.734</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2793,6 +2881,12 @@
       <c r="AB20" t="n">
         <v>152300</v>
       </c>
+      <c r="AC20" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.599</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3000,6 +3094,12 @@
       </c>
       <c r="AB22" t="n">
         <v>351500</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.583</v>
       </c>
     </row>
     <row r="23">
@@ -3133,6 +3233,12 @@
       <c r="AB23" t="n">
         <v>259200</v>
       </c>
+      <c r="AC23" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.037</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3340,6 +3446,12 @@
       </c>
       <c r="AB25" t="n">
         <v>315200</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.071</v>
       </c>
     </row>
     <row r="26">
@@ -3547,6 +3659,12 @@
       <c r="AB27" t="n">
         <v>94100</v>
       </c>
+      <c r="AC27" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.328</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3675,6 +3793,12 @@
       <c r="AB28" t="n">
         <v>420700</v>
       </c>
+      <c r="AC28" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.02</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3803,6 +3927,12 @@
       <c r="AB29" t="n">
         <v>234500</v>
       </c>
+      <c r="AC29" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.328</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3934,6 +4064,12 @@
       </c>
       <c r="AB30" t="n">
         <v>295300</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.734</v>
       </c>
     </row>
     <row r="31">
@@ -4223,6 +4359,12 @@
       <c r="AB33" t="n">
         <v>93200</v>
       </c>
+      <c r="AC33" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.328</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4351,6 +4493,12 @@
       </c>
       <c r="AB34" t="n">
         <v>586700</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="35">
@@ -4484,6 +4632,12 @@
       <c r="AB35" t="n">
         <v>183700</v>
       </c>
+      <c r="AC35" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4613,6 +4767,12 @@
       </c>
       <c r="AB36" t="n">
         <v>76800</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.038</v>
       </c>
     </row>
     <row r="37">
@@ -4741,6 +4901,12 @@
       </c>
       <c r="AB37" t="n">
         <v>171700</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.734</v>
       </c>
     </row>
     <row r="38">
@@ -4949,6 +5115,12 @@
       </c>
       <c r="AB39" t="n">
         <v>435400</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.515</v>
       </c>
     </row>
     <row r="40">
@@ -5160,6 +5332,12 @@
       <c r="AB41" t="n">
         <v>171900</v>
       </c>
+      <c r="AC41" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.583</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5370,6 +5548,12 @@
       <c r="AB43" t="n">
         <v>169700</v>
       </c>
+      <c r="AC43" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.916</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5496,6 +5680,12 @@
       <c r="AB44" t="n">
         <v>277300</v>
       </c>
+      <c r="AC44" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.734</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5696,6 +5886,12 @@
       </c>
       <c r="AB46" t="n">
         <v>348500</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.846</v>
       </c>
     </row>
     <row r="47">
@@ -5982,6 +6178,12 @@
       <c r="AB49" t="n">
         <v>347000</v>
       </c>
+      <c r="AC49" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.974</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6192,6 +6394,12 @@
       <c r="AB51" t="n">
         <v>225500</v>
       </c>
+      <c r="AC51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.038</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6324,6 +6532,12 @@
       <c r="AB52" t="n">
         <v>217200</v>
       </c>
+      <c r="AC52" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.623</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6611,6 +6825,12 @@
       </c>
       <c r="AB55" t="n">
         <v>253400</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.734</v>
       </c>
     </row>
     <row r="56">
@@ -6744,6 +6964,12 @@
       <c r="AB56" t="n">
         <v>263100</v>
       </c>
+      <c r="AC56" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.797</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6871,6 +7097,12 @@
       </c>
       <c r="AB57" t="n">
         <v>207000</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.916</v>
       </c>
     </row>
     <row r="58">
@@ -7001,6 +7233,12 @@
       <c r="AB58" t="n">
         <v>1115400</v>
       </c>
+      <c r="AC58" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7203,6 +7441,12 @@
       </c>
       <c r="AB60" t="n">
         <v>266100</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>2.446</v>
       </c>
     </row>
     <row r="61">
@@ -7496,6 +7740,12 @@
       <c r="AB63" t="n">
         <v>227000</v>
       </c>
+      <c r="AC63" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.626</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7628,6 +7878,12 @@
       <c r="AB64" t="n">
         <v>214000</v>
       </c>
+      <c r="AC64" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.037</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7745,6 +8001,12 @@
       <c r="AB65" t="n">
         <v>182400</v>
       </c>
+      <c r="AC65" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.734</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7874,6 +8136,12 @@
       </c>
       <c r="AB66" t="n">
         <v>395300</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.802</v>
       </c>
     </row>
     <row r="67">
@@ -8007,6 +8275,12 @@
       <c r="AB67" t="n">
         <v>272100</v>
       </c>
+      <c r="AC67" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.312</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8139,6 +8413,12 @@
       <c r="AB68" t="n">
         <v>248200</v>
       </c>
+      <c r="AC68" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.025</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8271,6 +8551,12 @@
       <c r="AB69" t="n">
         <v>221200</v>
       </c>
+      <c r="AC69" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.552</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8403,6 +8689,12 @@
       <c r="AB70" t="n">
         <v>879500</v>
       </c>
+      <c r="AC70" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8528,6 +8820,12 @@
       </c>
       <c r="AB71" t="n">
         <v>221500</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.312</v>
       </c>
     </row>
     <row r="72">
@@ -8661,6 +8959,12 @@
       <c r="AB72" t="n">
         <v>197900</v>
       </c>
+      <c r="AC72" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.734</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8793,6 +9097,12 @@
       <c r="AB73" t="n">
         <v>346900</v>
       </c>
+      <c r="AC73" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.978</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8921,6 +9231,12 @@
       <c r="AB74" t="n">
         <v>157100</v>
       </c>
+      <c r="AC74" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.037</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9043,6 +9359,12 @@
       </c>
       <c r="AB75" t="n">
         <v>364300</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.974</v>
       </c>
     </row>
     <row r="76">
@@ -9172,6 +9494,12 @@
       <c r="AB76" t="n">
         <v>475200</v>
       </c>
+      <c r="AC76" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>2.446</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9303,6 +9631,12 @@
       </c>
       <c r="AB77" t="n">
         <v>172000</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0.978</v>
       </c>
     </row>
     <row r="78">
@@ -9437,6 +9771,12 @@
       </c>
       <c r="AB78" t="n">
         <v>345600</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.027</v>
       </c>
     </row>
     <row r="79">
@@ -9570,6 +9910,12 @@
       <c r="AB79" t="n">
         <v>170300</v>
       </c>
+      <c r="AC79" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.797</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9702,6 +10048,12 @@
       <c r="AB80" t="n">
         <v>415600</v>
       </c>
+      <c r="AC80" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9827,6 +10179,12 @@
       </c>
       <c r="AB81" t="n">
         <v>383100</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1.037</v>
       </c>
     </row>
     <row r="82">
@@ -9957,6 +10315,12 @@
       <c r="AB82" t="n">
         <v>296400</v>
       </c>
+      <c r="AC82" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1.58</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10085,6 +10449,12 @@
       <c r="AB83" t="n">
         <v>751700</v>
       </c>
+      <c r="AC83" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>1.599</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10213,6 +10583,12 @@
       <c r="AB84" t="n">
         <v>337800</v>
       </c>
+      <c r="AC84" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1.274</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10338,6 +10714,12 @@
       <c r="AB85" t="n">
         <v>924700</v>
       </c>
+      <c r="AC85" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10470,6 +10852,12 @@
       <c r="AB86" t="n">
         <v>215100</v>
       </c>
+      <c r="AC86" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1.349</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10597,6 +10985,12 @@
       </c>
       <c r="AB87" t="n">
         <v>230100</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>1.025</v>
       </c>
     </row>
     <row r="88">
@@ -10730,6 +11124,12 @@
       <c r="AB88" t="n">
         <v>149500</v>
       </c>
+      <c r="AC88" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1.071</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10861,6 +11261,12 @@
       </c>
       <c r="AB89" t="n">
         <v>232400</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="90">
@@ -10993,6 +11399,12 @@
       <c r="AB90" t="n">
         <v>381900</v>
       </c>
+      <c r="AC90" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>1.974</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11120,6 +11532,12 @@
       </c>
       <c r="AB91" t="n">
         <v>193200</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="92">
@@ -11409,6 +11827,12 @@
       <c r="AB94" t="n">
         <v>322800</v>
       </c>
+      <c r="AC94" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>2.089</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11536,6 +11960,12 @@
       </c>
       <c r="AB95" t="n">
         <v>377800</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>1.583</v>
       </c>
     </row>
     <row r="96">
@@ -11669,6 +12099,12 @@
       <c r="AB96" t="n">
         <v>498600</v>
       </c>
+      <c r="AC96" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>1.802</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11801,6 +12237,12 @@
       <c r="AB97" t="n">
         <v>328100</v>
       </c>
+      <c r="AC97" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>1.485</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12085,6 +12527,12 @@
       <c r="AB100" t="n">
         <v>484600</v>
       </c>
+      <c r="AC100" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12213,6 +12661,12 @@
       <c r="AB101" t="n">
         <v>495700</v>
       </c>
+      <c r="AC101" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1.268</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12344,6 +12798,12 @@
       </c>
       <c r="AB102" t="n">
         <v>219700</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>1.734</v>
       </c>
     </row>
     <row r="103">
@@ -12475,6 +12935,12 @@
       <c r="AB103" t="n">
         <v>848500</v>
       </c>
+      <c r="AC103" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12600,6 +13066,12 @@
       </c>
       <c r="AB104" t="n">
         <v>1380500</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>1.846</v>
       </c>
     </row>
     <row r="105">
@@ -12726,6 +13198,12 @@
       <c r="AB105" t="n">
         <v>1187800</v>
       </c>
+      <c r="AC105" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>1.846</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13087,6 +13565,12 @@
       </c>
       <c r="AB109" t="n">
         <v>912100</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>1.227</v>
       </c>
     </row>
     <row r="110">
@@ -13220,6 +13704,12 @@
       <c r="AB110" t="n">
         <v>178100</v>
       </c>
+      <c r="AC110" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>1.58</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13352,6 +13842,12 @@
       <c r="AB111" t="n">
         <v>326200</v>
       </c>
+      <c r="AC111" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>1.227</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13484,6 +13980,12 @@
       <c r="AB112" t="n">
         <v>222700</v>
       </c>
+      <c r="AC112" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>2.112</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13615,6 +14117,12 @@
       </c>
       <c r="AB113" t="n">
         <v>185100</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>1.626</v>
       </c>
     </row>
     <row r="114">
@@ -13904,6 +14412,12 @@
       <c r="AB116" t="n">
         <v>125100</v>
       </c>
+      <c r="AC116" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>1.599</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14114,6 +14628,12 @@
       <c r="AB118" t="n">
         <v>276000</v>
       </c>
+      <c r="AC118" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>2.446</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14245,6 +14765,12 @@
       </c>
       <c r="AB119" t="n">
         <v>375300</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>2.446</v>
       </c>
     </row>
     <row r="120">
@@ -14378,6 +14904,12 @@
       <c r="AB120" t="n">
         <v>107000</v>
       </c>
+      <c r="AC120" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1.328</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14584,6 +15116,12 @@
       <c r="AB122" t="n">
         <v>242200</v>
       </c>
+      <c r="AC122" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1.974</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14709,6 +15247,12 @@
       </c>
       <c r="AB123" t="n">
         <v>189600</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>1.349</v>
       </c>
     </row>
     <row r="124">
@@ -14916,6 +15460,12 @@
       <c r="AB125" t="n">
         <v>366300</v>
       </c>
+      <c r="AC125" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>1.485</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15043,6 +15593,12 @@
       </c>
       <c r="AB126" t="n">
         <v>724600</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="127">
@@ -15176,6 +15732,12 @@
       <c r="AB127" t="n">
         <v>179500</v>
       </c>
+      <c r="AC127" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>1.267</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15308,6 +15870,12 @@
       <c r="AB128" t="n">
         <v>208200</v>
       </c>
+      <c r="AC128" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>1.583</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15440,6 +16008,12 @@
       <c r="AB129" t="n">
         <v>339500</v>
       </c>
+      <c r="AC129" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>2.112</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15646,6 +16220,12 @@
       </c>
       <c r="AB131" t="n">
         <v>834100</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>4.714</v>
       </c>
     </row>
     <row r="132">
@@ -15781,6 +16361,12 @@
       <c r="AB132" t="n">
         <v>243500</v>
       </c>
+      <c r="AC132" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>1.631</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15912,6 +16498,12 @@
       <c r="AB133" t="n">
         <v>453300</v>
       </c>
+      <c r="AC133" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.631</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16046,6 +16638,12 @@
       <c r="AB134" t="n">
         <v>108200</v>
       </c>
+      <c r="AC134" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1.487</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16177,6 +16775,12 @@
       <c r="AB135" t="n">
         <v>167100</v>
       </c>
+      <c r="AC135" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1.487</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16311,6 +16915,12 @@
       <c r="AB136" t="n">
         <v>206300</v>
       </c>
+      <c r="AC136" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>1.827</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16445,6 +17055,12 @@
       <c r="AB137" t="n">
         <v>238200</v>
       </c>
+      <c r="AC137" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>1.472</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16579,6 +17195,12 @@
       <c r="AB138" t="n">
         <v>311800</v>
       </c>
+      <c r="AC138" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.793</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16713,6 +17335,12 @@
       <c r="AB139" t="n">
         <v>427400</v>
       </c>
+      <c r="AC139" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.793</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16847,6 +17475,12 @@
       <c r="AB140" t="n">
         <v>269800</v>
       </c>
+      <c r="AC140" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.867</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16977,6 +17611,12 @@
       <c r="AB141" t="n">
         <v>291400</v>
       </c>
+      <c r="AC141" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.867</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17107,6 +17747,12 @@
       <c r="AB142" t="n">
         <v>271400</v>
       </c>
+      <c r="AC142" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.899</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17237,6 +17883,12 @@
       <c r="AB143" t="n">
         <v>270000</v>
       </c>
+      <c r="AC143" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.899</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -17367,6 +18019,12 @@
       <c r="AB144" t="n">
         <v>224500</v>
       </c>
+      <c r="AC144" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>1.425</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -17497,6 +18155,12 @@
       <c r="AB145" t="n">
         <v>400200</v>
       </c>
+      <c r="AC145" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>1.672</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17627,6 +18291,12 @@
       <c r="AB146" t="n">
         <v>311200</v>
       </c>
+      <c r="AC146" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>1.195</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17753,6 +18423,12 @@
       </c>
       <c r="AB147" t="n">
         <v>336300</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>1.807</v>
       </c>
     </row>
     <row r="148">
@@ -17884,6 +18560,12 @@
       <c r="AB148" t="n">
         <v>557600</v>
       </c>
+      <c r="AC148" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>1.515</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -18014,6 +18696,12 @@
       <c r="AB149" t="n">
         <v>452600</v>
       </c>
+      <c r="AC149" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>1.827</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -18144,6 +18832,12 @@
       <c r="AB150" t="n">
         <v>187300</v>
       </c>
+      <c r="AC150" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>1.472</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18273,6 +18967,12 @@
       </c>
       <c r="AB151" t="n">
         <v>469100</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>1.631</v>
       </c>
     </row>
   </sheetData>

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -7831,21 +7831,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTYS)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;McGhee Tyson Airport (KTYS) is the official NOAA reference station for Knoxville. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013891), Knoxville records an &lt;strong&gt;annual mean temperature of 59.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 70.0&amp;deg;F&lt;/strong&gt; against an annual minimum of 49.1&amp;deg;F, approximately &lt;strong&gt;3,528.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,574.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;51.93 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;4.6 inches&lt;/strong&gt;. The roughly 2.2:1 HDD-to-CDD ratio reflects a dual-load climate in the Tennessee Valley &amp;mdash; meaningful heating and cooling demand, with 52 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:40000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Knoxville city, Tennessee) report &lt;strong&gt;84,882 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.0% electricity&lt;/strong&gt; (62,794 units), &lt;strong&gt;24.7% utility natural gas&lt;/strong&gt; (20,963 units), and 410 on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories, where historically affordable hydroelectric power made heat-pump and electric-resistance heating economically competitive.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: KUB Municipal Utility (TVA Distributor)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Knoxville&amp;rsquo;s electric service is provided by the &lt;strong&gt;Knoxville Utilities Board (KUB)&lt;/strong&gt;, a municipally owned utility that distributes TVA power. KUB / TVA EnergyRight administers residential HVAC rebates; contact KUB directly for the current heat pump and smart thermostat rebate amounts. Like Chattanooga&amp;rsquo;s EPB and Huntsville Utilities, KUB&amp;rsquo;s municipal status means customers contract with the City rather than a private investor-owned utility.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate &amp;amp; Dehumidification (Zone 4A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Knoxville&amp;rsquo;s combination of 1,574.4 CDD and 51.93 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in the Tennessee Valley&amp;rsquo;s humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License (CMC-C)&lt;/strong&gt; issued by the Tennessee Board for Licensing Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Knoxville are set by the City of Knoxville Plans Review &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTYS)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;McGhee Tyson Airport (KTYS) is the official NOAA reference station for Knoxville. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013891), Knoxville records approximately &lt;strong&gt;3,636 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,526 cooling degree days&lt;/strong&gt;, an annual precipitation normal of approximately &lt;strong&gt;52 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;6.5 inches&lt;/strong&gt;. The city averages &lt;strong&gt;31.4 days per year above 90&amp;deg;F&lt;/strong&gt; and &lt;strong&gt;67 days below freezing&lt;/strong&gt;. The roughly 2.4:1 HDD-to-CDD ratio reflects a true dual-load climate in the eastern Tennessee Valley &amp;mdash; meaningful heating and cooling demand, with the 52 inches of annual precipitation driving heavy summer humidity loads. A distinctive operational concern in Knoxville is &lt;strong&gt;summer ground-level ozone&lt;/strong&gt;: the Tennessee Department of Environment &amp;amp; Conservation periodically issues Code Orange air-quality alerts for the Knoxville-Sevierville region, and EPA designations (&lt;a href="https://archive.epa.gov/ozonedesignations/web/pdf/r4_knoxville_tsd_final.pdf" target="_blank" rel="nofollow noopener"&gt;EPA Region 4 technical support document&lt;/a&gt;) historically identified higher-elevation monitors within Great Smoky Mountains National Park as exceeding ozone thresholds. Real-time alerts are tracked on &lt;a href="https://www.airnow.gov/state/?name=tennessee" target="_blank" rel="nofollow noopener"&gt;EPA AirNow&lt;/a&gt;; sensitive-population HVAC operation should incorporate fresh-air filtration on alert days.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:40000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Knoxville city, Tennessee) report &lt;strong&gt;84,882 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.0% electricity&lt;/strong&gt; (62,794 units), &lt;strong&gt;24.7% utility natural gas&lt;/strong&gt; (20,963 units), and 410 units on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories, where historically affordable hydroelectric and nuclear power made electric-resistance and heat-pump heating economically competitive against gas. &lt;strong&gt;Owner-occupancy is 46.6%&lt;/strong&gt; (reflecting the University of Tennessee&amp;rsquo;s significant rental footprint), and the &lt;strong&gt;median home value is $214,000&lt;/strong&gt;. Tennessee&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 12.82&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the lowest in the project, reinforcing the economic case for heat-pump primary heat.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;KUB &amp;amp; TVA EnergyRight Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Knoxville&amp;rsquo;s electric service is provided by the &lt;strong&gt;Knoxville Utilities Board (KUB)&lt;/strong&gt;, a municipally owned utility that distributes wholesale power from the Tennessee Valley Authority. Residential HVAC rebates are administered through KUB&amp;rsquo;s partnership with the &lt;a href="https://energyright.com/residential/rebates/heat-pump/" target="_blank" rel="nofollow noopener"&gt;TVA EnergyRight program&lt;/a&gt;. Current published amounts: &lt;strong&gt;up to $1,500 for a qualifying high-efficiency heat pump (TVA Preferred tier)&lt;/strong&gt;, with a typical baseline rebate of $500&amp;ndash;$800 depending on efficiency and local power-company match; &lt;strong&gt;up to $700 for a qualifying high-efficiency central air conditioner&lt;/strong&gt;; and &lt;strong&gt;up to $1,300 for a qualifying ENERGY STAR heat pump water heater&lt;/strong&gt;. TVA EnergyRight rebates require installation by a member of the &lt;strong&gt;TVA Quality Contractor Network (QCN)&lt;/strong&gt;; gas-to-electric conversion is not currently rebate-eligible (replacement of existing electric heating is required). Tennessee&amp;rsquo;s federally funded &lt;a href="https://www.tn.gov/environment/program-areas/energy/state-energy-office--seo-/programs-projects/programs-and-projects/inflation-reduction-act/home-energy-rebate-programs.html" target="_blank" rel="nofollow noopener"&gt;HEAR program&lt;/a&gt; (approximately $83.4 million allocation, administered by TDEC Office of Energy Programs in partnership with TVA&amp;rsquo;s QCN) received conditional DOE approval in January 2025 with statewide launch targeted for Q3 2026. Once active, HEAR will allow gas-to-heat-pump conversion rebates of up to $8,000 per qualifying household; until then, existing TVA EnergyRight rebates remain the primary published path.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors performing projects of &lt;strong&gt;$25,000 or more&lt;/strong&gt; to hold a Mechanical Contractor license issued by the Tennessee Board for Licensing Contractors (&lt;a href="https://programs.dsireusa.org/system/program?fromSir=0&amp;amp;state=TN" target="_blank" rel="nofollow noopener"&gt;state contractor regulator&lt;/a&gt;). The HVAC-specific subclassification is &lt;strong&gt;CMC-C (Mechanical &amp;mdash; HVAC/Refrigeration Contractor)&lt;/strong&gt;, with a &lt;strong&gt;$250 application fee&lt;/strong&gt;, a $53 statewide business and law exam, and a $106 statewide trade exam. Bonding is not automatically required at the state level but may be triggered by the Board&amp;rsquo;s financial-statement review or by local Knox County permitting requirements. Mechanical permits in Knoxville are issued by the &lt;strong&gt;City of Knoxville Plans Review &amp;amp; Inspections Division&lt;/strong&gt; &amp;mdash; verify the current fee schedule and any local bonding requirement directly with that office before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -13933,21 +13919,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCEF)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Westover Metropolitan Airport (KCEF) is the official NOAA reference station for the Springfield area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014764), Springfield records an &lt;strong&gt;annual mean temperature of 47.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 38.6&amp;deg;F, approximately &lt;strong&gt;6,795.2 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;446.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.12 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;68.7 inches&lt;/strong&gt;. The &lt;strong&gt;15.2:1 HDD-to-CDD ratio&lt;/strong&gt; makes Springfield one of the most heating-dominant cities in the project. The Connecticut River valley funnels cold air and lake-effect moisture, producing nearly 69 inches of annual snowfall.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Springfield city, Massachusetts) report &lt;strong&gt;58,046 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.6% utility natural gas&lt;/strong&gt; (34,017 units), &lt;strong&gt;20.2% electricity&lt;/strong&gt; (11,705 units), &lt;strong&gt;13.7% fuel oil or kerosene&lt;/strong&gt; (7,952 units), and &lt;strong&gt;3.4% bottled/tank/LP gas&lt;/strong&gt; (1,958 units). The 13.7% fuel-oil share is among the highest in the project &amp;mdash; a legacy of New England&amp;rsquo;s industrial-era housing stock. Fuel-oil-to-heat-pump conversion represents a significant upgrade opportunity.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Heating Climate &amp;amp; Fuel-Oil Conversion&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Springfield&amp;rsquo;s 6,795.2 HDD profile and 68.7 inches of annual snowfall require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any fuel conversion. The 1951 median housing age means envelope upgrades are particularly critical. Outdoor condensers need elevated mounting (18&amp;ndash;24 inches above grade) and clear winter access given the heavy snow accumulation.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Massachusetts Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a statewide HVAC-specific license. Instead, local permits are required, and sheet metal and pipefitting work may require separate trade licenses. Verify a contractor&amp;rsquo;s qualifications, insurance, and local licensing before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Eversource (WMECO) Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Eversource (formerly Western Massachusetts Electric Company / WMECO) administers residential energy efficiency rebates for its Springfield service territory through Mass Save. Contact Eversource or visit Mass Save for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Springfield are set by local permitting authorities. Contact the City of Springfield for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCEF)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Westover Metropolitan Airport (KCEF) is the official NOAA reference station for the Springfield-Pioneer Valley area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Springfield records approximately &lt;strong&gt;5,681 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;747 cooling degree days&lt;/strong&gt;, an annual precipitation normal of approximately &lt;strong&gt;48 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;43.8 inches&lt;/strong&gt;. The city averages &lt;strong&gt;10.3 days per year above 90&amp;deg;F&lt;/strong&gt; and &lt;strong&gt;91.9 days below freezing&lt;/strong&gt;. The roughly &lt;strong&gt;7.6:1 HDD-to-CDD ratio&lt;/strong&gt; makes Springfield strongly heating-dominant. The Connecticut River valley funnels Atlantic moisture into snow and periodic ice events; per &lt;a href="https://www.weather.gov/box/winter" target="_blank" rel="nofollow noopener"&gt;NWS Boston/Norton winter-weather guidance&lt;/a&gt; (serving western Massachusetts), nor&amp;rsquo;easter snowstorms routinely deliver multi-day, foot-plus accumulation events. Roof collapses, prolonged power outages, and burst pipes are explicit recurring risks in the regional winter-storm guidance, all of which intersect HVAC operation: outdoor condensers need elevated mounting and cleared snow-shed paths, and any heat-pump system should be sized to maintain set-point during sustained sub-zero F design-day conditions.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:67000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Springfield city, Massachusetts) report &lt;strong&gt;58,046 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt; &amp;mdash; one of the older medians in the project, reflecting the city&amp;rsquo;s post-war industrial peak. Heating-fuel distribution: &lt;strong&gt;58.6% utility natural gas&lt;/strong&gt; (34,017 units), &lt;strong&gt;20.2% electricity&lt;/strong&gt; (11,705 units), &lt;strong&gt;13.7% fuel oil or kerosene&lt;/strong&gt; (7,952 units), and &lt;strong&gt;3.4% bottled/tank/LP gas&lt;/strong&gt; (1,958 units). Springfield&amp;rsquo;s &lt;strong&gt;13.7% fuel-oil share&lt;/strong&gt; &amp;mdash; nearly 8,000 remaining oil-heated homes &amp;mdash; is among the highest in the project and represents a major heat-pump conversion opportunity. &lt;strong&gt;Median home value is $222,700&lt;/strong&gt;; &lt;strong&gt;owner-occupancy sits at 49.5%&lt;/strong&gt;. Massachusetts&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 30.46&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the highest in the lower 48, making cold-climate heat-pump performance (COP &amp;ge; 1.75 at 5&amp;deg;F) economically essential to a successful conversion.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mass Save (Eversource WMECo) &amp;amp; HEAR Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Springfield&amp;rsquo;s electric service is provided by &lt;strong&gt;Eversource (formerly Western Massachusetts Electric Company / WMECo)&lt;/strong&gt;. Residential HVAC rebates are administered through the statewide &lt;a href="https://www.masssave.com/residential/rebates-offers-services/heating-and-cooling/heat-pumps/air-source-heat-pumps" target="_blank" rel="nofollow noopener"&gt;Mass Save program&lt;/a&gt;, the statewide ratepayer-funded efficiency program operated jointly by Eversource, National Grid, and other state utilities. Current 2026 published heat-pump rebate tiers (Springfield-eligible): &lt;strong&gt;$2,650 per ton (Whole-Home Rebate, capped at $8,500)&lt;/strong&gt; when an ENERGY STAR Cold Climate heat pump replaces oil, propane, or electric resistance as the sole heating system; &lt;strong&gt;$1,125 per ton (Partial-Home / Supplemental, capped at $8,500)&lt;/strong&gt;; and &lt;strong&gt;$250 per ton (Basic, capped at $2,500)&lt;/strong&gt; for unit additions to unconditioned space. Equipment must appear on the Mass Save Qualified Products List, use next-generation refrigerant (R-32 or R-454B), and be installed by a contractor in the &lt;strong&gt;Mass Save Heat Pump Installer Network&lt;/strong&gt;; paperwork must be filed by Feb 28, 2027 for 2026 installations. Massachusetts has fully integrated its federally funded &lt;a href="https://homes.rewiringamerica.org/federal-incentives/home-electrification-appliance-rebates" target="_blank" rel="nofollow noopener"&gt;HEAR program&lt;/a&gt; (approximately $72.8 million IRA allocation) into Mass Save&amp;rsquo;s administrative infrastructure: HEAR-eligible households earning &lt;strong&gt;&amp;le;80% AMI receive 100% of project costs covered up to $14,000&lt;/strong&gt;, and households 80&amp;ndash;150% AMI receive 50% coverage up to $7,000.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Massachusetts Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a single statewide &amp;ldquo;HVAC contractor&amp;rdquo; license; instead, three separate trade boards regulate the work depending on scope. Any work involving natural gas or propane piping, gas appliance connections, or boiler/furnace gas connections requires a license from the &lt;a href="https://www.mass.gov/orgs/board-of-state-examiners-of-plumbers-and-gas-fitters" target="_blank" rel="nofollow noopener"&gt;Massachusetts Board of State Examiners of Plumbers &amp;amp; Gas Fitters&lt;/a&gt;; the Master Gas Fitter license is required for any individual contracting directly with property owners on gas work. Sheet metal and refrigeration credentials are issued by the Division of Professional Licensure&amp;rsquo;s Board of Sheet Metal Workers. A licensed Master or Journeyman Plumber may perform gas work, but a Gas Fitter may not perform plumbing work. Mechanical building permits in Springfield are issued by the &lt;strong&gt;City of Springfield Building Department&lt;/strong&gt;; verify the current fee schedule and confirm a contractor&amp;rsquo;s specific Massachusetts trade credentials before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S112" t="n">
@@ -18655,15 +18627,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPWM)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Portland International Jetport (KPWM) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014764), Portland records an &lt;strong&gt;annual mean temperature of 47.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 38.6&amp;deg;F, approximately &lt;strong&gt;6,795.2 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;446.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.12 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;68.7 inches&lt;/strong&gt;. The 15.2:1 HDD-to-CDD ratio makes Portland one of the most heating-dominant cities in the project, with minimal cooling demand.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:60545&amp;amp;in=state:23" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Portland city, Maine) report &lt;strong&gt;32,393 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1946&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;39.4% utility natural gas&lt;/strong&gt; (12,761 units), &lt;strong&gt;32.9% fuel oil or kerosene&lt;/strong&gt; (10,666 units), &lt;strong&gt;19.3% electricity&lt;/strong&gt; (6,240 units), and &lt;strong&gt;5.3% bottled/tank/LP gas&lt;/strong&gt; (1,716 units). The &lt;strong&gt;32.9% fuel-oil share&lt;/strong&gt; is the third-highest in the project (after Bangor 51.7% and Manchester 25.9%). Over 10,000 Portland homes still heat with oil &amp;mdash; reflecting Maine&amp;rsquo;s limited natural gas pipeline infrastructure.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel-Oil Market &amp;amp; Heat Pump Conversion&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Portland&amp;rsquo;s 6,795.2 HDD and 68.7&amp;rdquo; snowfall require cold-climate-rated heat pumps. Maine&amp;rsquo;s Efficiency Maine program offers significant heat pump rebates specifically targeting fuel-oil-heated homes. Central Maine Power (CMP) is the primary electric utility; contact CMP and Efficiency Maine for current rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel Board Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine requires HVAC technicians to hold a &lt;strong&gt;Master Technician License&lt;/strong&gt; issued by the Maine Fuel Board. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPWM)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Portland International Jetport (KPWM) is the official NOAA reference station for Portland, Maine. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Portland records approximately &lt;strong&gt;7,106 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;360 cooling degree days&lt;/strong&gt; &amp;mdash; a &lt;strong&gt;19.7:1 HDD-to-CDD ratio&lt;/strong&gt; that makes Portland one of the most heating-dominant markets in the project. Annual snowfall is &lt;strong&gt;61.9 inches&lt;/strong&gt;, the city averages &lt;strong&gt;142.2 days per year below 32&amp;deg;F&lt;/strong&gt;, and only &lt;strong&gt;3.8 days above 90&amp;deg;F&lt;/strong&gt;. Coastal Maine sits directly in the Atlantic nor&amp;rsquo;easter track, and per the &lt;a href="https://www.weather.gov/safety/winter" target="_blank" rel="nofollow noopener"&gt;NWS Winter Weather Safety&lt;/a&gt; guidance, single nor&amp;rsquo;easter events routinely deliver 12+ inches of snow with sustained winds &amp;mdash; extended grid outages of multiple days are an annual planning reality. Outdoor condenser placement must allow for snow-shed clearance, elevated mounting (typically 18&amp;ndash;24 inches above grade), and ice-build-up clearance during periodic ice storms.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:60545&amp;amp;in=state:23" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Portland city, Maine) report &lt;strong&gt;32,393 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1946&lt;/strong&gt; &amp;mdash; among the oldest in the project. Heating-fuel distribution: &lt;strong&gt;39.4% utility natural gas&lt;/strong&gt; (12,761 units), &lt;strong&gt;32.9% fuel oil or kerosene&lt;/strong&gt; (10,666 units), &lt;strong&gt;19.3% electricity&lt;/strong&gt; (6,240 units), and &lt;strong&gt;5.3% bottled/tank/LP gas&lt;/strong&gt; (1,716 units). The 32.9% fuel-oil share &amp;mdash; over &lt;strong&gt;10,600 Portland homes still heating with delivered oil&lt;/strong&gt; &amp;mdash; reflects Maine&amp;rsquo;s limited natural gas pipeline infrastructure and is the leading driver of the state&amp;rsquo;s push for heat-pump adoption. The &lt;strong&gt;$452,600 median home value&lt;/strong&gt; reflects Portland&amp;rsquo;s high-value coastal housing market; &lt;strong&gt;46.7% owner-occupancy&lt;/strong&gt; reflects a meaningful renter share. Maine&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 32.17&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the highest in the lower 48, making cold-climate heat-pump efficiency (HSPF2 &amp;ge; 8.1, COP &amp;ge; 1.75 at 5&amp;deg;F) economically critical.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Efficiency Maine Trust Heat Pump Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Central Maine Power (CMP) is the primary electric utility in Portland, but residential energy-efficiency rebates are administered statewide by the &lt;a href="https://www.efficiencymaine.com/at-home/residential-heat-pump-rebates/" target="_blank" rel="nofollow noopener"&gt;Efficiency Maine Trust&lt;/a&gt;, an independent quasi-state agency. Current 2026 whole-home heat-pump rebate tiers (per qualifying ENERGY STAR Cold Climate indoor head, capped at three indoor units per household): &lt;strong&gt;$1,000 per indoor unit (Standard, no income test)&lt;/strong&gt;; &lt;strong&gt;$2,000 per indoor unit (Moderate Income, &amp;le;150% AMI)&lt;/strong&gt;; and &lt;strong&gt;$3,000 per indoor unit (Low Income, &amp;le;80% AMI)&lt;/strong&gt;. Maximum total rebate is &lt;strong&gt;$3,000 / $6,000 / $9,000&lt;/strong&gt; across the three tiers respectively. Maine&amp;rsquo;s federally funded &lt;a href="https://www.efficiencymaine.com/ira-home-energy-rebates/" target="_blank" rel="nofollow noopener"&gt;Home Electrification &amp;amp; Appliance Rebates (HEAR) program&lt;/a&gt;, allocated approximately $35.7 million in IRA formula funds, became active in September 2024 but is currently restricted to two narrow categories: new affordable multifamily housing and single-family manufactured (mobile) homes occupied by income-eligible households. Standard single-family Portland homeowners are &lt;strong&gt;not&lt;/strong&gt; currently HEAR-eligible &amp;mdash; the core rebate path is the Efficiency Maine tiers above.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Maine Fuel Board Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Maine regulates oil-burner, propane, natural-gas, and solid-fuel work through the &lt;a href="https://www.maine.gov/pfr/professionallicensing/professions/maine-fuel-board" target="_blank" rel="nofollow noopener"&gt;Maine Fuel Board&lt;/a&gt; (Office of Professional &amp;amp; Occupational Regulation). The &lt;strong&gt;Master Oil &amp;amp; Solid Fuel Technician license&lt;/strong&gt; &amp;mdash; required for any technician contracting directly with property owners on oil-fired heating systems &amp;mdash; requires &lt;strong&gt;at least 4 years of licensed experience (including at least 2 years as a licensed Journeyman)&lt;/strong&gt;, a passing exam score of 70%, and carries a &lt;strong&gt;$200 license fee&lt;/strong&gt; plus a $21 criminal background check fee. Heat-pump work that does not involve combustion fuels is regulated under a separate technician path. Mechanical/HVAC building permit fees in Portland are set by the City of Portland Permitting and Inspections Department; verify the current fee schedule directly with that office.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S149" t="n">
@@ -18791,15 +18755,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCRW)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Yeager Airport (KCRW) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013866), Charleston records an &lt;strong&gt;annual mean temperature of 56.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 66.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 45.5&amp;deg;F, approximately &lt;strong&gt;4,353.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,162.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;46.24 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;31.5 inches&lt;/strong&gt;. The roughly 3.7:1 HDD-to-CDD ratio reflects a heating-leaning dual-load climate in the Kanawha Valley.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14600&amp;amp;in=state:54" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charleston city, West Virginia) report &lt;strong&gt;21,237 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1956&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.4% utility natural gas&lt;/strong&gt; (12,392 units), &lt;strong&gt;40.0% electricity&lt;/strong&gt; (8,506 units), and 167 on bottled/tank/LP gas. Gas dominance reflects WV&amp;rsquo;s Appalachian gas production region, with meaningful electric share from historically affordable Appalachian coal-generated power.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Appalachian Climate (Zone 4A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates in the Kanawha Valley produce both heating and summer humidity loads. Appalachian Power (AEP) administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;WV Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC contractors to hold an &lt;strong&gt;HVAC Technician Certification&lt;/strong&gt; issued by the WV Contractor Licensing Board. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCRW)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Yeager Airport (KCRW) is the official NOAA reference station for Charleston, West Virginia. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013866), Charleston records an &lt;strong&gt;annual mean temperature of 56.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 66.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 45.5&amp;deg;F, approximately &lt;strong&gt;4,480 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,097 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;46.24 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;36.4 inches&lt;/strong&gt;. Charleston averages &lt;strong&gt;15.9 days per year above 90&amp;deg;F&lt;/strong&gt; and &lt;strong&gt;87.9 days below freezing&lt;/strong&gt;. The roughly 4.1:1 HDD-to-CDD ratio reflects a heating-leaning dual-load climate in the Kanawha Valley. The narrow valley topography matters operationally: cold-air drainage and inversions concentrate winter pollution and create occasional fine-particulate alert days. Per the American Lung Association &lt;a href="https://www.lung.org/research/sota" target="_blank" rel="nofollow noopener"&gt;State of the Air&lt;/a&gt; 2025 report, the Charleston-Huntington-Ashland metro ranked 82nd most polluted nationally for short-term particle pollution (driven heavily by wildfire smoke transport), while still receiving an A grade for ozone for the third consecutive year. Appalachian winter ice storms also remain a recurring grid-reliability concern.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14600&amp;amp;in=state:54" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charleston city, West Virginia) report &lt;strong&gt;21,237 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1956&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;58.4% utility natural gas&lt;/strong&gt; (12,392 units), &lt;strong&gt;40.1% electricity&lt;/strong&gt; (8,506 units), and 167 units on bottled/tank/LP gas. The &lt;strong&gt;62.8% owner-occupancy rate&lt;/strong&gt; is one of the higher figures in the project; &lt;strong&gt;median home value sits at $187,300&lt;/strong&gt;. Gas dominance reflects West Virginia&amp;rsquo;s status as the second-largest U.S. producer of marketed natural gas, with extensive Marcellus and Utica shale production keeping pipeline access strong in the Kanawha Valley. The 40.1% electric share leans on Appalachian coal-fired generation; West Virginia&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 14.41&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is below the national average. The 1956 median build year means a meaningful share of housing predates modern envelope standards, making weatherization a high-leverage upgrade before any heat-pump conversion.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Appalachian Power TakeCharge WV &amp;amp; State HEAR Program&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charleston&amp;rsquo;s electric service is provided by &lt;strong&gt;Appalachian Power (an AEP subsidiary)&lt;/strong&gt;, which administers the published &lt;a href="https://takechargewv.com/rebates" target="_blank" rel="nofollow noopener"&gt;TakeCharge WV residential rebate program&lt;/a&gt; for its West Virginia customers. Current TakeCharge WV residential rebate amounts: &lt;strong&gt;up to $500 for a qualifying heat pump&lt;/strong&gt;, &lt;strong&gt;$200 for insulation&lt;/strong&gt;, and &lt;strong&gt;$75 for a smart thermostat&lt;/strong&gt;. Applications must be submitted within 45 days of purchase. Separately, the West Virginia Office of Energy received DOE approval in January 2025 for the state&amp;rsquo;s &lt;a href="https://energywv.org/funding-opportunities/home-energy-rebate-programs/home-electrification-and-appliance-rebates/" target="_blank" rel="nofollow noopener"&gt;Home Electrification &amp;amp; Appliance Rebates (HEAR) program&lt;/a&gt;, with &lt;strong&gt;$88.2 million in IRA funding&lt;/strong&gt; covering both HEAR and HOMES. Once consumer applications open statewide, qualifying low-income households (&amp;le;80% AMI) may receive up to &lt;strong&gt;$8,000 per heat pump&lt;/strong&gt; with up to 100% project-cost coverage; moderate-income households (80&amp;ndash;150% AMI) receive partial coverage. TakeCharge WV rebates can stack with HEAR for eligible Appalachian Power customers.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;West Virginia Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;West Virginia requires HVAC technicians to hold an &lt;a href="https://labor.wv.gov/licensing/hvac-technician-certification" target="_blank" rel="nofollow noopener"&gt;HVAC Technician Certification&lt;/a&gt; issued by the WV Division of Labor; effective January 1, 2016, no person may perform heating, ventilating, or cooling system work in West Virginia without this certification. The technician credential requires &lt;strong&gt;at least 2,000 hours of HVAC work, training, and experience&lt;/strong&gt; plus a passing exam (administered by ProV beginning September 1, 2024). Any HVAC project on a residence totaling &lt;strong&gt;$5,000 or more&lt;/strong&gt; in materials and labor (or $25,000 or more on a commercial project) additionally requires the firm to hold a &lt;a href="https://wvcontractors.com/contractor-licensing/" target="_blank" rel="nofollow noopener"&gt;WV Contractor License&lt;/a&gt; with a classification covering HVAC work, with a licensed Technician serving as the qualifier. Verify a Charleston contractor&amp;rsquo;s current credentials on the WV Division of Labor public license lookup before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S150" t="n">
@@ -18927,15 +18883,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCHS)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charleston International Airport (KCHS) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013880), Charleston records an &lt;strong&gt;annual mean temperature of 66.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 76.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 56.4&amp;deg;F, approximately &lt;strong&gt;1,844.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,434.5 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;52.51 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.3 inches&lt;/strong&gt;. The 1.3:1 CDD-to-HDD ratio makes Charleston SC a cooling-dominant market, with 52 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:13330&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charleston city, South Carolina) report &lt;strong&gt;66,408 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1994&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;74.2% electricity&lt;/strong&gt; (49,266 units), &lt;strong&gt;23.8% utility natural gas&lt;/strong&gt; (15,793 units), and 442 on bottled/tank/LP gas. The strong electric majority reflects the Lowcountry&amp;rsquo;s warm climate where heat-pump primary heat handles the modest winter load efficiently.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lowcountry Warm-Humid Climate &amp;amp; Hurricane Exposure (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent loads. Charleston&amp;rsquo;s coastal Lowcountry position adds hurricane exposure and salt-air corrosion considerations for outdoor equipment. Dominion Energy South Carolina administers residential rebate programs; contact them for current amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC LLR. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCHS)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charleston International Airport (KCHS) is the official NOAA reference station for Charleston, South Carolina. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013880), Charleston records an &lt;strong&gt;annual mean temperature of 66.5&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 76.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 56.4&amp;deg;F, approximately &lt;strong&gt;1,977 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,304 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;52.51 inches&lt;/strong&gt;, and an annual snowfall normal of just &lt;strong&gt;0.5 inches&lt;/strong&gt;. Charleston averages &lt;strong&gt;55.2 days per year above 90&amp;deg;F&lt;/strong&gt; and only &lt;strong&gt;24.4 days below freezing&lt;/strong&gt;. The 1.2:1 CDD-to-HDD ratio places Charleston among the most cooling-dominant markets in the project, with summer latent (humidity) loads the dominant design driver. Charleston also faces meaningful Atlantic hurricane exposure: per the &lt;a href="https://www.weather.gov/chs/TChistory" target="_blank" rel="nofollow noopener"&gt;NWS Charleston Tropical Cyclone History&lt;/a&gt;, &lt;strong&gt;41 tropical cyclones made landfall in the NWS Charleston area between 1851 and 2018&lt;/strong&gt;, including four major (Category 3+) storms &amp;mdash; the 1893 Great Charleston Hurricane, Hazel (1954), Gracie (1959), and Hugo (1989). Coastal salt-air corrosion shortens the service life of outdoor condenser coils relative to inland markets.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:13330&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Charleston city, South Carolina) report &lt;strong&gt;66,408 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1994&lt;/strong&gt; &amp;mdash; one of the newer median ages among Southeast cities, reflecting decades of Lowcountry growth. Heating-fuel distribution: &lt;strong&gt;74.2% electricity&lt;/strong&gt; (49,266 units), &lt;strong&gt;23.8% utility natural gas&lt;/strong&gt; (15,793 units), and 442 units on bottled/tank/LP gas. The &lt;strong&gt;55.6% owner-occupancy rate&lt;/strong&gt; and &lt;strong&gt;median home value of $469,100&lt;/strong&gt; reflect Charleston&amp;rsquo;s high-value coastal housing market. The strong electric majority reflects the modest winter heating load in Zone 3A &amp;mdash; heat-pump primary heat handles the 1,977 HDD requirement efficiently without auxiliary fuel. South Carolina&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 16.15&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is moderate by national standards.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dominion Energy South Carolina Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Charleston&amp;rsquo;s electric service is provided by &lt;a href="https://www.dominionenergy.com/south-carolina/save-energy/heating-and-cooling-rebates" target="_blank" rel="nofollow noopener"&gt;Dominion Energy South Carolina&lt;/a&gt;, which administers a published residential HVAC rebate program for eligible customers. Current published amounts: &lt;strong&gt;$400&amp;ndash;$500&lt;/strong&gt; toward the purchase and installation of an ENERGY STAR&amp;reg; central air conditioner or heat pump (replacement of existing equipment); &lt;strong&gt;$650&lt;/strong&gt; when an electric furnace is replaced with an ENERGY STAR&amp;reg; heat pump; and &lt;strong&gt;$750&lt;/strong&gt; for an ENERGY STAR&amp;reg; certified heat pump water heater. South Carolina&amp;rsquo;s state-administered &lt;a href="https://energy.sc.gov/programs/funding/rebates" target="_blank" rel="nofollow noopener"&gt;Home Electrification &amp;amp; Appliance Rebates (HEAR) program&lt;/a&gt;, funded under the Inflation Reduction Act and administered by the South Carolina Energy Office, was not yet open for consumer applications as of early 2026 &amp;mdash; the SCEO is finalizing software and contractor enrollment, with statewide launch anticipated later in 2026. Once open, HEAR will provide up to &lt;strong&gt;$14,000 per household&lt;/strong&gt; for electrification upgrades for households at or below 150% of county AMI (&lt;a href="https://homes.rewiringamerica.org/federal-incentives/home-electrification-appliance-rebates" target="_blank" rel="nofollow noopener"&gt;program rules&lt;/a&gt;).&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina regulates HVAC work through two paths. &lt;strong&gt;Residential&lt;/strong&gt; HVAC work is licensed by the South Carolina &lt;a href="https://llr.sc.gov/res/" target="_blank" rel="nofollow noopener"&gt;Residential Builders Commission&lt;/a&gt; (Department of Labor, Licensing &amp;amp; Regulation). The Residential HVAC contractor license fee is &lt;strong&gt;$220&lt;/strong&gt;, requires the qualifying party to pass the PSI trade exam plus the SC business and law exam, and requires a &lt;strong&gt;$10,000 surety bond&lt;/strong&gt; if the total cost of any project exceeds $5,000. Licenses renew every two years. &lt;strong&gt;Commercial&lt;/strong&gt; mechanical work is regulated by the &lt;a href="https://www.llr.sc.gov/clb/" target="_blank" rel="nofollow noopener"&gt;South Carolina Contractor&amp;rsquo;s Licensing Board&lt;/a&gt;; the commercial Mechanical Contractor (subclassification HT, AC, etc.) license carries a $350 initial fee, requires two years of work experience, and uses a financial-statement-based group classification rather than a fixed bond amount. Verify a specific Charleston contractor&amp;rsquo;s current license status on the LLR public lookup before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S151" t="n">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -5285,21 +5285,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFAY)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fayetteville Regional Airport (KFAY) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013722), Fayetteville records an &lt;strong&gt;annual mean temperature of 61.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.0&amp;deg;F&lt;/strong&gt; against an annual minimum of 50.5&amp;deg;F, approximately &lt;strong&gt;3,153.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,804.5 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;46.07 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;5.2 inches&lt;/strong&gt;. The roughly 1.7:1 HDD-to-CDD ratio reflects a dual-load climate in the North Carolina Sandhills &amp;mdash; significant heating and significant cooling demand, with 46 inches of precipitation driving meaningful summer humidity loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:22920&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Fayetteville city, North Carolina) report &lt;strong&gt;81,499 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1983&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.8% electricity&lt;/strong&gt; (59,334 units), &lt;strong&gt;22.9% utility natural gas&lt;/strong&gt; (18,652 units), and &lt;strong&gt;2.5% bottled/tank/LP gas&lt;/strong&gt; (2,050 units). The strong electric-heating majority reflects Zone 3A&amp;rsquo;s mild winters that favor heat-pump primary heat. The 1983 median housing age and significant military-affiliated housing stock (proximity to Fort Liberty, formerly Fort Bragg) shape local demand patterns.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate &amp;amp; Dehumidification (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Fayetteville&amp;rsquo;s combination of 1,804.5 CDD and 46.07 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential &amp;mdash; oversizing AC capacity worsens humidity control by short-cycling. Variable-speed compressor systems are particularly valuable in the Sandhills&amp;rsquo; humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Carolina requires HVAC contractors to hold a &lt;strong&gt;Heating Contractor License&lt;/strong&gt; (H-1, H-2, or H-3 classification depending on scope) issued by the North Carolina Board of Examiners of Plumbing, Heating and Fire Sprinkler Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Progress Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Progress administers the Smart $aver residential rebate program for its Fayetteville service territory. Contact Duke Energy Progress directly or visit the Duke Energy Smart $aver page for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fayetteville are set by the City of Fayetteville Permitting &amp;amp; Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFAY)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fayetteville Regional Airport / Grannis Field (KFAY, &lt;a href="https://www.ncdc.noaa.gov/cdo-web/datasets/GHCND/stations/GHCND:USW00093740/detail" target="_blank" rel="nofollow noopener"&gt;GHCND:USW00093740&lt;/a&gt;) is the official NOAA reference station for Fayetteville, North Carolina. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Fayetteville records approximately &lt;strong&gt;2,906 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,010 annual cooling degree days&lt;/strong&gt;, an average of &lt;strong&gt;52.6 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;49.1 days below freezing&lt;/strong&gt;, and roughly &lt;strong&gt;3 inches&lt;/strong&gt; of annual snowfall. The Sandhills location south of Raleigh delivers a near-balanced 1.4:1 HDD:CDD ratio &amp;mdash; both heating and cooling loads are material, and replacement equipment must be sized for both seasons. Hot, humid July&amp;ndash;August conditions drive cooling latent load; occasional 0&amp;deg;F-class cold snaps from polar-vortex incursions make properly sized auxiliary heat (electric strip or gas backup) important for air-source heat pumps. Tropical-storm remnants (Florence 2018, Matthew 2016) also occasionally produce multi-day grid outages, making whole-house generator compatibility a worthwhile consideration during equipment replacement.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:22920&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fayetteville city, North Carolina) report a &lt;strong&gt;median year built of 1983&lt;/strong&gt;, with a heating-fuel distribution of &lt;strong&gt;72.8% electricity&lt;/strong&gt; and &lt;strong&gt;22.9% utility natural gas&lt;/strong&gt;. The strong electric majority reflects decades of heat-pump-friendly building stock across Cumberland County and the Fort Liberty (formerly Fort Bragg) housing footprint. The &lt;strong&gt;46.5% owner-occupancy rate&lt;/strong&gt; is depressed by the large transient military-family rental population. The &lt;strong&gt;median home value of $171,900&lt;/strong&gt; is among the most affordable in the project, reflecting the city&amp;rsquo;s working-class housing market. North Carolina&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 14.64&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is below the U.S. national average.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Progress Smart $aver &amp;amp; Energy Saver NC&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fayetteville&amp;rsquo;s electric service is provided by &lt;a href="https://www.duke-energy.com/home/products/smart-saver" target="_blank" rel="nofollow noopener"&gt;Duke Energy Progress&lt;/a&gt;, whose Smart $aver residential rebate program offers &lt;strong&gt;$500&amp;ndash;$1,000&lt;/strong&gt; for qualifying central heat-pump and AC installations, with higher tiers for variable-speed and geothermal systems meeting specified SEER2 / HSPF2 thresholds. The North Carolina Utilities Commission approved an increase in Smart $aver HVAC, insulation, and water-heater incentives effective January 1, 2025. Duke also runs a separate Smart $aver heat-pump-water-heater rebate (currently $500&amp;ndash;$800 depending on efficiency tier). North Carolina is one of the few states to have &lt;a href="https://www.deq.nc.gov/energy-climate/state-energy-office/energy-saver-north-carolina" target="_blank" rel="nofollow noopener"&gt;fully launched its Energy Saver NC home-energy rebate program&lt;/a&gt; &amp;mdash; as of February 2026, both the HOMES and HEAR pathways are open in all 100 counties through the NC Department of Environmental Quality, with over $208 million in federal Inflation Reduction Act funding allocated. Eligible Fayetteville households (under 150% AMI) can receive up to &lt;strong&gt;$8,000&lt;/strong&gt; for an ENERGY STAR-certified electric heat pump under HEAR. Stacking Smart $aver + Energy Saver NC is permitted.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC work in Fayetteville is licensed by the &lt;a href="https://nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating, and Fire Sprinkler Contractors&lt;/a&gt;, which issues three heating classifications: &lt;strong&gt;H-1&lt;/strong&gt; (water-based heating in any building), &lt;strong&gt;H-2&lt;/strong&gt; (forced-air heating &amp;amp; cooling units over 15 tons), and &lt;strong&gt;H-3&lt;/strong&gt; (forced-air heating &amp;amp; cooling units 15 tons or under). Most residential Fayetteville installs are H-3-class work. The Heating Group examination is administered by PSI Testing Services, costs &lt;strong&gt;$100 per exam&lt;/strong&gt;, and requires &lt;strong&gt;2 years (4,000 hours)&lt;/strong&gt; of supervised on-site experience &amp;mdash; up to half of which can be substituted with documented academic or technical training. Contractor applicants also sit a 90-minute Business and Law exam. The Board&amp;rsquo;s public lookup at nclicensing.org lets a Fayetteville homeowner verify the contractor&amp;rsquo;s active classification and disciplinary history before signing. Anyone handling refrigerant in the course of HVAC service must also hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law (CFR Title 40 Part 82).&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -9849,21 +9835,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMOB)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mobile Regional Airport (KMOB) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013894), Mobile records an &lt;strong&gt;annual mean temperature of 67.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 77.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 57.4&amp;deg;F, approximately &lt;strong&gt;1,616.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,598.7 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;67.08 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.2 inches&lt;/strong&gt;. The &lt;strong&gt;67.08-inch annual precipitation is the highest of any project city&lt;/strong&gt; &amp;mdash; Mobile&amp;rsquo;s Gulf Coast position makes it one of the wettest major cities in the United States. The 1.6:1 CDD-to-HDD ratio makes it a cooling-dominant market where dehumidification is a primary HVAC design concern.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:50000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Mobile city, Alabama) report &lt;strong&gt;77,587 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1974&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;55.9% electricity&lt;/strong&gt; (43,387 units), &lt;strong&gt;42.1% utility natural gas&lt;/strong&gt; (32,627 units), and 1,093 on bottled/tank/LP gas (1.4%). The electric-majority profile is consistent with the Gulf Coast&amp;rsquo;s cooling-dominant climate where heat-pump primary heat is the practical standard.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Precipitation &amp;amp; Hurricane Exposure (Zone 2A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates produce extreme latent (moisture) cooling loads. Mobile&amp;rsquo;s combination of 2,598.7 CDD and 67.08 inches of annual precipitation &amp;mdash; the wettest in the project &amp;mdash; means dehumidification is the dominant HVAC comfort variable. Variable-speed compressor systems with enhanced dehumidification modes are essential. Hurricane exposure along the Gulf Coast means outdoor condenser placement, elevated pad mounts, and tie-down anchoring are practical considerations.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HVAC Contractor Licensing (HACR Board)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama requires HVAC contractors to hold a license issued by the &lt;strong&gt;Alabama Board of Heating, Air Conditioning, and Refrigeration Contractors (Board of HACR Contractors)&lt;/strong&gt;. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama Power Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama Power administers residential rebate programs for its Mobile service territory. Contact Alabama Power directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Mobile are set by local permitting authorities. Contact the City of Mobile for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMOB)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mobile Regional Airport (KMOB) is the official NOAA reference station for Mobile, Alabama. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Mobile records approximately &lt;strong&gt;1,694 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,516 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;65.1 days per year above 90&amp;deg;F&lt;/strong&gt;, only &lt;strong&gt;20.1 days below freezing&lt;/strong&gt;, and an essentially negligible &lt;strong&gt;0.2 inches&lt;/strong&gt; of annual snowfall. The 1.5:1 CDD-to-HDD ratio firmly places Mobile in the cooling-dominant Hot-Humid (IECC Zone 2A) classification, where equipment sizing should be driven by summer latent (humidity) load, not sensible heat alone. Mobile also faces the Gulf Coast&amp;rsquo;s tropical-cyclone exposure &amp;mdash; coastal salt-air corrosion shortens outdoor condenser-coil service life relative to inland markets, and storm-grade tie-down anchoring of condensers is standard practice on the Bay. Mobile is also one of the wettest cities in the U.S. by annual rainfall (~66 inches per the same NCEI normals), which drives meaningful attention to condensate-drain sizing and to outdoor-pad elevation against hurricane storm surge.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:50000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Mobile city, Alabama) report a &lt;strong&gt;median year built of 1974&lt;/strong&gt;, with a heating-fuel distribution of &lt;strong&gt;55.9% electricity&lt;/strong&gt; and &lt;strong&gt;42.1% utility natural gas&lt;/strong&gt;. The roughly even electric / gas split is characteristic of older Gulf Coast cities where pipeline gas service preceded widespread heat-pump adoption. The &lt;strong&gt;51.4% owner-occupancy rate&lt;/strong&gt; is below the AL state average. The &lt;strong&gt;median home value of $170,300&lt;/strong&gt; is among the most affordable in the project. Alabama&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 16.18&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is moderately above the U.S. average, which improves the payback math for high-SEER2 replacement equipment.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama Power Rebates &amp;mdash; HEAR Status&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mobile&amp;rsquo;s electric service is provided by &lt;a href="https://www.alabamapower.com/residential/save-money-and-energy/rebates-and-incentives.html" target="_blank" rel="nofollow noopener"&gt;Alabama Power&lt;/a&gt;, which administers a published residential HVAC rebate program. Current published amounts: a &lt;strong&gt;$1,000 rebate&lt;/strong&gt; for qualifying high-efficiency heat pumps (eligibility tied to a minimum SEER2 / HSPF2 efficiency rating), and a &lt;strong&gt;$1,000 gas-to-electric conversion bonus&lt;/strong&gt; when an existing gas furnace is replaced with an electric heat pump. Smart-thermostat incentives offer up to &lt;strong&gt;$200&lt;/strong&gt;. Applications must be submitted within 90 days of equipment purchase, and Alabama Power reserves the right to perform an on-site inspection before paying the rebate. If the application data is found to be inaccurate post-payment, the customer is contractually obligated to repay the rebate. Alabama&amp;rsquo;s state-administered &lt;a href="https://adeca.alabama.gov/ira-rebates/" target="_blank" rel="nofollow noopener"&gt;HEAR &amp;amp; HOMES programs&lt;/a&gt; through the Alabama Department of Economic and Community Affairs (ADECA) are &lt;strong&gt;not yet open&lt;/strong&gt; as of early 2026 &amp;mdash; ADECA issued an implementation-consultant RFP in late 2024 but no consumer launch date has been announced. Sign up at rebates@adeca.alabama.gov for launch notifications.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HVAC Contractor Licensing (HACR Board)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC work in Mobile is licensed by the &lt;a href="https://hacr.alabama.gov/" target="_blank" rel="nofollow noopener"&gt;Alabama Board of Heating, Air Conditioning &amp;amp; Refrigeration Contractors (HACR)&lt;/a&gt;. The HVAC contractor examination fee is &lt;strong&gt;$175 per exam&lt;/strong&gt; (or $350 for both HVAC and Refrigeration), and the licence fee is &lt;strong&gt;$220&lt;/strong&gt;; active contractor renewals run &lt;strong&gt;$190 annually&lt;/strong&gt;. Active HVAC contractors are required to post a &lt;strong&gt;$20,000 performance (surety) bond&lt;/strong&gt; with the Board. Experience pathways: a registered two-year apprenticeship under a licensed contractor, graduation from an approved Alabama community-college HVAC program, or &lt;strong&gt;3,000 hours&lt;/strong&gt; (approximately 18 months) of supervised work experience within the past five years. Renewal requires &lt;strong&gt;4 hours of continuing education annually&lt;/strong&gt;. Anyone handling refrigerant in the course of HVAC service must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law. Verify a Mobile-area contractor&amp;rsquo;s status on the HACR public lookup at hacr.alabama.gov, and confirm local permit status with the &lt;a href="https://www.cityofmobile.org/government/urban-development/inspections/" target="_blank" rel="nofollow noopener"&gt;City of Mobile Urban Development Department&amp;rsquo;s Building Inspections office&lt;/a&gt; before signing.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -11063,21 +11035,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPIA)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;General Wayne A. Downing Peoria International Airport (KPIA) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014842), Peoria records an &lt;strong&gt;annual mean temperature of 52.7&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 62.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 43.0&amp;deg;F, approximately &lt;strong&gt;5,613.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,157.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;37.55 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;26.2 inches&lt;/strong&gt;. The roughly 4.9:1 HDD-to-CDD ratio makes Peoria a heating-dominant market with meaningful summer cooling demand. The 26-inch snowfall drives outdoor equipment clearance and defrost-cycle planning.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:59000&amp;amp;in=state:17" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Peoria city, Illinois) report &lt;strong&gt;48,950 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1966&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;68.7% utility natural gas&lt;/strong&gt; (33,619 units), &lt;strong&gt;29.6% electricity&lt;/strong&gt; (14,471 units), and 335 on bottled/tank/LP gas. The gas-dominant mix and mid-1960s housing stock mean furnace AFUE upgrades and envelope improvements are high-impact investments.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations (Zone 5A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Peoria&amp;rsquo;s 5,613.8 HDD profile and documented sub-zero central Illinois winter extremes require cold-climate-rated heat pumps for any gas-to-electric conversion. Outdoor condensers benefit from elevated mounting and clear winter access.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Illinois Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Illinois does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Peoria must obtain permits through local authorities. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ameren Illinois Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ameren Illinois administers residential energy efficiency rebates for its Peoria service territory. Contact Ameren Illinois directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Peoria are set by local permitting authorities. Contact the City of Peoria for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KPIA)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;General Wayne A. Downing Peoria International Airport (KPIA) is the official NOAA reference station for Peoria, Illinois. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Peoria records approximately &lt;strong&gt;5,831 annual heating degree days&lt;/strong&gt; against just &lt;strong&gt;1,040 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;18.7 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;115.9 days below freezing&lt;/strong&gt;, and roughly &lt;strong&gt;24.6 inches&lt;/strong&gt; of annual snowfall. The 5.6:1 HDD:CDD ratio places Peoria firmly in the heating-dominant Cool-Humid (IECC Zone 5A) band &amp;mdash; winter loads are about five times summer loads, and equipment selection should prioritize cold-climate heat-pump performance (HSPF2 &amp;ge; 8.1) or, more commonly in central Illinois, high-AFUE gas furnaces with central AC for the modest summer cooling season. Polar-vortex winter design temperatures occasionally drop below -10&amp;deg;F, making auxiliary backup heat capacity a non-optional design consideration. Peoria&amp;rsquo;s central-Illinois prairie location also exposes equipment to severe-thunderstorm (and occasional tornado) wind events &amp;mdash; condenser tie-downs and surge-protection devices are worthwhile add-ons during equipment replacement in this market.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:59000&amp;amp;in=state:17" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Peoria city, Illinois) report a &lt;strong&gt;median year built of 1966&lt;/strong&gt;, with a heating-fuel distribution heavily skewed gas: &lt;strong&gt;68.7% utility natural gas&lt;/strong&gt; and &lt;strong&gt;29.6% electricity&lt;/strong&gt;. The strong gas dominance is characteristic of central Midwest cities &amp;mdash; pipeline infrastructure is well-developed and gas remains cost-competitive against electricity for the long heating season. The &lt;strong&gt;58.2% owner-occupancy rate&lt;/strong&gt; is near the IL state average. The &lt;strong&gt;median home value of $149,500&lt;/strong&gt; is among the most affordable in the project. Illinois&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 17.83&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is well above the U.S. average, which improves the payback math for high-efficiency replacement equipment.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ameren Illinois Energy Efficiency Program&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Peoria&amp;rsquo;s electric and natural-gas service is provided by &lt;a href="https://amerenillinoissavings.com/" target="_blank" rel="nofollow noopener"&gt;Ameren Illinois&lt;/a&gt;, whose Energy Efficiency Program offers published residential HVAC rebates. Current published amounts (2026): &lt;strong&gt;$900&lt;/strong&gt; for a qualifying ducted (central) heat pump and &lt;strong&gt;$630&lt;/strong&gt; for a qualifying ductless mini-split heat pump, plus &lt;strong&gt;$800&lt;/strong&gt; (online rebate or instant in-store coupon at Lowe&amp;rsquo;s and Home Depot) for an ENERGY STAR&amp;reg; heat-pump water heater. Ameren&amp;rsquo;s Marketplace also offers smaller rebates on smart thermostats, smart-home equipment, and air-sealing measures. The full rebate schedule is updated each program cycle and published on the Ameren Illinois Savings portal. Illinois&amp;rsquo;s state-administered &lt;a href="https://epa.illinois.gov/topics/energy/energy-rebates.html" target="_blank" rel="nofollow noopener"&gt;HEAR &amp;amp; HOMES rebate programs&lt;/a&gt; through the Illinois EPA Office of Energy are &lt;strong&gt;not yet operational&lt;/strong&gt; as of early 2026 &amp;mdash; the Illinois EPA HEAR application has not yet been processed by USDOE for administration or distribution. When live, Illinois plans to allocate 100% of HEAR funds to households below 80% of Area Median Income.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Illinois HVAC Licensing &amp;mdash; Local Jurisdiction&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Illinois does &lt;strong&gt;not issue a statewide HVAC contractor or technician license&lt;/strong&gt; &amp;mdash; the &lt;a href="https://idfpr.illinois.gov/" target="_blank" rel="nofollow noopener"&gt;Illinois Department of Financial and Professional Regulation (IDFPR)&lt;/a&gt; licenses plumbers and roofers at the state level only, and the Illinois Department of Public Health regulates plumbing through a separate program. HVAC licensing is delegated to local municipal jurisdictions, where requirements vary by city and county. The &lt;a href="https://www.peoriagov.org/214/Permits-Inspections" target="_blank" rel="nofollow noopener"&gt;City of Peoria Development Services Department&lt;/a&gt; issues the local mechanical permit and may require a contractor registration; bond amounts where required typically range from $5,000 to $10,000. Because Illinois lacks a statewide trade exam, due diligence on a Peoria-area contractor relies on three signals: (1) the city contractor-registration record, (2) proof of general-liability and workers&amp;rsquo;-compensation insurance, and (3) current &lt;strong&gt;EPA Section 608 refrigerant certification&lt;/strong&gt;, which is required under federal law (CFR Title 40 Part 82) of anyone handling refrigerant. Verify all three before signing.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -13643,21 +13601,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSHV)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Shreveport Regional Airport (KSHV) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013957), Shreveport records an &lt;strong&gt;annual mean temperature of 66.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 77.5&amp;deg;F&lt;/strong&gt; against an annual minimum of 55.6&amp;deg;F, approximately &lt;strong&gt;2,067.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,676.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;51.43 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;0.9 inches&lt;/strong&gt;. The 1.3:1 CDD-to-HDD ratio makes Shreveport a cooling-dominant market, and the 51-inch precipitation total drives significant summer latent (humidity) loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:70000&amp;amp;in=state:22" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Shreveport city, Louisiana) report &lt;strong&gt;75,353 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1973&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;54.4% electricity&lt;/strong&gt; (40,962 units), &lt;strong&gt;43.7% utility natural gas&lt;/strong&gt; (32,917 units), and 624 on bottled/tank/LP gas. The near-even electric/gas split reflects the transitional climate where both heat pumps and gas furnaces are competitive primary heating systems.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate &amp;amp; Dehumidification (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Shreveport&amp;rsquo;s combination of 2,676.2 CDD and 51.43 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in northwest Louisiana&amp;rsquo;s humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana HVAC Contractor Licensing (LSLBC)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Louisiana requires HVAC contractors to hold a &lt;strong&gt;Mechanical Work Contractor License&lt;/strong&gt; issued by the Louisiana State Licensing Board for Contractors (LSLBC). Verify a specific contractor&amp;rsquo;s current LSLBC license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SWEPCO Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Southwestern Electric Power Company (SWEPCO), an AEP company, is the primary electric utility for the Shreveport area. Contact SWEPCO directly for the current residential HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Shreveport are set by local permitting authorities. Contact the City of Shreveport for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KSHV)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Shreveport Regional Airport (KSHV) is the official NOAA reference station for Shreveport, Louisiana. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Shreveport records approximately &lt;strong&gt;2,225 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,481 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;87.7 days per year above 90&amp;deg;F&lt;/strong&gt; (among the highest in the project sample), &lt;strong&gt;31.8 days below freezing&lt;/strong&gt;, and only &lt;strong&gt;1 inch&lt;/strong&gt; of annual snowfall. The 1.1:1 CDD-to-HDD ratio just barely tilts cooling-dominant on paper, but the &lt;strong&gt;87+ days above 90&amp;deg;F&lt;/strong&gt; is what actually drives equipment sizing in the Ark-La-Tex &amp;mdash; long, brutal late-summer afternoons impose severe sustained sensible and latent loads. IECC Zone 3A (Warm-Humid) selection rules apply: properly sized heat pumps with backup electric resistance handle the modest winter heating load economically. Shreveport also occasionally sees damaging severe-thunderstorm and ice-storm events &amp;mdash; the February 2021 Texas-Louisiana cold snap drove sub-10&amp;deg;F readings across the region and exposed undersized auxiliary heat in many heat-pump installs, an instructive case for current replacement-equipment specification.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:70000&amp;amp;in=state:22" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Shreveport city, Louisiana) report a &lt;strong&gt;median year built of 1973&lt;/strong&gt;, with a heating-fuel distribution of &lt;strong&gt;54.4% electricity&lt;/strong&gt; and &lt;strong&gt;43.7% utility natural gas&lt;/strong&gt;. The roughly even electric / gas split reflects the city&amp;rsquo;s mid-century housing stock and the historic dominance of pipeline gas in the Haynesville-shale region. The &lt;strong&gt;53.8% owner-occupancy rate&lt;/strong&gt; is near the LA state average. The &lt;strong&gt;median home value of $178,100&lt;/strong&gt; reflects an affordable Ark-La-Tex housing market. Louisiana&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 12.87&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the lowest in the U.S., which keeps central-AC operating costs manageable despite the long cooling season.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;SWEPCO Louisiana HVAC Incentive Program&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Shreveport&amp;rsquo;s electric service is provided by &lt;a href="https://www.swepco.com/savings/home/money/incentives/hvac" target="_blank" rel="nofollow noopener"&gt;Southwestern Electric Power Company (SWEPCO)&lt;/a&gt;, a subsidiary of American Electric Power. SWEPCO administers the &lt;a href="https://www.swepcosolutions.com/programs/residential-programs/louisiana-hvac-incentive-program/" target="_blank" rel="nofollow noopener"&gt;Louisiana HVAC Incentive Program&lt;/a&gt;, which offers up to &lt;strong&gt;$3,500&lt;/strong&gt; for a qualifying high-efficiency replacement heat-pump installation through a SWEPCO-approved contractor &amp;mdash; the incentive is included in the contractor&amp;rsquo;s quote rather than submitted as a post-install rebate, simplifying paperwork for the homeowner. SWEPCO also runs a separate heat-pump-water-heater rebate program for Louisiana and Texas customers governed by the rules and guidelines published on the utility&amp;rsquo;s savings portal. Louisiana&amp;rsquo;s state-administered &lt;a href="https://denr.louisiana.gov/page/home-energy-rebates-programs" target="_blank" rel="nofollow noopener"&gt;HEAR &amp;amp; HOMES program&lt;/a&gt;, jointly administered by the Louisiana Department of Energy and Natural Resources Office of Energy and the Office of Community Development Disaster Recovery Unit, has been awarded over $200 million in Inflation Reduction Act funding for single-family and multi-family upgrades but is &lt;strong&gt;not yet open to consumer applications&lt;/strong&gt; as of early 2026.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Louisiana Mechanical Contractor Licensing (LSLBC)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC work in Shreveport is licensed by the &lt;a href="https://lslbc.gov/" target="_blank" rel="nofollow noopener"&gt;Louisiana State Licensing Board for Contractors (LSLBC)&lt;/a&gt; under the Mechanical Work Contractor classification, which covers HVAC, refrigeration, gas piping, and process piping. A commercial mechanical license is required for any project exceeding &lt;strong&gt;$10,000&lt;/strong&gt; (labor plus materials). Application fees: &lt;strong&gt;$100&lt;/strong&gt; for one classification, &lt;strong&gt;$195&lt;/strong&gt; for two. Applicants must pass two PSI exams &amp;mdash; a 100-question closed-book Trade Exam (&lt;strong&gt;$120&lt;/strong&gt;) and a 80-question open-book Business and Law Exam (&lt;strong&gt;$120&lt;/strong&gt;, 70% passing). A &lt;strong&gt;$5,000 surety bond&lt;/strong&gt; may be required, and contractors must carry minimum &lt;strong&gt;$100,000 general-liability insurance&lt;/strong&gt;. Out-of-state contractors pay a &lt;strong&gt;$400&lt;/strong&gt; additional fee. Anyone handling refrigerant in the course of HVAC service must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law. Verify a Caddo Parish contractor on the LSLBC public lookup before signing, and confirm the local mechanical permit pull through the City of Shreveport Permits &amp;amp; Inspections Division.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S110" t="n">
@@ -14829,21 +14773,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTOL)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Express Airport (KTOL) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014848), Toledo records an &lt;strong&gt;annual mean temperature of 49.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 58.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 39.9&amp;deg;F, approximately &lt;strong&gt;6,399.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;722.1 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.23 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;64.5 inches&lt;/strong&gt;. The roughly 8.9:1 HDD-to-CDD ratio makes Toledo one of the most heating-dominant cities in the project. The 64.5-inch snowfall &amp;mdash; driven by Lake Erie lake-effect weather &amp;mdash; creates demanding outdoor-equipment conditions.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:77000&amp;amp;in=state:39" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Toledo city, Ohio) report &lt;strong&gt;118,508 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1955&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.9% utility natural gas&lt;/strong&gt; (87,569 units), &lt;strong&gt;23.6% electricity&lt;/strong&gt; (27,987 units), and 1,680 on bottled/tank/LP gas. The strong gas dominance combined with mid-1950s housing stock means furnace AFUE upgrades, ductwork remediation, and air-sealing work are particularly impactful.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lake Erie Lake-Effect Snow &amp;amp; HVAC Equipment&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Toledo&amp;rsquo;s 6,399.8 HDD profile and 64.5 inches of Lake Erie lake-effect snowfall require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any gas-to-electric conversion. Outdoor condensers need elevated mounting (18&amp;ndash;24 inches above grade), clear defrost drainage, and reliable winter service access.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio HVAC Contractor Licensing (OCILB)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Ohio requires HVAC contractors to hold an &lt;strong&gt;HVAC Contractor License&lt;/strong&gt; issued by the Ohio Construction Industry Licensing Board (OCILB). Verify a specific contractor&amp;rsquo;s current OCILB license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Toledo Edison / FirstEnergy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Edison, a FirstEnergy company, is the primary electric utility for the Toledo area. Contact Toledo Edison or FirstEnergy directly for the current residential HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Toledo are set by local permitting authorities. Contact the City of Toledo for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTOL)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo Express Airport (KTOL) is the official NOAA reference station for Toledo, Ohio. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Toledo records approximately &lt;strong&gt;6,145 annual heating degree days&lt;/strong&gt; against just &lt;strong&gt;793 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;14.3 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;121.9 days below freezing&lt;/strong&gt;, and roughly &lt;strong&gt;37.6 inches&lt;/strong&gt; of annual snowfall. The 7.7:1 HDD:CDD ratio is one of the most heating-dominant in the project &amp;mdash; Toledo is squarely in IECC Zone 5A (Cool-Humid), and equipment selection should weight winter capacity heavily. Cold-climate heat pumps (HSPF2 &amp;ge; 8.1) or dual-fuel configurations with a gas-furnace backup below the balance point are the right answer for most replacement installs in the Glass City. Lake Erie&amp;rsquo;s lake-effect snow and frequent gray winter days also depress winter solar gains, making envelope-tightness measures (air sealing, attic insulation upgrades) high-leverage complements to any HVAC replacement.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:77000&amp;amp;in=state:39" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Toledo city, Ohio) report a &lt;strong&gt;median year built of 1955&lt;/strong&gt; &amp;mdash; one of the oldest in the project, reflecting the city&amp;rsquo;s mid-century industrial-era housing stock. Heating-fuel distribution: &lt;strong&gt;73.9% utility natural gas&lt;/strong&gt; and &lt;strong&gt;23.6% electricity&lt;/strong&gt;. The strong gas dominance is typical of Great Lakes / Rust Belt cities where pipeline infrastructure was built out alongside auto and glass manufacturing. The &lt;strong&gt;52.7% owner-occupancy rate&lt;/strong&gt; sits near the OH state average. The &lt;strong&gt;median home value of $107,000&lt;/strong&gt; is the lowest in the project sample &amp;mdash; older smaller homes plus depressed Toledo metro comp values keep replacement-equipment payback periods short. Ohio&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 17.52&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is above the U.S. average, which makes high-efficiency-tier equipment selection more financially compelling.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;FirstEnergy Toledo Edison Rebates &amp;mdash; Limited Status&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Toledo&amp;rsquo;s electric service is provided by &lt;a href="https://www.firstenergycorp.com/save_energy/save_energy_ohio.html" target="_blank" rel="nofollow noopener"&gt;Toledo Edison (a FirstEnergy Ohio company)&lt;/a&gt;. After a comprehensive efficiency-program suspension in 2020 pursuant to PUCO order, the FirstEnergy Ohio utilities resumed a residential products rebate program from June 2023 through May 2024 that included a $500 heat pump water heater rebate but &lt;strong&gt;did not include central air-source heat pump rebates&lt;/strong&gt;. As of early 2026 the only active residential incentives are a &lt;strong&gt;smart-thermostat rebate&lt;/strong&gt; and the Community Connections demand-response program. FirstEnergy filed its sixth Electric Security Plan with PUCO in January 2025 proposing new residential efficiency programs &amp;mdash; if approved, central HVAC rebates may return. Ohio&amp;rsquo;s state-administered &lt;a href="https://development.ohio.gov/" target="_blank" rel="nofollow noopener"&gt;HEAR &amp;amp; HOMES programs&lt;/a&gt; were awarded $249 million in federal Inflation Reduction Act funding but have &lt;strong&gt;not launched as of early 2026&lt;/strong&gt; &amp;mdash; the Ohio Department of Development is finalizing program design. When live, HEAR will offer up to &lt;strong&gt;$8,000&lt;/strong&gt; for a qualifying heat pump for income-eligible households.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Ohio HVAC Contractor Licensing (OCILB)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC work in Toledo is regulated at the state level by the &lt;a href="https://com.ohio.gov/divisions-and-programs/industrial-compliance/professional-licensing/ohio-construction-industry-licensing-board" target="_blank" rel="nofollow noopener"&gt;Ohio Construction Industry Licensing Board (OCILB)&lt;/a&gt;. The HVAC contractor application fee is &lt;strong&gt;$50 per classification&lt;/strong&gt;; applicants must carry at least &lt;strong&gt;$500,000 in liability insurance&lt;/strong&gt; with OCILB listed as the certificate holder, plus workers&amp;rsquo; compensation if employees are involved. The state HVAC contractor exam is administered by PSI; passing requires 70% on both the trade and the business &amp;amp; law sections. Licenses renew biennially with a mandatory &lt;strong&gt;8 hours of annual continuing education&lt;/strong&gt;. State-level OCILB licensure does not require a surety bond, but Toledo and surrounding Lucas County jurisdictions may impose local bond requirements separate from the state licence. Local permit pulls run through the &lt;a href="https://toledo.oh.gov/services/permits-and-inspections" target="_blank" rel="nofollow noopener"&gt;City of Toledo Division of Building Inspection&lt;/a&gt;. Anyone handling refrigerant in the course of HVAC service must also hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law; verify that OCILB licence number and EPA-608 status before signing.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S120" t="n">
@@ -15795,21 +15725,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KINT)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Smith Reynolds Airport (KINT) is the official NOAA reference station for Winston-Salem. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013723), Winston-Salem records an &lt;strong&gt;annual mean temperature of 59.6&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 69.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 49.4&amp;deg;F, approximately &lt;strong&gt;3,499.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,552.2 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;43.95 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;7.1 inches&lt;/strong&gt;. The roughly 2.3:1 HDD-to-CDD ratio reflects a dual-load climate in the NC Piedmont &amp;mdash; meaningful heating and cooling demand, with 44 inches of precipitation driving summer humidity loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:75000&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Winston-Salem city, North Carolina) report &lt;strong&gt;100,278 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1980&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;60.9% electricity&lt;/strong&gt; (61,022 units), &lt;strong&gt;31.6% utility natural gas&lt;/strong&gt; (31,696 units), &lt;strong&gt;4.4% fuel oil or kerosene&lt;/strong&gt; (4,372 units), and 2.1% bottled/tank/LP gas (2,142 units). The 4.4% fuel-oil share is notably high for a Southern city &amp;mdash; a legacy of the NC Piedmont&amp;rsquo;s historic Moravian-era housing stock and industrial development. Fuel-oil-to-heat-pump conversion is a viable upgrade path in these older homes.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate &amp;amp; Dehumidification (Zone 4A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Winston-Salem&amp;rsquo;s combination of 1,552.2 CDD and 43.95 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in the Piedmont&amp;rsquo;s humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Carolina requires HVAC contractors to hold a &lt;strong&gt;Heating Contractor License&lt;/strong&gt; (H-1, H-2, or H-3 classification) issued by the North Carolina Board of Examiners of Plumbing, Heating and Fire Sprinkler Contractors. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Winston-Salem service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Winston-Salem are set by the City of Winston-Salem Inspections Division. Contact the Division directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KINT, WBAN 93807)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Smith Reynolds Airport (KINT, &lt;a href="https://www.ncdc.noaa.gov/cdo-web/datasets/LCD/stations/WBAN:93807/detail" target="_blank" rel="nofollow noopener"&gt;WBAN:93807&lt;/a&gt;) is the official NOAA reference station for Winston-Salem, North Carolina. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Winston-Salem records approximately &lt;strong&gt;3,617 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,485 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;28.8 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;65.3 days below freezing&lt;/strong&gt;, and roughly &lt;strong&gt;7.5 inches&lt;/strong&gt; of annual snowfall. The 2.4:1 HDD:CDD ratio places the Triad firmly in the heating-dominant Mixed-Humid (IECC Zone 4A) band &amp;mdash; with winter loads about 60% larger than summer loads, equipment selection should prioritize cold-climate heat-pump performance ratings (HSPF2) or dual-fuel configurations with a gas-furnace backup below the balance point. Winston-Salem sits at roughly 1,000 ft elevation in the Piedmont, producing slightly cooler summer minimums and more frequent freeze events than coastal North Carolina &amp;mdash; a measurable factor for heat-pump defrost-cycle frequency and for condenser-pad freeze-protection during ice-storm events.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:75000&amp;amp;in=state:37" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Winston-Salem city, North Carolina) report a &lt;strong&gt;median year built of 1980&lt;/strong&gt;, with a heating-fuel distribution of &lt;strong&gt;60.9% electricity&lt;/strong&gt; and &lt;strong&gt;31.6% utility natural gas&lt;/strong&gt;. The roughly 2:1 electric-to-gas ratio reflects the gradual conversion of older Mid-Atlantic Piedmont gas-furnace stock to electric heat pumps. The &lt;strong&gt;54.6% owner-occupancy rate&lt;/strong&gt; is closer to the NC state average. The &lt;strong&gt;median home value of $208,200&lt;/strong&gt; reflects the mix of established neighborhoods (Buena Vista, Ardmore, Sherwood Forest, Country Club) and a growing downtown rental market. North Carolina&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 14.64&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is below the U.S. national average.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Smart $aver &amp;amp; Energy Saver NC&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Winston-Salem is served by &lt;a href="https://www.duke-energy.com/home/products/smart-saver" target="_blank" rel="nofollow noopener"&gt;Duke Energy Carolinas&lt;/a&gt;, whose Smart $aver residential rebate program offers &lt;strong&gt;$500&amp;ndash;$1,000&lt;/strong&gt; for qualifying central heat-pump and AC installations, with higher tiers for variable-speed and geothermal heat pumps meeting specified SEER2 / HSPF2 thresholds. The North Carolina Utilities Commission approved increases to Smart $aver HVAC, insulation, and water-heater incentives effective January 1, 2025. Duke also runs a separate Smart $aver heat-pump-water-heater rebate (currently $500&amp;ndash;$800 depending on efficiency tier) and a smart-thermostat enrollment incentive tied to demand-response. Stacking with state programs is allowed: &lt;a href="https://www.deq.nc.gov/energy-climate/state-energy-office/energy-saver-north-carolina" target="_blank" rel="nofollow noopener"&gt;Energy Saver NC&lt;/a&gt; &amp;mdash; launched in January 2025 by the NC Department of Environmental Quality and available in all 100 NC counties as of February 2026 &amp;mdash; offers up to &lt;strong&gt;$8,000&lt;/strong&gt; for an ENERGY STAR-certified electric heat pump for households at or below 150% Area Median Income through the federal HEAR pathway, plus a separate HOMES pathway open to all income levels based on modeled or measured whole-home energy savings.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Carolina Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC work in Winston-Salem is licensed by the &lt;a href="https://nclicensing.org/" target="_blank" rel="nofollow noopener"&gt;North Carolina State Board of Examiners of Plumbing, Heating, and Fire Sprinkler Contractors&lt;/a&gt;. Most residential installs in the Triad fall under the &lt;strong&gt;H-3 (forced-air heating &amp;amp; cooling, &amp;le;15 tons)&lt;/strong&gt; classification; larger commercial work falls under H-2 (&gt;15 tons) or H-1 (water-based heating). The Heating Group examination is administered by PSI Testing Services, costs &lt;strong&gt;$100 per exam&lt;/strong&gt;, and requires &lt;strong&gt;2 years (4,000 hours)&lt;/strong&gt; of supervised on-site experience. Contractor applicants also sit a 90-minute Business and Law exam. Verify a Forsyth County contractor&amp;rsquo;s active license status on the Board&amp;rsquo;s public lookup before signing &amp;mdash; the lookup also surfaces any open or closed disciplinary actions. Anyone handling refrigerant in the course of HVAC service must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law (CFR Title 40 Part 82). Local Forsyth County permit pulls run through the &lt;a href="https://www.cityofws.org/1167/Inspections" target="_blank" rel="nofollow noopener"&gt;Winston-Salem / Forsyth County Inspections Division&lt;/a&gt;.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S128" t="n">
@@ -16288,19 +16204,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCAE)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Columbia Metropolitan Airport (KCAE) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013883), Columbia records an &lt;strong&gt;annual mean temperature of 64.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 75.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 52.9&amp;deg;F, approximately &lt;strong&gt;2,472.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,236.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;45.24 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;1.2 inches&lt;/strong&gt;. The near-equal HDD:CDD balance reflects a genuine dual-load climate in the SC Midlands &amp;mdash; meaningful heating and cooling demand year-round.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:16000&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Columbia city, South Carolina) report &lt;strong&gt;51,784 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;71.0% electricity&lt;/strong&gt; (36,764 units), &lt;strong&gt;27.0% utility natural gas&lt;/strong&gt; (13,961 units), and 456 on bottled/tank/LP gas. The electric-majority profile reflects the warm-humid climate where heat-pump primary heat handles the moderate winter load efficiently.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Columbia&amp;rsquo;s combination of 2,236.6 CDD and 45.24 inches of precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems are particularly effective in the SC Midlands&amp;rsquo; humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing (LLR)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC Department of Labor, Licensing and Regulation (LLR). Verify a specific contractor&amp;rsquo;s current LLR license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dominion Energy South Carolina Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Dominion Energy South Carolina administers residential rebate programs for its Columbia service territory. Contact Dominion Energy SC directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Columbia are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCAE)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Columbia Metropolitan Airport (KCAE) is the official NOAA reference station for Columbia, South Carolina. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Columbia records approximately &lt;strong&gt;2,551 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,169 annual cooling degree days&lt;/strong&gt;, an average of &lt;strong&gt;71.6 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;47.2 days below freezing&lt;/strong&gt;, and just &lt;strong&gt;1.5 inches&lt;/strong&gt; of annual snowfall. The roughly 1.2:1 HDD:CDD ratio places Columbia in the warm-humid transition band &amp;mdash; long, hot, humid Midlands summers drive the cooling load, while shoulder-season humidity (latent load) dominates equipment sizing. Columbia&amp;rsquo;s Zone 3A (Warm-Humid) classification under the IECC means properly sized heat pumps with backup electric resistance handle nearly all residential heating economically without dual-fuel configurations. The Midlands Sandhills location, sheltered from Atlantic coastal exposure but inland of the Blue Ridge foothills, also produces some of the most extreme temperature differentials in South Carolina &amp;mdash; 100&amp;deg;F+ summer afternoons followed by 20&amp;deg;F radiative-cooling winter nights are common, and equipment must be specified to swing across roughly 80&amp;deg;F of seasonal differential annually.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:16000&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Columbia city, South Carolina) report a &lt;strong&gt;median year built of 1978&lt;/strong&gt; for the city&amp;rsquo;s housing stock, with a heating-fuel distribution of &lt;strong&gt;71.0% electricity&lt;/strong&gt; and &lt;strong&gt;27.0% utility natural gas&lt;/strong&gt;. The strong electric majority reflects Columbia&amp;rsquo;s relatively modest 2,551 HDD heating load &amp;mdash; central heat pumps cover the season efficiently, and conversion from gas-furnace to heat-pump primary heat on equipment changeout is a common replacement pattern. The &lt;strong&gt;47.3% owner-occupancy rate&lt;/strong&gt; is below the SC state average, and the &lt;strong&gt;median home value of $243,500&lt;/strong&gt; reflects the city&amp;rsquo;s mix of established Shandon / Forest Acres neighborhoods and university-adjacent rentals near USC. South Carolina&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 16.15&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is moderate by national standards.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Dominion Energy South Carolina Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Columbia&amp;rsquo;s electric service is provided by &lt;a href="https://www.dominionenergy.com/south-carolina/save-energy/heating-and-cooling-rebates" target="_blank" rel="nofollow noopener"&gt;Dominion Energy South Carolina&lt;/a&gt;, which administers a published residential HVAC rebate program for eligible customers. Current published amounts: &lt;strong&gt;$400&amp;ndash;$500&lt;/strong&gt; toward the purchase and installation of an ENERGY STAR&amp;reg; central air conditioner or heat pump (replacement of existing equipment); &lt;strong&gt;$650&lt;/strong&gt; when an electric furnace is replaced with an ENERGY STAR&amp;reg; heat pump; and &lt;strong&gt;$750&lt;/strong&gt; for an ENERGY STAR&amp;reg; certified heat pump water heater. South Carolina&amp;rsquo;s state-administered &lt;a href="https://energy.sc.gov/rebates" target="_blank" rel="nofollow noopener"&gt;Home Electrification &amp;amp; Appliance Rebates (HEAR) program&lt;/a&gt;, funded under the Inflation Reduction Act and administered by the South Carolina Energy Office, was not yet open to consumer applications as of early 2026 &amp;mdash; the SCEO is finalizing software and contractor enrollment, with statewide launch anticipated later in 2026. Once open, HEAR will cap at &lt;strong&gt;$14,000 per household&lt;/strong&gt; for electrification upgrades for households at or below 150% of county AMI.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina regulates residential HVAC work through the &lt;a href="https://llr.sc.gov/res/" target="_blank" rel="nofollow noopener"&gt;South Carolina Residential Builders Commission&lt;/a&gt; (Department of Labor, Licensing &amp;amp; Regulation). The Residential HVAC specialty contractor pathway requires the qualifying party to demonstrate at least &lt;strong&gt;one year of supervised HVAC work experience&lt;/strong&gt;, submit a $100 application fee with a current credit report, pass the PSI trade exam (&lt;strong&gt;$100&lt;/strong&gt; exam fee) plus the SC business and law exam, submit a &lt;strong&gt;$10,000 surety bond&lt;/strong&gt; if any project exceeds $5,000 in total cost, and pay the &lt;strong&gt;$220 license fee&lt;/strong&gt;. Licenses renew biennially &amp;mdash; renewals postmarked after June 30 are subject to a $50 late penalty (renewal total $270). Commercial mechanical work is regulated separately by the &lt;a href="https://www.llr.sc.gov/clb/" target="_blank" rel="nofollow noopener"&gt;South Carolina Contractor&amp;rsquo;s Licensing Board&lt;/a&gt;, with a financial-statement-based group classification that determines maximum project value rather than a fixed bond. Always verify a Columbia contractor&amp;rsquo;s active license status and bond on the LLR public lookup before signing a contract.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S132" t="n">
@@ -16428,19 +16332,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KGSP)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Greenville-Spartanburg International Airport (KGSP) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003870), Greenville records an &lt;strong&gt;annual mean temperature of 61.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 50.4&amp;deg;F, approximately &lt;strong&gt;3,018.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,719.8 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;49.67 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;3.9 inches&lt;/strong&gt;. The roughly 1.8:1 HDD-to-CDD ratio reflects a dual-load climate in the SC Upstate foothills &amp;mdash; slightly more heating-dominant than Columbia due to Greenville&amp;rsquo;s higher elevation near the Blue Ridge foothills.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:30850&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Greenville city, South Carolina) report &lt;strong&gt;34,898 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1987&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;66.2% electricity&lt;/strong&gt; (23,093 units), &lt;strong&gt;30.4% utility natural gas&lt;/strong&gt; (10,603 units), and 498 on bottled/tank/LP gas. The electric-majority profile is consistent with the warm-humid climate where heat-pump primary heat is the practical standard.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Blue Ridge Foothills Climate (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Greenville&amp;rsquo;s Zone 3A position in the Blue Ridge foothills produces somewhat cooler winters than lowland SC cities like Columbia. The 3,018.6 HDD profile and 49.67 inches of precipitation mean HVAC systems need to handle both winter heating loads and summer dehumidification effectively.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing (LLR)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Carolina requires HVAC contractors to hold a &lt;strong&gt;Residential Builder or Contractor License&lt;/strong&gt; issued by the SC Department of Labor, Licensing and Regulation (LLR). Verify a specific contractor&amp;rsquo;s current LLR license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Duke Energy Carolinas administers residential rebate programs for its Greenville service territory. Contact Duke Energy Carolinas directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Greenville are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KGSP)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Greenville-Spartanburg International Airport (KGSP) serves as the regional NOAA reference station for the Greenville, South Carolina metro. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, the Upstate area records approximately &lt;strong&gt;3,287 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,643 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;33.3 days per year above 90&amp;deg;F&lt;/strong&gt;, and &lt;strong&gt;54.1 days below freezing&lt;/strong&gt;. The roughly 2:1 HDD:CDD ratio &amp;mdash; meaningfully more heating-dominated than coastal South Carolina &amp;mdash; reflects Greenville&amp;rsquo;s higher elevation (about 1,025 ft) along the Blue Ridge foothills. Equipment sizing in the Upstate must give serious weight to winter heating capacity in addition to summer cooling, and dual-fuel heat-pump configurations (electric heat pump primary, gas furnace backup below balance point) are common in higher-end replacement installs. Greenville&amp;rsquo;s position at the foot of the Blue Ridge escarpment also produces meaningful micro-climate variation across short distances &amp;mdash; high-elevation neighborhoods east of downtown can run 5&amp;ndash;7&amp;deg;F cooler than the city core during summer evenings, reducing the practical cooling load. Manual J load-calculation discipline matters more in the Upstate than in flat-coastal SC.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:30850&amp;amp;in=state:45" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Greenville city, South Carolina) report a &lt;strong&gt;median year built of 1987&lt;/strong&gt; &amp;mdash; one of the newer median ages in the project sample, reflecting rapid Upstate growth since the BMW Spartanburg plant opened in 1994. Heating-fuel distribution: &lt;strong&gt;66.2% electricity&lt;/strong&gt; and &lt;strong&gt;30.4% utility natural gas&lt;/strong&gt;. The &lt;strong&gt;41.2% owner-occupancy rate&lt;/strong&gt; is below the South Carolina state average (62.9%), reflecting Greenville&amp;rsquo;s rapidly growing rental market in and around downtown. The &lt;strong&gt;median home value of $453,300&lt;/strong&gt; is the highest in the South Carolina city sample, driven by Upstate migration and downtown revitalization. South Carolina&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 16.15&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) applies statewide.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Duke Energy Carolinas Smart $aver Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Greenville is served by &lt;a href="https://www.duke-energy.com/home/products/smart-saver" target="_blank" rel="nofollow noopener"&gt;Duke Energy Carolinas&lt;/a&gt;, whose Smart $aver residential rebate program covers HVAC upgrades. Current published amounts under the Smart $aver program range from &lt;strong&gt;$500 to $1,000&lt;/strong&gt; for qualifying central heat-pump and air-conditioner installations, with higher tiers available for variable-speed and geothermal heat-pump systems meeting specified SEER2 / HSPF2 thresholds. The North Carolina Utilities Commission approved an increase in HVAC, insulation, and water-heater incentives effective January 1, 2025 (the increases also apply to Duke Carolinas&amp;rsquo; SC service territory). Duke also runs a separate Smart $aver heat-pump-water-heater rebate (currently $500&amp;ndash;$800 depending on efficiency tier), and a smart-thermostat enrollment incentive tied to Duke&amp;rsquo;s demand-response program. South Carolina&amp;rsquo;s state-administered &lt;a href="https://energy.sc.gov/rebates" target="_blank" rel="nofollow noopener"&gt;Home Electrification &amp;amp; Appliance Rebates (HEAR) program&lt;/a&gt; was not yet open for consumer applications as of early 2026 &amp;mdash; the SC Energy Office is finalizing software and contractor enrollment, with statewide launch anticipated later in 2026. When live, HEAR will cap at &lt;strong&gt;$14,000 per household&lt;/strong&gt; for income-eligible homeowners.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Carolina Contractor Licensing&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Residential HVAC work in Greenville is licensed through the &lt;a href="https://llr.sc.gov/res/" target="_blank" rel="nofollow noopener"&gt;South Carolina Residential Builders Commission&lt;/a&gt; (LLR). The Residential HVAC specialty pathway requires the qualifying party to demonstrate at least &lt;strong&gt;one year of supervised HVAC work experience&lt;/strong&gt;, submit a $100 application fee with a current credit report, pass the PSI trade exam (&lt;strong&gt;$100 exam fee&lt;/strong&gt;) plus the SC business and law exam, submit a &lt;strong&gt;$10,000 surety bond&lt;/strong&gt; if any project exceeds $5,000 in total cost, and pay the &lt;strong&gt;$220 license fee&lt;/strong&gt;. Licenses renew biennially with renewal-fee discipline strictly enforced &amp;mdash; renewals postmarked after June 30 are subject to a $50 late penalty. Commercial mechanical work falls under the separate &lt;a href="https://www.llr.sc.gov/clb/" target="_blank" rel="nofollow noopener"&gt;South Carolina Contractor&amp;rsquo;s Licensing Board&lt;/a&gt; with a financial-statement-based group classification. Verify an Upstate contractor&amp;rsquo;s active license status and bond on the LLR public lookup before signing a contract.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S133" t="n">
@@ -16565,19 +16457,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KJAN)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jackson-Medgar Wiley Evers International Airport (KJAN) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003940), Jackson records an &lt;strong&gt;annual mean temperature of 65.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 76.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 54.5&amp;deg;F, approximately &lt;strong&gt;2,221.8 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,402.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;57.35 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;1.0 inches&lt;/strong&gt;. The CDD exceeds HDD, making Jackson a cooling-dominant market. The 57.35-inch precipitation total drives significant summer latent (humidity) loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:36000&amp;amp;in=state:28" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Jackson city, Mississippi) report &lt;strong&gt;61,956 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1969&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;51.1% electricity&lt;/strong&gt; (31,642 units), &lt;strong&gt;46.3% utility natural gas&lt;/strong&gt; (28,689 units), and 755 on bottled/tank/LP gas. The near-even electric/gas split reflects the transitional climate where both systems are competitive.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hot-Humid Climate &amp;amp; Dehumidification (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Jackson&amp;rsquo;s combination of 2,402.3 CDD and 57.35 inches of precipitation means variable-speed compressor systems with enhanced dehumidification modes are particularly effective.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mississippi HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mississippi requires HVAC contractors to hold an &lt;strong&gt;HVAC License&lt;/strong&gt; issued by the Mississippi State Board of Contractors. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Mississippi Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Entergy Mississippi administers residential energy efficiency programs for its Jackson service territory. Contact Entergy Mississippi directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Jackson are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KJAN)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jackson-Medgar Wiley Evers International Airport (KJAN) is the official NOAA reference station for Jackson, Mississippi. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Jackson records approximately &lt;strong&gt;2,392 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,258 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;71 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;40.5 days below freezing&lt;/strong&gt;, and just &lt;strong&gt;0.8 inches&lt;/strong&gt; of annual snowfall. The roughly 1:1 HDD:CDD ratio belies the asymmetry of the seasons &amp;mdash; Jackson&amp;rsquo;s long, humid Mississippi River-basin summers (71+ days above 90&amp;deg;F with high dewpoints) impose severe latent cooling loads, while the mild winters allow heat pumps to handle nearly all heating economically. IECC Zone 3A (Warm-Humid) sizing rules apply: prioritize summer latent capacity in cooling-mode selection. Jackson also lies in the upper end of the Mississippi River alluvial plain, where high water-table conditions and frequent severe-thunderstorm activity make condensate-drain sizing, surge protection, and hail-rated condenser pads worthwhile considerations during equipment replacement.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:36000&amp;amp;in=state:28" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Jackson city, Mississippi) report a &lt;strong&gt;median year built of 1969&lt;/strong&gt; &amp;mdash; the second-oldest housing stock in this batch, reflecting the city&amp;rsquo;s mid-century residential build-out followed by limited new construction in recent decades. Heating-fuel distribution: &lt;strong&gt;51.1% electricity&lt;/strong&gt; and &lt;strong&gt;46.3% utility natural gas&lt;/strong&gt;. The near-balance reflects the historic role of pipeline gas in Mississippi cities. The &lt;strong&gt;48.6% owner-occupancy rate&lt;/strong&gt; is depressed by population loss over the past 20 years. The &lt;strong&gt;median home value of $108,200&lt;/strong&gt; is among the lowest in the project &amp;mdash; older smaller homes plus weak metro comp values keep replacement-equipment payback periods short. Mississippi&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 14.72&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is near the U.S. average.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Entergy Mississippi Solutions Rebates&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Jackson&amp;rsquo;s electric service is provided by &lt;a href="https://www.entergy-mississippi.com/your_home/save_money/ee/heating-cooling/" target="_blank" rel="nofollow noopener"&gt;Entergy Mississippi&lt;/a&gt;, whose Entergy Solutions residential program offers up to &lt;strong&gt;$1,100&lt;/strong&gt; in incentives toward a high-efficiency replacement heat pump or central air conditioner; the program also offers separate rebates for heat-pump water heaters, smart thermostats, and duct sealing. Heat-pump water-heater rebates fall under Entergy&amp;rsquo;s separate Residential Appliances program. The Entergy Solutions program is administered through participating contractors who handle the rebate paperwork on the homeowner&amp;rsquo;s behalf, with most savings appearing as a discount in the original installation quote. Mississippi&amp;rsquo;s state-administered &lt;a href="https://mississippi.org/community-resources/office-energy/" target="_blank" rel="nofollow noopener"&gt;Home Energy Rebates (HER) program&lt;/a&gt; is being managed by the Mississippi Office of Energy under the Mississippi Development Authority in partnership with local utilities. Mississippi has &lt;strong&gt;not yet launched&lt;/strong&gt; its federal HEAR / HOMES rebate streams as of early 2026; consumer applications are not yet being accepted.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mississippi HVAC Contractor Licensing (MSBOC)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;HVAC work in Jackson is licensed by the &lt;a href="https://www.msboc.us/" target="_blank" rel="nofollow noopener"&gt;Mississippi State Board of Contractors (MSBOC)&lt;/a&gt; under the Mechanical Contractor classification, which spans HVAC installation, refrigeration, and gas piping. The major-classification application fee is &lt;strong&gt;$400&lt;/strong&gt; (non-refundable), with an additional &lt;strong&gt;$50&lt;/strong&gt; per additional classification carried on the same licence. A state-issued HVAC contractor license is required for residential remodeling or repair projects exceeding &lt;strong&gt;$10,000&lt;/strong&gt;, and for new residential construction or any commercial project exceeding &lt;strong&gt;$50,000&lt;/strong&gt;. The MSBOC does not impose a uniform statewide surety bond on HVAC contractors, but local jurisdictions in Hinds County may impose their own bond requirements (commonly $5,000&amp;ndash;$10,000). Anyone handling refrigerant in the course of HVAC service must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law (CFR Title 40 Part 82). Verify a Jackson-area contractor&amp;rsquo;s active licence on the MSBOC public lookup at msboc.us, and confirm the local mechanical permit through the City of Jackson Building Permit Office before signing.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S134" t="n">
@@ -17122,19 +17002,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBIL)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Billings Logan International Airport (KBIL) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024033), Billings records an &lt;strong&gt;annual mean temperature of 48.2&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 59.4&amp;deg;F&lt;/strong&gt; against an annual minimum of 37.0&amp;deg;F, approximately &lt;strong&gt;6,753.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;662.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;14.31 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;57.4 inches&lt;/strong&gt;. The roughly 10.2:1 HDD-to-CDD ratio makes Billings one of the most heating-dominant cities in the project. The semi-arid 14-inch precipitation combined with 57 inches of snowfall is characteristic of Montana&amp;rsquo;s high-plains climate &amp;mdash; dry powdery snow rather than heavy wet snow.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:06550&amp;amp;in=state:30" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Billings city, Montana) report &lt;strong&gt;50,340 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1979&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;73.7% utility natural gas&lt;/strong&gt; (37,110 units), &lt;strong&gt;22.9% electricity&lt;/strong&gt; (11,543 units), and 632 on bottled/tank/LP gas. The strong gas dominance is consistent with Montana&amp;rsquo;s position as a natural gas producing state.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Dry Climate (Zone 6B)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 6B cold-dry climates like Billings produce extended heating seasons with very low indoor relative humidity. The 6,753.7 HDD profile requires cold-climate-rated heat pumps, and the dry winter air supports whole-house humidification considerations. The 57.4-inch snowfall means outdoor condensers need elevated mounting and clear winter access.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Montana Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Montana does not issue a statewide HVAC license. The Montana Department of Labor registers HVAC contractors. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NorthWestern Energy Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;NorthWestern Energy administers residential rebate programs for its Billings service territory. Contact NorthWestern Energy directly for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees &amp;amp; Federal Tax Credits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Billings are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, state contractor licensing boards, and the published rebate pages of the relevant local utility. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBIL)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Billings Logan International Airport (KBIL) is the official NOAA reference station for Billings, Montana. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt;, Billings records approximately &lt;strong&gt;6,781 annual heating degree days&lt;/strong&gt; against just &lt;strong&gt;637 annual cooling degree days&lt;/strong&gt;, &lt;strong&gt;28.4 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;138 days below freezing&lt;/strong&gt;, and roughly &lt;strong&gt;55 inches&lt;/strong&gt; of annual snowfall. The 10.6:1 HDD:CDD ratio is among the most heating-dominant in the project &amp;mdash; Billings sits in IECC Zone 6B (Cold-Dry), with subzero winter design temperatures and rapid daily swings driven by Chinook winds off the Beartooth Front. Equipment selection must prioritize cold-climate heat-pump performance (HSPF2 &amp;ge; 8.5) or, more commonly in the Billings market, high-AFUE gas furnaces with central AC for the relatively short summer cooling season.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:06550&amp;amp;in=state:30" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Billings city, Montana) report a &lt;strong&gt;median year built of 1979&lt;/strong&gt;, with a heating-fuel distribution heavily skewed gas: &lt;strong&gt;73.7% utility natural gas&lt;/strong&gt; and &lt;strong&gt;22.9% electricity&lt;/strong&gt;. The dominance of pipeline gas reflects both the punishing winter design temperature and the cost economics of NorthWestern Energy&amp;rsquo;s natural-gas tariff &amp;mdash; Montana&amp;rsquo;s residential &lt;strong&gt;average gas rate of $0.79 / therm&lt;/strong&gt; is among the lowest in the U.S. (&lt;a href="https://www.eia.gov/dnav/ng/ng_pri_sum_a_EPG0_PRS_DMcf_a.htm" target="_blank" rel="nofollow noopener"&gt;EIA Natural Gas Prices&lt;/a&gt;). The &lt;strong&gt;64.8% owner-occupancy rate&lt;/strong&gt; is well above the U.S. average. The &lt;strong&gt;median home value of $311,800&lt;/strong&gt; reflects rapid Yellowstone-region in-migration since 2020. Montana&amp;rsquo;s residential &lt;strong&gt;average electricity rate of 13.33&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is below the U.S. average, but the cold climate keeps electric-resistance heating economically uncompetitive against gas.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;NorthWestern Energy E+ Rebates &amp;amp; Montana HEAR&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Billings&amp;rsquo; electric and gas service is provided by &lt;a href="https://northwesternenergy.com/billing-payment/ways-to-save/rebates-incentives" target="_blank" rel="nofollow noopener"&gt;NorthWestern Energy&lt;/a&gt;, which administers the E+ residential rebate program covering air-source and ground-source heat pumps, smart thermostats, and envelope improvements (insulation / weatherization). Specific air-source heat-pump incentive amounts vary by equipment efficiency tier and are published in the utility&amp;rsquo;s &lt;a href="https://www.northwesternenergy.com/docs/default-source/default-document-library/billing-and-payment/e-programs/e-rebate-electric-existing-home.pdf" target="_blank" rel="nofollow noopener"&gt;Existing-Home Electric Rebate document&lt;/a&gt;; current amounts are valid through June 30, 2026 &amp;mdash; verify the live tier with the utility before signing, as rebate schedules update annually. NorthWestern Energy also offers an instant incentive of up to &lt;strong&gt;$3,000&lt;/strong&gt; for replacing an existing electric water heater with a heat-pump water heater. Montana&amp;rsquo;s state-administered &lt;a href="https://deq.mt.gov/energy/Programs/efficiency" target="_blank" rel="nofollow noopener"&gt;Home Energy Rebates Program (HEAR &amp;amp; HOMES)&lt;/a&gt; received early administrative-planning funds in October 2023 but is &lt;strong&gt;not yet open to consumer applications&lt;/strong&gt; as of early 2026 &amp;mdash; DEQ has paused further planning work pending final DOE implementation award and updated federal program guidance. No consumer launch date is currently announced.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Montana Contractor Registration&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Montana does not issue a statewide HVAC-specific contractor licence; instead, anyone running an HVAC business must register with the &lt;a href="https://erd.dli.mt.gov/work-comp-regulations/montana-contractor/construction-contractor-registration" target="_blank" rel="nofollow noopener"&gt;Montana Department of Labor &amp;amp; Industry as a Construction Contractor&lt;/a&gt;. The Construction Contractor Registration (CCR) costs &lt;strong&gt;$70 (non-refundable)&lt;/strong&gt; and is valid for &lt;strong&gt;two years&lt;/strong&gt;; CCR holders must show proof of workers&amp;rsquo; compensation coverage. Independent contractors operating without employees may instead obtain an Independent Contractor Exemption Certificate (ICEC) for &lt;strong&gt;$125 (two years)&lt;/strong&gt;. There is no state trade exam or experience requirement, but anyone handling refrigerants must hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law (CFR Title 40 Part 82). Verify a Billings contractor&amp;rsquo;s registration status on the DLI public lookup before signing. Local permit-pull discipline matters as a compensating control: the &lt;a href="https://www.billingsmt.gov/421/Building-Codes-Information" target="_blank" rel="nofollow noopener"&gt;City of Billings Codes &amp;amp; Information Division&lt;/a&gt; requires a mechanical permit for any HVAC equipment changeout, and the inspector signs off on the work irrespective of state-level licence status.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; and the state programs described above.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S138" t="n">

--- a/cities_updated.xlsx
+++ b/cities_updated.xlsx
@@ -3186,21 +3186,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCHA)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lovell Field (KCHA) is the official NOAA reference station for Chattanooga. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00013882), Chattanooga records an &lt;strong&gt;annual mean temperature of 61.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 72.2&amp;deg;F&lt;/strong&gt; against an annual minimum of 51.5&amp;deg;F, approximately &lt;strong&gt;3,029.2 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,920.6 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;55.00 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;3.6 inches&lt;/strong&gt;. The roughly 1.6:1 HDD-to-CDD ratio reflects a genuine dual-load climate in the Tennessee Valley &amp;mdash; meaningful heating and cooling demand throughout the year. The 55-inch precipitation total also drives significant summer latent (humidity) loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 House Heating Fuel and B25035 Median Year Structure Built for Chattanooga city, Tennessee) report &lt;strong&gt;77,916 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1975&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.9% electricity&lt;/strong&gt; (56,831 units), &lt;strong&gt;25.2% utility natural gas&lt;/strong&gt; (19,607 units), and 739 on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories, where historically affordable hydroelectric power made electric resistance and heat-pump heating economically competitive with gas.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: EPB Municipal Utility (TVA Distributor)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Chattanooga&amp;rsquo;s electric service is provided by the &lt;strong&gt;Electric Power Board (EPB)&lt;/strong&gt;, a municipally owned utility that distributes TVA power. EPB is nationally recognized for its community-wide fiber-optic network and smart-grid infrastructure. EPB / TVA EnergyRight administers residential HVAC rebates; contact EPB directly or visit the TVA EnergyRight page for the current heat pump and smart thermostat rebate amounts. Municipal utility status means Chattanooga electric customers contract with the City rather than with a private investor-owned utility.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Mixed-Humid Climate Considerations (Zone 4A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 4A mixed-humid climates produce significant summer latent (moisture) loads. Chattanooga&amp;rsquo;s combination of 1,920.6 CDD and 55.00 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems with enhanced dehumidification modes are particularly effective in the Tennessee Valley&amp;rsquo;s humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors to hold a &lt;strong&gt;Mechanical Contractor License (CMC-C)&lt;/strong&gt; issued by the Tennessee Board for Licensing Contractors. Verify a specific contractor&amp;rsquo;s current license status on the Board&amp;rsquo;s public lookup before contracting. Permit-pulling responsibility typically rests with the licensed installing contractor.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Chattanooga are set by the City of Chattanooga Land Development Office. Contact the Office directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, the Tennessee Board for Licensing Contractors, and the published rebate pages of EPB and TVA EnergyRight. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;EPB Municipal Utility &amp;amp; the Gigabit Smart-Grid Distinction&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Chattanooga's electric service is provided by the &lt;strong&gt;Electric Power Board (EPB)&lt;/strong&gt; &amp;mdash; not by Knoxville's KUB and not by any investor-owned utility &amp;mdash; a municipally owned distributor that buys wholesale power from the Tennessee Valley Authority. EPB is materially different from peer TVA distributors in one specific way: in 2010 EPB built a community-wide fiber-optic network paired with an automated smart-grid distribution system, and Chattanooga is one of only a handful of U.S. cities with utility-owned gigabit fiber to every electric meter. The HVAC-relevant consequence is that EPB has unusually granular outage and load-shape data, and offers smart-thermostat demand-response programs that tie directly into that real-time data feed. Residential HVAC rebates flow through the &lt;a href="https://energyright.com/residential/rebates/heat-pump/" target="_blank" rel="nofollow noopener"&gt;TVA EnergyRight&lt;/a&gt; framework with EPB providing the local-utility match; equipment must be installed by a contractor in the &lt;strong&gt;TVA Quality Contractor Network (QCN)&lt;/strong&gt;, and gas-to-heat-pump conversion is &lt;strong&gt;not currently rebate-eligible&lt;/strong&gt; (replacement of existing electric heating is the required pathway). Tennessee's federally funded &lt;a href="https://www.tn.gov/environment/program-areas/energy/state-energy-office--seo-/programs-projects/programs-and-projects/inflation-reduction-act/home-energy-rebate-programs.html" target="_blank" rel="nofollow noopener"&gt;HEAR program&lt;/a&gt; (approximately $83.4 million allocation, administered by TDEC Office of Energy Programs in partnership with TVA's QCN) received conditional DOE approval in January 2025 with statewide launch targeted for Q3 2026. Once active, HEAR will allow gas-to-heat-pump conversion rebates of up to $8,000 per qualifying household; until then, existing TVA EnergyRight rebates remain the primary published path.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:14000&amp;amp;in=state:47" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Chattanooga city, Tennessee) report &lt;strong&gt;77,916 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1975&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;72.9% electricity&lt;/strong&gt; (56,831 units), &lt;strong&gt;25.2% utility natural gas&lt;/strong&gt; (19,607 units), and 739 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is 53.1%&lt;/strong&gt;; the &lt;strong&gt;median home value is $259,200&lt;/strong&gt;. Tennessee's residential &lt;strong&gt;average electricity rate of 12.82&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the lowest in the project, which reinforces the long-standing TVA-region economic preference for electric resistance and heat-pump primary heat over piped natural gas. Chattanooga's North Shore (37405) and Brainerd (37411) neighborhoods contain a meaningful share of 1920s&amp;ndash;1940s pre-war stock where envelope upgrades typically precede equipment replacement for best results.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KCHA) &amp;amp; Ridge-and-Valley Temperature Inversions&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Chattanooga is geographically distinct from Knoxville: it sits at the southern terminus of the &lt;strong&gt;Ridge-and-Valley Appalachian physiographic province&lt;/strong&gt;, with downtown wedged in the Tennessee River gorge between Lookout Mountain and Missionary Ridge. The orographic enclosure produces frequent &lt;strong&gt;winter temperature inversions&lt;/strong&gt; &amp;mdash; cold dense air pools in the valley floor below warmer air aloft &amp;mdash; which traps both fine particulate (PM2.5) and ozone precursors. Per &lt;a href="https://www.airnow.gov/state/?name=tennessee" target="_blank" rel="nofollow noopener"&gt;EPA AirNow&lt;/a&gt;, Chattanooga has recurring Code Orange air-quality alerts that are operationally different from Knoxville's higher-elevation Smoky Mountain monitor pattern &amp;mdash; in Chattanooga the trapped air sits at building level, making MERV-13+ fresh-air filtration a routine specification on alert days, not an edge case. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Lovell Field, KCHA / USW00013882), Chattanooga records approximately &lt;strong&gt;3,239 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,744 cooling degree days&lt;/strong&gt;, &lt;strong&gt;47.7 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;58.3 days below freezing&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;55.00 inches&lt;/strong&gt;, and an annual snowfall normal of only &lt;strong&gt;3.9 inches&lt;/strong&gt;. The 55-inch precipitation drives substantial summer latent loads &amp;mdash; variable-speed dehumidification is a baseline specification.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Tennessee CMC-C Licensing &amp;mdash; The $25,000 Threshold &amp;amp; Local Bonding&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tennessee requires HVAC contractors performing projects of &lt;strong&gt;$25,000 or more&lt;/strong&gt; to hold a Mechanical Contractor license issued by the &lt;a href="https://www.tn.gov/commerce/regboards/contractor.html" target="_blank" rel="nofollow noopener"&gt;Tennessee Board for Licensing Contractors&lt;/a&gt;; the HVAC-specific subclassification is &lt;strong&gt;CMC-C (Mechanical &amp;mdash; HVAC/Refrigeration Contractor)&lt;/strong&gt;. The $25,000 threshold matters for Chattanooga homeowners specifically because a typical Chattanooga heat-pump-plus-air-handler-plus-ductwork retrofit frequently crosses that dollar line &amp;mdash; verify the contractor's CMC-C status if your quote is at or above $25,000. The Board does not automatically require statewide bonding, but the Board's &lt;strong&gt;financial-statement review&lt;/strong&gt; can trigger a Letter of Credit or surety bond requirement at the state level, and the City of Chattanooga Land Development Office may impose its own local bonding requirement on permit issuance. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law &amp;mdash; particularly relevant given the AIM Act-driven phasedown of R-410A in favor of R-454B and R-32 equipment. Mechanical permits in Chattanooga are pulled through the City of Chattanooga Land Development Office.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Chattanooga homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, focus on TVA EnergyRight rebates plus the upcoming TN HEAR launch &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -5487,21 +5473,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFWA)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fort Wayne International Airport (KFWA) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014827), Fort Wayne records an &lt;strong&gt;annual mean temperature of 50.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 60.3&amp;deg;F&lt;/strong&gt; against an annual minimum of 41.4&amp;deg;F, approximately &lt;strong&gt;5,967.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;849.1 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.48 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;33.6 inches&lt;/strong&gt;. The roughly 7:1 HDD-to-CDD ratio makes Fort Wayne a heavily heating-dominant market where furnace efficiency, building envelope performance, and snow clearance around outdoor equipment are the primary HVAC design drivers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:25000&amp;amp;in=state:18" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fort Wayne city, Indiana) report &lt;strong&gt;109,604 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1971&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;70.7% utility natural gas&lt;/strong&gt; (77,492 units), &lt;strong&gt;26.9% electricity&lt;/strong&gt; (29,499 units), and 1,455 on bottled/tank/LP gas. The strong gas dominance and early-1970s housing stock mean furnace AFUE upgrades and ductwork remediation are high-impact investments.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations (Zone 5A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Fort Wayne&amp;rsquo;s 5,967.7 HDD profile and 33.6 inches of annual snowfall require cold-climate-rated heat pumps for any gas-to-electric conversion. Outdoor condensers benefit from elevated mounting (12&amp;ndash;24 inches above grade) and clear winter access for service. The 1971 median housing age means many homes may benefit from envelope improvements alongside equipment upgrades.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Indiana HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Fort Wayne must obtain permits through the Fort Wayne Department of Planning Services. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting, and confirm they will pull the required local permits.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;I&amp;amp;M / AEP Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana Michigan Power (I&amp;amp;M), an AEP company, administers the Energy Savings Rebate Program for its Fort Wayne service territory. Contact I&amp;amp;M directly for the current heat pump, smart thermostat, and central AC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Fort Wayne are set by the Fort Wayne Department of Planning Services. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, and the published rebate pages of Indiana Michigan Power and NIPSCO. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KFWA) &amp;amp; Lake-Effect Snow Influence&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fort Wayne sits roughly 130 miles southeast of Lake Michigan and 90 miles south of Lake Erie, just outside the heaviest lake-effect snow belts but close enough that southerly-tracked clipper systems occasionally drop substantial accumulations. Per &lt;a href="https://www.weather.gov/iwx/" target="_blank" rel="nofollow noopener"&gt;NWS Northern Indiana&lt;/a&gt;, the Fort Wayne area sees a roughly even mix of Great Lakes synoptic snow and Ohio Valley moisture systems &amp;mdash; outdoor condensers benefit from elevated mounting at 18&amp;ndash;24 inches above grade to clear drifting snow against fences and structures. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Fort Wayne International Airport, KFWA / USW00014827), Fort Wayne records approximately &lt;strong&gt;6,102 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;809 cooling degree days&lt;/strong&gt;, just &lt;strong&gt;13.4 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;123.2 days below freezing&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;39.48 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;33.5 inches&lt;/strong&gt;. The 7.5:1 HDD-to-CDD ratio makes Fort Wayne a heavily heating-dominant market where furnace AFUE, building-envelope performance, and snow-clearance around outdoor equipment dominate HVAC design considerations.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:25000&amp;amp;in=state:18" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Fort Wayne city, Indiana) report &lt;strong&gt;109,604 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1971&lt;/strong&gt; &amp;mdash; older than most of the project, reflecting Fort Wayne's industrial-era roots. Heating-fuel distribution: &lt;strong&gt;70.7% utility natural gas&lt;/strong&gt; (77,492 units), &lt;strong&gt;26.9% electricity&lt;/strong&gt; (29,499 units), and 1,455 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is 62.2%&lt;/strong&gt;; the &lt;strong&gt;median home value is $169,700&lt;/strong&gt; &amp;mdash; among the most affordable in the project. Indiana's residential &lt;strong&gt;average electricity rate of 16.06&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is moderately above the U.S. average. The strong gas dominance plus the 1971-era housing stock mean envelope upgrades (attic insulation, air sealing, ductwork remediation) typically pay back faster than equipment swaps alone &amp;mdash; a blower-door test before equipment quoting is high-value diligence.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Fort Wayne Dual-Utility Setup &amp;mdash; I&amp;amp;M Electric, NIPSCO Gas&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Fort Wayne has a structurally distinct utility setup: &lt;strong&gt;electric service comes from Indiana Michigan Power (I&amp;amp;M)&lt;/strong&gt;, an AEP company, while &lt;strong&gt;natural gas service comes from NIPSCO (Northern Indiana Public Service Company)&lt;/strong&gt;. Two utilities, two rebate programs. I&amp;amp;M administers the &lt;a href="https://www.indianamichiganpower.com/save/" target="_blank" rel="nofollow noopener"&gt;Energy Savings Rebate Program&lt;/a&gt; for residential heat-pump, central AC, and smart-thermostat installations; NIPSCO administers a separate &lt;a href="https://www.nipsco.com/save-money/save-money-and-energy" target="_blank" rel="nofollow noopener"&gt;gas-side rebate program&lt;/a&gt; for high-efficiency furnaces. Rebate amounts vary by equipment efficiency tier on both sides &amp;mdash; contact I&amp;amp;M for electric/heat-pump rebates and NIPSCO for gas-furnace rebates separately for current published amounts. Indiana's federally funded HEAR program is being administered by the &lt;a href="https://www.in.gov/oed/" target="_blank" rel="nofollow noopener"&gt;Indiana Office of Energy Development&lt;/a&gt;; as of early 2026 IN HEAR's consumer launch is &lt;strong&gt;not yet active&lt;/strong&gt; &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for Indiana-specific HEAR launch status.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Indiana Licensing &amp;mdash; No Statewide HVAC, Allen County / Fort Wayne Municipal&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Indiana does not issue a statewide HVAC contractor license. The &lt;a href="https://www.in.gov/pla/contractor/" target="_blank" rel="nofollow noopener"&gt;Indiana Professional Licensing Agency&lt;/a&gt; licenses plumbers, electricians, and some specialty trades at the state level but leaves HVAC mechanical licensing to local jurisdictions. &lt;strong&gt;Fort Wayne requires a mechanical contractor license&lt;/strong&gt; issued through the &lt;strong&gt;Fort Wayne Department of Planning Services&lt;/strong&gt; and Allen County permitting authority for work in unincorporated Allen County. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law &amp;mdash; relevant given the AIM Act-driven transition from R-410A to R-454B and R-32 equipment. Mechanical/HVAC permit fees in Fort Wayne are set by the Department of Planning Services; verify the contractor's local license status and current permit fee schedule with that office before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Fort Wayne homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, I&amp;amp;M and NIPSCO rebates plus the eventual IN HEAR launch are the operative funding sources &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -6471,21 +6443,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBDL)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bradley International Airport (KBDL) is the official NOAA reference station for the Hartford area. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014740), Hartford records an &lt;strong&gt;annual mean temperature of 51.0&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 61.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 40.9&amp;deg;F, approximately &lt;strong&gt;5,883.3 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;819.3 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;47.05 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;51.7 inches&lt;/strong&gt;. The roughly 7.2:1 HDD-to-CDD ratio makes Hartford a heavily heating-dominant market. The 51.7-inch snowfall normal (Connecticut River valley nor&amp;rsquo;easters) drives outdoor equipment clearance and winter service access planning.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:09" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Hartford city, Connecticut) report &lt;strong&gt;49,023 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1953&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;65.8% utility natural gas&lt;/strong&gt; (32,251 units), &lt;strong&gt;23.3% electricity&lt;/strong&gt; (11,403 units), and &lt;strong&gt;7.0% fuel oil or kerosene&lt;/strong&gt; (3,449 units), with 983 on bottled/tank/LP gas. The 7% fuel-oil share is typical of Connecticut&amp;rsquo;s historic Northeast housing stock. Fuel-oil-to-heat-pump conversion remains a meaningful upgrade opportunity in these older homes.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Northeast Heating Climate &amp;amp; Fuel-Oil Legacy&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Hartford&amp;rsquo;s 5,883.3 HDD profile and 51.7 inches of annual snowfall require cold-climate-rated heat pumps for heat-pump conversion. The 1953 median housing age means envelope upgrades (insulation, air sealing, window replacement) frequently accompany heat-pump installation for best results. Connecticut&amp;rsquo;s inland location (vs. coastal Bridgeport) produces colder winter extremes, making cold-climate equipment specification particularly important.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Connecticut Contractor Licensing (DCP S-1)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Connecticut requires HVAC contractors to hold a &lt;strong&gt;Heating, Piping and Cooling Contractor License (S-1 classification)&lt;/strong&gt; issued by the Connecticut Department of Consumer Protection (DCP). The DCP administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current DCP license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energize Connecticut / Eversource Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Energize Connecticut, in partnership with Eversource, administers residential heat pump incentives for Hartford customers. Contact Energize CT or Eversource directly for the current heat pump rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Hartford are set by the City of Hartford Department of Development Services, Licenses &amp;amp; Inspections. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, the Connecticut Department of Consumer Protection, and the published rebate pages of Energize Connecticut. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBDL) &amp;amp; Connecticut River Valley Snow Patterns&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Hartford sits in the Connecticut River valley, an inland funnel for Atlantic moisture that produces snowfall totals substantially higher than coastal Bridgeport or New Haven. Per &lt;a href="https://www.weather.gov/box/winter" target="_blank" rel="nofollow noopener"&gt;NWS Boston/Norton winter-weather guidance&lt;/a&gt; (which covers central Connecticut), the Connecticut River valley funnels Atlantic moisture into multi-day nor'easter accumulation events that explicitly drive recurring roof-collapse, burst-pipe, and prolonged-outage risk &amp;mdash; all of which intersect HVAC operation. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Bradley International Airport, KBDL / USW00014740), Hartford records approximately &lt;strong&gt;5,999 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;756 cooling degree days&lt;/strong&gt;, &lt;strong&gt;14.6 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;124.9 days below freezing&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;47.05 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;40.5 inches&lt;/strong&gt;. The 7.9:1 HDD-to-CDD ratio makes Hartford a heavily heating-dominant market &amp;mdash; outdoor condensers should be installed with &lt;strong&gt;elevated mounting at 24 inches above grade&lt;/strong&gt; and dedicated snow-shed clearance to the structure.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pre-War Housing Stock &amp;amp; Insurance-Industry Demographic&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Hartford has one of the oldest median housing stocks in the project. Per the &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:09" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Hartford city, Connecticut), the city has &lt;strong&gt;49,023 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1953&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;65.8% utility natural gas&lt;/strong&gt; (32,251 units), &lt;strong&gt;23.3% electricity&lt;/strong&gt; (11,403 units), &lt;strong&gt;7.0% fuel oil or kerosene&lt;/strong&gt; (3,449 units), with 983 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is just 25.7%&lt;/strong&gt; &amp;mdash; among the very lowest in the project, reflecting Hartford's dense multi-family stock; the &lt;strong&gt;median home value is $217,200&lt;/strong&gt;. Connecticut's residential &lt;strong&gt;average electricity rate of 30.77&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the very highest in the U.S. lower 48 &amp;mdash; cold-climate heat-pump performance (COP &amp;ge; 1.75 at 5&amp;deg;F) is economically essential for any oil-to-electric or gas-to-electric conversion, and equipment specification matters more here than in low-rate markets.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Energize Connecticut Heat Pump Incentive &amp;amp; CT HEAR Status&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Hartford's electric service is provided by &lt;strong&gt;Eversource Connecticut&lt;/strong&gt; (legally distinct from Eversource Massachusetts &amp;mdash; same parent company, separate state-regulated entity, separate rate base). Residential HVAC rebates are administered through &lt;a href="https://energizect.com/your-home/solutions-list/home-energy-solutions" target="_blank" rel="nofollow noopener"&gt;Energize Connecticut&lt;/a&gt;, the statewide ratepayer-funded efficiency program operated jointly by Eversource and Avangrid (UI) with oversight from the CT Department of Energy and Environmental Protection. The Energize CT Heat Pump Incentive offers tiered rebates for cold-climate air-source heat pumps; published amounts vary by equipment efficiency tier and refrigerant type &amp;mdash; check the Energize CT site for current published amounts before purchasing equipment. Connecticut's federally funded HEAR program is being administered by the &lt;a href="https://portal.ct.gov/deep" target="_blank" rel="nofollow noopener"&gt;CT Department of Energy and Environmental Protection (DEEP)&lt;/a&gt;; as of early 2026 CT HEAR's consumer launch is &lt;strong&gt;not yet active for income-eligible whole-home rebates&lt;/strong&gt;, though the existing Energize CT framework already provides substantial heat-pump coverage statewide &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for Connecticut-specific HEAR launch updates.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Connecticut DCP S-1 Licensing &amp;amp; Trade Reciprocity&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Connecticut requires HVAC contractors to hold a &lt;strong&gt;Heating, Piping and Cooling Contractor License (S-1 classification)&lt;/strong&gt; issued by the &lt;a href="https://portal.ct.gov/dcp" target="_blank" rel="nofollow noopener"&gt;Connecticut Department of Consumer Protection (DCP)&lt;/a&gt;. The DCP S-1 is the unrestricted contractor license, while the &lt;strong&gt;S-2 is a journeyman/installer credential&lt;/strong&gt; that must work under an S-1 contractor's supervision. Connecticut does not have automatic statewide license reciprocity with neighboring Massachusetts or New York &amp;mdash; contractors crossing state lines must hold the appropriate Connecticut credential. Continuing education is required for renewal: &lt;strong&gt;10 hours per renewal period&lt;/strong&gt;, including code-update content. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law &amp;mdash; particularly relevant for Hartford's old oil-converted housing stock as the federal AIM Act phasedown accelerates the R-410A retirement. Mechanical permits in Hartford are issued through the &lt;strong&gt;City of Hartford Department of Development Services, Licenses &amp;amp; Inspections&lt;/strong&gt;.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Hartford homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, Energize Connecticut and the eventual CT HEAR launch are the operative funding sources &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -6903,21 +6861,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KHSV)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville International Airport (KHSV) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00003856), Huntsville records an &lt;strong&gt;annual mean temperature of 62.9&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 73.8&amp;deg;F&lt;/strong&gt; against an annual minimum of 52.1&amp;deg;F, approximately &lt;strong&gt;2,831.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,106.9 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;54.29 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;2.4 inches&lt;/strong&gt;. The roughly 1.3:1 HDD-to-CDD ratio reflects a balanced dual-load climate &amp;mdash; meaningful heating and meaningful cooling demand, with 54 inches of precipitation driving significant summer humidity loads.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Huntsville city, Alabama) report &lt;strong&gt;94,058 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;75.8% electricity&lt;/strong&gt; (71,266 units), &lt;strong&gt;22.2% utility natural gas&lt;/strong&gt; (20,912 units), and 1,037 on bottled/tank/LP gas. The strong electric-heating majority is characteristic of TVA distributor territories in the Tennessee Valley, where historically affordable power made heat-pump and electric-resistance heating economically competitive.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Huntsville Utilities (TVA Distributor) &amp;amp; NASA/Defense Economy&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville&amp;rsquo;s electric service is provided by &lt;strong&gt;Huntsville Utilities&lt;/strong&gt;, a municipally owned utility that distributes TVA power. Huntsville Utilities / TVA EnergyRight administers residential HVAC rebates; contact Huntsville Utilities directly for the current heat pump and smart thermostat rebate amounts. Huntsville&amp;rsquo;s major employer base &amp;mdash; including NASA Marshall Space Flight Center and Redstone Arsenal &amp;mdash; drives housing construction activity and HVAC demand patterns in the area.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Warm-Humid Climate Considerations (Zone 3A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3A warm-humid climates produce significant summer latent (moisture) loads. Huntsville&amp;rsquo;s combination of 2,106.9 CDD and 54.29 inches of annual precipitation means properly sized cooling equipment with adequate dehumidification capability is essential. Variable-speed compressor systems with enhanced dehumidification modes are particularly effective in the Tennessee Valley&amp;rsquo;s humid summers.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HVAC Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama requires HVAC contractors to hold a license issued by the &lt;strong&gt;Alabama Board of Heating, Air Conditioning, and Refrigeration Contractors (Board of HACR Contractors)&lt;/strong&gt;. The Board administers examinations and issues licenses statewide. Verify a specific contractor&amp;rsquo;s current license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Huntsville are set by the City of Huntsville Inspection Services Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, the Alabama HACR Board, and the published rebate pages of the Tennessee Valley Authority. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Aerospace-Driven Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville's housing stock is distinctively younger than most Alabama markets because the city's economy is anchored by NASA Marshall Space Flight Center, Redstone Arsenal, and the Cummings Research Park technology corridor &amp;mdash; all of which have driven sustained construction since the 1970s. The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:37000&amp;amp;in=state:01" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035) report &lt;strong&gt;94,058 occupied housing units&lt;/strong&gt; in Huntsville with a &lt;strong&gt;median year built of 1984&lt;/strong&gt; &amp;mdash; meaningfully newer than the 1974 median that prevails in older Alabama industrial cities. Heating-fuel distribution: &lt;strong&gt;75.8% electricity&lt;/strong&gt; (71,266 units), &lt;strong&gt;22.2% utility natural gas&lt;/strong&gt; (20,912 units), and 1,037 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is 58.1%&lt;/strong&gt; and the &lt;strong&gt;median home value is $263,100&lt;/strong&gt; &amp;mdash; the highest in the state &amp;mdash; reflecting federal-civilian and contractor incomes. The dominant-electric profile is a TVA-territory hallmark.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KHSV) &amp;amp; Tornado Alley Exposure&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville sits inside the documented &lt;strong&gt;Dixie Alley tornado corridor&lt;/strong&gt;, and per &lt;a href="https://www.weather.gov/hun/" target="_blank" rel="nofollow noopener"&gt;NWS Huntsville&lt;/a&gt;, the Tennessee Valley records one of the highest densities of long-track EF2+ tornadoes in the United States &amp;mdash; outdoor HVAC equipment in Huntsville should be installed with anchored hurricane-grade tie-downs and clear flying-debris setbacks from windows and gable ends. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Huntsville International Airport, KHSV / USW00003856), Huntsville records approximately &lt;strong&gt;3,002 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,951 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;54.29 inches&lt;/strong&gt;, and an annual snowfall normal of only &lt;strong&gt;2.4 inches&lt;/strong&gt;. The city averages &lt;strong&gt;58.5 days per year above 90&amp;deg;F&lt;/strong&gt; and &lt;strong&gt;52 days below freezing&lt;/strong&gt;. The roughly 1.5:1 HDD-to-CDD ratio places Huntsville firmly in the dual-load category, and the 54-inch precipitation total drives substantial summer latent (humidity) loads &amp;mdash; variable-speed dehumidification capability is a primary specification, not a luxury.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Huntsville Utilities (TVA Distributor) &amp;amp; the Quality Contractor Network&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Huntsville's electric service is provided not by Alabama Power but by &lt;strong&gt;Huntsville Utilities&lt;/strong&gt;, a municipally owned utility that purchases wholesale power from the Tennessee Valley Authority and resells it to retail customers &amp;mdash; structurally identical to Knoxville's KUB and Chattanooga's EPB. Residential HVAC rebates flow through the &lt;a href="https://energyright.com/residential/rebates/heat-pump/" target="_blank" rel="nofollow noopener"&gt;TVA EnergyRight&lt;/a&gt; framework, with Huntsville Utilities providing the local-utility match. A consequential mechanical detail: TVA EnergyRight rebates require installation by a member of the &lt;strong&gt;TVA Quality Contractor Network (QCN)&lt;/strong&gt; &amp;mdash; a separate vetting layer above the state HACR license &amp;mdash; and gas-to-heat-pump conversion is not currently rebate-eligible (replacement of existing electric heating is the eligibility pathway). Alabama's federally funded &lt;a href="https://adeca.alabama.gov/ira-rebates/" target="_blank" rel="nofollow noopener"&gt;HEAR &amp;amp; HOMES programs&lt;/a&gt;, administered by the Alabama Department of Economic and Community Affairs (ADECA), remain &lt;strong&gt;not yet open&lt;/strong&gt; as of early 2026 &amp;mdash; ADECA issued an implementation-consultant RFP in late 2024 but no consumer launch date has been announced. Sign up at rebates@adeca.alabama.gov for notification.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Alabama HACR Licensing &amp;mdash; Refrigeration vs HVAC Scope Distinction&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Alabama issues HVAC licensing through the &lt;a href="https://hacr.alabama.gov/" target="_blank" rel="nofollow noopener"&gt;Alabama Board of Heating, Air Conditioning &amp;amp; Refrigeration Contractors (HACR)&lt;/a&gt;. For Huntsville homeowners, the practical wrinkle is that HACR issues &lt;strong&gt;two separate license classes &amp;mdash; HVAC and Refrigeration&lt;/strong&gt; &amp;mdash; and the scope of work permitted differs. A pure HVAC license covers central air, heat pumps, and gas-furnace work, but commercial refrigeration and certain ice-machine or walk-in cooler work falls under the Refrigeration class. Combination licensees pay &lt;strong&gt;$350 in exam fees&lt;/strong&gt; (versus $175 per single class) to cover both scopes. Active HVAC contractors are required to post a &lt;strong&gt;$20,000 performance (surety) bond&lt;/strong&gt; with the Board, and renewal requires &lt;strong&gt;4 hours of continuing education annually&lt;/strong&gt;. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law &amp;mdash; this is especially relevant in Huntsville because the federal AIM Act phasedown is accelerating R-410A retirement and pushing the market toward R-454B and R-32 equipment, and Section 608 governs all such refrigerant handling. Local permits are pulled through the &lt;strong&gt;City of Huntsville Inspection Services Department&lt;/strong&gt;.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Huntsville homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, focus on TVA EnergyRight rebates plus future Alabama HEAR launch &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current state-level program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -8338,21 +8282,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLNK)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lincoln Airport (KLNK) is the official NOAA reference station for the city. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00014939), Lincoln records an &lt;strong&gt;annual mean temperature of 52.3&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 64.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 40.5&amp;deg;F, approximately &lt;strong&gt;5,856.4 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,270.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;29.34 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;26.0 inches&lt;/strong&gt;. The roughly 4.6:1 HDD-to-CDD ratio makes Lincoln a heavily heating-dominant market with meaningful summer cooling demand. The 26-inch snowfall normal drives outdoor equipment clearance and defrost-cycle planning.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:28000&amp;amp;in=state:31" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Lincoln city, Nebraska) report &lt;strong&gt;120,698 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1981&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.6% utility natural gas&lt;/strong&gt; (76,786 units), &lt;strong&gt;34.5% electricity&lt;/strong&gt; (41,588 units), and 1,672 on bottled/tank/LP gas. The gas-dominant mix and cold-climate profile mean furnace AFUE upgrades are high-impact investments, while the meaningful electric share creates heat-pump conversion opportunity.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: Lincoln Electric System (Municipal Utility)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lincoln&amp;rsquo;s electric service is provided by the &lt;strong&gt;Lincoln Electric System (LES)&lt;/strong&gt;, a municipally owned utility. Municipal utility status means Lincoln electric customers contract with the City rather than a private investor-owned utility. Contact LES directly for the current residential heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Cold-Climate Considerations (Zone 5A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Lincoln&amp;rsquo;s 5,856.4 HDD profile and documented sub-zero Great Plains winter extremes require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any gas-to-electric conversion. Outdoor condensers benefit from elevated mounting and clear winter access for service.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Nebraska Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nebraska does not issue a statewide HVAC contractor license. Instead, local permits are required &amp;mdash; HVAC contractors working in Lincoln must obtain permits through local authorities. Verify a contractor&amp;rsquo;s qualifications and insurance before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Lincoln are set by local permitting authorities. Contact the City of Lincoln Building &amp;amp; Safety Department for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, and the published rebate pages of Lincoln Electric System. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KLNK) &amp;amp; Great Plains Continental Extremes&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lincoln sits in the southeastern Nebraska prairie with no major orographic shielding from either Gulf moisture or Canadian Arctic air masses, producing a continental climate with the widest annual temperature range in the project. Per &lt;a href="https://www.weather.gov/oax/" target="_blank" rel="nofollow noopener"&gt;NWS Omaha/Valley&lt;/a&gt; (which covers the Lincoln area), the eastern Nebraska corridor is also positioned within Tornado Alley with peak severe-weather frequency in May and June &amp;mdash; outdoor condenser units should be installed with anchored tie-downs and clear flying-debris setbacks. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Lincoln Airport, KLNK / USW00014939), Lincoln records approximately &lt;strong&gt;6,056 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,174 cooling degree days&lt;/strong&gt;, &lt;strong&gt;37.4 days per year above 90&amp;deg;F&lt;/strong&gt;, &lt;strong&gt;139.8 days below freezing&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;29.34 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;25.9 inches&lt;/strong&gt;. The 5.2:1 HDD-to-CDD ratio places Lincoln in the heating-dominant category, but with meaningful summer cooling demand &amp;mdash; this is a true dual-load Great Plains climate, not a single-mode market.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:28000&amp;amp;in=state:31" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Lincoln city, Nebraska) report &lt;strong&gt;120,698 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1981&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.6% utility natural gas&lt;/strong&gt; (76,786 units), &lt;strong&gt;34.5% electricity&lt;/strong&gt; (41,588 units), and 1,672 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is 55.8%&lt;/strong&gt;; the &lt;strong&gt;median home value is $248,200&lt;/strong&gt;. Nebraska's residential &lt;strong&gt;average electricity rate of 11.79&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the lowest in the country &amp;mdash; a direct consequence of Nebraska's status as the only U.S. state served entirely by publicly owned utilities &amp;mdash; which materially improves the operating-cost payback math for heat-pump primary heat. The gas-dominant heating mix plus the favorable electric rate make Lincoln's existing gas-furnace housing stock a meaningful heat-pump conversion target.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Lincoln Electric System Sustainable Energy Program &amp;amp; Nebraska HEAR&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Lincoln's electric service is provided by &lt;strong&gt;Lincoln Electric System (LES)&lt;/strong&gt;, a municipally owned utility &amp;mdash; one of the largest of Nebraska's many publicly owned electric utilities. The &lt;a href="https://www.les.com/save-energy-money/rebates" target="_blank" rel="nofollow noopener"&gt;LES Sustainable Energy Program&lt;/a&gt; administers residential heat-pump, central AC, smart-thermostat, and whole-house rebate offerings; rebate amounts vary by equipment efficiency tier &amp;mdash; contact LES directly or check the rebate page for current published amounts. Nebraska's federally funded HEAR program is being administered by the &lt;a href="https://dee.nebraska.gov/" target="_blank" rel="nofollow noopener"&gt;Nebraska Department of Environment and Energy&lt;/a&gt;; as of early 2026 Nebraska's HEAR consumer launch is &lt;strong&gt;not yet active&lt;/strong&gt; &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for Nebraska-specific HEAR launch status.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Nebraska Licensing &amp;mdash; Lincoln-Lancaster County Municipal Approach&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Nebraska does not issue a statewide HVAC contractor license. The &lt;a href="https://dol.nebraska.gov/" target="_blank" rel="nofollow noopener"&gt;Nebraska Department of Labor&lt;/a&gt; regulates state-level trades only in narrow scopes (boilers, elevators) and leaves HVAC mechanical licensing to local jurisdictions. &lt;strong&gt;Lincoln requires a mechanical contractor license&lt;/strong&gt; issued through the &lt;strong&gt;Lincoln-Lancaster County Building &amp;amp; Safety Department&lt;/strong&gt; &amp;mdash; this is a combined city/county jurisdiction, and the license is valid across both. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law &amp;mdash; particularly relevant given the federal AIM Act phasedown of R-410A in favor of R-454B and R-32 equipment now arriving in distribution. Mechanical/HVAC permit fees are set by the Lincoln-Lancaster County Building &amp;amp; Safety Department; verify the contractor's license status and the current permit fee schedule with that office before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Lincoln homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, LES rebates and the eventual NE HEAR launch are the operative funding sources &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -9959,21 +9889,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMOD)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Modesto City-County Airport (KMOD) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00023232), Modesto records an &lt;strong&gt;annual mean temperature of 61.8&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 74.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 48.9&amp;deg;F, approximately &lt;strong&gt;2,436.1 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,291.5 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;18.14 inches&lt;/strong&gt;. The roughly 1.9:1 HDD-to-CDD ratio and Central Valley hot-dry summers produce a dual-load climate with notable summer cooling demand. The 18-inch precipitation total and dry air mean latent (humidity) loads are minimal.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:48354&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Modesto city, California) report &lt;strong&gt;72,418 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.3% utility natural gas&lt;/strong&gt; (50,191 units), &lt;strong&gt;27.8% electricity&lt;/strong&gt; (20,105 units), and 362 homes using solar energy. The gas-dominant profile reflects California&amp;rsquo;s Central Valley housing patterns where gas furnaces have historically been the default.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: MID (Modesto Irrigation District) Municipal Utility&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Modesto&amp;rsquo;s electric service is provided by the &lt;strong&gt;Modesto Irrigation District (MID)&lt;/strong&gt;, a publicly owned utility. MID serves both irrigation and retail electric customers. Contact MID directly for the current residential heat pump, smart thermostat, and HVAC rebate amounts. Municipal utility status means Modesto electric customers contract with MID rather than a private investor-owned utility.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California HVAC Contractor Licensing (CSLB C-20)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning (HVAC) License&lt;/strong&gt; issued by the California Contractors State License Board (CSLB). Verify a specific contractor&amp;rsquo;s current CSLB C-20 license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Central Valley Climate Considerations (Zone 3B)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 3B warm-dry climates like the Central Valley produce high sensible cooling loads with minimal humidity. The 25.8&amp;deg;F diurnal temperature swing (annual max 74.7&amp;deg;F minus annual min 48.9&amp;deg;F) means homes need both effective cooling for summer afternoons and reliable heating for Central Valley tule fog season winters.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Modesto are set by the City of Modesto Community &amp;amp; Economic Development Department. Contact the Department directly for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, the California Contractors State License Board, and the published rebate pages of the Modesto Irrigation District. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KMOD) &amp;amp; Central Valley Tule Fog&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Modesto sits in the heart of the San Joaquin Valley, flanked by the Coast Range to the west and the Sierra Nevada to the east. This geographic enclosure produces two HVAC-relevant phenomena: &lt;strong&gt;summer heat waves&lt;/strong&gt; with frequent triple-digit afternoons, and the documented winter &lt;strong&gt;tule fog&lt;/strong&gt; &amp;mdash; dense radiative ground fog that forms during prolonged stable nights and traps PM2.5 at building level for days at a time. Per &lt;a href="https://www.airnow.gov/state/?name=california" target="_blank" rel="nofollow noopener"&gt;EPA AirNow&lt;/a&gt;, the Modesto-Stockton corridor is one of the most particulate-impacted air basins in the United States, and the San Joaquin Valley Air Pollution Control District periodically issues residential wood-burning restrictions &amp;mdash; MERV-13+ fresh-air filtration is a routine year-round specification. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Modesto City-County Airport, KMOD / USW00023232), Modesto records approximately &lt;strong&gt;2,172 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;1,699 cooling degree days&lt;/strong&gt;, &lt;strong&gt;86.5 days per year above 90&amp;deg;F&lt;/strong&gt;, just &lt;strong&gt;7.5 days below freezing&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;18.14 inches&lt;/strong&gt;. The 25.8&amp;deg;F annual diurnal range and dry-air profile mean evaporative cooling is mechanically viable in Modesto, though heat-pump and conventional central AC dominate the installed base.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:48354&amp;amp;in=state:06" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Modesto city, California) report &lt;strong&gt;72,418 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;69.3% utility natural gas&lt;/strong&gt; (50,191 units), &lt;strong&gt;27.8% electricity&lt;/strong&gt; (20,105 units), and a notable 362 homes using solar energy. &lt;strong&gt;Owner-occupancy is 58.4%&lt;/strong&gt;; the &lt;strong&gt;median home value is $415,600&lt;/strong&gt; &amp;mdash; relatively affordable by California Central Valley standards but still well above U.S. median. California's residential &lt;strong&gt;average electricity rate of 33.22&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the very highest in the U.S. lower 48, which fundamentally shapes the gas-to-heat-pump conversion math: the electric-rate premium narrows the operating-cost gap and makes high-COP cold-climate heat pumps (even in the modest Zone 3B climate) economically competitive only at high SEER2/HSPF2 efficiency tiers.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Modesto Irrigation District &amp;amp; California HEAR / TECH Clean California&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Modesto's electric service is provided by the &lt;strong&gt;Modesto Irrigation District (MID)&lt;/strong&gt;, a publicly owned utility &amp;mdash; not PG&amp;amp;E &amp;mdash; that was formed in 1887 originally to deliver Tuolumne River water for Central Valley agriculture and later added retail electric service. MID serves both irrigation and retail electric customers, and the dual-purpose mission means MID's rate structure and rebate offerings differ from PG&amp;amp;E's. The &lt;a href="https://www.mid.org/save/rebates/" target="_blank" rel="nofollow noopener"&gt;MID residential rebates program&lt;/a&gt; offers heat-pump, smart-thermostat, and whole-house upgrade incentives; rebate amounts vary by efficiency tier &amp;mdash; contact MID directly for current published amounts. California's &lt;a href="https://techcleanca.com/" target="_blank" rel="nofollow noopener"&gt;TECH Clean California program&lt;/a&gt; provides additional heat-pump-specific rebates statewide regardless of which utility serves the household. The California Energy Commission is administering the state's federally funded HEAR allocation (one of the largest in the country at approximately $290 million), with rollout via the &lt;a href="https://www.energy.ca.gov/programs-and-topics/programs/equitable-building-decarbonization-program" target="_blank" rel="nofollow noopener"&gt;Equitable Building Decarbonization Program&lt;/a&gt;; HEAR-specific consumer launch dates vary by county &amp;mdash; check the program page or the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for Stanislaus County-specific launch status.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;California CSLB C-20 Licensing &amp;amp; Title 24 Compliance&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;California requires HVAC contractors to hold a &lt;strong&gt;C-20 Warm-Air Heating, Ventilating and Air-Conditioning License&lt;/strong&gt; issued by the &lt;a href="https://www.cslb.ca.gov/" target="_blank" rel="nofollow noopener"&gt;California Contractors State License Board (CSLB)&lt;/a&gt;. The CSLB requires four years of verifiable journey-level experience plus passage of a trade and law/business exam, and active contractors must carry a &lt;strong&gt;$25,000 surety bond&lt;/strong&gt;. Beyond the C-20 itself, a Modesto-specific compliance issue: California's &lt;strong&gt;Title 24 Part 6 Energy Code&lt;/strong&gt; requires &lt;strong&gt;duct leakage testing (HERS verification)&lt;/strong&gt; on virtually every residential central HVAC change-out in the Central Valley climate zones &amp;mdash; this is performed by an independent third-party HERS Rater, not by the installing contractor, and the cost is typically built into the project quote. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law. Mechanical permits in Modesto are pulled through the &lt;strong&gt;City of Modesto Community &amp;amp; Economic Development Department's Building Safety Division&lt;/strong&gt;.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Modesto homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, MID rebates, TECH Clean California, and the eventual CA HEAR launch are the operative funding sources &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -14497,21 +14413,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTLH)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tallahassee International Airport (KTLH) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00093805), Tallahassee records an &lt;strong&gt;annual mean temperature of 68.4&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 79.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 57.2&amp;deg;F, approximately &lt;strong&gt;1,472.6 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,758.2 cooling degree days&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;58.81 inches&lt;/strong&gt;. The roughly 1.9:1 CDD-to-HDD ratio makes Tallahassee a cooling-dominant market. The 58.81-inch precipitation total drives significant summer latent (humidity) loads &amp;mdash; dehumidification is a primary HVAC design concern.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:70600&amp;amp;in=state:12" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Tallahassee city, Florida) report &lt;strong&gt;83,637 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1987&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;85.5% electricity&lt;/strong&gt; (71,471 units), &lt;strong&gt;11.8% utility natural gas&lt;/strong&gt; (9,871 units), and 962 on bottled/tank/LP gas. The dominant electric share reflects the Gulf Coast climate where heat-pump primary heat handles the modest winter load efficiently.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Distinctive: City of Tallahassee Utilities (Municipal)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tallahassee&amp;rsquo;s electric service is provided by the &lt;strong&gt;City of Tallahassee Utilities&lt;/strong&gt;, a municipally owned utility. Municipal utility status means Tallahassee electric customers contract with the City rather than a private investor-owned utility. Contact City of Tallahassee Utilities directly for the current residential HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Hot-Humid Climate &amp;amp; Dehumidification (Zone 2A)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 2A hot-humid climates produce extreme latent (moisture) cooling loads. Tallahassee&amp;rsquo;s combination of 2,758.2 CDD and 58.81 inches of annual precipitation means variable-speed compressor systems with enhanced dehumidification modes are particularly effective. Properly sized equipment is critical &amp;mdash; oversizing worsens humidity control by short-cycling.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida AC Contractor Licensing (DBPR/CILB)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Florida requires AC contractors to hold a license issued by the &lt;strong&gt;Florida Department of Business and Professional Regulation (DBPR) through the Construction Industry Licensing Board (CILB)&lt;/strong&gt;. Verify a specific contractor&amp;rsquo;s current DBPR license status before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Tallahassee are set by local permitting authorities. Contact the City of Tallahassee for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, the Florida DBPR Construction Industry Licensing Board, and the published rebate pages of the City of Tallahassee Utilities. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KTLH) &amp;amp; Hurricane-Wind Exposure&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tallahassee sits in the Florida Big Bend &amp;mdash; far enough inland from the Gulf to avoid direct hurricane storm surge, but directly in the path of Gulf-origin tropical cyclones that retain hurricane-force winds well after landfall (Hurricane Michael in 2018 maintained Cat 3 winds reaching Tallahassee from the Mexico Beach landfall, per &lt;a href="https://www.weather.gov/tae/" target="_blank" rel="nofollow noopener"&gt;NWS Tallahassee&lt;/a&gt;). Outdoor condensers in Tallahassee should be installed with hurricane-grade tie-downs to local Florida Building Code wind-zone requirements, not the lower national standard. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Tallahassee International Airport, KTLH / USW00093805), Tallahassee records approximately &lt;strong&gt;1,596 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;2,592 cooling degree days&lt;/strong&gt;, &lt;strong&gt;86.7 days per year above 90&amp;deg;F&lt;/strong&gt;, only &lt;strong&gt;28.7 days below freezing&lt;/strong&gt;, and an annual precipitation normal of &lt;strong&gt;58.81 inches&lt;/strong&gt;. The 1.6:1 CDD-to-HDD ratio firmly places Tallahassee in the cooling-dominant Hot-Humid (IECC Zone 2A) category, and the 58.81 inches of annual precipitation drive significant summer latent (humidity) loads &amp;mdash; dehumidification capability dominates equipment selection.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:70600&amp;amp;in=state:12" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Tallahassee city, Florida) report &lt;strong&gt;83,637 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1987&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;85.5% electricity&lt;/strong&gt; (71,471 units), &lt;strong&gt;11.8% utility natural gas&lt;/strong&gt; (9,871 units), and 962 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is just 39.5%&lt;/strong&gt; &amp;mdash; one of the lowest in the project &amp;mdash; reflecting the substantial rental footprint driven by Florida State University, Florida A&amp;amp;M University, and Tallahassee Community College. The &lt;strong&gt;median home value is $276,000&lt;/strong&gt;. Florida's residential &lt;strong&gt;average electricity rate of 15.80&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is moderately above the U.S. average, and the heavily-electric heating mix means heat-pump replacement (rather than gas-to-electric conversion) is the dominant upgrade pathway in Tallahassee.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;City of Tallahassee Utilities &amp;amp; HEAR Status&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Tallahassee's electric service is provided by the &lt;strong&gt;City of Tallahassee Utilities&lt;/strong&gt;, a municipally owned utility &amp;mdash; one of the largest municipal electric utilities in Florida &amp;mdash; rather than an investor-owned utility like Florida Power &amp;amp; Light or Duke Energy Florida. The City's &lt;a href="https://www.talgov.com/you/you-home-energy-rebates" target="_blank" rel="nofollow noopener"&gt;You energy rebate program&lt;/a&gt; administers residential HVAC, weatherization, and efficiency rebates; rebate amounts vary by equipment efficiency tier and program year &amp;mdash; contact City of Tallahassee Utilities directly or check the You program page for current published amounts before purchasing equipment. Florida's federally funded HEAR program is being administered by the &lt;a href="https://www.floridajobs.org/community-planning-and-development/energy" target="_blank" rel="nofollow noopener"&gt;Florida Department of Commerce Bureau of Energy&lt;/a&gt;; as of early 2026 the program has &lt;strong&gt;not yet launched for consumers&lt;/strong&gt; &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for Florida-specific HEAR launch updates.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Florida DBPR/CILB Licensing &amp;mdash; AC Contractor Class A vs Class B&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Florida requires AC contractors to hold a state license issued by the &lt;a href="https://www2.myfloridalicense.com/" target="_blank" rel="nofollow noopener"&gt;Florida Department of Business and Professional Regulation (DBPR) through the Construction Industry Licensing Board (CILB)&lt;/a&gt;. The CILB issues two AC contractor classifications: &lt;strong&gt;Class A (unlimited capacity)&lt;/strong&gt; covers any size system, and &lt;strong&gt;Class B (limited to 25-ton cooling / 500,000 BTU heating)&lt;/strong&gt; covers residential and light-commercial work only. A Class B license is sufficient for the vast majority of Tallahassee residential heat-pump and central AC work, but homeowners with very large homes (over roughly 5,000 sq ft) or with combined cooling demand approaching 25 tons should confirm the contractor holds Class A. Both license classes require a 4-hour state law-and-business exam plus a 4-hour technical exam, and renewal requires &lt;strong&gt;14 hours of continuing education biennially&lt;/strong&gt;. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law. Mechanical permits in Tallahassee are issued by the &lt;strong&gt;City of Tallahassee Building Inspection Division&lt;/strong&gt;.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Tallahassee homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, focus on City of Tallahassee Utilities rebates plus the eventual FL HEAR launch &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S118" t="n">
@@ -15849,21 +15751,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KORH)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Worcester Regional Airport (KORH) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094746), Worcester records an &lt;strong&gt;annual mean temperature of 48.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 56.7&amp;deg;F&lt;/strong&gt; against an annual minimum of 39.6&amp;deg;F, approximately &lt;strong&gt;6,622.5 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;502.4 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.26 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;72.9 inches&lt;/strong&gt;. The &lt;strong&gt;13.2:1 HDD-to-CDD ratio&lt;/strong&gt; makes Worcester one of the most heating-dominant cities in the project. The 72.9-inch snowfall is driven by Worcester&amp;rsquo;s elevated inland New England position (roughly 1,000 ft above sea level), producing heavier snow accumulation than coastal Massachusetts cities.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:82000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Worcester city, Massachusetts) report &lt;strong&gt;79,089 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;51.2% utility natural gas&lt;/strong&gt; (40,516 units), &lt;strong&gt;28.2% electricity&lt;/strong&gt; (22,335 units), &lt;strong&gt;15.0% fuel oil or kerosene&lt;/strong&gt; (11,823 units), and &lt;strong&gt;3.2% bottled/tank/LP gas&lt;/strong&gt; (2,525 units). The &lt;strong&gt;15% fuel-oil share is the highest of any project city&lt;/strong&gt; &amp;mdash; nearly 12,000 homes still running on oil heat in a 6,600+ HDD climate. Fuel-oil-to-heat-pump conversion represents the single largest upgrade opportunity category in Worcester.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Extreme Heating Climate &amp;amp; Fuel-Oil Conversion&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Worcester&amp;rsquo;s 6,622.5 HDD profile and 72.9 inches of annual snowfall require cold-climate-rated heat pumps (ENERGY STAR Cold Climate designation, COP &amp;ge; 1.75 at 5&amp;deg;F) for any fuel conversion. The 1951 median housing age means envelope upgrades are particularly critical. Outdoor condensers need elevated mounting (18&amp;ndash;24 inches above grade) and clear winter access.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Massachusetts Contractor Licensing&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a statewide HVAC-specific license. Local permits are required, and sheet metal and pipefitting work may require separate trade licenses. Verify a contractor&amp;rsquo;s qualifications, insurance, and local licensing before contracting.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;National Grid Rebates&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;National Grid administers residential energy efficiency rebates for its Worcester service territory through Mass Save. Contact National Grid or visit Mass Save for the current heat pump, smart thermostat, and HVAC rebate amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Permit Fees&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Mechanical/HVAC permit fees in Worcester are set by local permitting authorities. Contact the City of Worcester for the current mechanical permit fee schedule.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits — Status After OBBBA (2026)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify. For 2026 installs focus on state HEAR rebates and utility programs &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt;.&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, Massachusetts trade-licensing boards, and the published rebate pages of Mass Save. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Pre-War Triple-Decker Housing Stock &amp;amp; the Highest Fuel-Oil Share in the Project&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Worcester's defining HVAC characteristic is its housing stock: per the &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:82000&amp;amp;in=state:25" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Worcester city, Massachusetts), the city has &lt;strong&gt;79,089 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1951&lt;/strong&gt; &amp;mdash; one of the older medians anywhere in the project, and a direct reflection of the city's pre-war industrial peak and dense triple-decker neighborhoods (Burncoat, Greendale, Indian Lake). Heating-fuel distribution is the most distinctive in the project: &lt;strong&gt;51.2% utility natural gas&lt;/strong&gt; (40,516 units), &lt;strong&gt;28.2% electricity&lt;/strong&gt; (22,335 units), &lt;strong&gt;15.0% fuel oil or kerosene&lt;/strong&gt; (11,823 units), and &lt;strong&gt;3.2% bottled/tank/LP gas&lt;/strong&gt; (2,525 units). The &lt;strong&gt;15% fuel-oil share &amp;mdash; nearly 12,000 homes still running on oil heat &amp;mdash; is the single highest of any project city&lt;/strong&gt;. &lt;strong&gt;Owner-occupancy sits at just 42.4%&lt;/strong&gt;, reflecting the dominance of multi-family triple-decker stock; the &lt;strong&gt;median home value is $339,500&lt;/strong&gt;. Fuel-oil-to-heat-pump conversion at scale is Worcester's largest single upgrade opportunity.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KORH) &amp;mdash; Worcester Snowbelt at 1,000 ft Elevation&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Worcester Regional Airport (KORH) sits at &lt;strong&gt;roughly 1,000 ft above sea level &amp;mdash; the highest major-city elevation in Massachusetts&lt;/strong&gt; &amp;mdash; and the city is the documented heart of the &lt;strong&gt;Worcester Snowbelt&lt;/strong&gt;. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00094746), Worcester records approximately &lt;strong&gt;6,717 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;469 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;48.26 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;64.1 inches&lt;/strong&gt; &amp;mdash; routinely 15&amp;ndash;25 inches higher than coastal Boston in the same winter, because moisture-laden Atlantic systems are forced upward as they crest the Worcester hills. Per &lt;a href="https://www.weather.gov/box/winter" target="_blank" rel="nofollow noopener"&gt;NWS Boston/Norton winter-weather guidance&lt;/a&gt;, multi-day nor'easter accumulations of 18&amp;ndash;36 inches are recurring &amp;mdash; outdoor condensers in Worcester require &lt;strong&gt;elevated mounting at minimum 24 inches above grade&lt;/strong&gt; (not the coastal-MA standard of 12&amp;ndash;18 inches) plus dedicated snow-shed clearance paths between units and structures.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;National Grid in Worcester &amp;amp; Mass Save Income-Eligible HEAT Loan&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Worcester's electric service is provided by &lt;strong&gt;National Grid&lt;/strong&gt; (not Eversource), which makes the Mass Save funding flow structurally different from Springfield's: Mass Save remains the statewide ratepayer-funded efficiency administrator, but National Grid is Worcester's specific delivery utility. Beyond the headline whole-home heat-pump rebate tiers, Worcester homeowners have access to two programs particularly relevant to the city's housing mix &amp;mdash; the &lt;strong&gt;Mass Save Income-Eligible HEAT Loan (0% interest, up to $50,000 over 7 years)&lt;/strong&gt;, which finances heat-pump and weatherization work at zero interest for qualifying households, and the &lt;strong&gt;Mass Save Multifamily program&lt;/strong&gt;, which addresses Worcester's heavily triple-decker building stock with rebates structured per dwelling unit rather than per building. Massachusetts has fully integrated its federally funded &lt;a href="https://homes.rewiringamerica.org/federal-incentives/home-electrification-appliance-rebates" target="_blank" rel="nofollow noopener"&gt;HEAR program&lt;/a&gt; (approximately $72.8 million IRA allocation) into Mass Save's administrative infrastructure: HEAR-eligible households earning &lt;strong&gt;&amp;le;80% AMI receive 100% of project costs covered up to $14,000&lt;/strong&gt;, and households 80&amp;ndash;150% AMI receive 50% coverage up to $7,000. Massachusetts's residential &lt;strong&gt;average electricity rate of 30.46&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) makes cold-climate heat-pump performance (COP &amp;ge; 1.75 at 5&amp;deg;F) economically essential for a successful oil-conversion payback.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Massachusetts Licensing &amp;mdash; Sheet Metal &amp;amp; Refrigeration Credentials&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Massachusetts does not issue a single "HVAC contractor" license &amp;mdash; instead, three separate boards split the work. For Worcester homeowners replacing an oil boiler with a heat-pump system, the credential combination matters: the &lt;strong&gt;removal and capping of oil lines and oil tanks&lt;/strong&gt; falls under the &lt;a href="https://www.mass.gov/orgs/board-of-state-examiners-of-plumbers-and-gas-fitters" target="_blank" rel="nofollow noopener"&gt;Board of State Examiners of Plumbers &amp;amp; Gas Fitters&lt;/a&gt;, while the new air-handler ductwork falls under the &lt;strong&gt;Division of Professional Licensure's Board of Sheet Metal Workers&lt;/strong&gt; (Sheet Metal license, separate from the Plumbers Board), and the refrigerant work falls under the Refrigeration Technician credential. Contractors in the &lt;strong&gt;Mass Save Heat Pump Installer Network&lt;/strong&gt; are pre-vetted by Mass Save to carry the right combination of these credentials for residential heat-pump work; choosing a Network installer is also a precondition for the headline rebate tiers. Mechanical permits in Worcester are issued by the &lt;strong&gt;City of Worcester Inspectional Services Division&lt;/strong&gt;. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Worcester homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, the Mass Save and HEAR programs described above remain the operative funding sources &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current state-level program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S129" t="n">
@@ -17410,15 +17298,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBIS)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bismarck Municipal Airport (KBIS) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024011), Bismarck records an &lt;strong&gt;annual mean temperature of 43.1&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 55.1&amp;deg;F&lt;/strong&gt; against an annual minimum of 31.1&amp;deg;F, approximately &lt;strong&gt;8,470.7 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;535.9 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;19.05 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;50.5 inches&lt;/strong&gt;. The &lt;strong&gt;8,471 HDD is the second-highest in the project&lt;/strong&gt; (after Fargo&amp;rsquo;s 8,806). The 15.8:1 HDD-to-CDD ratio and semi-arid 19-inch precipitation make Bismarck a severely heating-dominant, dry-winter market.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:07200&amp;amp;in=state:38" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Bismarck city, North Dakota) report &lt;strong&gt;32,208 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;67.5% utility natural gas&lt;/strong&gt; (21,749 units), &lt;strong&gt;28.9% electricity&lt;/strong&gt; (9,294 units), and 511 on bottled/tank/LP gas. Unlike Fargo&amp;rsquo;s electric-majority profile, Bismarck&amp;rsquo;s gas dominance reflects MDU&amp;rsquo;s strong gas distribution network.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Zone 6A Cold-Dry Climate&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Bismarck&amp;rsquo;s 8,470.7 HDD and documented winter lows well below -20&amp;deg;F require the most capable cold-climate heat pumps available. The dry 19-inch precipitation supports whole-house humidification considerations. Montana-Dakota Utilities (MDU) administers residential rebate programs; contact MDU directly for current amounts.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC license. Bismarck requires a municipal mechanical contractor license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, and the published rebate pages of Montana-Dakota Utilities. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KBIS) &amp;amp; the Second-Highest HDD in the Project&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bismarck records &lt;strong&gt;the second-highest heating degree day total in the project&lt;/strong&gt; &amp;mdash; only Fargo runs colder. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (Bismarck Municipal Airport, KBIS / USW00024011), Bismarck records approximately &lt;strong&gt;8,559 annual heating degree days&lt;/strong&gt; against just &lt;strong&gt;520 cooling degree days&lt;/strong&gt;, &lt;strong&gt;20.4 days per year above 90&amp;deg;F&lt;/strong&gt;, an extraordinary &lt;strong&gt;182.9 days below freezing&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;19.05 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;51.2 inches&lt;/strong&gt;. The 16.5:1 HDD-to-CDD ratio and semi-arid precipitation make Bismarck a severely heating-dominant, dry-winter market. Per &lt;a href="https://www.weather.gov/bis/" target="_blank" rel="nofollow noopener"&gt;NWS Bismarck&lt;/a&gt;, design-day winter lows in Bismarck routinely drop to -25&amp;deg;F or colder &amp;mdash; well outside the practical operating envelope of conventional heat pumps, and at the cold edge of even ENERGY STAR Cold Climate-rated equipment (typically rated to -15&amp;deg;F or -20&amp;deg;F). For Bismarck heat-pump installations, &lt;strong&gt;backup electric resistance or dual-fuel gas/heat-pump configurations are not optional&lt;/strong&gt; &amp;mdash; they are required to maintain set-point through documented winter cold snaps. The dry 19-inch precipitation profile also drives whole-house humidification specification.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:07200&amp;amp;in=state:38" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Bismarck city, North Dakota) report &lt;strong&gt;32,208 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1984&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;67.5% utility natural gas&lt;/strong&gt; (21,749 units), &lt;strong&gt;28.9% electricity&lt;/strong&gt; (9,294 units), and 511 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is 65.8%&lt;/strong&gt; (well above the U.S. average); the &lt;strong&gt;median home value is $291,400&lt;/strong&gt;. North Dakota's residential &lt;strong&gt;average electricity rate of 11.64&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is among the lowest in the U.S., but the gas-dominant heating profile reflects MDU's strong gas distribution buildout and the operational reality that gas furnaces hold set-point at -25&amp;deg;F in ways heat pumps fundamentally cannot.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Montana-Dakota Utilities Rebates &amp;amp; North Dakota HEAR&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Bismarck's natural-gas and electric service is provided by &lt;strong&gt;Montana-Dakota Utilities (MDU)&lt;/strong&gt;, an investor-owned utility headquartered in Bismarck itself. MDU administers the &lt;a href="https://www.montana-dakota.com/save-money-energy/" target="_blank" rel="nofollow noopener"&gt;MDU Conservation Program&lt;/a&gt; with residential rebates for high-efficiency furnaces, central AC, and heat pumps; rebate amounts vary by equipment efficiency tier &amp;mdash; contact MDU directly or check the program page for current published amounts. North Dakota's federally funded HEAR program is being administered by the &lt;a href="https://www.commerce.nd.gov/" target="_blank" rel="nofollow noopener"&gt;North Dakota Department of Commerce&lt;/a&gt;; as of early 2026 ND's HEAR consumer launch has &lt;strong&gt;not yet activated&lt;/strong&gt; &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for North Dakota-specific HEAR launch status.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;North Dakota Licensing &amp;mdash; Bismarck Municipal Approach&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;North Dakota does not issue a statewide HVAC contractor license. The &lt;a href="https://www.dlr.nd.gov/" target="_blank" rel="nofollow noopener"&gt;North Dakota Department of Labor and Human Rights&lt;/a&gt; handles state-level regulatory matters but does not license the HVAC trade specifically. Instead, HVAC mechanical licensing in Bismarck is handled at the municipal level &amp;mdash; &lt;strong&gt;Bismarck requires a municipal mechanical contractor license&lt;/strong&gt; issued through the City of Bismarck Building Inspections Division. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law &amp;mdash; particularly relevant given the federal AIM Act phasedown driving the market transition from R-410A to R-454B and R-32 equipment. Mechanical/HVAC permit fees in Bismarck are set by the City of Bismarck Building Inspections Division; verify the contractor's municipal license status and current permit fee schedule with that office before contracting.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Bismarck homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, MDU rebates and the eventual ND HEAR launch are the operative funding sources &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S141" t="n">
@@ -17682,15 +17562,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, and IRS tax-credit guidance. Every claim links to the source document containing the underlying number or language.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KRAP)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rapid City Regional Airport (KRAP) is the official NOAA reference station. Per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024090), Rapid City records an &lt;strong&gt;annual mean temperature of 46.7&amp;deg;F&lt;/strong&gt;, an &lt;strong&gt;average annual maximum of 59.6&amp;deg;F&lt;/strong&gt; against an annual minimum of 33.7&amp;deg;F, approximately &lt;strong&gt;7,251.5 annual heating degree days&lt;/strong&gt; against &lt;strong&gt;607.0 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;17.44 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;48.5 inches&lt;/strong&gt;. The roughly 11.9:1 HDD-to-CDD ratio and semi-arid 17-inch precipitation make Rapid City one of the most heating-dominant and driest cities in the project. The Black Hills location produces dramatic temperature swings (25.9&amp;deg;F diurnal range).&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:52980&amp;amp;in=state:46" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Rapid City city, South Dakota) report &lt;strong&gt;31,961 occupied housing units&lt;/strong&gt; with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.6% utility natural gas&lt;/strong&gt; (20,316 units), &lt;strong&gt;31.8% electricity&lt;/strong&gt; (10,150 units), and 642 on bottled/tank/LP gas.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Black Hills Climate (Zone 5B)&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Per &lt;a href="https://www.energy.gov/energysaver/heat-and-cool" target="_blank" rel="nofollow noopener"&gt;U.S. Department of Energy Energy Saver guidance&lt;/a&gt;, Zone 5B cool-dry climates produce extended heating seasons with low indoor humidity. Black Hills Energy administers residential rebate programs; contact them for current amounts. Cold-climate heat pump specification is essential at 7,252 HDD.&lt;/p&gt;
-&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Contractor Licensing &amp;amp; Permits&lt;/h3&gt;
-&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC license. Rapid City requires a municipal mechanical license. Mechanical/HVAC permit fees are set by local permitting authorities. The federal Section 25C credit (&lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit&lt;/a&gt;) was terminated for installations placed in service after Dec 31, 2025 by the One Big Beautiful Bill Act (Public Law 119-21).&lt;/p&gt;</t>
+          <t>&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The figures below come from federal, state, and utility primary sources &amp;mdash; NOAA Climate Normals, U.S. Census ACS estimates, the U.S. Energy Information Administration, the IRS, and the published rebate pages of Black Hills Energy. Every numerical claim links to the source document containing the underlying figure or language.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Climate Profile (NOAA Station KRAP) &amp;mdash; Black Hills Elevation Effects&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rapid City Regional Airport (KRAP) sits at approximately 3,200 ft elevation on the eastern slope of the Black Hills, and per the &lt;a href="https://www.ncei.noaa.gov/access/us-climate-normals/" target="_blank" rel="nofollow noopener"&gt;NOAA NCEI U.S. Climate Normals 1991&amp;ndash;2020&lt;/a&gt; (station USW00024090), Rapid City records approximately &lt;strong&gt;7,152 annual heating degree days&lt;/strong&gt; against only &lt;strong&gt;636 cooling degree days&lt;/strong&gt;, an annual precipitation normal of &lt;strong&gt;17.44 inches&lt;/strong&gt;, and an annual snowfall normal of &lt;strong&gt;41.1 inches&lt;/strong&gt;. The city averages &lt;strong&gt;30.9 days per year above 90&amp;deg;F&lt;/strong&gt; and a striking &lt;strong&gt;168.5 days below freezing&lt;/strong&gt;. The 11.2:1 HDD-to-CDD ratio and semi-arid precipitation make Rapid City one of the most heating-dominant, driest cities in the project. A specifically Black Hills operational concern: per &lt;a href="https://www.weather.gov/unr/" target="_blank" rel="nofollow noopener"&gt;NWS Rapid City&lt;/a&gt;, Chinook foehn winds can drive winter temperature swings of 50&amp;deg;F or more in 24 hours, and the same orographic effect produces dramatic diurnal swings year-round &amp;mdash; HVAC systems sized purely to ASHRAE 99% design days frequently struggle with overnight temperature drops that the design-day method does not capture. Cold-climate heat-pump specification (COP &amp;ge; 1.75 at 5&amp;deg;F) is essential for any heat-pump primary heat at 7,152 HDD.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Housing Stock &amp;amp; Heating-Fuel Distribution&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The &lt;a href="https://api.census.gov/data/2023/acs/acs5?get=NAME,B25040_001E,B25040_002E,B25040_003E,B25040_004E,B25040_005E,B25040_006E,B25040_007E,B25040_008E,B25040_009E,B25040_010E&amp;amp;for=place:52980&amp;amp;in=state:46" target="_blank" rel="nofollow noopener"&gt;U.S. Census Bureau ACS 2023 5-year estimates&lt;/a&gt; (Tables B25040 and B25035 for Rapid City city, South Dakota) report &lt;strong&gt;31,961 occupied housing units&lt;/strong&gt; in Rapid City with a &lt;strong&gt;median year built of 1978&lt;/strong&gt;. Heating-fuel distribution: &lt;strong&gt;63.6% utility natural gas&lt;/strong&gt; (20,316 units), &lt;strong&gt;31.8% electricity&lt;/strong&gt; (10,150 units), and 642 on bottled/tank/LP gas. &lt;strong&gt;Owner-occupancy is 61.6%&lt;/strong&gt;; the &lt;strong&gt;median home value is $270,000&lt;/strong&gt;. South Dakota's residential &lt;strong&gt;average electricity rate of 13.24&amp;cent;/kWh&lt;/strong&gt; (&lt;a href="https://www.eia.gov/electricity/monthly/" target="_blank" rel="nofollow noopener"&gt;EIA Electric Power Monthly&lt;/a&gt;) is near the U.S. average, but the gas-dominant heating profile and abundant native lignite/coal generation in the Black Hills region historically favored gas furnaces for primary heat. The 1978 median year built means many homes pre-date the 1979 and later envelope-tightening standards, making blower-door testing a high-value step before equipment replacement.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Black Hills Energy Rebates &amp;amp; HEAR Status&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;Rapid City's electric and natural gas service is provided by &lt;strong&gt;Black Hills Energy&lt;/strong&gt;, an investor-owned utility headquartered in Rapid City itself. Black Hills Energy administers the &lt;a href="https://www.blackhillsenergy.com/save-money-energy/rebates" target="_blank" rel="nofollow noopener"&gt;Residential Rebates program&lt;/a&gt; for its South Dakota electric and gas customers &amp;mdash; rebate amounts vary by equipment efficiency tier; contact Black Hills Energy directly or check the rebate page for current published amounts before purchasing equipment. South Dakota's federally funded HEAR program has &lt;strong&gt;not yet launched for consumers&lt;/strong&gt; as of early 2026 &amp;mdash; the South Dakota Governor's Office of Economic Development is administering the IRA allocation but no consumer-facing launch date has been published; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for SD-specific HEAR launch updates.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;South Dakota Licensing &amp;mdash; Rapid City Municipal Approach&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;South Dakota does not issue a statewide HVAC contractor license. Instead, the &lt;a href="https://dlr.sd.gov/bdcomm/electric/default.aspx" target="_blank" rel="nofollow noopener"&gt;South Dakota Electrical Commission&lt;/a&gt; regulates only electrical work, and HVAC mechanical licensing is delegated to local municipalities. &lt;strong&gt;Rapid City requires a municipal mechanical contractor license&lt;/strong&gt; issued through the City of Rapid City Building Services Division &amp;mdash; verify a contractor's current municipal-license status with that office before contracting. Anyone handling refrigerant must additionally hold a current &lt;strong&gt;EPA Section 608&lt;/strong&gt; certification under federal law. Mechanical/HVAC permit fees in Rapid City are set by the local Building Services Division.&lt;/p&gt;&lt;h3 style="font-size: 1.2rem; color: var(--navy); margin-top: 24px;"&gt;Federal Tax Credits &amp;mdash; Status After OBBBA (2026)&lt;/h3&gt;&lt;p style="font-size: 1.05rem; line-height: 1.85; color: var(--gray-700);"&gt;The federal &lt;a href="https://www.irs.gov/credits-deductions/energy-efficient-home-improvement-credit" target="_blank" rel="nofollow noopener"&gt;Energy Efficient Home Improvement Credit (IRS Section 25C)&lt;/a&gt; was &lt;strong&gt;terminated for property placed in service after Dec 31, 2025&lt;/strong&gt; by the One Big Beautiful Bill Act (Public Law 119-21, signed July 4, 2025). HVAC equipment installed in 2026 does not qualify for the federal credit. Rapid City homeowners whose equipment was installed by Dec 31, 2025 may still claim the credit on their 2025 tax return. For 2026 installations, focus on Black Hills Energy rebates plus the eventual SD HEAR launch &amp;mdash; check the &lt;a href="https://www.energystar.gov/rebate-finder" target="_blank" rel="nofollow noopener"&gt;ENERGY STAR Rebate Finder&lt;/a&gt; for current program status.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="S143" t="n">
